--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -4046,8 +4046,8 @@
         <v>01 Nacional</v>
       </c>
       <c r="AM17" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
-        <v>-</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Certus")</f>
+        <v>Certus</v>
       </c>
       <c r="AN17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -5169,8 +5169,8 @@
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
       <c r="AM22" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
-        <v>-</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Certus")</f>
+        <v>Certus</v>
       </c>
       <c r="AN22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
@@ -6167,8 +6167,8 @@
         <v>49094672</v>
       </c>
       <c r="G27" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.42333783E8)</f>
-        <v>942333783</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.94896575E8)</f>
+        <v>994896575</v>
       </c>
       <c r="H27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Espinoza.angela31490855@gmail.com")</f>
@@ -7296,8 +7296,8 @@
         <v>61421896</v>
       </c>
       <c r="G32" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.96523414E8)</f>
-        <v>996523414</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.06059033E8)</f>
+        <v>906059033</v>
       </c>
       <c r="H32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"rihannaberrisco@gmail.com")</f>
@@ -9787,8 +9787,8 @@
         <v>72159287</v>
       </c>
       <c r="G43" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.45278929E8)</f>
-        <v>945278929</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.92286053E8)</f>
+        <v>992286053</v>
       </c>
       <c r="H43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"slujandelacruz923@gmail.com")</f>
@@ -11256,8 +11256,8 @@
         <v>05 301 a 550</v>
       </c>
       <c r="AM49" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
-        <v>-</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISIL")</f>
+        <v>ISIL</v>
       </c>
       <c r="AN49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
@@ -11426,8 +11426,8 @@
         <v>350</v>
       </c>
       <c r="X50" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"15/05/2025")</f>
-        <v>15/05/2025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
+        <v>31/05/2025</v>
       </c>
       <c r="Y50" s="1"/>
       <c r="Z50" s="1" t="str">
@@ -12821,8 +12821,8 @@
         <v>0</v>
       </c>
       <c r="AJ56" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1335033.0)</f>
+        <v>1335033</v>
       </c>
       <c r="AK56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
@@ -12833,8 +12833,8 @@
         <v>04 200 a 300</v>
       </c>
       <c r="AM56" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
-        <v>-</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Universidad La Salle")</f>
+        <v>Universidad La Salle</v>
       </c>
       <c r="AN56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
@@ -13958,7 +13958,10 @@
       </c>
       <c r="AK61" s="1"/>
       <c r="AL61" s="1"/>
-      <c r="AM61" s="1"/>
+      <c r="AM61" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ISIL")</f>
+        <v>ISIL</v>
+      </c>
       <c r="AN61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
@@ -14182,7 +14185,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01 Nacional")</f>
         <v>01 Nacional</v>
       </c>
-      <c r="AM62" s="1"/>
+      <c r="AM62" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Cibertec")</f>
+        <v>Cibertec</v>
+      </c>
       <c r="AN62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
@@ -15067,8 +15073,8 @@
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
       <c r="AM66" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
-        <v>-</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Universidad de Piura")</f>
+        <v>Universidad de Piura</v>
       </c>
       <c r="AN66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
@@ -15233,14 +15239,20 @@
         <v>PAGO FRACCIONADO</v>
       </c>
       <c r="W67" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),700.0)</f>
-        <v>700</v>
-      </c>
-      <c r="X67" s="1"/>
-      <c r="Y67" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X67" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"28/05/2025")</f>
+        <v>28/05/2025</v>
+      </c>
+      <c r="Y67" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
       <c r="Z67" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
-        <v>PAGO FRACCIONADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
       </c>
       <c r="AA67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
@@ -15320,8 +15332,8 @@
         <v>45747</v>
       </c>
       <c r="AU67" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),44.0)</f>
-        <v>44</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
       </c>
       <c r="AV67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
@@ -15344,8 +15356,8 @@
         <v>Fiorella Lanegra</v>
       </c>
       <c r="BA67" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
-        <v>0.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BB67" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1000.0)</f>
@@ -15457,7 +15469,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="X68" s="1"/>
+      <c r="X68" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="Y68" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45800.0)</f>
         <v>45800</v>
@@ -15681,7 +15696,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="X69" s="1"/>
+      <c r="X69" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="Y69" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45801.0)</f>
         <v>45801</v>
@@ -15813,325 +15831,1120 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
-      <c r="W70" s="1"/>
-      <c r="X70" s="1"/>
-      <c r="Y70" s="1"/>
-      <c r="Z70" s="1"/>
-      <c r="AA70" s="1"/>
+      <c r="A70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),69.0)</f>
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5179581.0)</f>
+        <v>5179581</v>
+      </c>
+      <c r="C70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000426904")</f>
+        <v>0000426904</v>
+      </c>
+      <c r="D70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PIERO YERAY")</f>
+        <v>PIERO YERAY</v>
+      </c>
+      <c r="E70" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VELIZ MENDOZA")</f>
+        <v>VELIZ MENDOZA</v>
+      </c>
+      <c r="F70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.1207319E7)</f>
+        <v>61207319</v>
+      </c>
+      <c r="G70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.29434237E8)</f>
+        <v>929434237</v>
+      </c>
+      <c r="H70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"pieroyeray@gmail.com")</f>
+        <v>pieroyeray@gmail.com</v>
+      </c>
+      <c r="I70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA")</f>
+        <v>BECA</v>
+      </c>
+      <c r="Q70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA CARRERAS CORE")</f>
+        <v>BECA CARRERAS CORE</v>
+      </c>
+      <c r="R70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRIGO")</f>
+        <v>RODRIGO</v>
+      </c>
+      <c r="T70" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="U70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W70" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y70" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="Z70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB70" s="1"/>
-      <c r="AC70" s="1"/>
-      <c r="AD70" s="1"/>
-      <c r="AE70" s="1"/>
-      <c r="AF70" s="1"/>
-      <c r="AG70" s="1"/>
-      <c r="AH70" s="1"/>
-      <c r="AI70" s="1"/>
-      <c r="AJ70" s="1"/>
-      <c r="AK70" s="1"/>
-      <c r="AL70" s="1"/>
-      <c r="AM70" s="1"/>
-      <c r="AN70" s="1"/>
-      <c r="AO70" s="1"/>
-      <c r="AP70" s="1"/>
-      <c r="AQ70" s="1"/>
-      <c r="AR70" s="1"/>
-      <c r="AS70" s="1"/>
-      <c r="AT70" s="1"/>
-      <c r="AU70" s="1"/>
-      <c r="AV70" s="1"/>
-      <c r="AW70" s="1"/>
-      <c r="AX70" s="1"/>
-      <c r="AY70" s="1"/>
-      <c r="AZ70" s="1"/>
-      <c r="BA70" s="1"/>
-      <c r="BB70" s="1"/>
-      <c r="BC70" s="1"/>
-      <c r="BD70" s="1"/>
+      <c r="AC70" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD70" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE70" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1250.0)</f>
+        <v>1250</v>
+      </c>
+      <c r="AF70" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="AG70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),449553.0)</f>
+        <v>449553</v>
+      </c>
+      <c r="AK70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"06 551 a 800")</f>
+        <v>06 551 a 800</v>
+      </c>
+      <c r="AM70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="AN70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="AO70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2024.0)</f>
+        <v>2024</v>
+      </c>
+      <c r="AP70" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ70" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR70" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45779.0)</f>
+        <v>45779</v>
+      </c>
+      <c r="AS70" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT70" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),24.0)</f>
+        <v>24</v>
+      </c>
+      <c r="AV70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
+        <v>OUTBOUND</v>
+      </c>
+      <c r="AW70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
+        <v>OUTBOUND</v>
+      </c>
+      <c r="AX70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
+        <v>OUTBOUND</v>
+      </c>
+      <c r="AY70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fiorella Lanegra")</f>
+        <v>Fiorella Lanegra</v>
+      </c>
+      <c r="BA70" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB70" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="BC70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD70" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="BE70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
-      <c r="W71" s="1"/>
-      <c r="X71" s="1"/>
-      <c r="Y71" s="1"/>
-      <c r="Z71" s="1"/>
-      <c r="AA71" s="1"/>
+      <c r="A71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1025852.0)</f>
+        <v>1025852</v>
+      </c>
+      <c r="C71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427019")</f>
+        <v>0000427019</v>
+      </c>
+      <c r="D71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GONZALO AARON ")</f>
+        <v>GONZALO AARON </v>
+      </c>
+      <c r="E71" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"QUEVEDO MESIA")</f>
+        <v>QUEVEDO MESIA</v>
+      </c>
+      <c r="F71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.3124994E7)</f>
+        <v>73124994</v>
+      </c>
+      <c r="G71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.65918127E8)</f>
+        <v>965918127</v>
+      </c>
+      <c r="H71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mesiagonzalo741@gmail.com")</f>
+        <v>mesiagonzalo741@gmail.com</v>
+      </c>
+      <c r="I71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño Gráfico Publicitario")</f>
+        <v>Diseño Gráfico Publicitario</v>
+      </c>
+      <c r="J71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño")</f>
+        <v>Diseño</v>
+      </c>
+      <c r="K71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO CON CONVA")</f>
+        <v>TRASLADO CON CONVA</v>
+      </c>
+      <c r="P71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T71" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="U71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W71" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="Z71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB71" s="1"/>
-      <c r="AC71" s="1"/>
-      <c r="AD71" s="1"/>
-      <c r="AE71" s="1"/>
-      <c r="AF71" s="1"/>
-      <c r="AG71" s="1"/>
-      <c r="AH71" s="1"/>
-      <c r="AI71" s="1"/>
-      <c r="AJ71" s="1"/>
-      <c r="AK71" s="1"/>
-      <c r="AL71" s="1"/>
-      <c r="AM71" s="1"/>
-      <c r="AN71" s="1"/>
-      <c r="AO71" s="1"/>
-      <c r="AP71" s="1"/>
-      <c r="AQ71" s="1"/>
-      <c r="AR71" s="1"/>
-      <c r="AS71" s="1"/>
-      <c r="AT71" s="1"/>
-      <c r="AU71" s="1"/>
-      <c r="AV71" s="1"/>
-      <c r="AW71" s="1"/>
-      <c r="AX71" s="1"/>
-      <c r="AY71" s="1"/>
-      <c r="AZ71" s="1"/>
-      <c r="BA71" s="1"/>
-      <c r="BB71" s="1"/>
-      <c r="BC71" s="1"/>
-      <c r="BD71" s="1"/>
+      <c r="AC71" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD71" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE71" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1100.0)</f>
+        <v>1100</v>
+      </c>
+      <c r="AF71" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1100.0)</f>
+        <v>1100</v>
+      </c>
+      <c r="AG71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1355478.0)</f>
+        <v>1355478</v>
+      </c>
+      <c r="AK71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Menos de 5 kms")</f>
+        <v>Menos de 5 kms</v>
+      </c>
+      <c r="AL71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"06 551 a 800")</f>
+        <v>06 551 a 800</v>
+      </c>
+      <c r="AM71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Universidad San Martin de Porres")</f>
+        <v>Universidad San Martin de Porres</v>
+      </c>
+      <c r="AN71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
+      <c r="AO71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2019.0)</f>
+        <v>2019</v>
+      </c>
+      <c r="AP71" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AS71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT71" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRADICIONAL")</f>
+        <v>TRADICIONAL</v>
+      </c>
+      <c r="AW71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"INBOUND")</f>
+        <v>INBOUND</v>
+      </c>
+      <c r="AX71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"INBOUND")</f>
+        <v>INBOUND</v>
+      </c>
+      <c r="AY71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Fiorella Lanegra")</f>
+        <v>Fiorella Lanegra</v>
+      </c>
+      <c r="BA71" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB71" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1100.0)</f>
+        <v>1100</v>
+      </c>
+      <c r="BC71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD71" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="BE71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
-      <c r="W72" s="1"/>
-      <c r="X72" s="1"/>
+      <c r="A72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),71.0)</f>
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),671687.0)</f>
+        <v>671687</v>
+      </c>
+      <c r="C72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"2016004992")</f>
+        <v>2016004992</v>
+      </c>
+      <c r="D72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS ANTONIO ")</f>
+        <v>LUIS ANTONIO </v>
+      </c>
+      <c r="E72" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SAUÑE LUDEÑA")</f>
+        <v>SAUÑE LUDEÑA</v>
+      </c>
+      <c r="F72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.3796776E7)</f>
+        <v>73796776</v>
+      </c>
+      <c r="G72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.22568973E8)</f>
+        <v>922568973</v>
+      </c>
+      <c r="H72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"luis.saune.ludena@gmail.com")</f>
+        <v>luis.saune.ludena@gmail.com</v>
+      </c>
+      <c r="I72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitectura")</f>
+        <v>Arquitectura</v>
+      </c>
+      <c r="J72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Arquitecturas")</f>
+        <v>Arquitecturas</v>
+      </c>
+      <c r="K72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO CON CONVA")</f>
+        <v>TRASLADO CON CONVA</v>
+      </c>
+      <c r="P72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T72" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45804.0)</f>
+        <v>45804</v>
+      </c>
+      <c r="U72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pago Link")</f>
+        <v>Pago Link</v>
+      </c>
+      <c r="V72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="W72" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),550.0)</f>
+        <v>550</v>
+      </c>
+      <c r="X72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
+        <v>31/05/2025</v>
+      </c>
       <c r="Y72" s="1"/>
-      <c r="Z72" s="1"/>
-      <c r="AA72" s="1"/>
+      <c r="Z72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="AA72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB72" s="1"/>
-      <c r="AC72" s="1"/>
-      <c r="AD72" s="1"/>
-      <c r="AE72" s="1"/>
-      <c r="AF72" s="1"/>
-      <c r="AG72" s="1"/>
-      <c r="AH72" s="1"/>
-      <c r="AI72" s="1"/>
-      <c r="AJ72" s="1"/>
-      <c r="AK72" s="1"/>
-      <c r="AL72" s="1"/>
-      <c r="AM72" s="1"/>
-      <c r="AN72" s="1"/>
-      <c r="AO72" s="1"/>
-      <c r="AP72" s="1"/>
-      <c r="AQ72" s="1"/>
-      <c r="AR72" s="1"/>
-      <c r="AS72" s="1"/>
-      <c r="AT72" s="1"/>
-      <c r="AU72" s="1"/>
-      <c r="AV72" s="1"/>
-      <c r="AW72" s="1"/>
-      <c r="AX72" s="1"/>
-      <c r="AY72" s="1"/>
-      <c r="AZ72" s="1"/>
-      <c r="BA72" s="1"/>
-      <c r="BB72" s="1"/>
-      <c r="BC72" s="1"/>
-      <c r="BD72" s="1"/>
+      <c r="AC72" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD72" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE72" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AF72" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AG72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),774521.0)</f>
+        <v>774521</v>
+      </c>
+      <c r="AK72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
+      <c r="AM72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Instituto de Educación Superior Tecnológico Privado Toulouse Lautrec")</f>
+        <v>Instituto de Educación Superior Tecnológico Privado Toulouse Lautrec</v>
+      </c>
+      <c r="AN72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
+      <c r="AO72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2022.0)</f>
+        <v>2022</v>
+      </c>
+      <c r="AP72" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ72" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR72" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45795.0)</f>
+        <v>45795</v>
+      </c>
+      <c r="AS72" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT72" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
+        <v>9</v>
+      </c>
+      <c r="AV72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Juan Manuel Rodríguez")</f>
+        <v>Juan Manuel Rodríguez</v>
+      </c>
+      <c r="BA72" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.35294117647058826)</f>
+        <v>0.3529411765</v>
+      </c>
+      <c r="BB72" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="BC72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD72" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="BE72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
-      <c r="U73" s="1"/>
-      <c r="V73" s="1"/>
-      <c r="W73" s="1"/>
-      <c r="X73" s="1"/>
-      <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
+      <c r="A73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),72.0)</f>
+        <v>72</v>
+      </c>
+      <c r="B73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1578825.0)</f>
+        <v>1578825</v>
+      </c>
+      <c r="C73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000025424")</f>
+        <v>0000025424</v>
+      </c>
+      <c r="D73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ALVARO RUBEN RAUL ")</f>
+        <v>ALVARO RUBEN RAUL </v>
+      </c>
+      <c r="E73" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PEREZ RAMOS")</f>
+        <v>PEREZ RAMOS</v>
+      </c>
+      <c r="F73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.3367148E7)</f>
+        <v>73367148</v>
+      </c>
+      <c r="G73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.25991387E8)</f>
+        <v>925991387</v>
+      </c>
+      <c r="H73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Alvaroperezramos2004@gmail.com")</f>
+        <v>Alvaroperezramos2004@gmail.com</v>
+      </c>
+      <c r="I73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO SIN CONVA")</f>
+        <v>TRASLADO SIN CONVA</v>
+      </c>
+      <c r="P73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RECA")</f>
+        <v>RECA</v>
+      </c>
+      <c r="Q73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRIGO")</f>
+        <v>RODRIGO</v>
+      </c>
+      <c r="T73" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="U73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W73" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="Z73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB73" s="1"/>
-      <c r="AC73" s="1"/>
-      <c r="AD73" s="1"/>
-      <c r="AE73" s="1"/>
-      <c r="AF73" s="1"/>
-      <c r="AG73" s="1"/>
-      <c r="AH73" s="1"/>
-      <c r="AI73" s="1"/>
-      <c r="AJ73" s="1"/>
-      <c r="AK73" s="1"/>
-      <c r="AL73" s="1"/>
+      <c r="AC73" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD73" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE73" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="AF73" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="AG73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),773879.0)</f>
+        <v>773879</v>
+      </c>
+      <c r="AK73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
+        <v>Más de 15 kms</v>
+      </c>
+      <c r="AL73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"04 200 a 300")</f>
+        <v>04 200 a 300</v>
+      </c>
       <c r="AM73" s="1"/>
-      <c r="AN73" s="1"/>
-      <c r="AO73" s="1"/>
-      <c r="AP73" s="1"/>
-      <c r="AQ73" s="1"/>
-      <c r="AR73" s="1"/>
-      <c r="AS73" s="1"/>
-      <c r="AT73" s="1"/>
-      <c r="AU73" s="1"/>
-      <c r="AV73" s="1"/>
-      <c r="AW73" s="1"/>
-      <c r="AX73" s="1"/>
-      <c r="AY73" s="1"/>
-      <c r="AZ73" s="1"/>
-      <c r="BA73" s="1"/>
-      <c r="BB73" s="1"/>
-      <c r="BC73" s="1"/>
-      <c r="BD73" s="1"/>
+      <c r="AN73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
+      <c r="AO73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2022.0)</f>
+        <v>2022</v>
+      </c>
+      <c r="AP73" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45766.0)</f>
+        <v>45766</v>
+      </c>
+      <c r="AS73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45748.0)</f>
+        <v>45748</v>
+      </c>
+      <c r="AT73" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45747.0)</f>
+        <v>45747</v>
+      </c>
+      <c r="AU73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),39.0)</f>
+        <v>39</v>
+      </c>
+      <c r="AV73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEARCH MARCA")</f>
+        <v>SEARCH MARCA</v>
+      </c>
+      <c r="AY73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Andrea Araujo Antara")</f>
+        <v>Andrea Araujo Antara</v>
+      </c>
+      <c r="BA73" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB73" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="BC73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD73" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="BE73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-      <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-      <c r="M74" s="1"/>
-      <c r="N74" s="1"/>
-      <c r="O74" s="1"/>
-      <c r="P74" s="1"/>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
-      <c r="U74" s="1"/>
-      <c r="V74" s="1"/>
-      <c r="W74" s="1"/>
-      <c r="X74" s="1"/>
-      <c r="Y74" s="1"/>
-      <c r="Z74" s="1"/>
-      <c r="AA74" s="1"/>
+      <c r="A74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),73.0)</f>
+        <v>73</v>
+      </c>
+      <c r="B74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4991146.0)</f>
+        <v>4991146</v>
+      </c>
+      <c r="C74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427170")</f>
+        <v>0000427170</v>
+      </c>
+      <c r="D74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CRISTIAN MANUEL")</f>
+        <v>CRISTIAN MANUEL</v>
+      </c>
+      <c r="E74" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRIGUEZ LARREA")</f>
+        <v>RODRIGUEZ LARREA</v>
+      </c>
+      <c r="F74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.0860131E7)</f>
+        <v>60860131</v>
+      </c>
+      <c r="G74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.99905918E8)</f>
+        <v>999905918</v>
+      </c>
+      <c r="H74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"cristian126.2.03@gmail.com")</f>
+        <v>cristian126.2.03@gmail.com</v>
+      </c>
+      <c r="I74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO")</f>
+        <v>TRASLADO</v>
+      </c>
+      <c r="P74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RECA")</f>
+        <v>RECA</v>
+      </c>
+      <c r="Q74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RECATEGORIZACIÓN")</f>
+        <v>RECATEGORIZACIÓN</v>
+      </c>
+      <c r="R74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FABIOLA")</f>
+        <v>FABIOLA</v>
+      </c>
+      <c r="T74" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="U74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W74" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y74" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="Z74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB74" s="1"/>
-      <c r="AC74" s="1"/>
-      <c r="AD74" s="1"/>
-      <c r="AE74" s="1"/>
-      <c r="AF74" s="1"/>
-      <c r="AG74" s="1"/>
-      <c r="AH74" s="1"/>
-      <c r="AI74" s="1"/>
+      <c r="AC74" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD74" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE74" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="AF74" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="AG74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="AJ74" s="1"/>
-      <c r="AK74" s="1"/>
-      <c r="AL74" s="1"/>
+      <c r="AK74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
+        <v>Más de 15 kms</v>
+      </c>
+      <c r="AL74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
       <c r="AM74" s="1"/>
-      <c r="AN74" s="1"/>
+      <c r="AN74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="AO74" s="1"/>
-      <c r="AP74" s="1"/>
-      <c r="AQ74" s="1"/>
-      <c r="AR74" s="1"/>
-      <c r="AS74" s="1"/>
-      <c r="AT74" s="1"/>
-      <c r="AU74" s="1"/>
-      <c r="AV74" s="1"/>
-      <c r="AW74" s="1"/>
-      <c r="AX74" s="1"/>
-      <c r="AY74" s="1"/>
-      <c r="AZ74" s="1"/>
-      <c r="BA74" s="1"/>
-      <c r="BB74" s="1"/>
-      <c r="BC74" s="1"/>
-      <c r="BD74" s="1"/>
+      <c r="AP74" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ74" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR74" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45805.0)</f>
+        <v>45805</v>
+      </c>
+      <c r="AS74" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT74" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AV74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Angelica Iparraguirre")</f>
+        <v>Angelica Iparraguirre</v>
+      </c>
+      <c r="BA74" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB74" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="BC74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD74" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="BE74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>

--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -498,6 +498,10 @@
         <v>CURSO A NIVELAR</v>
       </c>
       <c r="BE1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CONFIRMADO INICIA UCAL")</f>
+        <v>CONFIRMADO INICIA UCAL</v>
+      </c>
+      <c r="BF1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Respuestas NEE")</f>
         <v>Respuestas NEE</v>
       </c>
@@ -716,15 +720,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),900.0)</f>
         <v>900</v>
       </c>
-      <c r="BC2" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC2" s="1"/>
       <c r="BD2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE2" s="1" t="str">
+      <c r="BE2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -951,7 +956,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE3" s="1" t="str">
+      <c r="BE3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1178,7 +1187,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE4" s="1" t="str">
+      <c r="BE4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1397,15 +1410,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),900.0)</f>
         <v>900</v>
       </c>
-      <c r="BC5" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC5" s="1"/>
       <c r="BD5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE5" s="1" t="str">
+      <c r="BE5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1624,15 +1638,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),900.0)</f>
         <v>900</v>
       </c>
-      <c r="BC6" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC6" s="1"/>
       <c r="BD6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE6" s="1" t="str">
+      <c r="BE6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1845,15 +1860,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),900.0)</f>
         <v>900</v>
       </c>
-      <c r="BC7" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC7" s="1"/>
       <c r="BD7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE7" s="1" t="str">
+      <c r="BE7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2080,7 +2096,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE8" s="1" t="str">
+      <c r="BE8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2299,15 +2319,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),900.0)</f>
         <v>900</v>
       </c>
-      <c r="BC9" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC9" s="1"/>
       <c r="BD9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE9" s="1" t="str">
+      <c r="BE9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2526,15 +2547,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),820.0)</f>
         <v>820</v>
       </c>
-      <c r="BC10" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC10" s="1"/>
       <c r="BD10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE10" s="1" t="str">
+      <c r="BE10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2761,7 +2783,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE11" s="1" t="str">
+      <c r="BE11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2988,7 +3014,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE12" s="1" t="str">
+      <c r="BE12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3215,7 +3245,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE13" s="1" t="str">
+      <c r="BE13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3434,15 +3468,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1280.0)</f>
         <v>1280</v>
       </c>
-      <c r="BC14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC14" s="1"/>
       <c r="BD14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE14" s="1" t="str">
+      <c r="BE14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3661,15 +3696,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),700.0)</f>
         <v>700</v>
       </c>
-      <c r="BC15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC15" s="1"/>
       <c r="BD15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE15" s="1" t="str">
+      <c r="BE15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3890,7 +3926,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE16" s="1" t="str">
+      <c r="BE16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4109,15 +4149,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),700.0)</f>
         <v>700</v>
       </c>
-      <c r="BC17" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC17" s="1"/>
       <c r="BD17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE17" s="1" t="str">
+      <c r="BE17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4336,15 +4377,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1030.0)</f>
         <v>1030</v>
       </c>
-      <c r="BC18" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC18" s="1"/>
       <c r="BD18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE18" s="1" t="str">
+      <c r="BE18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4557,15 +4599,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1600.0)</f>
         <v>1600</v>
       </c>
-      <c r="BC19" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC19" s="1"/>
       <c r="BD19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE19" s="1" t="str">
+      <c r="BE19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4792,7 +4835,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE20" s="1" t="str">
+      <c r="BE20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5019,7 +5066,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE21" s="1" t="str">
+      <c r="BE21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5232,15 +5283,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
         <v>750</v>
       </c>
-      <c r="BC22" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC22" s="1"/>
       <c r="BD22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE22" s="1" t="str">
+      <c r="BE22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5335,17 +5387,20 @@
         <v>PAGO FRACCIONADO</v>
       </c>
       <c r="W23" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
-        <v>375</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
         <v>31/05/2025</v>
       </c>
-      <c r="Y23" s="1"/>
+      <c r="Y23" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
       <c r="Z23" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
-        <v>PAGO FRACCIONADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
       </c>
       <c r="AA23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
@@ -5408,7 +5463,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45717.0)</f>
         <v>45717</v>
       </c>
-      <c r="AQ23" s="1"/>
+      <c r="AQ23" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
       <c r="AR23" s="2">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45668.0)</f>
         <v>45668</v>
@@ -5422,8 +5480,8 @@
         <v>45656</v>
       </c>
       <c r="AU23" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),70.0)</f>
-        <v>70</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),139.0)</f>
+        <v>139</v>
       </c>
       <c r="AV23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"OUTBOUND")</f>
@@ -5446,22 +5504,23 @@
         <v>Andrea Crisanto</v>
       </c>
       <c r="BA23" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
-        <v>0.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BB23" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
         <v>750</v>
       </c>
-      <c r="BC23" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC23" s="1"/>
       <c r="BD23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE23" s="1" t="str">
+      <c r="BE23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5680,15 +5739,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),840.0)</f>
         <v>840</v>
       </c>
-      <c r="BC24" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC24" s="1"/>
       <c r="BD24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE24" s="1" t="str">
+      <c r="BE24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5909,7 +5969,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE25" s="1" t="str">
+      <c r="BE25" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF25" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6128,15 +6192,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1650.0)</f>
         <v>1650</v>
       </c>
-      <c r="BC26" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC26" s="1"/>
       <c r="BD26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE26" s="1" t="str">
+      <c r="BE26" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6357,7 +6422,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas")</f>
         <v>Matemáticas</v>
       </c>
-      <c r="BE27" s="1" t="str">
+      <c r="BE27" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6584,7 +6653,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE28" s="1" t="str">
+      <c r="BE28" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6811,7 +6884,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE29" s="1" t="str">
+      <c r="BE29" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF29" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7038,7 +7115,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE30" s="1" t="str">
+      <c r="BE30" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF30" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7257,15 +7338,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
         <v>750</v>
       </c>
-      <c r="BC31" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC31" s="1"/>
       <c r="BD31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE31" s="1" t="str">
+      <c r="BE31" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7492,7 +7574,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE32" s="1" t="str">
+      <c r="BE32" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7719,7 +7805,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ninguno")</f>
         <v>Ninguno</v>
       </c>
-      <c r="BE33" s="1" t="str">
+      <c r="BE33" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF33" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7946,7 +8036,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE34" s="1" t="str">
+      <c r="BE34" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8173,7 +8267,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE35" s="1" t="str">
+      <c r="BE35" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8394,7 +8492,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE36" s="1" t="str">
+      <c r="BE36" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF36" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8621,7 +8723,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ninguno")</f>
         <v>Ninguno</v>
       </c>
-      <c r="BE37" s="1" t="str">
+      <c r="BE37" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF37" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8840,15 +8946,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
       </c>
-      <c r="BC38" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC38" s="1"/>
       <c r="BD38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE38" s="1" t="str">
+      <c r="BE38" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9075,7 +9182,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE39" s="1" t="str">
+      <c r="BE39" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF39" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9302,7 +9413,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Redaccion")</f>
         <v>Redaccion</v>
       </c>
-      <c r="BE40" s="1" t="str">
+      <c r="BE40" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF40" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9529,7 +9644,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Redaccion")</f>
         <v>Redaccion</v>
       </c>
-      <c r="BE41" s="1" t="str">
+      <c r="BE41" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF41" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9756,7 +9875,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE42" s="1" t="str">
+      <c r="BE42" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF42" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9977,7 +10100,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Redaccion")</f>
         <v>Redaccion</v>
       </c>
-      <c r="BE43" s="1" t="str">
+      <c r="BE43" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10198,7 +10325,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE44" s="1" t="str">
+      <c r="BE44" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10425,7 +10556,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE45" s="1" t="str">
+      <c r="BE45" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10652,7 +10787,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE46" s="1" t="str">
+      <c r="BE46" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF46" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10879,7 +11018,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE47" s="1" t="str">
+      <c r="BE47" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF47" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11092,15 +11235,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
       </c>
-      <c r="BC48" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC48" s="1"/>
       <c r="BD48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE48" s="1" t="str">
+      <c r="BE48" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11327,7 +11471,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE49" s="1" t="str">
+      <c r="BE49" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11543,15 +11691,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),830.0)</f>
         <v>830</v>
       </c>
-      <c r="BC50" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC50" s="1"/>
       <c r="BD50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE50" s="1" t="str">
+      <c r="BE50" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11778,7 +11927,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Redaccion")</f>
         <v>Redaccion</v>
       </c>
-      <c r="BE51" s="1" t="str">
+      <c r="BE51" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF51" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12005,7 +12158,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE52" s="1" t="str">
+      <c r="BE52" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF52" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12223,7 +12380,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas y Redaccion")</f>
         <v>Matemáticas y Redaccion</v>
       </c>
-      <c r="BE53" s="1" t="str">
+      <c r="BE53" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12450,7 +12611,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE54" s="1" t="str">
+      <c r="BE54" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12677,7 +12842,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Redaccion")</f>
         <v>Redaccion</v>
       </c>
-      <c r="BE55" s="1" t="str">
+      <c r="BE55" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12904,7 +13073,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE56" s="1" t="str">
+      <c r="BE56" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13123,15 +13296,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),900.0)</f>
         <v>900</v>
       </c>
-      <c r="BC57" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC57" s="1"/>
       <c r="BD57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE57" s="1" t="str">
+      <c r="BE57" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13358,7 +13532,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Redaccion")</f>
         <v>Redaccion</v>
       </c>
-      <c r="BE58" s="1" t="str">
+      <c r="BE58" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF58" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13585,7 +13763,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Matemáticas")</f>
         <v>Matemáticas</v>
       </c>
-      <c r="BE59" s="1" t="str">
+      <c r="BE59" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF59" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13804,15 +13986,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
       </c>
-      <c r="BC60" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC60" s="1"/>
       <c r="BD60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE60" s="1" t="str">
+      <c r="BE60" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14030,7 +14213,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE61" s="1" t="str">
+      <c r="BE61" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14249,15 +14436,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
       </c>
-      <c r="BC62" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC62" s="1"/>
       <c r="BD62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE62" s="1" t="str">
+      <c r="BE62" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14484,7 +14672,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE63" s="1" t="str">
+      <c r="BE63" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF63" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14702,7 +14894,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE64" s="1" t="str">
+      <c r="BE64" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF64" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14923,7 +15119,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE65" s="1" t="str">
+      <c r="BE65" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15136,15 +15336,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1450.0)</f>
         <v>1450</v>
       </c>
-      <c r="BC66" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC66" s="1"/>
       <c r="BD66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE66" s="1" t="str">
+      <c r="BE66" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15363,15 +15564,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1000.0)</f>
         <v>1000</v>
       </c>
-      <c r="BC67" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC67" s="1"/>
       <c r="BD67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE67" s="1" t="str">
+      <c r="BE67" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15598,7 +15800,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE68" s="1" t="str">
+      <c r="BE68" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15825,7 +16031,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE69" s="1" t="str">
+      <c r="BE69" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16052,7 +16262,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE70" s="1" t="str">
+      <c r="BE70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16271,15 +16485,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1100.0)</f>
         <v>1100</v>
       </c>
-      <c r="BC71" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC71" s="1"/>
       <c r="BD71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE71" s="1" t="str">
+      <c r="BE71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16495,15 +16710,16 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
       </c>
-      <c r="BC72" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC72" s="1"/>
       <c r="BD72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE72" s="1" t="str">
+      <c r="BE72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16727,7 +16943,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE73" s="1" t="str">
+      <c r="BE73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16790,8 +17010,8 @@
         <v>Diurno</v>
       </c>
       <c r="O74" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO")</f>
-        <v>TRASLADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO SIN CONVA")</f>
+        <v>TRASLADO SIN CONVA</v>
       </c>
       <c r="P74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RECA")</f>
@@ -16870,7 +17090,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="AJ74" s="1"/>
+      <c r="AJ74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1323856.0)</f>
+        <v>1323856</v>
+      </c>
       <c r="AK74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
         <v>Más de 15 kms</v>
@@ -16945,7 +17168,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="BE74" s="1" t="str">
+      <c r="BE74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17010,7 +17237,8 @@
       <c r="BB75" s="1"/>
       <c r="BC75" s="1"/>
       <c r="BD75" s="1"/>
-      <c r="BE75" s="1" t="str">
+      <c r="BE75" s="1"/>
+      <c r="BF75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17075,7 +17303,8 @@
       <c r="BB76" s="1"/>
       <c r="BC76" s="1"/>
       <c r="BD76" s="1"/>
-      <c r="BE76" s="1" t="str">
+      <c r="BE76" s="1"/>
+      <c r="BF76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17140,7 +17369,8 @@
       <c r="BB77" s="1"/>
       <c r="BC77" s="1"/>
       <c r="BD77" s="1"/>
-      <c r="BE77" s="1" t="str">
+      <c r="BE77" s="1"/>
+      <c r="BF77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17205,7 +17435,8 @@
       <c r="BB78" s="1"/>
       <c r="BC78" s="1"/>
       <c r="BD78" s="1"/>
-      <c r="BE78" s="1" t="str">
+      <c r="BE78" s="1"/>
+      <c r="BF78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17270,7 +17501,8 @@
       <c r="BB79" s="1"/>
       <c r="BC79" s="1"/>
       <c r="BD79" s="1"/>
-      <c r="BE79" s="1" t="str">
+      <c r="BE79" s="1"/>
+      <c r="BF79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17335,7 +17567,8 @@
       <c r="BB80" s="1"/>
       <c r="BC80" s="1"/>
       <c r="BD80" s="1"/>
-      <c r="BE80" s="1" t="str">
+      <c r="BE80" s="1"/>
+      <c r="BF80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17400,7 +17633,8 @@
       <c r="BB81" s="1"/>
       <c r="BC81" s="1"/>
       <c r="BD81" s="1"/>
-      <c r="BE81" s="1" t="str">
+      <c r="BE81" s="1"/>
+      <c r="BF81" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17465,7 +17699,8 @@
       <c r="BB82" s="1"/>
       <c r="BC82" s="1"/>
       <c r="BD82" s="1"/>
-      <c r="BE82" s="1" t="str">
+      <c r="BE82" s="1"/>
+      <c r="BF82" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17530,7 +17765,8 @@
       <c r="BB83" s="1"/>
       <c r="BC83" s="1"/>
       <c r="BD83" s="1"/>
-      <c r="BE83" s="1" t="str">
+      <c r="BE83" s="1"/>
+      <c r="BF83" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17595,7 +17831,8 @@
       <c r="BB84" s="1"/>
       <c r="BC84" s="1"/>
       <c r="BD84" s="1"/>
-      <c r="BE84" s="1" t="str">
+      <c r="BE84" s="1"/>
+      <c r="BF84" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17660,7 +17897,8 @@
       <c r="BB85" s="1"/>
       <c r="BC85" s="1"/>
       <c r="BD85" s="1"/>
-      <c r="BE85" s="1" t="str">
+      <c r="BE85" s="1"/>
+      <c r="BF85" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17725,7 +17963,8 @@
       <c r="BB86" s="1"/>
       <c r="BC86" s="1"/>
       <c r="BD86" s="1"/>
-      <c r="BE86" s="1" t="str">
+      <c r="BE86" s="1"/>
+      <c r="BF86" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17790,7 +18029,8 @@
       <c r="BB87" s="1"/>
       <c r="BC87" s="1"/>
       <c r="BD87" s="1"/>
-      <c r="BE87" s="1" t="str">
+      <c r="BE87" s="1"/>
+      <c r="BF87" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17855,7 +18095,8 @@
       <c r="BB88" s="1"/>
       <c r="BC88" s="1"/>
       <c r="BD88" s="1"/>
-      <c r="BE88" s="1" t="str">
+      <c r="BE88" s="1"/>
+      <c r="BF88" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17920,7 +18161,8 @@
       <c r="BB89" s="1"/>
       <c r="BC89" s="1"/>
       <c r="BD89" s="1"/>
-      <c r="BE89" s="1" t="str">
+      <c r="BE89" s="1"/>
+      <c r="BF89" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17985,7 +18227,8 @@
       <c r="BB90" s="1"/>
       <c r="BC90" s="1"/>
       <c r="BD90" s="1"/>
-      <c r="BE90" s="1" t="str">
+      <c r="BE90" s="1"/>
+      <c r="BF90" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18050,7 +18293,8 @@
       <c r="BB91" s="1"/>
       <c r="BC91" s="1"/>
       <c r="BD91" s="1"/>
-      <c r="BE91" s="1" t="str">
+      <c r="BE91" s="1"/>
+      <c r="BF91" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18115,7 +18359,8 @@
       <c r="BB92" s="1"/>
       <c r="BC92" s="1"/>
       <c r="BD92" s="1"/>
-      <c r="BE92" s="1" t="str">
+      <c r="BE92" s="1"/>
+      <c r="BF92" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18180,7 +18425,8 @@
       <c r="BB93" s="1"/>
       <c r="BC93" s="1"/>
       <c r="BD93" s="1"/>
-      <c r="BE93" s="1" t="str">
+      <c r="BE93" s="1"/>
+      <c r="BF93" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18245,7 +18491,8 @@
       <c r="BB94" s="1"/>
       <c r="BC94" s="1"/>
       <c r="BD94" s="1"/>
-      <c r="BE94" s="1" t="str">
+      <c r="BE94" s="1"/>
+      <c r="BF94" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18310,7 +18557,8 @@
       <c r="BB95" s="1"/>
       <c r="BC95" s="1"/>
       <c r="BD95" s="1"/>
-      <c r="BE95" s="1" t="str">
+      <c r="BE95" s="1"/>
+      <c r="BF95" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18375,7 +18623,8 @@
       <c r="BB96" s="1"/>
       <c r="BC96" s="1"/>
       <c r="BD96" s="1"/>
-      <c r="BE96" s="1" t="str">
+      <c r="BE96" s="1"/>
+      <c r="BF96" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18440,7 +18689,8 @@
       <c r="BB97" s="1"/>
       <c r="BC97" s="1"/>
       <c r="BD97" s="1"/>
-      <c r="BE97" s="1" t="str">
+      <c r="BE97" s="1"/>
+      <c r="BF97" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18505,7 +18755,8 @@
       <c r="BB98" s="1"/>
       <c r="BC98" s="1"/>
       <c r="BD98" s="1"/>
-      <c r="BE98" s="1" t="str">
+      <c r="BE98" s="1"/>
+      <c r="BF98" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18570,7 +18821,8 @@
       <c r="BB99" s="1"/>
       <c r="BC99" s="1"/>
       <c r="BD99" s="1"/>
-      <c r="BE99" s="1" t="str">
+      <c r="BE99" s="1"/>
+      <c r="BF99" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18635,7 +18887,8 @@
       <c r="BB100" s="1"/>
       <c r="BC100" s="1"/>
       <c r="BD100" s="1"/>
-      <c r="BE100" s="1" t="str">
+      <c r="BE100" s="1"/>
+      <c r="BF100" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18700,7 +18953,8 @@
       <c r="BB101" s="1"/>
       <c r="BC101" s="1"/>
       <c r="BD101" s="1"/>
-      <c r="BE101" s="1" t="str">
+      <c r="BE101" s="1"/>
+      <c r="BF101" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18765,7 +19019,8 @@
       <c r="BB102" s="1"/>
       <c r="BC102" s="1"/>
       <c r="BD102" s="1"/>
-      <c r="BE102" s="1" t="str">
+      <c r="BE102" s="1"/>
+      <c r="BF102" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18830,7 +19085,8 @@
       <c r="BB103" s="1"/>
       <c r="BC103" s="1"/>
       <c r="BD103" s="1"/>
-      <c r="BE103" s="1" t="str">
+      <c r="BE103" s="1"/>
+      <c r="BF103" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18895,7 +19151,8 @@
       <c r="BB104" s="1"/>
       <c r="BC104" s="1"/>
       <c r="BD104" s="1"/>
-      <c r="BE104" s="1" t="str">
+      <c r="BE104" s="1"/>
+      <c r="BF104" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18960,7 +19217,8 @@
       <c r="BB105" s="1"/>
       <c r="BC105" s="1"/>
       <c r="BD105" s="1"/>
-      <c r="BE105" s="1" t="str">
+      <c r="BE105" s="1"/>
+      <c r="BF105" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19025,7 +19283,8 @@
       <c r="BB106" s="1"/>
       <c r="BC106" s="1"/>
       <c r="BD106" s="1"/>
-      <c r="BE106" s="1" t="str">
+      <c r="BE106" s="1"/>
+      <c r="BF106" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19090,7 +19349,8 @@
       <c r="BB107" s="1"/>
       <c r="BC107" s="1"/>
       <c r="BD107" s="1"/>
-      <c r="BE107" s="1" t="str">
+      <c r="BE107" s="1"/>
+      <c r="BF107" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19155,7 +19415,8 @@
       <c r="BB108" s="1"/>
       <c r="BC108" s="1"/>
       <c r="BD108" s="1"/>
-      <c r="BE108" s="1" t="str">
+      <c r="BE108" s="1"/>
+      <c r="BF108" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19220,7 +19481,8 @@
       <c r="BB109" s="1"/>
       <c r="BC109" s="1"/>
       <c r="BD109" s="1"/>
-      <c r="BE109" s="1" t="str">
+      <c r="BE109" s="1"/>
+      <c r="BF109" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19285,7 +19547,8 @@
       <c r="BB110" s="1"/>
       <c r="BC110" s="1"/>
       <c r="BD110" s="1"/>
-      <c r="BE110" s="1" t="str">
+      <c r="BE110" s="1"/>
+      <c r="BF110" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19350,7 +19613,8 @@
       <c r="BB111" s="1"/>
       <c r="BC111" s="1"/>
       <c r="BD111" s="1"/>
-      <c r="BE111" s="1" t="str">
+      <c r="BE111" s="1"/>
+      <c r="BF111" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19415,7 +19679,8 @@
       <c r="BB112" s="1"/>
       <c r="BC112" s="1"/>
       <c r="BD112" s="1"/>
-      <c r="BE112" s="1" t="str">
+      <c r="BE112" s="1"/>
+      <c r="BF112" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19480,7 +19745,8 @@
       <c r="BB113" s="1"/>
       <c r="BC113" s="1"/>
       <c r="BD113" s="1"/>
-      <c r="BE113" s="1" t="str">
+      <c r="BE113" s="1"/>
+      <c r="BF113" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19545,7 +19811,8 @@
       <c r="BB114" s="1"/>
       <c r="BC114" s="1"/>
       <c r="BD114" s="1"/>
-      <c r="BE114" s="1" t="str">
+      <c r="BE114" s="1"/>
+      <c r="BF114" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19610,7 +19877,8 @@
       <c r="BB115" s="1"/>
       <c r="BC115" s="1"/>
       <c r="BD115" s="1"/>
-      <c r="BE115" s="1" t="str">
+      <c r="BE115" s="1"/>
+      <c r="BF115" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19675,7 +19943,8 @@
       <c r="BB116" s="1"/>
       <c r="BC116" s="1"/>
       <c r="BD116" s="1"/>
-      <c r="BE116" s="1" t="str">
+      <c r="BE116" s="1"/>
+      <c r="BF116" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19740,7 +20009,8 @@
       <c r="BB117" s="1"/>
       <c r="BC117" s="1"/>
       <c r="BD117" s="1"/>
-      <c r="BE117" s="1" t="str">
+      <c r="BE117" s="1"/>
+      <c r="BF117" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19805,7 +20075,8 @@
       <c r="BB118" s="1"/>
       <c r="BC118" s="1"/>
       <c r="BD118" s="1"/>
-      <c r="BE118" s="1" t="str">
+      <c r="BE118" s="1"/>
+      <c r="BF118" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19870,7 +20141,8 @@
       <c r="BB119" s="1"/>
       <c r="BC119" s="1"/>
       <c r="BD119" s="1"/>
-      <c r="BE119" s="1" t="str">
+      <c r="BE119" s="1"/>
+      <c r="BF119" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19935,7 +20207,8 @@
       <c r="BB120" s="1"/>
       <c r="BC120" s="1"/>
       <c r="BD120" s="1"/>
-      <c r="BE120" s="1" t="str">
+      <c r="BE120" s="1"/>
+      <c r="BF120" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20000,7 +20273,8 @@
       <c r="BB121" s="1"/>
       <c r="BC121" s="1"/>
       <c r="BD121" s="1"/>
-      <c r="BE121" s="1" t="str">
+      <c r="BE121" s="1"/>
+      <c r="BF121" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20065,7 +20339,8 @@
       <c r="BB122" s="1"/>
       <c r="BC122" s="1"/>
       <c r="BD122" s="1"/>
-      <c r="BE122" s="1" t="str">
+      <c r="BE122" s="1"/>
+      <c r="BF122" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20130,7 +20405,8 @@
       <c r="BB123" s="1"/>
       <c r="BC123" s="1"/>
       <c r="BD123" s="1"/>
-      <c r="BE123" s="1" t="str">
+      <c r="BE123" s="1"/>
+      <c r="BF123" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20195,7 +20471,8 @@
       <c r="BB124" s="1"/>
       <c r="BC124" s="1"/>
       <c r="BD124" s="1"/>
-      <c r="BE124" s="1" t="str">
+      <c r="BE124" s="1"/>
+      <c r="BF124" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20260,7 +20537,8 @@
       <c r="BB125" s="1"/>
       <c r="BC125" s="1"/>
       <c r="BD125" s="1"/>
-      <c r="BE125" s="1" t="str">
+      <c r="BE125" s="1"/>
+      <c r="BF125" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20325,7 +20603,8 @@
       <c r="BB126" s="1"/>
       <c r="BC126" s="1"/>
       <c r="BD126" s="1"/>
-      <c r="BE126" s="1" t="str">
+      <c r="BE126" s="1"/>
+      <c r="BF126" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20390,7 +20669,8 @@
       <c r="BB127" s="1"/>
       <c r="BC127" s="1"/>
       <c r="BD127" s="1"/>
-      <c r="BE127" s="1" t="str">
+      <c r="BE127" s="1"/>
+      <c r="BF127" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20455,7 +20735,8 @@
       <c r="BB128" s="1"/>
       <c r="BC128" s="1"/>
       <c r="BD128" s="1"/>
-      <c r="BE128" s="1" t="str">
+      <c r="BE128" s="1"/>
+      <c r="BF128" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20520,7 +20801,8 @@
       <c r="BB129" s="1"/>
       <c r="BC129" s="1"/>
       <c r="BD129" s="1"/>
-      <c r="BE129" s="1" t="str">
+      <c r="BE129" s="1"/>
+      <c r="BF129" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20585,7 +20867,8 @@
       <c r="BB130" s="1"/>
       <c r="BC130" s="1"/>
       <c r="BD130" s="1"/>
-      <c r="BE130" s="1" t="str">
+      <c r="BE130" s="1"/>
+      <c r="BF130" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20650,7 +20933,8 @@
       <c r="BB131" s="1"/>
       <c r="BC131" s="1"/>
       <c r="BD131" s="1"/>
-      <c r="BE131" s="1" t="str">
+      <c r="BE131" s="1"/>
+      <c r="BF131" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20715,7 +20999,8 @@
       <c r="BB132" s="1"/>
       <c r="BC132" s="1"/>
       <c r="BD132" s="1"/>
-      <c r="BE132" s="1" t="str">
+      <c r="BE132" s="1"/>
+      <c r="BF132" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20780,7 +21065,8 @@
       <c r="BB133" s="1"/>
       <c r="BC133" s="1"/>
       <c r="BD133" s="1"/>
-      <c r="BE133" s="1" t="str">
+      <c r="BE133" s="1"/>
+      <c r="BF133" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20845,7 +21131,8 @@
       <c r="BB134" s="1"/>
       <c r="BC134" s="1"/>
       <c r="BD134" s="1"/>
-      <c r="BE134" s="1" t="str">
+      <c r="BE134" s="1"/>
+      <c r="BF134" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20910,7 +21197,8 @@
       <c r="BB135" s="1"/>
       <c r="BC135" s="1"/>
       <c r="BD135" s="1"/>
-      <c r="BE135" s="1" t="str">
+      <c r="BE135" s="1"/>
+      <c r="BF135" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20975,7 +21263,8 @@
       <c r="BB136" s="1"/>
       <c r="BC136" s="1"/>
       <c r="BD136" s="1"/>
-      <c r="BE136" s="1" t="str">
+      <c r="BE136" s="1"/>
+      <c r="BF136" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21040,7 +21329,8 @@
       <c r="BB137" s="1"/>
       <c r="BC137" s="1"/>
       <c r="BD137" s="1"/>
-      <c r="BE137" s="1" t="str">
+      <c r="BE137" s="1"/>
+      <c r="BF137" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21105,7 +21395,8 @@
       <c r="BB138" s="1"/>
       <c r="BC138" s="1"/>
       <c r="BD138" s="1"/>
-      <c r="BE138" s="1" t="str">
+      <c r="BE138" s="1"/>
+      <c r="BF138" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21170,7 +21461,8 @@
       <c r="BB139" s="1"/>
       <c r="BC139" s="1"/>
       <c r="BD139" s="1"/>
-      <c r="BE139" s="1" t="str">
+      <c r="BE139" s="1"/>
+      <c r="BF139" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21235,7 +21527,8 @@
       <c r="BB140" s="1"/>
       <c r="BC140" s="1"/>
       <c r="BD140" s="1"/>
-      <c r="BE140" s="1" t="str">
+      <c r="BE140" s="1"/>
+      <c r="BF140" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21300,7 +21593,8 @@
       <c r="BB141" s="1"/>
       <c r="BC141" s="1"/>
       <c r="BD141" s="1"/>
-      <c r="BE141" s="1" t="str">
+      <c r="BE141" s="1"/>
+      <c r="BF141" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21365,7 +21659,8 @@
       <c r="BB142" s="1"/>
       <c r="BC142" s="1"/>
       <c r="BD142" s="1"/>
-      <c r="BE142" s="1" t="str">
+      <c r="BE142" s="1"/>
+      <c r="BF142" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21430,7 +21725,8 @@
       <c r="BB143" s="1"/>
       <c r="BC143" s="1"/>
       <c r="BD143" s="1"/>
-      <c r="BE143" s="1" t="str">
+      <c r="BE143" s="1"/>
+      <c r="BF143" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21495,7 +21791,8 @@
       <c r="BB144" s="1"/>
       <c r="BC144" s="1"/>
       <c r="BD144" s="1"/>
-      <c r="BE144" s="1" t="str">
+      <c r="BE144" s="1"/>
+      <c r="BF144" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21560,7 +21857,8 @@
       <c r="BB145" s="1"/>
       <c r="BC145" s="1"/>
       <c r="BD145" s="1"/>
-      <c r="BE145" s="1" t="str">
+      <c r="BE145" s="1"/>
+      <c r="BF145" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21625,7 +21923,8 @@
       <c r="BB146" s="1"/>
       <c r="BC146" s="1"/>
       <c r="BD146" s="1"/>
-      <c r="BE146" s="1" t="str">
+      <c r="BE146" s="1"/>
+      <c r="BF146" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21690,7 +21989,8 @@
       <c r="BB147" s="1"/>
       <c r="BC147" s="1"/>
       <c r="BD147" s="1"/>
-      <c r="BE147" s="1" t="str">
+      <c r="BE147" s="1"/>
+      <c r="BF147" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21755,7 +22055,8 @@
       <c r="BB148" s="1"/>
       <c r="BC148" s="1"/>
       <c r="BD148" s="1"/>
-      <c r="BE148" s="1" t="str">
+      <c r="BE148" s="1"/>
+      <c r="BF148" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21820,7 +22121,8 @@
       <c r="BB149" s="1"/>
       <c r="BC149" s="1"/>
       <c r="BD149" s="1"/>
-      <c r="BE149" s="1" t="str">
+      <c r="BE149" s="1"/>
+      <c r="BF149" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21885,7 +22187,8 @@
       <c r="BB150" s="1"/>
       <c r="BC150" s="1"/>
       <c r="BD150" s="1"/>
-      <c r="BE150" s="1" t="str">
+      <c r="BE150" s="1"/>
+      <c r="BF150" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21950,7 +22253,8 @@
       <c r="BB151" s="1"/>
       <c r="BC151" s="1"/>
       <c r="BD151" s="1"/>
-      <c r="BE151" s="1" t="str">
+      <c r="BE151" s="1"/>
+      <c r="BF151" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22015,7 +22319,8 @@
       <c r="BB152" s="1"/>
       <c r="BC152" s="1"/>
       <c r="BD152" s="1"/>
-      <c r="BE152" s="1" t="str">
+      <c r="BE152" s="1"/>
+      <c r="BF152" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22080,7 +22385,8 @@
       <c r="BB153" s="1"/>
       <c r="BC153" s="1"/>
       <c r="BD153" s="1"/>
-      <c r="BE153" s="1" t="str">
+      <c r="BE153" s="1"/>
+      <c r="BF153" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22145,7 +22451,8 @@
       <c r="BB154" s="1"/>
       <c r="BC154" s="1"/>
       <c r="BD154" s="1"/>
-      <c r="BE154" s="1" t="str">
+      <c r="BE154" s="1"/>
+      <c r="BF154" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22210,7 +22517,8 @@
       <c r="BB155" s="1"/>
       <c r="BC155" s="1"/>
       <c r="BD155" s="1"/>
-      <c r="BE155" s="1" t="str">
+      <c r="BE155" s="1"/>
+      <c r="BF155" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22275,7 +22583,8 @@
       <c r="BB156" s="1"/>
       <c r="BC156" s="1"/>
       <c r="BD156" s="1"/>
-      <c r="BE156" s="1" t="str">
+      <c r="BE156" s="1"/>
+      <c r="BF156" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22340,7 +22649,8 @@
       <c r="BB157" s="1"/>
       <c r="BC157" s="1"/>
       <c r="BD157" s="1"/>
-      <c r="BE157" s="1" t="str">
+      <c r="BE157" s="1"/>
+      <c r="BF157" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22405,7 +22715,8 @@
       <c r="BB158" s="1"/>
       <c r="BC158" s="1"/>
       <c r="BD158" s="1"/>
-      <c r="BE158" s="1" t="str">
+      <c r="BE158" s="1"/>
+      <c r="BF158" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22470,7 +22781,8 @@
       <c r="BB159" s="1"/>
       <c r="BC159" s="1"/>
       <c r="BD159" s="1"/>
-      <c r="BE159" s="1" t="str">
+      <c r="BE159" s="1"/>
+      <c r="BF159" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22535,7 +22847,8 @@
       <c r="BB160" s="1"/>
       <c r="BC160" s="1"/>
       <c r="BD160" s="1"/>
-      <c r="BE160" s="1" t="str">
+      <c r="BE160" s="1"/>
+      <c r="BF160" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22600,7 +22913,8 @@
       <c r="BB161" s="1"/>
       <c r="BC161" s="1"/>
       <c r="BD161" s="1"/>
-      <c r="BE161" s="1" t="str">
+      <c r="BE161" s="1"/>
+      <c r="BF161" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22665,7 +22979,8 @@
       <c r="BB162" s="1"/>
       <c r="BC162" s="1"/>
       <c r="BD162" s="1"/>
-      <c r="BE162" s="1" t="str">
+      <c r="BE162" s="1"/>
+      <c r="BF162" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22730,7 +23045,8 @@
       <c r="BB163" s="1"/>
       <c r="BC163" s="1"/>
       <c r="BD163" s="1"/>
-      <c r="BE163" s="1" t="str">
+      <c r="BE163" s="1"/>
+      <c r="BF163" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22795,7 +23111,8 @@
       <c r="BB164" s="1"/>
       <c r="BC164" s="1"/>
       <c r="BD164" s="1"/>
-      <c r="BE164" s="1" t="str">
+      <c r="BE164" s="1"/>
+      <c r="BF164" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22860,7 +23177,8 @@
       <c r="BB165" s="1"/>
       <c r="BC165" s="1"/>
       <c r="BD165" s="1"/>
-      <c r="BE165" s="1" t="str">
+      <c r="BE165" s="1"/>
+      <c r="BF165" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22925,7 +23243,8 @@
       <c r="BB166" s="1"/>
       <c r="BC166" s="1"/>
       <c r="BD166" s="1"/>
-      <c r="BE166" s="1" t="str">
+      <c r="BE166" s="1"/>
+      <c r="BF166" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22990,7 +23309,8 @@
       <c r="BB167" s="1"/>
       <c r="BC167" s="1"/>
       <c r="BD167" s="1"/>
-      <c r="BE167" s="1" t="str">
+      <c r="BE167" s="1"/>
+      <c r="BF167" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23055,7 +23375,8 @@
       <c r="BB168" s="1"/>
       <c r="BC168" s="1"/>
       <c r="BD168" s="1"/>
-      <c r="BE168" s="1" t="str">
+      <c r="BE168" s="1"/>
+      <c r="BF168" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23120,7 +23441,8 @@
       <c r="BB169" s="1"/>
       <c r="BC169" s="1"/>
       <c r="BD169" s="1"/>
-      <c r="BE169" s="1" t="str">
+      <c r="BE169" s="1"/>
+      <c r="BF169" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23185,7 +23507,8 @@
       <c r="BB170" s="1"/>
       <c r="BC170" s="1"/>
       <c r="BD170" s="1"/>
-      <c r="BE170" s="1" t="str">
+      <c r="BE170" s="1"/>
+      <c r="BF170" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23250,7 +23573,8 @@
       <c r="BB171" s="1"/>
       <c r="BC171" s="1"/>
       <c r="BD171" s="1"/>
-      <c r="BE171" s="1" t="str">
+      <c r="BE171" s="1"/>
+      <c r="BF171" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23315,7 +23639,8 @@
       <c r="BB172" s="1"/>
       <c r="BC172" s="1"/>
       <c r="BD172" s="1"/>
-      <c r="BE172" s="1" t="str">
+      <c r="BE172" s="1"/>
+      <c r="BF172" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23380,7 +23705,8 @@
       <c r="BB173" s="1"/>
       <c r="BC173" s="1"/>
       <c r="BD173" s="1"/>
-      <c r="BE173" s="1" t="str">
+      <c r="BE173" s="1"/>
+      <c r="BF173" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23445,7 +23771,8 @@
       <c r="BB174" s="1"/>
       <c r="BC174" s="1"/>
       <c r="BD174" s="1"/>
-      <c r="BE174" s="1" t="str">
+      <c r="BE174" s="1"/>
+      <c r="BF174" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23510,7 +23837,8 @@
       <c r="BB175" s="1"/>
       <c r="BC175" s="1"/>
       <c r="BD175" s="1"/>
-      <c r="BE175" s="1" t="str">
+      <c r="BE175" s="1"/>
+      <c r="BF175" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23575,7 +23903,8 @@
       <c r="BB176" s="1"/>
       <c r="BC176" s="1"/>
       <c r="BD176" s="1"/>
-      <c r="BE176" s="1" t="str">
+      <c r="BE176" s="1"/>
+      <c r="BF176" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23640,7 +23969,8 @@
       <c r="BB177" s="1"/>
       <c r="BC177" s="1"/>
       <c r="BD177" s="1"/>
-      <c r="BE177" s="1" t="str">
+      <c r="BE177" s="1"/>
+      <c r="BF177" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23705,7 +24035,8 @@
       <c r="BB178" s="1"/>
       <c r="BC178" s="1"/>
       <c r="BD178" s="1"/>
-      <c r="BE178" s="1" t="str">
+      <c r="BE178" s="1"/>
+      <c r="BF178" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23770,7 +24101,8 @@
       <c r="BB179" s="1"/>
       <c r="BC179" s="1"/>
       <c r="BD179" s="1"/>
-      <c r="BE179" s="1" t="str">
+      <c r="BE179" s="1"/>
+      <c r="BF179" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23835,7 +24167,8 @@
       <c r="BB180" s="1"/>
       <c r="BC180" s="1"/>
       <c r="BD180" s="1"/>
-      <c r="BE180" s="1" t="str">
+      <c r="BE180" s="1"/>
+      <c r="BF180" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23900,7 +24233,8 @@
       <c r="BB181" s="1"/>
       <c r="BC181" s="1"/>
       <c r="BD181" s="1"/>
-      <c r="BE181" s="1" t="str">
+      <c r="BE181" s="1"/>
+      <c r="BF181" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23965,7 +24299,8 @@
       <c r="BB182" s="1"/>
       <c r="BC182" s="1"/>
       <c r="BD182" s="1"/>
-      <c r="BE182" s="1" t="str">
+      <c r="BE182" s="1"/>
+      <c r="BF182" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24030,7 +24365,8 @@
       <c r="BB183" s="1"/>
       <c r="BC183" s="1"/>
       <c r="BD183" s="1"/>
-      <c r="BE183" s="1" t="str">
+      <c r="BE183" s="1"/>
+      <c r="BF183" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24095,7 +24431,8 @@
       <c r="BB184" s="1"/>
       <c r="BC184" s="1"/>
       <c r="BD184" s="1"/>
-      <c r="BE184" s="1" t="str">
+      <c r="BE184" s="1"/>
+      <c r="BF184" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24160,7 +24497,8 @@
       <c r="BB185" s="1"/>
       <c r="BC185" s="1"/>
       <c r="BD185" s="1"/>
-      <c r="BE185" s="1" t="str">
+      <c r="BE185" s="1"/>
+      <c r="BF185" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24225,7 +24563,8 @@
       <c r="BB186" s="1"/>
       <c r="BC186" s="1"/>
       <c r="BD186" s="1"/>
-      <c r="BE186" s="1" t="str">
+      <c r="BE186" s="1"/>
+      <c r="BF186" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24290,7 +24629,8 @@
       <c r="BB187" s="1"/>
       <c r="BC187" s="1"/>
       <c r="BD187" s="1"/>
-      <c r="BE187" s="1" t="str">
+      <c r="BE187" s="1"/>
+      <c r="BF187" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24355,7 +24695,8 @@
       <c r="BB188" s="1"/>
       <c r="BC188" s="1"/>
       <c r="BD188" s="1"/>
-      <c r="BE188" s="1" t="str">
+      <c r="BE188" s="1"/>
+      <c r="BF188" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24420,7 +24761,8 @@
       <c r="BB189" s="1"/>
       <c r="BC189" s="1"/>
       <c r="BD189" s="1"/>
-      <c r="BE189" s="1" t="str">
+      <c r="BE189" s="1"/>
+      <c r="BF189" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24485,7 +24827,8 @@
       <c r="BB190" s="1"/>
       <c r="BC190" s="1"/>
       <c r="BD190" s="1"/>
-      <c r="BE190" s="1" t="str">
+      <c r="BE190" s="1"/>
+      <c r="BF190" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24550,7 +24893,8 @@
       <c r="BB191" s="1"/>
       <c r="BC191" s="1"/>
       <c r="BD191" s="1"/>
-      <c r="BE191" s="1" t="str">
+      <c r="BE191" s="1"/>
+      <c r="BF191" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24615,7 +24959,8 @@
       <c r="BB192" s="1"/>
       <c r="BC192" s="1"/>
       <c r="BD192" s="1"/>
-      <c r="BE192" s="1" t="str">
+      <c r="BE192" s="1"/>
+      <c r="BF192" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24680,7 +25025,8 @@
       <c r="BB193" s="1"/>
       <c r="BC193" s="1"/>
       <c r="BD193" s="1"/>
-      <c r="BE193" s="1" t="str">
+      <c r="BE193" s="1"/>
+      <c r="BF193" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24745,7 +25091,8 @@
       <c r="BB194" s="1"/>
       <c r="BC194" s="1"/>
       <c r="BD194" s="1"/>
-      <c r="BE194" s="1" t="str">
+      <c r="BE194" s="1"/>
+      <c r="BF194" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24810,7 +25157,8 @@
       <c r="BB195" s="1"/>
       <c r="BC195" s="1"/>
       <c r="BD195" s="1"/>
-      <c r="BE195" s="1" t="str">
+      <c r="BE195" s="1"/>
+      <c r="BF195" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24875,7 +25223,8 @@
       <c r="BB196" s="1"/>
       <c r="BC196" s="1"/>
       <c r="BD196" s="1"/>
-      <c r="BE196" s="1" t="str">
+      <c r="BE196" s="1"/>
+      <c r="BF196" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24940,7 +25289,8 @@
       <c r="BB197" s="1"/>
       <c r="BC197" s="1"/>
       <c r="BD197" s="1"/>
-      <c r="BE197" s="1" t="str">
+      <c r="BE197" s="1"/>
+      <c r="BF197" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25005,7 +25355,8 @@
       <c r="BB198" s="1"/>
       <c r="BC198" s="1"/>
       <c r="BD198" s="1"/>
-      <c r="BE198" s="1" t="str">
+      <c r="BE198" s="1"/>
+      <c r="BF198" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25070,7 +25421,8 @@
       <c r="BB199" s="1"/>
       <c r="BC199" s="1"/>
       <c r="BD199" s="1"/>
-      <c r="BE199" s="1" t="str">
+      <c r="BE199" s="1"/>
+      <c r="BF199" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25135,7 +25487,8 @@
       <c r="BB200" s="1"/>
       <c r="BC200" s="1"/>
       <c r="BD200" s="1"/>
-      <c r="BE200" s="1" t="str">
+      <c r="BE200" s="1"/>
+      <c r="BF200" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25200,7 +25553,8 @@
       <c r="BB201" s="1"/>
       <c r="BC201" s="1"/>
       <c r="BD201" s="1"/>
-      <c r="BE201" s="1" t="str">
+      <c r="BE201" s="1"/>
+      <c r="BF201" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25265,7 +25619,8 @@
       <c r="BB202" s="1"/>
       <c r="BC202" s="1"/>
       <c r="BD202" s="1"/>
-      <c r="BE202" s="1" t="str">
+      <c r="BE202" s="1"/>
+      <c r="BF202" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25330,7 +25685,8 @@
       <c r="BB203" s="1"/>
       <c r="BC203" s="1"/>
       <c r="BD203" s="1"/>
-      <c r="BE203" s="1" t="str">
+      <c r="BE203" s="1"/>
+      <c r="BF203" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25395,7 +25751,8 @@
       <c r="BB204" s="1"/>
       <c r="BC204" s="1"/>
       <c r="BD204" s="1"/>
-      <c r="BE204" s="1" t="str">
+      <c r="BE204" s="1"/>
+      <c r="BF204" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25460,7 +25817,8 @@
       <c r="BB205" s="1"/>
       <c r="BC205" s="1"/>
       <c r="BD205" s="1"/>
-      <c r="BE205" s="1" t="str">
+      <c r="BE205" s="1"/>
+      <c r="BF205" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25525,7 +25883,8 @@
       <c r="BB206" s="1"/>
       <c r="BC206" s="1"/>
       <c r="BD206" s="1"/>
-      <c r="BE206" s="1" t="str">
+      <c r="BE206" s="1"/>
+      <c r="BF206" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25590,7 +25949,8 @@
       <c r="BB207" s="1"/>
       <c r="BC207" s="1"/>
       <c r="BD207" s="1"/>
-      <c r="BE207" s="1" t="str">
+      <c r="BE207" s="1"/>
+      <c r="BF207" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25655,7 +26015,8 @@
       <c r="BB208" s="1"/>
       <c r="BC208" s="1"/>
       <c r="BD208" s="1"/>
-      <c r="BE208" s="1" t="str">
+      <c r="BE208" s="1"/>
+      <c r="BF208" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25720,7 +26081,8 @@
       <c r="BB209" s="1"/>
       <c r="BC209" s="1"/>
       <c r="BD209" s="1"/>
-      <c r="BE209" s="1" t="str">
+      <c r="BE209" s="1"/>
+      <c r="BF209" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25785,7 +26147,8 @@
       <c r="BB210" s="1"/>
       <c r="BC210" s="1"/>
       <c r="BD210" s="1"/>
-      <c r="BE210" s="1" t="str">
+      <c r="BE210" s="1"/>
+      <c r="BF210" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25850,7 +26213,8 @@
       <c r="BB211" s="1"/>
       <c r="BC211" s="1"/>
       <c r="BD211" s="1"/>
-      <c r="BE211" s="1" t="str">
+      <c r="BE211" s="1"/>
+      <c r="BF211" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25915,7 +26279,8 @@
       <c r="BB212" s="1"/>
       <c r="BC212" s="1"/>
       <c r="BD212" s="1"/>
-      <c r="BE212" s="1" t="str">
+      <c r="BE212" s="1"/>
+      <c r="BF212" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25980,7 +26345,8 @@
       <c r="BB213" s="1"/>
       <c r="BC213" s="1"/>
       <c r="BD213" s="1"/>
-      <c r="BE213" s="1" t="str">
+      <c r="BE213" s="1"/>
+      <c r="BF213" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26045,7 +26411,8 @@
       <c r="BB214" s="1"/>
       <c r="BC214" s="1"/>
       <c r="BD214" s="1"/>
-      <c r="BE214" s="1" t="str">
+      <c r="BE214" s="1"/>
+      <c r="BF214" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26110,7 +26477,8 @@
       <c r="BB215" s="1"/>
       <c r="BC215" s="1"/>
       <c r="BD215" s="1"/>
-      <c r="BE215" s="1" t="str">
+      <c r="BE215" s="1"/>
+      <c r="BF215" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26175,7 +26543,8 @@
       <c r="BB216" s="1"/>
       <c r="BC216" s="1"/>
       <c r="BD216" s="1"/>
-      <c r="BE216" s="1" t="str">
+      <c r="BE216" s="1"/>
+      <c r="BF216" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26240,7 +26609,8 @@
       <c r="BB217" s="1"/>
       <c r="BC217" s="1"/>
       <c r="BD217" s="1"/>
-      <c r="BE217" s="1" t="str">
+      <c r="BE217" s="1"/>
+      <c r="BF217" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26305,7 +26675,8 @@
       <c r="BB218" s="1"/>
       <c r="BC218" s="1"/>
       <c r="BD218" s="1"/>
-      <c r="BE218" s="1" t="str">
+      <c r="BE218" s="1"/>
+      <c r="BF218" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26370,7 +26741,8 @@
       <c r="BB219" s="1"/>
       <c r="BC219" s="1"/>
       <c r="BD219" s="1"/>
-      <c r="BE219" s="1" t="str">
+      <c r="BE219" s="1"/>
+      <c r="BF219" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26435,7 +26807,8 @@
       <c r="BB220" s="1"/>
       <c r="BC220" s="1"/>
       <c r="BD220" s="1"/>
-      <c r="BE220" s="1" t="str">
+      <c r="BE220" s="1"/>
+      <c r="BF220" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26500,7 +26873,8 @@
       <c r="BB221" s="1"/>
       <c r="BC221" s="1"/>
       <c r="BD221" s="1"/>
-      <c r="BE221" s="1" t="str">
+      <c r="BE221" s="1"/>
+      <c r="BF221" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26565,7 +26939,8 @@
       <c r="BB222" s="1"/>
       <c r="BC222" s="1"/>
       <c r="BD222" s="1"/>
-      <c r="BE222" s="1" t="str">
+      <c r="BE222" s="1"/>
+      <c r="BF222" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26630,7 +27005,8 @@
       <c r="BB223" s="1"/>
       <c r="BC223" s="1"/>
       <c r="BD223" s="1"/>
-      <c r="BE223" s="1" t="str">
+      <c r="BE223" s="1"/>
+      <c r="BF223" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26695,7 +27071,8 @@
       <c r="BB224" s="1"/>
       <c r="BC224" s="1"/>
       <c r="BD224" s="1"/>
-      <c r="BE224" s="1" t="str">
+      <c r="BE224" s="1"/>
+      <c r="BF224" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26760,7 +27137,8 @@
       <c r="BB225" s="1"/>
       <c r="BC225" s="1"/>
       <c r="BD225" s="1"/>
-      <c r="BE225" s="1" t="str">
+      <c r="BE225" s="1"/>
+      <c r="BF225" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26825,7 +27203,8 @@
       <c r="BB226" s="1"/>
       <c r="BC226" s="1"/>
       <c r="BD226" s="1"/>
-      <c r="BE226" s="1" t="str">
+      <c r="BE226" s="1"/>
+      <c r="BF226" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26890,7 +27269,8 @@
       <c r="BB227" s="1"/>
       <c r="BC227" s="1"/>
       <c r="BD227" s="1"/>
-      <c r="BE227" s="1" t="str">
+      <c r="BE227" s="1"/>
+      <c r="BF227" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26955,7 +27335,8 @@
       <c r="BB228" s="1"/>
       <c r="BC228" s="1"/>
       <c r="BD228" s="1"/>
-      <c r="BE228" s="1" t="str">
+      <c r="BE228" s="1"/>
+      <c r="BF228" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27020,7 +27401,8 @@
       <c r="BB229" s="1"/>
       <c r="BC229" s="1"/>
       <c r="BD229" s="1"/>
-      <c r="BE229" s="1" t="str">
+      <c r="BE229" s="1"/>
+      <c r="BF229" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27085,7 +27467,8 @@
       <c r="BB230" s="1"/>
       <c r="BC230" s="1"/>
       <c r="BD230" s="1"/>
-      <c r="BE230" s="1" t="str">
+      <c r="BE230" s="1"/>
+      <c r="BF230" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27150,7 +27533,8 @@
       <c r="BB231" s="1"/>
       <c r="BC231" s="1"/>
       <c r="BD231" s="1"/>
-      <c r="BE231" s="1" t="str">
+      <c r="BE231" s="1"/>
+      <c r="BF231" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27215,7 +27599,8 @@
       <c r="BB232" s="1"/>
       <c r="BC232" s="1"/>
       <c r="BD232" s="1"/>
-      <c r="BE232" s="1" t="str">
+      <c r="BE232" s="1"/>
+      <c r="BF232" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27280,7 +27665,8 @@
       <c r="BB233" s="1"/>
       <c r="BC233" s="1"/>
       <c r="BD233" s="1"/>
-      <c r="BE233" s="1" t="str">
+      <c r="BE233" s="1"/>
+      <c r="BF233" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27345,7 +27731,8 @@
       <c r="BB234" s="1"/>
       <c r="BC234" s="1"/>
       <c r="BD234" s="1"/>
-      <c r="BE234" s="1" t="str">
+      <c r="BE234" s="1"/>
+      <c r="BF234" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27410,7 +27797,8 @@
       <c r="BB235" s="1"/>
       <c r="BC235" s="1"/>
       <c r="BD235" s="1"/>
-      <c r="BE235" s="1" t="str">
+      <c r="BE235" s="1"/>
+      <c r="BF235" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27475,7 +27863,8 @@
       <c r="BB236" s="1"/>
       <c r="BC236" s="1"/>
       <c r="BD236" s="1"/>
-      <c r="BE236" s="1" t="str">
+      <c r="BE236" s="1"/>
+      <c r="BF236" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27540,7 +27929,8 @@
       <c r="BB237" s="1"/>
       <c r="BC237" s="1"/>
       <c r="BD237" s="1"/>
-      <c r="BE237" s="1" t="str">
+      <c r="BE237" s="1"/>
+      <c r="BF237" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27605,7 +27995,8 @@
       <c r="BB238" s="1"/>
       <c r="BC238" s="1"/>
       <c r="BD238" s="1"/>
-      <c r="BE238" s="1" t="str">
+      <c r="BE238" s="1"/>
+      <c r="BF238" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27670,7 +28061,8 @@
       <c r="BB239" s="1"/>
       <c r="BC239" s="1"/>
       <c r="BD239" s="1"/>
-      <c r="BE239" s="1" t="str">
+      <c r="BE239" s="1"/>
+      <c r="BF239" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27735,7 +28127,8 @@
       <c r="BB240" s="1"/>
       <c r="BC240" s="1"/>
       <c r="BD240" s="1"/>
-      <c r="BE240" s="1" t="str">
+      <c r="BE240" s="1"/>
+      <c r="BF240" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27800,7 +28193,8 @@
       <c r="BB241" s="1"/>
       <c r="BC241" s="1"/>
       <c r="BD241" s="1"/>
-      <c r="BE241" s="1" t="str">
+      <c r="BE241" s="1"/>
+      <c r="BF241" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27865,7 +28259,8 @@
       <c r="BB242" s="1"/>
       <c r="BC242" s="1"/>
       <c r="BD242" s="1"/>
-      <c r="BE242" s="1" t="str">
+      <c r="BE242" s="1"/>
+      <c r="BF242" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27930,7 +28325,8 @@
       <c r="BB243" s="1"/>
       <c r="BC243" s="1"/>
       <c r="BD243" s="1"/>
-      <c r="BE243" s="1" t="str">
+      <c r="BE243" s="1"/>
+      <c r="BF243" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27995,7 +28391,8 @@
       <c r="BB244" s="1"/>
       <c r="BC244" s="1"/>
       <c r="BD244" s="1"/>
-      <c r="BE244" s="1" t="str">
+      <c r="BE244" s="1"/>
+      <c r="BF244" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28060,7 +28457,8 @@
       <c r="BB245" s="1"/>
       <c r="BC245" s="1"/>
       <c r="BD245" s="1"/>
-      <c r="BE245" s="1" t="str">
+      <c r="BE245" s="1"/>
+      <c r="BF245" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28125,7 +28523,8 @@
       <c r="BB246" s="1"/>
       <c r="BC246" s="1"/>
       <c r="BD246" s="1"/>
-      <c r="BE246" s="1" t="str">
+      <c r="BE246" s="1"/>
+      <c r="BF246" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28190,7 +28589,8 @@
       <c r="BB247" s="1"/>
       <c r="BC247" s="1"/>
       <c r="BD247" s="1"/>
-      <c r="BE247" s="1" t="str">
+      <c r="BE247" s="1"/>
+      <c r="BF247" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28255,7 +28655,8 @@
       <c r="BB248" s="1"/>
       <c r="BC248" s="1"/>
       <c r="BD248" s="1"/>
-      <c r="BE248" s="1" t="str">
+      <c r="BE248" s="1"/>
+      <c r="BF248" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28320,7 +28721,8 @@
       <c r="BB249" s="1"/>
       <c r="BC249" s="1"/>
       <c r="BD249" s="1"/>
-      <c r="BE249" s="1" t="str">
+      <c r="BE249" s="1"/>
+      <c r="BF249" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28385,7 +28787,8 @@
       <c r="BB250" s="1"/>
       <c r="BC250" s="1"/>
       <c r="BD250" s="1"/>
-      <c r="BE250" s="1" t="str">
+      <c r="BE250" s="1"/>
+      <c r="BF250" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28450,7 +28853,8 @@
       <c r="BB251" s="1"/>
       <c r="BC251" s="1"/>
       <c r="BD251" s="1"/>
-      <c r="BE251" s="1" t="str">
+      <c r="BE251" s="1"/>
+      <c r="BF251" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28515,7 +28919,8 @@
       <c r="BB252" s="1"/>
       <c r="BC252" s="1"/>
       <c r="BD252" s="1"/>
-      <c r="BE252" s="1" t="str">
+      <c r="BE252" s="1"/>
+      <c r="BF252" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28580,7 +28985,8 @@
       <c r="BB253" s="1"/>
       <c r="BC253" s="1"/>
       <c r="BD253" s="1"/>
-      <c r="BE253" s="1" t="str">
+      <c r="BE253" s="1"/>
+      <c r="BF253" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28645,7 +29051,8 @@
       <c r="BB254" s="1"/>
       <c r="BC254" s="1"/>
       <c r="BD254" s="1"/>
-      <c r="BE254" s="1" t="str">
+      <c r="BE254" s="1"/>
+      <c r="BF254" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28710,7 +29117,8 @@
       <c r="BB255" s="1"/>
       <c r="BC255" s="1"/>
       <c r="BD255" s="1"/>
-      <c r="BE255" s="1" t="str">
+      <c r="BE255" s="1"/>
+      <c r="BF255" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28775,7 +29183,8 @@
       <c r="BB256" s="1"/>
       <c r="BC256" s="1"/>
       <c r="BD256" s="1"/>
-      <c r="BE256" s="1" t="str">
+      <c r="BE256" s="1"/>
+      <c r="BF256" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28840,7 +29249,8 @@
       <c r="BB257" s="1"/>
       <c r="BC257" s="1"/>
       <c r="BD257" s="1"/>
-      <c r="BE257" s="1" t="str">
+      <c r="BE257" s="1"/>
+      <c r="BF257" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28905,7 +29315,8 @@
       <c r="BB258" s="1"/>
       <c r="BC258" s="1"/>
       <c r="BD258" s="1"/>
-      <c r="BE258" s="1" t="str">
+      <c r="BE258" s="1"/>
+      <c r="BF258" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28970,7 +29381,8 @@
       <c r="BB259" s="1"/>
       <c r="BC259" s="1"/>
       <c r="BD259" s="1"/>
-      <c r="BE259" s="1" t="str">
+      <c r="BE259" s="1"/>
+      <c r="BF259" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29035,7 +29447,8 @@
       <c r="BB260" s="1"/>
       <c r="BC260" s="1"/>
       <c r="BD260" s="1"/>
-      <c r="BE260" s="1" t="str">
+      <c r="BE260" s="1"/>
+      <c r="BF260" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29100,7 +29513,8 @@
       <c r="BB261" s="1"/>
       <c r="BC261" s="1"/>
       <c r="BD261" s="1"/>
-      <c r="BE261" s="1" t="str">
+      <c r="BE261" s="1"/>
+      <c r="BF261" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29165,7 +29579,8 @@
       <c r="BB262" s="1"/>
       <c r="BC262" s="1"/>
       <c r="BD262" s="1"/>
-      <c r="BE262" s="1" t="str">
+      <c r="BE262" s="1"/>
+      <c r="BF262" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29230,7 +29645,8 @@
       <c r="BB263" s="1"/>
       <c r="BC263" s="1"/>
       <c r="BD263" s="1"/>
-      <c r="BE263" s="1" t="str">
+      <c r="BE263" s="1"/>
+      <c r="BF263" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29295,7 +29711,8 @@
       <c r="BB264" s="1"/>
       <c r="BC264" s="1"/>
       <c r="BD264" s="1"/>
-      <c r="BE264" s="1" t="str">
+      <c r="BE264" s="1"/>
+      <c r="BF264" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29360,7 +29777,8 @@
       <c r="BB265" s="1"/>
       <c r="BC265" s="1"/>
       <c r="BD265" s="1"/>
-      <c r="BE265" s="1" t="str">
+      <c r="BE265" s="1"/>
+      <c r="BF265" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29425,7 +29843,8 @@
       <c r="BB266" s="1"/>
       <c r="BC266" s="1"/>
       <c r="BD266" s="1"/>
-      <c r="BE266" s="1" t="str">
+      <c r="BE266" s="1"/>
+      <c r="BF266" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29490,7 +29909,8 @@
       <c r="BB267" s="1"/>
       <c r="BC267" s="1"/>
       <c r="BD267" s="1"/>
-      <c r="BE267" s="1" t="str">
+      <c r="BE267" s="1"/>
+      <c r="BF267" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29555,7 +29975,8 @@
       <c r="BB268" s="1"/>
       <c r="BC268" s="1"/>
       <c r="BD268" s="1"/>
-      <c r="BE268" s="1" t="str">
+      <c r="BE268" s="1"/>
+      <c r="BF268" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29620,7 +30041,8 @@
       <c r="BB269" s="1"/>
       <c r="BC269" s="1"/>
       <c r="BD269" s="1"/>
-      <c r="BE269" s="1" t="str">
+      <c r="BE269" s="1"/>
+      <c r="BF269" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29685,7 +30107,8 @@
       <c r="BB270" s="1"/>
       <c r="BC270" s="1"/>
       <c r="BD270" s="1"/>
-      <c r="BE270" s="1" t="str">
+      <c r="BE270" s="1"/>
+      <c r="BF270" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29750,7 +30173,8 @@
       <c r="BB271" s="1"/>
       <c r="BC271" s="1"/>
       <c r="BD271" s="1"/>
-      <c r="BE271" s="1" t="str">
+      <c r="BE271" s="1"/>
+      <c r="BF271" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29815,7 +30239,8 @@
       <c r="BB272" s="1"/>
       <c r="BC272" s="1"/>
       <c r="BD272" s="1"/>
-      <c r="BE272" s="1" t="str">
+      <c r="BE272" s="1"/>
+      <c r="BF272" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29880,7 +30305,8 @@
       <c r="BB273" s="1"/>
       <c r="BC273" s="1"/>
       <c r="BD273" s="1"/>
-      <c r="BE273" s="1" t="str">
+      <c r="BE273" s="1"/>
+      <c r="BF273" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29945,7 +30371,8 @@
       <c r="BB274" s="1"/>
       <c r="BC274" s="1"/>
       <c r="BD274" s="1"/>
-      <c r="BE274" s="1" t="str">
+      <c r="BE274" s="1"/>
+      <c r="BF274" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30010,7 +30437,8 @@
       <c r="BB275" s="1"/>
       <c r="BC275" s="1"/>
       <c r="BD275" s="1"/>
-      <c r="BE275" s="1" t="str">
+      <c r="BE275" s="1"/>
+      <c r="BF275" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30075,7 +30503,8 @@
       <c r="BB276" s="1"/>
       <c r="BC276" s="1"/>
       <c r="BD276" s="1"/>
-      <c r="BE276" s="1" t="str">
+      <c r="BE276" s="1"/>
+      <c r="BF276" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30140,7 +30569,8 @@
       <c r="BB277" s="1"/>
       <c r="BC277" s="1"/>
       <c r="BD277" s="1"/>
-      <c r="BE277" s="1" t="str">
+      <c r="BE277" s="1"/>
+      <c r="BF277" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30205,7 +30635,8 @@
       <c r="BB278" s="1"/>
       <c r="BC278" s="1"/>
       <c r="BD278" s="1"/>
-      <c r="BE278" s="1" t="str">
+      <c r="BE278" s="1"/>
+      <c r="BF278" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30270,7 +30701,8 @@
       <c r="BB279" s="1"/>
       <c r="BC279" s="1"/>
       <c r="BD279" s="1"/>
-      <c r="BE279" s="1" t="str">
+      <c r="BE279" s="1"/>
+      <c r="BF279" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30335,7 +30767,8 @@
       <c r="BB280" s="1"/>
       <c r="BC280" s="1"/>
       <c r="BD280" s="1"/>
-      <c r="BE280" s="1" t="str">
+      <c r="BE280" s="1"/>
+      <c r="BF280" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30400,7 +30833,8 @@
       <c r="BB281" s="1"/>
       <c r="BC281" s="1"/>
       <c r="BD281" s="1"/>
-      <c r="BE281" s="1" t="str">
+      <c r="BE281" s="1"/>
+      <c r="BF281" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30465,7 +30899,8 @@
       <c r="BB282" s="1"/>
       <c r="BC282" s="1"/>
       <c r="BD282" s="1"/>
-      <c r="BE282" s="1" t="str">
+      <c r="BE282" s="1"/>
+      <c r="BF282" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30530,7 +30965,8 @@
       <c r="BB283" s="1"/>
       <c r="BC283" s="1"/>
       <c r="BD283" s="1"/>
-      <c r="BE283" s="1" t="str">
+      <c r="BE283" s="1"/>
+      <c r="BF283" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30595,7 +31031,8 @@
       <c r="BB284" s="1"/>
       <c r="BC284" s="1"/>
       <c r="BD284" s="1"/>
-      <c r="BE284" s="1" t="str">
+      <c r="BE284" s="1"/>
+      <c r="BF284" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30660,7 +31097,8 @@
       <c r="BB285" s="1"/>
       <c r="BC285" s="1"/>
       <c r="BD285" s="1"/>
-      <c r="BE285" s="1" t="str">
+      <c r="BE285" s="1"/>
+      <c r="BF285" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30725,7 +31163,8 @@
       <c r="BB286" s="1"/>
       <c r="BC286" s="1"/>
       <c r="BD286" s="1"/>
-      <c r="BE286" s="1" t="str">
+      <c r="BE286" s="1"/>
+      <c r="BF286" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30790,7 +31229,8 @@
       <c r="BB287" s="1"/>
       <c r="BC287" s="1"/>
       <c r="BD287" s="1"/>
-      <c r="BE287" s="1" t="str">
+      <c r="BE287" s="1"/>
+      <c r="BF287" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30855,7 +31295,8 @@
       <c r="BB288" s="1"/>
       <c r="BC288" s="1"/>
       <c r="BD288" s="1"/>
-      <c r="BE288" s="1" t="str">
+      <c r="BE288" s="1"/>
+      <c r="BF288" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30920,7 +31361,8 @@
       <c r="BB289" s="1"/>
       <c r="BC289" s="1"/>
       <c r="BD289" s="1"/>
-      <c r="BE289" s="1" t="str">
+      <c r="BE289" s="1"/>
+      <c r="BF289" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30985,7 +31427,8 @@
       <c r="BB290" s="1"/>
       <c r="BC290" s="1"/>
       <c r="BD290" s="1"/>
-      <c r="BE290" s="1" t="str">
+      <c r="BE290" s="1"/>
+      <c r="BF290" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31050,7 +31493,8 @@
       <c r="BB291" s="1"/>
       <c r="BC291" s="1"/>
       <c r="BD291" s="1"/>
-      <c r="BE291" s="1" t="str">
+      <c r="BE291" s="1"/>
+      <c r="BF291" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31115,7 +31559,8 @@
       <c r="BB292" s="1"/>
       <c r="BC292" s="1"/>
       <c r="BD292" s="1"/>
-      <c r="BE292" s="1" t="str">
+      <c r="BE292" s="1"/>
+      <c r="BF292" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31180,7 +31625,8 @@
       <c r="BB293" s="1"/>
       <c r="BC293" s="1"/>
       <c r="BD293" s="1"/>
-      <c r="BE293" s="1" t="str">
+      <c r="BE293" s="1"/>
+      <c r="BF293" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31245,7 +31691,8 @@
       <c r="BB294" s="1"/>
       <c r="BC294" s="1"/>
       <c r="BD294" s="1"/>
-      <c r="BE294" s="1" t="str">
+      <c r="BE294" s="1"/>
+      <c r="BF294" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31310,7 +31757,8 @@
       <c r="BB295" s="1"/>
       <c r="BC295" s="1"/>
       <c r="BD295" s="1"/>
-      <c r="BE295" s="1" t="str">
+      <c r="BE295" s="1"/>
+      <c r="BF295" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31375,7 +31823,8 @@
       <c r="BB296" s="1"/>
       <c r="BC296" s="1"/>
       <c r="BD296" s="1"/>
-      <c r="BE296" s="1" t="str">
+      <c r="BE296" s="1"/>
+      <c r="BF296" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31440,7 +31889,8 @@
       <c r="BB297" s="1"/>
       <c r="BC297" s="1"/>
       <c r="BD297" s="1"/>
-      <c r="BE297" s="1" t="str">
+      <c r="BE297" s="1"/>
+      <c r="BF297" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31505,7 +31955,8 @@
       <c r="BB298" s="1"/>
       <c r="BC298" s="1"/>
       <c r="BD298" s="1"/>
-      <c r="BE298" s="1" t="str">
+      <c r="BE298" s="1"/>
+      <c r="BF298" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31570,7 +32021,8 @@
       <c r="BB299" s="1"/>
       <c r="BC299" s="1"/>
       <c r="BD299" s="1"/>
-      <c r="BE299" s="1" t="str">
+      <c r="BE299" s="1"/>
+      <c r="BF299" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31635,7 +32087,8 @@
       <c r="BB300" s="1"/>
       <c r="BC300" s="1"/>
       <c r="BD300" s="1"/>
-      <c r="BE300" s="1" t="str">
+      <c r="BE300" s="1"/>
+      <c r="BF300" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31700,7 +32153,8 @@
       <c r="BB301" s="1"/>
       <c r="BC301" s="1"/>
       <c r="BD301" s="1"/>
-      <c r="BE301" s="1" t="str">
+      <c r="BE301" s="1"/>
+      <c r="BF301" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31765,7 +32219,8 @@
       <c r="BB302" s="1"/>
       <c r="BC302" s="1"/>
       <c r="BD302" s="1"/>
-      <c r="BE302" s="1" t="str">
+      <c r="BE302" s="1"/>
+      <c r="BF302" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31830,7 +32285,8 @@
       <c r="BB303" s="1"/>
       <c r="BC303" s="1"/>
       <c r="BD303" s="1"/>
-      <c r="BE303" s="1" t="str">
+      <c r="BE303" s="1"/>
+      <c r="BF303" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31895,7 +32351,8 @@
       <c r="BB304" s="1"/>
       <c r="BC304" s="1"/>
       <c r="BD304" s="1"/>
-      <c r="BE304" s="1" t="str">
+      <c r="BE304" s="1"/>
+      <c r="BF304" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31960,7 +32417,8 @@
       <c r="BB305" s="1"/>
       <c r="BC305" s="1"/>
       <c r="BD305" s="1"/>
-      <c r="BE305" s="1" t="str">
+      <c r="BE305" s="1"/>
+      <c r="BF305" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32025,7 +32483,8 @@
       <c r="BB306" s="1"/>
       <c r="BC306" s="1"/>
       <c r="BD306" s="1"/>
-      <c r="BE306" s="1" t="str">
+      <c r="BE306" s="1"/>
+      <c r="BF306" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32090,7 +32549,8 @@
       <c r="BB307" s="1"/>
       <c r="BC307" s="1"/>
       <c r="BD307" s="1"/>
-      <c r="BE307" s="1" t="str">
+      <c r="BE307" s="1"/>
+      <c r="BF307" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32155,7 +32615,8 @@
       <c r="BB308" s="1"/>
       <c r="BC308" s="1"/>
       <c r="BD308" s="1"/>
-      <c r="BE308" s="1" t="str">
+      <c r="BE308" s="1"/>
+      <c r="BF308" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32220,7 +32681,8 @@
       <c r="BB309" s="1"/>
       <c r="BC309" s="1"/>
       <c r="BD309" s="1"/>
-      <c r="BE309" s="1" t="str">
+      <c r="BE309" s="1"/>
+      <c r="BF309" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32285,7 +32747,8 @@
       <c r="BB310" s="1"/>
       <c r="BC310" s="1"/>
       <c r="BD310" s="1"/>
-      <c r="BE310" s="1" t="str">
+      <c r="BE310" s="1"/>
+      <c r="BF310" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32350,7 +32813,8 @@
       <c r="BB311" s="1"/>
       <c r="BC311" s="1"/>
       <c r="BD311" s="1"/>
-      <c r="BE311" s="1" t="str">
+      <c r="BE311" s="1"/>
+      <c r="BF311" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32415,7 +32879,8 @@
       <c r="BB312" s="1"/>
       <c r="BC312" s="1"/>
       <c r="BD312" s="1"/>
-      <c r="BE312" s="1" t="str">
+      <c r="BE312" s="1"/>
+      <c r="BF312" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32480,7 +32945,8 @@
       <c r="BB313" s="1"/>
       <c r="BC313" s="1"/>
       <c r="BD313" s="1"/>
-      <c r="BE313" s="1" t="str">
+      <c r="BE313" s="1"/>
+      <c r="BF313" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32545,7 +33011,8 @@
       <c r="BB314" s="1"/>
       <c r="BC314" s="1"/>
       <c r="BD314" s="1"/>
-      <c r="BE314" s="1" t="str">
+      <c r="BE314" s="1"/>
+      <c r="BF314" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32610,7 +33077,8 @@
       <c r="BB315" s="1"/>
       <c r="BC315" s="1"/>
       <c r="BD315" s="1"/>
-      <c r="BE315" s="1" t="str">
+      <c r="BE315" s="1"/>
+      <c r="BF315" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32675,7 +33143,8 @@
       <c r="BB316" s="1"/>
       <c r="BC316" s="1"/>
       <c r="BD316" s="1"/>
-      <c r="BE316" s="1" t="str">
+      <c r="BE316" s="1"/>
+      <c r="BF316" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32740,7 +33209,8 @@
       <c r="BB317" s="1"/>
       <c r="BC317" s="1"/>
       <c r="BD317" s="1"/>
-      <c r="BE317" s="1" t="str">
+      <c r="BE317" s="1"/>
+      <c r="BF317" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32805,7 +33275,8 @@
       <c r="BB318" s="1"/>
       <c r="BC318" s="1"/>
       <c r="BD318" s="1"/>
-      <c r="BE318" s="1" t="str">
+      <c r="BE318" s="1"/>
+      <c r="BF318" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32870,7 +33341,8 @@
       <c r="BB319" s="1"/>
       <c r="BC319" s="1"/>
       <c r="BD319" s="1"/>
-      <c r="BE319" s="1" t="str">
+      <c r="BE319" s="1"/>
+      <c r="BF319" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32935,7 +33407,8 @@
       <c r="BB320" s="1"/>
       <c r="BC320" s="1"/>
       <c r="BD320" s="1"/>
-      <c r="BE320" s="1" t="str">
+      <c r="BE320" s="1"/>
+      <c r="BF320" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33000,7 +33473,8 @@
       <c r="BB321" s="1"/>
       <c r="BC321" s="1"/>
       <c r="BD321" s="1"/>
-      <c r="BE321" s="1" t="str">
+      <c r="BE321" s="1"/>
+      <c r="BF321" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33065,7 +33539,8 @@
       <c r="BB322" s="1"/>
       <c r="BC322" s="1"/>
       <c r="BD322" s="1"/>
-      <c r="BE322" s="1" t="str">
+      <c r="BE322" s="1"/>
+      <c r="BF322" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33130,7 +33605,8 @@
       <c r="BB323" s="1"/>
       <c r="BC323" s="1"/>
       <c r="BD323" s="1"/>
-      <c r="BE323" s="1" t="str">
+      <c r="BE323" s="1"/>
+      <c r="BF323" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33195,7 +33671,8 @@
       <c r="BB324" s="1"/>
       <c r="BC324" s="1"/>
       <c r="BD324" s="1"/>
-      <c r="BE324" s="1" t="str">
+      <c r="BE324" s="1"/>
+      <c r="BF324" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33260,7 +33737,8 @@
       <c r="BB325" s="1"/>
       <c r="BC325" s="1"/>
       <c r="BD325" s="1"/>
-      <c r="BE325" s="1" t="str">
+      <c r="BE325" s="1"/>
+      <c r="BF325" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33325,7 +33803,8 @@
       <c r="BB326" s="1"/>
       <c r="BC326" s="1"/>
       <c r="BD326" s="1"/>
-      <c r="BE326" s="1" t="str">
+      <c r="BE326" s="1"/>
+      <c r="BF326" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33390,7 +33869,8 @@
       <c r="BB327" s="1"/>
       <c r="BC327" s="1"/>
       <c r="BD327" s="1"/>
-      <c r="BE327" s="1" t="str">
+      <c r="BE327" s="1"/>
+      <c r="BF327" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33455,7 +33935,8 @@
       <c r="BB328" s="1"/>
       <c r="BC328" s="1"/>
       <c r="BD328" s="1"/>
-      <c r="BE328" s="1" t="str">
+      <c r="BE328" s="1"/>
+      <c r="BF328" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33520,7 +34001,8 @@
       <c r="BB329" s="1"/>
       <c r="BC329" s="1"/>
       <c r="BD329" s="1"/>
-      <c r="BE329" s="1" t="str">
+      <c r="BE329" s="1"/>
+      <c r="BF329" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33585,7 +34067,8 @@
       <c r="BB330" s="1"/>
       <c r="BC330" s="1"/>
       <c r="BD330" s="1"/>
-      <c r="BE330" s="1" t="str">
+      <c r="BE330" s="1"/>
+      <c r="BF330" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33650,7 +34133,8 @@
       <c r="BB331" s="1"/>
       <c r="BC331" s="1"/>
       <c r="BD331" s="1"/>
-      <c r="BE331" s="1" t="str">
+      <c r="BE331" s="1"/>
+      <c r="BF331" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33715,7 +34199,8 @@
       <c r="BB332" s="1"/>
       <c r="BC332" s="1"/>
       <c r="BD332" s="1"/>
-      <c r="BE332" s="1" t="str">
+      <c r="BE332" s="1"/>
+      <c r="BF332" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33780,7 +34265,8 @@
       <c r="BB333" s="1"/>
       <c r="BC333" s="1"/>
       <c r="BD333" s="1"/>
-      <c r="BE333" s="1" t="str">
+      <c r="BE333" s="1"/>
+      <c r="BF333" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33845,7 +34331,8 @@
       <c r="BB334" s="1"/>
       <c r="BC334" s="1"/>
       <c r="BD334" s="1"/>
-      <c r="BE334" s="1" t="str">
+      <c r="BE334" s="1"/>
+      <c r="BF334" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33910,7 +34397,8 @@
       <c r="BB335" s="1"/>
       <c r="BC335" s="1"/>
       <c r="BD335" s="1"/>
-      <c r="BE335" s="1" t="str">
+      <c r="BE335" s="1"/>
+      <c r="BF335" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33975,7 +34463,8 @@
       <c r="BB336" s="1"/>
       <c r="BC336" s="1"/>
       <c r="BD336" s="1"/>
-      <c r="BE336" s="1" t="str">
+      <c r="BE336" s="1"/>
+      <c r="BF336" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34040,7 +34529,8 @@
       <c r="BB337" s="1"/>
       <c r="BC337" s="1"/>
       <c r="BD337" s="1"/>
-      <c r="BE337" s="1" t="str">
+      <c r="BE337" s="1"/>
+      <c r="BF337" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34105,7 +34595,8 @@
       <c r="BB338" s="1"/>
       <c r="BC338" s="1"/>
       <c r="BD338" s="1"/>
-      <c r="BE338" s="1" t="str">
+      <c r="BE338" s="1"/>
+      <c r="BF338" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34170,7 +34661,8 @@
       <c r="BB339" s="1"/>
       <c r="BC339" s="1"/>
       <c r="BD339" s="1"/>
-      <c r="BE339" s="1" t="str">
+      <c r="BE339" s="1"/>
+      <c r="BF339" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34235,7 +34727,8 @@
       <c r="BB340" s="1"/>
       <c r="BC340" s="1"/>
       <c r="BD340" s="1"/>
-      <c r="BE340" s="1" t="str">
+      <c r="BE340" s="1"/>
+      <c r="BF340" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34300,7 +34793,8 @@
       <c r="BB341" s="1"/>
       <c r="BC341" s="1"/>
       <c r="BD341" s="1"/>
-      <c r="BE341" s="1" t="str">
+      <c r="BE341" s="1"/>
+      <c r="BF341" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34365,7 +34859,8 @@
       <c r="BB342" s="1"/>
       <c r="BC342" s="1"/>
       <c r="BD342" s="1"/>
-      <c r="BE342" s="1" t="str">
+      <c r="BE342" s="1"/>
+      <c r="BF342" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34430,7 +34925,8 @@
       <c r="BB343" s="1"/>
       <c r="BC343" s="1"/>
       <c r="BD343" s="1"/>
-      <c r="BE343" s="1" t="str">
+      <c r="BE343" s="1"/>
+      <c r="BF343" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34495,7 +34991,8 @@
       <c r="BB344" s="1"/>
       <c r="BC344" s="1"/>
       <c r="BD344" s="1"/>
-      <c r="BE344" s="1" t="str">
+      <c r="BE344" s="1"/>
+      <c r="BF344" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34560,7 +35057,8 @@
       <c r="BB345" s="1"/>
       <c r="BC345" s="1"/>
       <c r="BD345" s="1"/>
-      <c r="BE345" s="1" t="str">
+      <c r="BE345" s="1"/>
+      <c r="BF345" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34625,7 +35123,8 @@
       <c r="BB346" s="1"/>
       <c r="BC346" s="1"/>
       <c r="BD346" s="1"/>
-      <c r="BE346" s="1" t="str">
+      <c r="BE346" s="1"/>
+      <c r="BF346" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34690,7 +35189,8 @@
       <c r="BB347" s="1"/>
       <c r="BC347" s="1"/>
       <c r="BD347" s="1"/>
-      <c r="BE347" s="1" t="str">
+      <c r="BE347" s="1"/>
+      <c r="BF347" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34755,7 +35255,8 @@
       <c r="BB348" s="1"/>
       <c r="BC348" s="1"/>
       <c r="BD348" s="1"/>
-      <c r="BE348" s="1" t="str">
+      <c r="BE348" s="1"/>
+      <c r="BF348" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34820,7 +35321,8 @@
       <c r="BB349" s="1"/>
       <c r="BC349" s="1"/>
       <c r="BD349" s="1"/>
-      <c r="BE349" s="1" t="str">
+      <c r="BE349" s="1"/>
+      <c r="BF349" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34885,7 +35387,8 @@
       <c r="BB350" s="1"/>
       <c r="BC350" s="1"/>
       <c r="BD350" s="1"/>
-      <c r="BE350" s="1" t="str">
+      <c r="BE350" s="1"/>
+      <c r="BF350" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34950,7 +35453,8 @@
       <c r="BB351" s="1"/>
       <c r="BC351" s="1"/>
       <c r="BD351" s="1"/>
-      <c r="BE351" s="1" t="str">
+      <c r="BE351" s="1"/>
+      <c r="BF351" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35015,7 +35519,8 @@
       <c r="BB352" s="1"/>
       <c r="BC352" s="1"/>
       <c r="BD352" s="1"/>
-      <c r="BE352" s="1" t="str">
+      <c r="BE352" s="1"/>
+      <c r="BF352" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35080,7 +35585,8 @@
       <c r="BB353" s="1"/>
       <c r="BC353" s="1"/>
       <c r="BD353" s="1"/>
-      <c r="BE353" s="1" t="str">
+      <c r="BE353" s="1"/>
+      <c r="BF353" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35145,7 +35651,8 @@
       <c r="BB354" s="1"/>
       <c r="BC354" s="1"/>
       <c r="BD354" s="1"/>
-      <c r="BE354" s="1" t="str">
+      <c r="BE354" s="1"/>
+      <c r="BF354" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35210,7 +35717,8 @@
       <c r="BB355" s="1"/>
       <c r="BC355" s="1"/>
       <c r="BD355" s="1"/>
-      <c r="BE355" s="1" t="str">
+      <c r="BE355" s="1"/>
+      <c r="BF355" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35275,7 +35783,8 @@
       <c r="BB356" s="1"/>
       <c r="BC356" s="1"/>
       <c r="BD356" s="1"/>
-      <c r="BE356" s="1" t="str">
+      <c r="BE356" s="1"/>
+      <c r="BF356" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35340,7 +35849,8 @@
       <c r="BB357" s="1"/>
       <c r="BC357" s="1"/>
       <c r="BD357" s="1"/>
-      <c r="BE357" s="1" t="str">
+      <c r="BE357" s="1"/>
+      <c r="BF357" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35405,7 +35915,8 @@
       <c r="BB358" s="1"/>
       <c r="BC358" s="1"/>
       <c r="BD358" s="1"/>
-      <c r="BE358" s="1" t="str">
+      <c r="BE358" s="1"/>
+      <c r="BF358" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35470,7 +35981,8 @@
       <c r="BB359" s="1"/>
       <c r="BC359" s="1"/>
       <c r="BD359" s="1"/>
-      <c r="BE359" s="1" t="str">
+      <c r="BE359" s="1"/>
+      <c r="BF359" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35535,7 +36047,8 @@
       <c r="BB360" s="1"/>
       <c r="BC360" s="1"/>
       <c r="BD360" s="1"/>
-      <c r="BE360" s="1" t="str">
+      <c r="BE360" s="1"/>
+      <c r="BF360" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35600,7 +36113,8 @@
       <c r="BB361" s="1"/>
       <c r="BC361" s="1"/>
       <c r="BD361" s="1"/>
-      <c r="BE361" s="1" t="str">
+      <c r="BE361" s="1"/>
+      <c r="BF361" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35665,7 +36179,8 @@
       <c r="BB362" s="1"/>
       <c r="BC362" s="1"/>
       <c r="BD362" s="1"/>
-      <c r="BE362" s="1" t="str">
+      <c r="BE362" s="1"/>
+      <c r="BF362" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35730,7 +36245,8 @@
       <c r="BB363" s="1"/>
       <c r="BC363" s="1"/>
       <c r="BD363" s="1"/>
-      <c r="BE363" s="1" t="str">
+      <c r="BE363" s="1"/>
+      <c r="BF363" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35795,7 +36311,8 @@
       <c r="BB364" s="1"/>
       <c r="BC364" s="1"/>
       <c r="BD364" s="1"/>
-      <c r="BE364" s="1" t="str">
+      <c r="BE364" s="1"/>
+      <c r="BF364" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35860,7 +36377,8 @@
       <c r="BB365" s="1"/>
       <c r="BC365" s="1"/>
       <c r="BD365" s="1"/>
-      <c r="BE365" s="1" t="str">
+      <c r="BE365" s="1"/>
+      <c r="BF365" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35925,7 +36443,8 @@
       <c r="BB366" s="1"/>
       <c r="BC366" s="1"/>
       <c r="BD366" s="1"/>
-      <c r="BE366" s="1" t="str">
+      <c r="BE366" s="1"/>
+      <c r="BF366" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35990,7 +36509,8 @@
       <c r="BB367" s="1"/>
       <c r="BC367" s="1"/>
       <c r="BD367" s="1"/>
-      <c r="BE367" s="1" t="str">
+      <c r="BE367" s="1"/>
+      <c r="BF367" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36055,7 +36575,8 @@
       <c r="BB368" s="1"/>
       <c r="BC368" s="1"/>
       <c r="BD368" s="1"/>
-      <c r="BE368" s="1" t="str">
+      <c r="BE368" s="1"/>
+      <c r="BF368" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36120,7 +36641,8 @@
       <c r="BB369" s="1"/>
       <c r="BC369" s="1"/>
       <c r="BD369" s="1"/>
-      <c r="BE369" s="1" t="str">
+      <c r="BE369" s="1"/>
+      <c r="BF369" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36185,7 +36707,8 @@
       <c r="BB370" s="1"/>
       <c r="BC370" s="1"/>
       <c r="BD370" s="1"/>
-      <c r="BE370" s="1" t="str">
+      <c r="BE370" s="1"/>
+      <c r="BF370" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36250,7 +36773,8 @@
       <c r="BB371" s="1"/>
       <c r="BC371" s="1"/>
       <c r="BD371" s="1"/>
-      <c r="BE371" s="1" t="str">
+      <c r="BE371" s="1"/>
+      <c r="BF371" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36315,7 +36839,8 @@
       <c r="BB372" s="1"/>
       <c r="BC372" s="1"/>
       <c r="BD372" s="1"/>
-      <c r="BE372" s="1" t="str">
+      <c r="BE372" s="1"/>
+      <c r="BF372" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36380,7 +36905,8 @@
       <c r="BB373" s="1"/>
       <c r="BC373" s="1"/>
       <c r="BD373" s="1"/>
-      <c r="BE373" s="1" t="str">
+      <c r="BE373" s="1"/>
+      <c r="BF373" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36445,7 +36971,8 @@
       <c r="BB374" s="1"/>
       <c r="BC374" s="1"/>
       <c r="BD374" s="1"/>
-      <c r="BE374" s="1" t="str">
+      <c r="BE374" s="1"/>
+      <c r="BF374" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36510,7 +37037,8 @@
       <c r="BB375" s="1"/>
       <c r="BC375" s="1"/>
       <c r="BD375" s="1"/>
-      <c r="BE375" s="1" t="str">
+      <c r="BE375" s="1"/>
+      <c r="BF375" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36575,7 +37103,8 @@
       <c r="BB376" s="1"/>
       <c r="BC376" s="1"/>
       <c r="BD376" s="1"/>
-      <c r="BE376" s="1" t="str">
+      <c r="BE376" s="1"/>
+      <c r="BF376" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36640,7 +37169,8 @@
       <c r="BB377" s="1"/>
       <c r="BC377" s="1"/>
       <c r="BD377" s="1"/>
-      <c r="BE377" s="1" t="str">
+      <c r="BE377" s="1"/>
+      <c r="BF377" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36705,7 +37235,8 @@
       <c r="BB378" s="1"/>
       <c r="BC378" s="1"/>
       <c r="BD378" s="1"/>
-      <c r="BE378" s="1" t="str">
+      <c r="BE378" s="1"/>
+      <c r="BF378" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36770,7 +37301,8 @@
       <c r="BB379" s="1"/>
       <c r="BC379" s="1"/>
       <c r="BD379" s="1"/>
-      <c r="BE379" s="1" t="str">
+      <c r="BE379" s="1"/>
+      <c r="BF379" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36835,7 +37367,8 @@
       <c r="BB380" s="1"/>
       <c r="BC380" s="1"/>
       <c r="BD380" s="1"/>
-      <c r="BE380" s="1" t="str">
+      <c r="BE380" s="1"/>
+      <c r="BF380" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36900,7 +37433,8 @@
       <c r="BB381" s="1"/>
       <c r="BC381" s="1"/>
       <c r="BD381" s="1"/>
-      <c r="BE381" s="1" t="str">
+      <c r="BE381" s="1"/>
+      <c r="BF381" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36965,7 +37499,8 @@
       <c r="BB382" s="1"/>
       <c r="BC382" s="1"/>
       <c r="BD382" s="1"/>
-      <c r="BE382" s="1" t="str">
+      <c r="BE382" s="1"/>
+      <c r="BF382" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37030,7 +37565,8 @@
       <c r="BB383" s="1"/>
       <c r="BC383" s="1"/>
       <c r="BD383" s="1"/>
-      <c r="BE383" s="1" t="str">
+      <c r="BE383" s="1"/>
+      <c r="BF383" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37095,7 +37631,8 @@
       <c r="BB384" s="1"/>
       <c r="BC384" s="1"/>
       <c r="BD384" s="1"/>
-      <c r="BE384" s="1" t="str">
+      <c r="BE384" s="1"/>
+      <c r="BF384" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37160,7 +37697,8 @@
       <c r="BB385" s="1"/>
       <c r="BC385" s="1"/>
       <c r="BD385" s="1"/>
-      <c r="BE385" s="1" t="str">
+      <c r="BE385" s="1"/>
+      <c r="BF385" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37225,7 +37763,8 @@
       <c r="BB386" s="1"/>
       <c r="BC386" s="1"/>
       <c r="BD386" s="1"/>
-      <c r="BE386" s="1" t="str">
+      <c r="BE386" s="1"/>
+      <c r="BF386" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37290,7 +37829,8 @@
       <c r="BB387" s="1"/>
       <c r="BC387" s="1"/>
       <c r="BD387" s="1"/>
-      <c r="BE387" s="1" t="str">
+      <c r="BE387" s="1"/>
+      <c r="BF387" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37355,7 +37895,8 @@
       <c r="BB388" s="1"/>
       <c r="BC388" s="1"/>
       <c r="BD388" s="1"/>
-      <c r="BE388" s="1" t="str">
+      <c r="BE388" s="1"/>
+      <c r="BF388" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37420,7 +37961,8 @@
       <c r="BB389" s="1"/>
       <c r="BC389" s="1"/>
       <c r="BD389" s="1"/>
-      <c r="BE389" s="1" t="str">
+      <c r="BE389" s="1"/>
+      <c r="BF389" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37485,7 +38027,8 @@
       <c r="BB390" s="1"/>
       <c r="BC390" s="1"/>
       <c r="BD390" s="1"/>
-      <c r="BE390" s="1" t="str">
+      <c r="BE390" s="1"/>
+      <c r="BF390" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37550,7 +38093,8 @@
       <c r="BB391" s="1"/>
       <c r="BC391" s="1"/>
       <c r="BD391" s="1"/>
-      <c r="BE391" s="1" t="str">
+      <c r="BE391" s="1"/>
+      <c r="BF391" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37615,7 +38159,8 @@
       <c r="BB392" s="1"/>
       <c r="BC392" s="1"/>
       <c r="BD392" s="1"/>
-      <c r="BE392" s="1" t="str">
+      <c r="BE392" s="1"/>
+      <c r="BF392" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37680,7 +38225,8 @@
       <c r="BB393" s="1"/>
       <c r="BC393" s="1"/>
       <c r="BD393" s="1"/>
-      <c r="BE393" s="1" t="str">
+      <c r="BE393" s="1"/>
+      <c r="BF393" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37745,7 +38291,8 @@
       <c r="BB394" s="1"/>
       <c r="BC394" s="1"/>
       <c r="BD394" s="1"/>
-      <c r="BE394" s="1" t="str">
+      <c r="BE394" s="1"/>
+      <c r="BF394" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37810,7 +38357,8 @@
       <c r="BB395" s="1"/>
       <c r="BC395" s="1"/>
       <c r="BD395" s="1"/>
-      <c r="BE395" s="1" t="str">
+      <c r="BE395" s="1"/>
+      <c r="BF395" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37875,7 +38423,8 @@
       <c r="BB396" s="1"/>
       <c r="BC396" s="1"/>
       <c r="BD396" s="1"/>
-      <c r="BE396" s="1" t="str">
+      <c r="BE396" s="1"/>
+      <c r="BF396" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37940,7 +38489,8 @@
       <c r="BB397" s="1"/>
       <c r="BC397" s="1"/>
       <c r="BD397" s="1"/>
-      <c r="BE397" s="1" t="str">
+      <c r="BE397" s="1"/>
+      <c r="BF397" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38005,7 +38555,8 @@
       <c r="BB398" s="1"/>
       <c r="BC398" s="1"/>
       <c r="BD398" s="1"/>
-      <c r="BE398" s="1" t="str">
+      <c r="BE398" s="1"/>
+      <c r="BF398" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38070,7 +38621,8 @@
       <c r="BB399" s="1"/>
       <c r="BC399" s="1"/>
       <c r="BD399" s="1"/>
-      <c r="BE399" s="1" t="str">
+      <c r="BE399" s="1"/>
+      <c r="BF399" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38135,7 +38687,8 @@
       <c r="BB400" s="1"/>
       <c r="BC400" s="1"/>
       <c r="BD400" s="1"/>
-      <c r="BE400" s="1" t="str">
+      <c r="BE400" s="1"/>
+      <c r="BF400" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38200,7 +38753,8 @@
       <c r="BB401" s="1"/>
       <c r="BC401" s="1"/>
       <c r="BD401" s="1"/>
-      <c r="BE401" s="1" t="str">
+      <c r="BE401" s="1"/>
+      <c r="BF401" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38265,7 +38819,8 @@
       <c r="BB402" s="1"/>
       <c r="BC402" s="1"/>
       <c r="BD402" s="1"/>
-      <c r="BE402" s="1" t="str">
+      <c r="BE402" s="1"/>
+      <c r="BF402" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38330,7 +38885,8 @@
       <c r="BB403" s="1"/>
       <c r="BC403" s="1"/>
       <c r="BD403" s="1"/>
-      <c r="BE403" s="1" t="str">
+      <c r="BE403" s="1"/>
+      <c r="BF403" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38395,7 +38951,8 @@
       <c r="BB404" s="1"/>
       <c r="BC404" s="1"/>
       <c r="BD404" s="1"/>
-      <c r="BE404" s="1" t="str">
+      <c r="BE404" s="1"/>
+      <c r="BF404" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38460,7 +39017,8 @@
       <c r="BB405" s="1"/>
       <c r="BC405" s="1"/>
       <c r="BD405" s="1"/>
-      <c r="BE405" s="1" t="str">
+      <c r="BE405" s="1"/>
+      <c r="BF405" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38525,7 +39083,8 @@
       <c r="BB406" s="1"/>
       <c r="BC406" s="1"/>
       <c r="BD406" s="1"/>
-      <c r="BE406" s="1" t="str">
+      <c r="BE406" s="1"/>
+      <c r="BF406" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38590,7 +39149,8 @@
       <c r="BB407" s="1"/>
       <c r="BC407" s="1"/>
       <c r="BD407" s="1"/>
-      <c r="BE407" s="1" t="str">
+      <c r="BE407" s="1"/>
+      <c r="BF407" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38655,7 +39215,8 @@
       <c r="BB408" s="1"/>
       <c r="BC408" s="1"/>
       <c r="BD408" s="1"/>
-      <c r="BE408" s="1" t="str">
+      <c r="BE408" s="1"/>
+      <c r="BF408" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38720,7 +39281,8 @@
       <c r="BB409" s="1"/>
       <c r="BC409" s="1"/>
       <c r="BD409" s="1"/>
-      <c r="BE409" s="1" t="str">
+      <c r="BE409" s="1"/>
+      <c r="BF409" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38785,7 +39347,8 @@
       <c r="BB410" s="1"/>
       <c r="BC410" s="1"/>
       <c r="BD410" s="1"/>
-      <c r="BE410" s="1" t="str">
+      <c r="BE410" s="1"/>
+      <c r="BF410" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38850,7 +39413,8 @@
       <c r="BB411" s="1"/>
       <c r="BC411" s="1"/>
       <c r="BD411" s="1"/>
-      <c r="BE411" s="1" t="str">
+      <c r="BE411" s="1"/>
+      <c r="BF411" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38915,7 +39479,8 @@
       <c r="BB412" s="1"/>
       <c r="BC412" s="1"/>
       <c r="BD412" s="1"/>
-      <c r="BE412" s="1" t="str">
+      <c r="BE412" s="1"/>
+      <c r="BF412" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38980,7 +39545,8 @@
       <c r="BB413" s="1"/>
       <c r="BC413" s="1"/>
       <c r="BD413" s="1"/>
-      <c r="BE413" s="1" t="str">
+      <c r="BE413" s="1"/>
+      <c r="BF413" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39045,7 +39611,8 @@
       <c r="BB414" s="1"/>
       <c r="BC414" s="1"/>
       <c r="BD414" s="1"/>
-      <c r="BE414" s="1" t="str">
+      <c r="BE414" s="1"/>
+      <c r="BF414" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39110,7 +39677,8 @@
       <c r="BB415" s="1"/>
       <c r="BC415" s="1"/>
       <c r="BD415" s="1"/>
-      <c r="BE415" s="1" t="str">
+      <c r="BE415" s="1"/>
+      <c r="BF415" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39175,7 +39743,8 @@
       <c r="BB416" s="1"/>
       <c r="BC416" s="1"/>
       <c r="BD416" s="1"/>
-      <c r="BE416" s="1" t="str">
+      <c r="BE416" s="1"/>
+      <c r="BF416" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39240,7 +39809,8 @@
       <c r="BB417" s="1"/>
       <c r="BC417" s="1"/>
       <c r="BD417" s="1"/>
-      <c r="BE417" s="1" t="str">
+      <c r="BE417" s="1"/>
+      <c r="BF417" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39305,7 +39875,8 @@
       <c r="BB418" s="1"/>
       <c r="BC418" s="1"/>
       <c r="BD418" s="1"/>
-      <c r="BE418" s="1" t="str">
+      <c r="BE418" s="1"/>
+      <c r="BF418" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39370,7 +39941,8 @@
       <c r="BB419" s="1"/>
       <c r="BC419" s="1"/>
       <c r="BD419" s="1"/>
-      <c r="BE419" s="1" t="str">
+      <c r="BE419" s="1"/>
+      <c r="BF419" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39435,7 +40007,8 @@
       <c r="BB420" s="1"/>
       <c r="BC420" s="1"/>
       <c r="BD420" s="1"/>
-      <c r="BE420" s="1" t="str">
+      <c r="BE420" s="1"/>
+      <c r="BF420" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39500,7 +40073,8 @@
       <c r="BB421" s="1"/>
       <c r="BC421" s="1"/>
       <c r="BD421" s="1"/>
-      <c r="BE421" s="1" t="str">
+      <c r="BE421" s="1"/>
+      <c r="BF421" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39565,7 +40139,8 @@
       <c r="BB422" s="1"/>
       <c r="BC422" s="1"/>
       <c r="BD422" s="1"/>
-      <c r="BE422" s="1" t="str">
+      <c r="BE422" s="1"/>
+      <c r="BF422" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39630,7 +40205,8 @@
       <c r="BB423" s="1"/>
       <c r="BC423" s="1"/>
       <c r="BD423" s="1"/>
-      <c r="BE423" s="1" t="str">
+      <c r="BE423" s="1"/>
+      <c r="BF423" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39695,7 +40271,8 @@
       <c r="BB424" s="1"/>
       <c r="BC424" s="1"/>
       <c r="BD424" s="1"/>
-      <c r="BE424" s="1" t="str">
+      <c r="BE424" s="1"/>
+      <c r="BF424" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39760,7 +40337,8 @@
       <c r="BB425" s="1"/>
       <c r="BC425" s="1"/>
       <c r="BD425" s="1"/>
-      <c r="BE425" s="1" t="str">
+      <c r="BE425" s="1"/>
+      <c r="BF425" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39825,7 +40403,8 @@
       <c r="BB426" s="1"/>
       <c r="BC426" s="1"/>
       <c r="BD426" s="1"/>
-      <c r="BE426" s="1" t="str">
+      <c r="BE426" s="1"/>
+      <c r="BF426" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39890,7 +40469,8 @@
       <c r="BB427" s="1"/>
       <c r="BC427" s="1"/>
       <c r="BD427" s="1"/>
-      <c r="BE427" s="1" t="str">
+      <c r="BE427" s="1"/>
+      <c r="BF427" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39955,7 +40535,8 @@
       <c r="BB428" s="1"/>
       <c r="BC428" s="1"/>
       <c r="BD428" s="1"/>
-      <c r="BE428" s="1" t="str">
+      <c r="BE428" s="1"/>
+      <c r="BF428" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40020,7 +40601,8 @@
       <c r="BB429" s="1"/>
       <c r="BC429" s="1"/>
       <c r="BD429" s="1"/>
-      <c r="BE429" s="1" t="str">
+      <c r="BE429" s="1"/>
+      <c r="BF429" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40085,7 +40667,8 @@
       <c r="BB430" s="1"/>
       <c r="BC430" s="1"/>
       <c r="BD430" s="1"/>
-      <c r="BE430" s="1" t="str">
+      <c r="BE430" s="1"/>
+      <c r="BF430" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40150,7 +40733,8 @@
       <c r="BB431" s="1"/>
       <c r="BC431" s="1"/>
       <c r="BD431" s="1"/>
-      <c r="BE431" s="1" t="str">
+      <c r="BE431" s="1"/>
+      <c r="BF431" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40215,7 +40799,8 @@
       <c r="BB432" s="1"/>
       <c r="BC432" s="1"/>
       <c r="BD432" s="1"/>
-      <c r="BE432" s="1" t="str">
+      <c r="BE432" s="1"/>
+      <c r="BF432" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40280,7 +40865,8 @@
       <c r="BB433" s="1"/>
       <c r="BC433" s="1"/>
       <c r="BD433" s="1"/>
-      <c r="BE433" s="1" t="str">
+      <c r="BE433" s="1"/>
+      <c r="BF433" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40345,7 +40931,8 @@
       <c r="BB434" s="1"/>
       <c r="BC434" s="1"/>
       <c r="BD434" s="1"/>
-      <c r="BE434" s="1" t="str">
+      <c r="BE434" s="1"/>
+      <c r="BF434" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40410,7 +40997,8 @@
       <c r="BB435" s="1"/>
       <c r="BC435" s="1"/>
       <c r="BD435" s="1"/>
-      <c r="BE435" s="1" t="str">
+      <c r="BE435" s="1"/>
+      <c r="BF435" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40475,7 +41063,8 @@
       <c r="BB436" s="1"/>
       <c r="BC436" s="1"/>
       <c r="BD436" s="1"/>
-      <c r="BE436" s="1" t="str">
+      <c r="BE436" s="1"/>
+      <c r="BF436" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40540,7 +41129,8 @@
       <c r="BB437" s="1"/>
       <c r="BC437" s="1"/>
       <c r="BD437" s="1"/>
-      <c r="BE437" s="1" t="str">
+      <c r="BE437" s="1"/>
+      <c r="BF437" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40605,7 +41195,8 @@
       <c r="BB438" s="1"/>
       <c r="BC438" s="1"/>
       <c r="BD438" s="1"/>
-      <c r="BE438" s="1" t="str">
+      <c r="BE438" s="1"/>
+      <c r="BF438" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40670,7 +41261,8 @@
       <c r="BB439" s="1"/>
       <c r="BC439" s="1"/>
       <c r="BD439" s="1"/>
-      <c r="BE439" s="1" t="str">
+      <c r="BE439" s="1"/>
+      <c r="BF439" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40735,7 +41327,8 @@
       <c r="BB440" s="1"/>
       <c r="BC440" s="1"/>
       <c r="BD440" s="1"/>
-      <c r="BE440" s="1" t="str">
+      <c r="BE440" s="1"/>
+      <c r="BF440" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40800,7 +41393,8 @@
       <c r="BB441" s="1"/>
       <c r="BC441" s="1"/>
       <c r="BD441" s="1"/>
-      <c r="BE441" s="1" t="str">
+      <c r="BE441" s="1"/>
+      <c r="BF441" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40865,7 +41459,8 @@
       <c r="BB442" s="1"/>
       <c r="BC442" s="1"/>
       <c r="BD442" s="1"/>
-      <c r="BE442" s="1" t="str">
+      <c r="BE442" s="1"/>
+      <c r="BF442" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40930,7 +41525,8 @@
       <c r="BB443" s="1"/>
       <c r="BC443" s="1"/>
       <c r="BD443" s="1"/>
-      <c r="BE443" s="1" t="str">
+      <c r="BE443" s="1"/>
+      <c r="BF443" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40995,7 +41591,8 @@
       <c r="BB444" s="1"/>
       <c r="BC444" s="1"/>
       <c r="BD444" s="1"/>
-      <c r="BE444" s="1" t="str">
+      <c r="BE444" s="1"/>
+      <c r="BF444" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41060,7 +41657,8 @@
       <c r="BB445" s="1"/>
       <c r="BC445" s="1"/>
       <c r="BD445" s="1"/>
-      <c r="BE445" s="1" t="str">
+      <c r="BE445" s="1"/>
+      <c r="BF445" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41125,7 +41723,8 @@
       <c r="BB446" s="1"/>
       <c r="BC446" s="1"/>
       <c r="BD446" s="1"/>
-      <c r="BE446" s="1" t="str">
+      <c r="BE446" s="1"/>
+      <c r="BF446" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41190,7 +41789,8 @@
       <c r="BB447" s="1"/>
       <c r="BC447" s="1"/>
       <c r="BD447" s="1"/>
-      <c r="BE447" s="1" t="str">
+      <c r="BE447" s="1"/>
+      <c r="BF447" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41255,7 +41855,8 @@
       <c r="BB448" s="1"/>
       <c r="BC448" s="1"/>
       <c r="BD448" s="1"/>
-      <c r="BE448" s="1" t="str">
+      <c r="BE448" s="1"/>
+      <c r="BF448" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41320,7 +41921,8 @@
       <c r="BB449" s="1"/>
       <c r="BC449" s="1"/>
       <c r="BD449" s="1"/>
-      <c r="BE449" s="1" t="str">
+      <c r="BE449" s="1"/>
+      <c r="BF449" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41385,7 +41987,8 @@
       <c r="BB450" s="1"/>
       <c r="BC450" s="1"/>
       <c r="BD450" s="1"/>
-      <c r="BE450" s="1" t="str">
+      <c r="BE450" s="1"/>
+      <c r="BF450" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41450,7 +42053,8 @@
       <c r="BB451" s="1"/>
       <c r="BC451" s="1"/>
       <c r="BD451" s="1"/>
-      <c r="BE451" s="1" t="str">
+      <c r="BE451" s="1"/>
+      <c r="BF451" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41515,7 +42119,8 @@
       <c r="BB452" s="1"/>
       <c r="BC452" s="1"/>
       <c r="BD452" s="1"/>
-      <c r="BE452" s="1" t="str">
+      <c r="BE452" s="1"/>
+      <c r="BF452" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41580,7 +42185,8 @@
       <c r="BB453" s="1"/>
       <c r="BC453" s="1"/>
       <c r="BD453" s="1"/>
-      <c r="BE453" s="1" t="str">
+      <c r="BE453" s="1"/>
+      <c r="BF453" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41645,7 +42251,8 @@
       <c r="BB454" s="1"/>
       <c r="BC454" s="1"/>
       <c r="BD454" s="1"/>
-      <c r="BE454" s="1" t="str">
+      <c r="BE454" s="1"/>
+      <c r="BF454" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41710,7 +42317,8 @@
       <c r="BB455" s="1"/>
       <c r="BC455" s="1"/>
       <c r="BD455" s="1"/>
-      <c r="BE455" s="1" t="str">
+      <c r="BE455" s="1"/>
+      <c r="BF455" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41775,7 +42383,8 @@
       <c r="BB456" s="1"/>
       <c r="BC456" s="1"/>
       <c r="BD456" s="1"/>
-      <c r="BE456" s="1" t="str">
+      <c r="BE456" s="1"/>
+      <c r="BF456" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41840,7 +42449,8 @@
       <c r="BB457" s="1"/>
       <c r="BC457" s="1"/>
       <c r="BD457" s="1"/>
-      <c r="BE457" s="1" t="str">
+      <c r="BE457" s="1"/>
+      <c r="BF457" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41905,7 +42515,8 @@
       <c r="BB458" s="1"/>
       <c r="BC458" s="1"/>
       <c r="BD458" s="1"/>
-      <c r="BE458" s="1" t="str">
+      <c r="BE458" s="1"/>
+      <c r="BF458" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41970,7 +42581,8 @@
       <c r="BB459" s="1"/>
       <c r="BC459" s="1"/>
       <c r="BD459" s="1"/>
-      <c r="BE459" s="1" t="str">
+      <c r="BE459" s="1"/>
+      <c r="BF459" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42035,7 +42647,8 @@
       <c r="BB460" s="1"/>
       <c r="BC460" s="1"/>
       <c r="BD460" s="1"/>
-      <c r="BE460" s="1" t="str">
+      <c r="BE460" s="1"/>
+      <c r="BF460" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42100,7 +42713,8 @@
       <c r="BB461" s="1"/>
       <c r="BC461" s="1"/>
       <c r="BD461" s="1"/>
-      <c r="BE461" s="1" t="str">
+      <c r="BE461" s="1"/>
+      <c r="BF461" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42165,7 +42779,8 @@
       <c r="BB462" s="1"/>
       <c r="BC462" s="1"/>
       <c r="BD462" s="1"/>
-      <c r="BE462" s="1" t="str">
+      <c r="BE462" s="1"/>
+      <c r="BF462" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42230,7 +42845,8 @@
       <c r="BB463" s="1"/>
       <c r="BC463" s="1"/>
       <c r="BD463" s="1"/>
-      <c r="BE463" s="1" t="str">
+      <c r="BE463" s="1"/>
+      <c r="BF463" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42295,7 +42911,8 @@
       <c r="BB464" s="1"/>
       <c r="BC464" s="1"/>
       <c r="BD464" s="1"/>
-      <c r="BE464" s="1" t="str">
+      <c r="BE464" s="1"/>
+      <c r="BF464" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42360,7 +42977,8 @@
       <c r="BB465" s="1"/>
       <c r="BC465" s="1"/>
       <c r="BD465" s="1"/>
-      <c r="BE465" s="1" t="str">
+      <c r="BE465" s="1"/>
+      <c r="BF465" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42425,7 +43043,8 @@
       <c r="BB466" s="1"/>
       <c r="BC466" s="1"/>
       <c r="BD466" s="1"/>
-      <c r="BE466" s="1" t="str">
+      <c r="BE466" s="1"/>
+      <c r="BF466" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42490,7 +43109,8 @@
       <c r="BB467" s="1"/>
       <c r="BC467" s="1"/>
       <c r="BD467" s="1"/>
-      <c r="BE467" s="1" t="str">
+      <c r="BE467" s="1"/>
+      <c r="BF467" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42555,7 +43175,8 @@
       <c r="BB468" s="1"/>
       <c r="BC468" s="1"/>
       <c r="BD468" s="1"/>
-      <c r="BE468" s="1" t="str">
+      <c r="BE468" s="1"/>
+      <c r="BF468" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42620,7 +43241,8 @@
       <c r="BB469" s="1"/>
       <c r="BC469" s="1"/>
       <c r="BD469" s="1"/>
-      <c r="BE469" s="1" t="str">
+      <c r="BE469" s="1"/>
+      <c r="BF469" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42685,7 +43307,8 @@
       <c r="BB470" s="1"/>
       <c r="BC470" s="1"/>
       <c r="BD470" s="1"/>
-      <c r="BE470" s="1" t="str">
+      <c r="BE470" s="1"/>
+      <c r="BF470" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42750,7 +43373,8 @@
       <c r="BB471" s="1"/>
       <c r="BC471" s="1"/>
       <c r="BD471" s="1"/>
-      <c r="BE471" s="1" t="str">
+      <c r="BE471" s="1"/>
+      <c r="BF471" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42815,7 +43439,8 @@
       <c r="BB472" s="1"/>
       <c r="BC472" s="1"/>
       <c r="BD472" s="1"/>
-      <c r="BE472" s="1" t="str">
+      <c r="BE472" s="1"/>
+      <c r="BF472" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42880,7 +43505,8 @@
       <c r="BB473" s="1"/>
       <c r="BC473" s="1"/>
       <c r="BD473" s="1"/>
-      <c r="BE473" s="1" t="str">
+      <c r="BE473" s="1"/>
+      <c r="BF473" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42945,7 +43571,8 @@
       <c r="BB474" s="1"/>
       <c r="BC474" s="1"/>
       <c r="BD474" s="1"/>
-      <c r="BE474" s="1" t="str">
+      <c r="BE474" s="1"/>
+      <c r="BF474" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43010,7 +43637,8 @@
       <c r="BB475" s="1"/>
       <c r="BC475" s="1"/>
       <c r="BD475" s="1"/>
-      <c r="BE475" s="1" t="str">
+      <c r="BE475" s="1"/>
+      <c r="BF475" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43075,7 +43703,8 @@
       <c r="BB476" s="1"/>
       <c r="BC476" s="1"/>
       <c r="BD476" s="1"/>
-      <c r="BE476" s="1" t="str">
+      <c r="BE476" s="1"/>
+      <c r="BF476" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43140,7 +43769,8 @@
       <c r="BB477" s="1"/>
       <c r="BC477" s="1"/>
       <c r="BD477" s="1"/>
-      <c r="BE477" s="1" t="str">
+      <c r="BE477" s="1"/>
+      <c r="BF477" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43205,7 +43835,8 @@
       <c r="BB478" s="1"/>
       <c r="BC478" s="1"/>
       <c r="BD478" s="1"/>
-      <c r="BE478" s="1" t="str">
+      <c r="BE478" s="1"/>
+      <c r="BF478" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43270,7 +43901,8 @@
       <c r="BB479" s="1"/>
       <c r="BC479" s="1"/>
       <c r="BD479" s="1"/>
-      <c r="BE479" s="1" t="str">
+      <c r="BE479" s="1"/>
+      <c r="BF479" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43335,7 +43967,8 @@
       <c r="BB480" s="1"/>
       <c r="BC480" s="1"/>
       <c r="BD480" s="1"/>
-      <c r="BE480" s="1" t="str">
+      <c r="BE480" s="1"/>
+      <c r="BF480" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43400,7 +44033,8 @@
       <c r="BB481" s="1"/>
       <c r="BC481" s="1"/>
       <c r="BD481" s="1"/>
-      <c r="BE481" s="1" t="str">
+      <c r="BE481" s="1"/>
+      <c r="BF481" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43465,7 +44099,8 @@
       <c r="BB482" s="1"/>
       <c r="BC482" s="1"/>
       <c r="BD482" s="1"/>
-      <c r="BE482" s="1" t="str">
+      <c r="BE482" s="1"/>
+      <c r="BF482" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43530,7 +44165,8 @@
       <c r="BB483" s="1"/>
       <c r="BC483" s="1"/>
       <c r="BD483" s="1"/>
-      <c r="BE483" s="1" t="str">
+      <c r="BE483" s="1"/>
+      <c r="BF483" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43595,7 +44231,8 @@
       <c r="BB484" s="1"/>
       <c r="BC484" s="1"/>
       <c r="BD484" s="1"/>
-      <c r="BE484" s="1" t="str">
+      <c r="BE484" s="1"/>
+      <c r="BF484" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43660,7 +44297,8 @@
       <c r="BB485" s="1"/>
       <c r="BC485" s="1"/>
       <c r="BD485" s="1"/>
-      <c r="BE485" s="1" t="str">
+      <c r="BE485" s="1"/>
+      <c r="BF485" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43725,7 +44363,8 @@
       <c r="BB486" s="1"/>
       <c r="BC486" s="1"/>
       <c r="BD486" s="1"/>
-      <c r="BE486" s="1" t="str">
+      <c r="BE486" s="1"/>
+      <c r="BF486" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43790,7 +44429,8 @@
       <c r="BB487" s="1"/>
       <c r="BC487" s="1"/>
       <c r="BD487" s="1"/>
-      <c r="BE487" s="1" t="str">
+      <c r="BE487" s="1"/>
+      <c r="BF487" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43855,7 +44495,8 @@
       <c r="BB488" s="1"/>
       <c r="BC488" s="1"/>
       <c r="BD488" s="1"/>
-      <c r="BE488" s="1" t="str">
+      <c r="BE488" s="1"/>
+      <c r="BF488" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43920,7 +44561,8 @@
       <c r="BB489" s="1"/>
       <c r="BC489" s="1"/>
       <c r="BD489" s="1"/>
-      <c r="BE489" s="1" t="str">
+      <c r="BE489" s="1"/>
+      <c r="BF489" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43985,7 +44627,8 @@
       <c r="BB490" s="1"/>
       <c r="BC490" s="1"/>
       <c r="BD490" s="1"/>
-      <c r="BE490" s="1" t="str">
+      <c r="BE490" s="1"/>
+      <c r="BF490" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44050,7 +44693,8 @@
       <c r="BB491" s="1"/>
       <c r="BC491" s="1"/>
       <c r="BD491" s="1"/>
-      <c r="BE491" s="1" t="str">
+      <c r="BE491" s="1"/>
+      <c r="BF491" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44115,7 +44759,8 @@
       <c r="BB492" s="1"/>
       <c r="BC492" s="1"/>
       <c r="BD492" s="1"/>
-      <c r="BE492" s="1" t="str">
+      <c r="BE492" s="1"/>
+      <c r="BF492" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44180,7 +44825,8 @@
       <c r="BB493" s="1"/>
       <c r="BC493" s="1"/>
       <c r="BD493" s="1"/>
-      <c r="BE493" s="1" t="str">
+      <c r="BE493" s="1"/>
+      <c r="BF493" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44245,7 +44891,8 @@
       <c r="BB494" s="1"/>
       <c r="BC494" s="1"/>
       <c r="BD494" s="1"/>
-      <c r="BE494" s="1" t="str">
+      <c r="BE494" s="1"/>
+      <c r="BF494" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44310,7 +44957,8 @@
       <c r="BB495" s="1"/>
       <c r="BC495" s="1"/>
       <c r="BD495" s="1"/>
-      <c r="BE495" s="1" t="str">
+      <c r="BE495" s="1"/>
+      <c r="BF495" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44375,7 +45023,8 @@
       <c r="BB496" s="1"/>
       <c r="BC496" s="1"/>
       <c r="BD496" s="1"/>
-      <c r="BE496" s="1" t="str">
+      <c r="BE496" s="1"/>
+      <c r="BF496" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44440,7 +45089,8 @@
       <c r="BB497" s="1"/>
       <c r="BC497" s="1"/>
       <c r="BD497" s="1"/>
-      <c r="BE497" s="1" t="str">
+      <c r="BE497" s="1"/>
+      <c r="BF497" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44505,7 +45155,8 @@
       <c r="BB498" s="1"/>
       <c r="BC498" s="1"/>
       <c r="BD498" s="1"/>
-      <c r="BE498" s="1" t="str">
+      <c r="BE498" s="1"/>
+      <c r="BF498" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44570,7 +45221,8 @@
       <c r="BB499" s="1"/>
       <c r="BC499" s="1"/>
       <c r="BD499" s="1"/>
-      <c r="BE499" s="1" t="str">
+      <c r="BE499" s="1"/>
+      <c r="BF499" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44635,7 +45287,8 @@
       <c r="BB500" s="1"/>
       <c r="BC500" s="1"/>
       <c r="BD500" s="1"/>
-      <c r="BE500" s="1" t="str">
+      <c r="BE500" s="1"/>
+      <c r="BF500" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44700,7 +45353,8 @@
       <c r="BB501" s="1"/>
       <c r="BC501" s="1"/>
       <c r="BD501" s="1"/>
-      <c r="BE501" s="1" t="str">
+      <c r="BE501" s="1"/>
+      <c r="BF501" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44765,7 +45419,8 @@
       <c r="BB502" s="1"/>
       <c r="BC502" s="1"/>
       <c r="BD502" s="1"/>
-      <c r="BE502" s="1" t="str">
+      <c r="BE502" s="1"/>
+      <c r="BF502" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44830,7 +45485,8 @@
       <c r="BB503" s="1"/>
       <c r="BC503" s="1"/>
       <c r="BD503" s="1"/>
-      <c r="BE503" s="1" t="str">
+      <c r="BE503" s="1"/>
+      <c r="BF503" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44895,7 +45551,8 @@
       <c r="BB504" s="1"/>
       <c r="BC504" s="1"/>
       <c r="BD504" s="1"/>
-      <c r="BE504" s="1" t="str">
+      <c r="BE504" s="1"/>
+      <c r="BF504" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44960,7 +45617,8 @@
       <c r="BB505" s="1"/>
       <c r="BC505" s="1"/>
       <c r="BD505" s="1"/>
-      <c r="BE505" s="1" t="str">
+      <c r="BE505" s="1"/>
+      <c r="BF505" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45025,7 +45683,8 @@
       <c r="BB506" s="1"/>
       <c r="BC506" s="1"/>
       <c r="BD506" s="1"/>
-      <c r="BE506" s="1" t="str">
+      <c r="BE506" s="1"/>
+      <c r="BF506" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45090,7 +45749,8 @@
       <c r="BB507" s="1"/>
       <c r="BC507" s="1"/>
       <c r="BD507" s="1"/>
-      <c r="BE507" s="1" t="str">
+      <c r="BE507" s="1"/>
+      <c r="BF507" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45155,7 +45815,8 @@
       <c r="BB508" s="1"/>
       <c r="BC508" s="1"/>
       <c r="BD508" s="1"/>
-      <c r="BE508" s="1" t="str">
+      <c r="BE508" s="1"/>
+      <c r="BF508" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45220,7 +45881,8 @@
       <c r="BB509" s="1"/>
       <c r="BC509" s="1"/>
       <c r="BD509" s="1"/>
-      <c r="BE509" s="1" t="str">
+      <c r="BE509" s="1"/>
+      <c r="BF509" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45285,7 +45947,8 @@
       <c r="BB510" s="1"/>
       <c r="BC510" s="1"/>
       <c r="BD510" s="1"/>
-      <c r="BE510" s="1" t="str">
+      <c r="BE510" s="1"/>
+      <c r="BF510" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45350,7 +46013,8 @@
       <c r="BB511" s="1"/>
       <c r="BC511" s="1"/>
       <c r="BD511" s="1"/>
-      <c r="BE511" s="1" t="str">
+      <c r="BE511" s="1"/>
+      <c r="BF511" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45415,7 +46079,8 @@
       <c r="BB512" s="1"/>
       <c r="BC512" s="1"/>
       <c r="BD512" s="1"/>
-      <c r="BE512" s="1" t="str">
+      <c r="BE512" s="1"/>
+      <c r="BF512" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45480,7 +46145,8 @@
       <c r="BB513" s="1"/>
       <c r="BC513" s="1"/>
       <c r="BD513" s="1"/>
-      <c r="BE513" s="1" t="str">
+      <c r="BE513" s="1"/>
+      <c r="BF513" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45545,7 +46211,8 @@
       <c r="BB514" s="1"/>
       <c r="BC514" s="1"/>
       <c r="BD514" s="1"/>
-      <c r="BE514" s="1" t="str">
+      <c r="BE514" s="1"/>
+      <c r="BF514" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45610,7 +46277,8 @@
       <c r="BB515" s="1"/>
       <c r="BC515" s="1"/>
       <c r="BD515" s="1"/>
-      <c r="BE515" s="1" t="str">
+      <c r="BE515" s="1"/>
+      <c r="BF515" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45675,7 +46343,8 @@
       <c r="BB516" s="1"/>
       <c r="BC516" s="1"/>
       <c r="BD516" s="1"/>
-      <c r="BE516" s="1" t="str">
+      <c r="BE516" s="1"/>
+      <c r="BF516" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45740,7 +46409,8 @@
       <c r="BB517" s="1"/>
       <c r="BC517" s="1"/>
       <c r="BD517" s="1"/>
-      <c r="BE517" s="1" t="str">
+      <c r="BE517" s="1"/>
+      <c r="BF517" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45805,7 +46475,8 @@
       <c r="BB518" s="1"/>
       <c r="BC518" s="1"/>
       <c r="BD518" s="1"/>
-      <c r="BE518" s="1" t="str">
+      <c r="BE518" s="1"/>
+      <c r="BF518" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45870,7 +46541,8 @@
       <c r="BB519" s="1"/>
       <c r="BC519" s="1"/>
       <c r="BD519" s="1"/>
-      <c r="BE519" s="1" t="str">
+      <c r="BE519" s="1"/>
+      <c r="BF519" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45935,7 +46607,8 @@
       <c r="BB520" s="1"/>
       <c r="BC520" s="1"/>
       <c r="BD520" s="1"/>
-      <c r="BE520" s="1" t="str">
+      <c r="BE520" s="1"/>
+      <c r="BF520" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46000,7 +46673,8 @@
       <c r="BB521" s="1"/>
       <c r="BC521" s="1"/>
       <c r="BD521" s="1"/>
-      <c r="BE521" s="1" t="str">
+      <c r="BE521" s="1"/>
+      <c r="BF521" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46065,7 +46739,8 @@
       <c r="BB522" s="1"/>
       <c r="BC522" s="1"/>
       <c r="BD522" s="1"/>
-      <c r="BE522" s="1" t="str">
+      <c r="BE522" s="1"/>
+      <c r="BF522" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46130,7 +46805,8 @@
       <c r="BB523" s="1"/>
       <c r="BC523" s="1"/>
       <c r="BD523" s="1"/>
-      <c r="BE523" s="1" t="str">
+      <c r="BE523" s="1"/>
+      <c r="BF523" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46195,7 +46871,8 @@
       <c r="BB524" s="1"/>
       <c r="BC524" s="1"/>
       <c r="BD524" s="1"/>
-      <c r="BE524" s="1" t="str">
+      <c r="BE524" s="1"/>
+      <c r="BF524" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46260,7 +46937,8 @@
       <c r="BB525" s="1"/>
       <c r="BC525" s="1"/>
       <c r="BD525" s="1"/>
-      <c r="BE525" s="1" t="str">
+      <c r="BE525" s="1"/>
+      <c r="BF525" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46325,7 +47003,8 @@
       <c r="BB526" s="1"/>
       <c r="BC526" s="1"/>
       <c r="BD526" s="1"/>
-      <c r="BE526" s="1" t="str">
+      <c r="BE526" s="1"/>
+      <c r="BF526" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46390,7 +47069,8 @@
       <c r="BB527" s="1"/>
       <c r="BC527" s="1"/>
       <c r="BD527" s="1"/>
-      <c r="BE527" s="1" t="str">
+      <c r="BE527" s="1"/>
+      <c r="BF527" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46455,7 +47135,8 @@
       <c r="BB528" s="1"/>
       <c r="BC528" s="1"/>
       <c r="BD528" s="1"/>
-      <c r="BE528" s="1" t="str">
+      <c r="BE528" s="1"/>
+      <c r="BF528" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46520,7 +47201,8 @@
       <c r="BB529" s="1"/>
       <c r="BC529" s="1"/>
       <c r="BD529" s="1"/>
-      <c r="BE529" s="1" t="str">
+      <c r="BE529" s="1"/>
+      <c r="BF529" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46585,7 +47267,8 @@
       <c r="BB530" s="1"/>
       <c r="BC530" s="1"/>
       <c r="BD530" s="1"/>
-      <c r="BE530" s="1" t="str">
+      <c r="BE530" s="1"/>
+      <c r="BF530" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46650,7 +47333,8 @@
       <c r="BB531" s="1"/>
       <c r="BC531" s="1"/>
       <c r="BD531" s="1"/>
-      <c r="BE531" s="1" t="str">
+      <c r="BE531" s="1"/>
+      <c r="BF531" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46715,7 +47399,8 @@
       <c r="BB532" s="1"/>
       <c r="BC532" s="1"/>
       <c r="BD532" s="1"/>
-      <c r="BE532" s="1" t="str">
+      <c r="BE532" s="1"/>
+      <c r="BF532" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46780,7 +47465,8 @@
       <c r="BB533" s="1"/>
       <c r="BC533" s="1"/>
       <c r="BD533" s="1"/>
-      <c r="BE533" s="1" t="str">
+      <c r="BE533" s="1"/>
+      <c r="BF533" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46845,7 +47531,8 @@
       <c r="BB534" s="1"/>
       <c r="BC534" s="1"/>
       <c r="BD534" s="1"/>
-      <c r="BE534" s="1" t="str">
+      <c r="BE534" s="1"/>
+      <c r="BF534" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46910,7 +47597,8 @@
       <c r="BB535" s="1"/>
       <c r="BC535" s="1"/>
       <c r="BD535" s="1"/>
-      <c r="BE535" s="1" t="str">
+      <c r="BE535" s="1"/>
+      <c r="BF535" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46975,7 +47663,8 @@
       <c r="BB536" s="1"/>
       <c r="BC536" s="1"/>
       <c r="BD536" s="1"/>
-      <c r="BE536" s="1" t="str">
+      <c r="BE536" s="1"/>
+      <c r="BF536" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47040,7 +47729,8 @@
       <c r="BB537" s="1"/>
       <c r="BC537" s="1"/>
       <c r="BD537" s="1"/>
-      <c r="BE537" s="1" t="str">
+      <c r="BE537" s="1"/>
+      <c r="BF537" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47105,7 +47795,8 @@
       <c r="BB538" s="1"/>
       <c r="BC538" s="1"/>
       <c r="BD538" s="1"/>
-      <c r="BE538" s="1" t="str">
+      <c r="BE538" s="1"/>
+      <c r="BF538" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47170,7 +47861,8 @@
       <c r="BB539" s="1"/>
       <c r="BC539" s="1"/>
       <c r="BD539" s="1"/>
-      <c r="BE539" s="1" t="str">
+      <c r="BE539" s="1"/>
+      <c r="BF539" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47235,7 +47927,8 @@
       <c r="BB540" s="1"/>
       <c r="BC540" s="1"/>
       <c r="BD540" s="1"/>
-      <c r="BE540" s="1" t="str">
+      <c r="BE540" s="1"/>
+      <c r="BF540" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47300,7 +47993,8 @@
       <c r="BB541" s="1"/>
       <c r="BC541" s="1"/>
       <c r="BD541" s="1"/>
-      <c r="BE541" s="1" t="str">
+      <c r="BE541" s="1"/>
+      <c r="BF541" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47365,7 +48059,8 @@
       <c r="BB542" s="1"/>
       <c r="BC542" s="1"/>
       <c r="BD542" s="1"/>
-      <c r="BE542" s="1" t="str">
+      <c r="BE542" s="1"/>
+      <c r="BF542" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47430,7 +48125,8 @@
       <c r="BB543" s="1"/>
       <c r="BC543" s="1"/>
       <c r="BD543" s="1"/>
-      <c r="BE543" s="1" t="str">
+      <c r="BE543" s="1"/>
+      <c r="BF543" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47495,7 +48191,8 @@
       <c r="BB544" s="1"/>
       <c r="BC544" s="1"/>
       <c r="BD544" s="1"/>
-      <c r="BE544" s="1" t="str">
+      <c r="BE544" s="1"/>
+      <c r="BF544" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47560,7 +48257,8 @@
       <c r="BB545" s="1"/>
       <c r="BC545" s="1"/>
       <c r="BD545" s="1"/>
-      <c r="BE545" s="1" t="str">
+      <c r="BE545" s="1"/>
+      <c r="BF545" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47625,7 +48323,8 @@
       <c r="BB546" s="1"/>
       <c r="BC546" s="1"/>
       <c r="BD546" s="1"/>
-      <c r="BE546" s="1" t="str">
+      <c r="BE546" s="1"/>
+      <c r="BF546" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47690,7 +48389,8 @@
       <c r="BB547" s="1"/>
       <c r="BC547" s="1"/>
       <c r="BD547" s="1"/>
-      <c r="BE547" s="1" t="str">
+      <c r="BE547" s="1"/>
+      <c r="BF547" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47755,7 +48455,8 @@
       <c r="BB548" s="1"/>
       <c r="BC548" s="1"/>
       <c r="BD548" s="1"/>
-      <c r="BE548" s="1" t="str">
+      <c r="BE548" s="1"/>
+      <c r="BF548" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47820,7 +48521,8 @@
       <c r="BB549" s="1"/>
       <c r="BC549" s="1"/>
       <c r="BD549" s="1"/>
-      <c r="BE549" s="1" t="str">
+      <c r="BE549" s="1"/>
+      <c r="BF549" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47885,7 +48587,8 @@
       <c r="BB550" s="1"/>
       <c r="BC550" s="1"/>
       <c r="BD550" s="1"/>
-      <c r="BE550" s="1" t="str">
+      <c r="BE550" s="1"/>
+      <c r="BF550" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47950,7 +48653,8 @@
       <c r="BB551" s="1"/>
       <c r="BC551" s="1"/>
       <c r="BD551" s="1"/>
-      <c r="BE551" s="1" t="str">
+      <c r="BE551" s="1"/>
+      <c r="BF551" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48015,7 +48719,8 @@
       <c r="BB552" s="1"/>
       <c r="BC552" s="1"/>
       <c r="BD552" s="1"/>
-      <c r="BE552" s="1" t="str">
+      <c r="BE552" s="1"/>
+      <c r="BF552" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48080,7 +48785,8 @@
       <c r="BB553" s="1"/>
       <c r="BC553" s="1"/>
       <c r="BD553" s="1"/>
-      <c r="BE553" s="1" t="str">
+      <c r="BE553" s="1"/>
+      <c r="BF553" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48145,7 +48851,8 @@
       <c r="BB554" s="1"/>
       <c r="BC554" s="1"/>
       <c r="BD554" s="1"/>
-      <c r="BE554" s="1" t="str">
+      <c r="BE554" s="1"/>
+      <c r="BF554" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48210,7 +48917,8 @@
       <c r="BB555" s="1"/>
       <c r="BC555" s="1"/>
       <c r="BD555" s="1"/>
-      <c r="BE555" s="1" t="str">
+      <c r="BE555" s="1"/>
+      <c r="BF555" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48275,7 +48983,8 @@
       <c r="BB556" s="1"/>
       <c r="BC556" s="1"/>
       <c r="BD556" s="1"/>
-      <c r="BE556" s="1" t="str">
+      <c r="BE556" s="1"/>
+      <c r="BF556" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48340,7 +49049,8 @@
       <c r="BB557" s="1"/>
       <c r="BC557" s="1"/>
       <c r="BD557" s="1"/>
-      <c r="BE557" s="1" t="str">
+      <c r="BE557" s="1"/>
+      <c r="BF557" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48405,7 +49115,8 @@
       <c r="BB558" s="1"/>
       <c r="BC558" s="1"/>
       <c r="BD558" s="1"/>
-      <c r="BE558" s="1" t="str">
+      <c r="BE558" s="1"/>
+      <c r="BF558" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48470,7 +49181,8 @@
       <c r="BB559" s="1"/>
       <c r="BC559" s="1"/>
       <c r="BD559" s="1"/>
-      <c r="BE559" s="1" t="str">
+      <c r="BE559" s="1"/>
+      <c r="BF559" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48535,7 +49247,8 @@
       <c r="BB560" s="1"/>
       <c r="BC560" s="1"/>
       <c r="BD560" s="1"/>
-      <c r="BE560" s="1" t="str">
+      <c r="BE560" s="1"/>
+      <c r="BF560" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48600,7 +49313,8 @@
       <c r="BB561" s="1"/>
       <c r="BC561" s="1"/>
       <c r="BD561" s="1"/>
-      <c r="BE561" s="1" t="str">
+      <c r="BE561" s="1"/>
+      <c r="BF561" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48665,7 +49379,8 @@
       <c r="BB562" s="1"/>
       <c r="BC562" s="1"/>
       <c r="BD562" s="1"/>
-      <c r="BE562" s="1" t="str">
+      <c r="BE562" s="1"/>
+      <c r="BF562" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48730,7 +49445,8 @@
       <c r="BB563" s="1"/>
       <c r="BC563" s="1"/>
       <c r="BD563" s="1"/>
-      <c r="BE563" s="1" t="str">
+      <c r="BE563" s="1"/>
+      <c r="BF563" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48795,7 +49511,8 @@
       <c r="BB564" s="1"/>
       <c r="BC564" s="1"/>
       <c r="BD564" s="1"/>
-      <c r="BE564" s="1" t="str">
+      <c r="BE564" s="1"/>
+      <c r="BF564" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48860,7 +49577,8 @@
       <c r="BB565" s="1"/>
       <c r="BC565" s="1"/>
       <c r="BD565" s="1"/>
-      <c r="BE565" s="1" t="str">
+      <c r="BE565" s="1"/>
+      <c r="BF565" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48925,7 +49643,8 @@
       <c r="BB566" s="1"/>
       <c r="BC566" s="1"/>
       <c r="BD566" s="1"/>
-      <c r="BE566" s="1" t="str">
+      <c r="BE566" s="1"/>
+      <c r="BF566" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48990,7 +49709,8 @@
       <c r="BB567" s="1"/>
       <c r="BC567" s="1"/>
       <c r="BD567" s="1"/>
-      <c r="BE567" s="1" t="str">
+      <c r="BE567" s="1"/>
+      <c r="BF567" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49055,7 +49775,8 @@
       <c r="BB568" s="1"/>
       <c r="BC568" s="1"/>
       <c r="BD568" s="1"/>
-      <c r="BE568" s="1" t="str">
+      <c r="BE568" s="1"/>
+      <c r="BF568" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49120,7 +49841,8 @@
       <c r="BB569" s="1"/>
       <c r="BC569" s="1"/>
       <c r="BD569" s="1"/>
-      <c r="BE569" s="1" t="str">
+      <c r="BE569" s="1"/>
+      <c r="BF569" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49185,7 +49907,8 @@
       <c r="BB570" s="1"/>
       <c r="BC570" s="1"/>
       <c r="BD570" s="1"/>
-      <c r="BE570" s="1" t="str">
+      <c r="BE570" s="1"/>
+      <c r="BF570" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49250,7 +49973,8 @@
       <c r="BB571" s="1"/>
       <c r="BC571" s="1"/>
       <c r="BD571" s="1"/>
-      <c r="BE571" s="1" t="str">
+      <c r="BE571" s="1"/>
+      <c r="BF571" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49315,7 +50039,8 @@
       <c r="BB572" s="1"/>
       <c r="BC572" s="1"/>
       <c r="BD572" s="1"/>
-      <c r="BE572" s="1" t="str">
+      <c r="BE572" s="1"/>
+      <c r="BF572" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49380,7 +50105,8 @@
       <c r="BB573" s="1"/>
       <c r="BC573" s="1"/>
       <c r="BD573" s="1"/>
-      <c r="BE573" s="1" t="str">
+      <c r="BE573" s="1"/>
+      <c r="BF573" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49445,7 +50171,8 @@
       <c r="BB574" s="1"/>
       <c r="BC574" s="1"/>
       <c r="BD574" s="1"/>
-      <c r="BE574" s="1" t="str">
+      <c r="BE574" s="1"/>
+      <c r="BF574" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49510,7 +50237,8 @@
       <c r="BB575" s="1"/>
       <c r="BC575" s="1"/>
       <c r="BD575" s="1"/>
-      <c r="BE575" s="1" t="str">
+      <c r="BE575" s="1"/>
+      <c r="BF575" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49575,7 +50303,8 @@
       <c r="BB576" s="1"/>
       <c r="BC576" s="1"/>
       <c r="BD576" s="1"/>
-      <c r="BE576" s="1" t="str">
+      <c r="BE576" s="1"/>
+      <c r="BF576" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49640,7 +50369,8 @@
       <c r="BB577" s="1"/>
       <c r="BC577" s="1"/>
       <c r="BD577" s="1"/>
-      <c r="BE577" s="1" t="str">
+      <c r="BE577" s="1"/>
+      <c r="BF577" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49705,7 +50435,8 @@
       <c r="BB578" s="1"/>
       <c r="BC578" s="1"/>
       <c r="BD578" s="1"/>
-      <c r="BE578" s="1" t="str">
+      <c r="BE578" s="1"/>
+      <c r="BF578" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49770,7 +50501,8 @@
       <c r="BB579" s="1"/>
       <c r="BC579" s="1"/>
       <c r="BD579" s="1"/>
-      <c r="BE579" s="1" t="str">
+      <c r="BE579" s="1"/>
+      <c r="BF579" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49835,7 +50567,8 @@
       <c r="BB580" s="1"/>
       <c r="BC580" s="1"/>
       <c r="BD580" s="1"/>
-      <c r="BE580" s="1" t="str">
+      <c r="BE580" s="1"/>
+      <c r="BF580" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49900,7 +50633,8 @@
       <c r="BB581" s="1"/>
       <c r="BC581" s="1"/>
       <c r="BD581" s="1"/>
-      <c r="BE581" s="1" t="str">
+      <c r="BE581" s="1"/>
+      <c r="BF581" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49965,7 +50699,8 @@
       <c r="BB582" s="1"/>
       <c r="BC582" s="1"/>
       <c r="BD582" s="1"/>
-      <c r="BE582" s="1" t="str">
+      <c r="BE582" s="1"/>
+      <c r="BF582" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50030,7 +50765,8 @@
       <c r="BB583" s="1"/>
       <c r="BC583" s="1"/>
       <c r="BD583" s="1"/>
-      <c r="BE583" s="1" t="str">
+      <c r="BE583" s="1"/>
+      <c r="BF583" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50095,7 +50831,8 @@
       <c r="BB584" s="1"/>
       <c r="BC584" s="1"/>
       <c r="BD584" s="1"/>
-      <c r="BE584" s="1" t="str">
+      <c r="BE584" s="1"/>
+      <c r="BF584" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50160,7 +50897,8 @@
       <c r="BB585" s="1"/>
       <c r="BC585" s="1"/>
       <c r="BD585" s="1"/>
-      <c r="BE585" s="1" t="str">
+      <c r="BE585" s="1"/>
+      <c r="BF585" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50225,7 +50963,8 @@
       <c r="BB586" s="1"/>
       <c r="BC586" s="1"/>
       <c r="BD586" s="1"/>
-      <c r="BE586" s="1" t="str">
+      <c r="BE586" s="1"/>
+      <c r="BF586" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50290,7 +51029,8 @@
       <c r="BB587" s="1"/>
       <c r="BC587" s="1"/>
       <c r="BD587" s="1"/>
-      <c r="BE587" s="1" t="str">
+      <c r="BE587" s="1"/>
+      <c r="BF587" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50355,7 +51095,8 @@
       <c r="BB588" s="1"/>
       <c r="BC588" s="1"/>
       <c r="BD588" s="1"/>
-      <c r="BE588" s="1" t="str">
+      <c r="BE588" s="1"/>
+      <c r="BF588" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50420,7 +51161,8 @@
       <c r="BB589" s="1"/>
       <c r="BC589" s="1"/>
       <c r="BD589" s="1"/>
-      <c r="BE589" s="1" t="str">
+      <c r="BE589" s="1"/>
+      <c r="BF589" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50485,7 +51227,8 @@
       <c r="BB590" s="1"/>
       <c r="BC590" s="1"/>
       <c r="BD590" s="1"/>
-      <c r="BE590" s="1" t="str">
+      <c r="BE590" s="1"/>
+      <c r="BF590" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50550,7 +51293,8 @@
       <c r="BB591" s="1"/>
       <c r="BC591" s="1"/>
       <c r="BD591" s="1"/>
-      <c r="BE591" s="1" t="str">
+      <c r="BE591" s="1"/>
+      <c r="BF591" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50615,7 +51359,8 @@
       <c r="BB592" s="1"/>
       <c r="BC592" s="1"/>
       <c r="BD592" s="1"/>
-      <c r="BE592" s="1" t="str">
+      <c r="BE592" s="1"/>
+      <c r="BF592" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50680,7 +51425,8 @@
       <c r="BB593" s="1"/>
       <c r="BC593" s="1"/>
       <c r="BD593" s="1"/>
-      <c r="BE593" s="1" t="str">
+      <c r="BE593" s="1"/>
+      <c r="BF593" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50745,7 +51491,8 @@
       <c r="BB594" s="1"/>
       <c r="BC594" s="1"/>
       <c r="BD594" s="1"/>
-      <c r="BE594" s="1" t="str">
+      <c r="BE594" s="1"/>
+      <c r="BF594" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50810,7 +51557,8 @@
       <c r="BB595" s="1"/>
       <c r="BC595" s="1"/>
       <c r="BD595" s="1"/>
-      <c r="BE595" s="1" t="str">
+      <c r="BE595" s="1"/>
+      <c r="BF595" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50875,7 +51623,8 @@
       <c r="BB596" s="1"/>
       <c r="BC596" s="1"/>
       <c r="BD596" s="1"/>
-      <c r="BE596" s="1" t="str">
+      <c r="BE596" s="1"/>
+      <c r="BF596" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50940,7 +51689,8 @@
       <c r="BB597" s="1"/>
       <c r="BC597" s="1"/>
       <c r="BD597" s="1"/>
-      <c r="BE597" s="1" t="str">
+      <c r="BE597" s="1"/>
+      <c r="BF597" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51005,7 +51755,8 @@
       <c r="BB598" s="1"/>
       <c r="BC598" s="1"/>
       <c r="BD598" s="1"/>
-      <c r="BE598" s="1" t="str">
+      <c r="BE598" s="1"/>
+      <c r="BF598" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51070,7 +51821,8 @@
       <c r="BB599" s="1"/>
       <c r="BC599" s="1"/>
       <c r="BD599" s="1"/>
-      <c r="BE599" s="1" t="str">
+      <c r="BE599" s="1"/>
+      <c r="BF599" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51135,7 +51887,8 @@
       <c r="BB600" s="1"/>
       <c r="BC600" s="1"/>
       <c r="BD600" s="1"/>
-      <c r="BE600" s="1" t="str">
+      <c r="BE600" s="1"/>
+      <c r="BF600" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51200,7 +51953,8 @@
       <c r="BB601" s="1"/>
       <c r="BC601" s="1"/>
       <c r="BD601" s="1"/>
-      <c r="BE601" s="1" t="str">
+      <c r="BE601" s="1"/>
+      <c r="BF601" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51265,7 +52019,8 @@
       <c r="BB602" s="1"/>
       <c r="BC602" s="1"/>
       <c r="BD602" s="1"/>
-      <c r="BE602" s="1" t="str">
+      <c r="BE602" s="1"/>
+      <c r="BF602" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51330,7 +52085,8 @@
       <c r="BB603" s="1"/>
       <c r="BC603" s="1"/>
       <c r="BD603" s="1"/>
-      <c r="BE603" s="1" t="str">
+      <c r="BE603" s="1"/>
+      <c r="BF603" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51395,7 +52151,8 @@
       <c r="BB604" s="1"/>
       <c r="BC604" s="1"/>
       <c r="BD604" s="1"/>
-      <c r="BE604" s="1" t="str">
+      <c r="BE604" s="1"/>
+      <c r="BF604" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51460,7 +52217,8 @@
       <c r="BB605" s="1"/>
       <c r="BC605" s="1"/>
       <c r="BD605" s="1"/>
-      <c r="BE605" s="1" t="str">
+      <c r="BE605" s="1"/>
+      <c r="BF605" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51525,7 +52283,8 @@
       <c r="BB606" s="1"/>
       <c r="BC606" s="1"/>
       <c r="BD606" s="1"/>
-      <c r="BE606" s="1" t="str">
+      <c r="BE606" s="1"/>
+      <c r="BF606" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51590,7 +52349,8 @@
       <c r="BB607" s="1"/>
       <c r="BC607" s="1"/>
       <c r="BD607" s="1"/>
-      <c r="BE607" s="1" t="str">
+      <c r="BE607" s="1"/>
+      <c r="BF607" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51655,7 +52415,8 @@
       <c r="BB608" s="1"/>
       <c r="BC608" s="1"/>
       <c r="BD608" s="1"/>
-      <c r="BE608" s="1" t="str">
+      <c r="BE608" s="1"/>
+      <c r="BF608" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51720,7 +52481,8 @@
       <c r="BB609" s="1"/>
       <c r="BC609" s="1"/>
       <c r="BD609" s="1"/>
-      <c r="BE609" s="1" t="str">
+      <c r="BE609" s="1"/>
+      <c r="BF609" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51785,7 +52547,8 @@
       <c r="BB610" s="1"/>
       <c r="BC610" s="1"/>
       <c r="BD610" s="1"/>
-      <c r="BE610" s="1" t="str">
+      <c r="BE610" s="1"/>
+      <c r="BF610" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51850,7 +52613,8 @@
       <c r="BB611" s="1"/>
       <c r="BC611" s="1"/>
       <c r="BD611" s="1"/>
-      <c r="BE611" s="1" t="str">
+      <c r="BE611" s="1"/>
+      <c r="BF611" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51915,7 +52679,8 @@
       <c r="BB612" s="1"/>
       <c r="BC612" s="1"/>
       <c r="BD612" s="1"/>
-      <c r="BE612" s="1" t="str">
+      <c r="BE612" s="1"/>
+      <c r="BF612" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51980,7 +52745,8 @@
       <c r="BB613" s="1"/>
       <c r="BC613" s="1"/>
       <c r="BD613" s="1"/>
-      <c r="BE613" s="1" t="str">
+      <c r="BE613" s="1"/>
+      <c r="BF613" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52045,7 +52811,8 @@
       <c r="BB614" s="1"/>
       <c r="BC614" s="1"/>
       <c r="BD614" s="1"/>
-      <c r="BE614" s="1" t="str">
+      <c r="BE614" s="1"/>
+      <c r="BF614" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52110,7 +52877,8 @@
       <c r="BB615" s="1"/>
       <c r="BC615" s="1"/>
       <c r="BD615" s="1"/>
-      <c r="BE615" s="1" t="str">
+      <c r="BE615" s="1"/>
+      <c r="BF615" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52175,7 +52943,8 @@
       <c r="BB616" s="1"/>
       <c r="BC616" s="1"/>
       <c r="BD616" s="1"/>
-      <c r="BE616" s="1" t="str">
+      <c r="BE616" s="1"/>
+      <c r="BF616" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52240,7 +53009,8 @@
       <c r="BB617" s="1"/>
       <c r="BC617" s="1"/>
       <c r="BD617" s="1"/>
-      <c r="BE617" s="1" t="str">
+      <c r="BE617" s="1"/>
+      <c r="BF617" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52305,7 +53075,8 @@
       <c r="BB618" s="1"/>
       <c r="BC618" s="1"/>
       <c r="BD618" s="1"/>
-      <c r="BE618" s="1" t="str">
+      <c r="BE618" s="1"/>
+      <c r="BF618" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52370,7 +53141,8 @@
       <c r="BB619" s="1"/>
       <c r="BC619" s="1"/>
       <c r="BD619" s="1"/>
-      <c r="BE619" s="1" t="str">
+      <c r="BE619" s="1"/>
+      <c r="BF619" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52435,7 +53207,8 @@
       <c r="BB620" s="1"/>
       <c r="BC620" s="1"/>
       <c r="BD620" s="1"/>
-      <c r="BE620" s="1" t="str">
+      <c r="BE620" s="1"/>
+      <c r="BF620" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52500,7 +53273,8 @@
       <c r="BB621" s="1"/>
       <c r="BC621" s="1"/>
       <c r="BD621" s="1"/>
-      <c r="BE621" s="1" t="str">
+      <c r="BE621" s="1"/>
+      <c r="BF621" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52565,7 +53339,8 @@
       <c r="BB622" s="1"/>
       <c r="BC622" s="1"/>
       <c r="BD622" s="1"/>
-      <c r="BE622" s="1" t="str">
+      <c r="BE622" s="1"/>
+      <c r="BF622" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52630,7 +53405,8 @@
       <c r="BB623" s="1"/>
       <c r="BC623" s="1"/>
       <c r="BD623" s="1"/>
-      <c r="BE623" s="1" t="str">
+      <c r="BE623" s="1"/>
+      <c r="BF623" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52695,7 +53471,8 @@
       <c r="BB624" s="1"/>
       <c r="BC624" s="1"/>
       <c r="BD624" s="1"/>
-      <c r="BE624" s="1" t="str">
+      <c r="BE624" s="1"/>
+      <c r="BF624" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52760,7 +53537,8 @@
       <c r="BB625" s="1"/>
       <c r="BC625" s="1"/>
       <c r="BD625" s="1"/>
-      <c r="BE625" s="1" t="str">
+      <c r="BE625" s="1"/>
+      <c r="BF625" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52825,7 +53603,8 @@
       <c r="BB626" s="1"/>
       <c r="BC626" s="1"/>
       <c r="BD626" s="1"/>
-      <c r="BE626" s="1" t="str">
+      <c r="BE626" s="1"/>
+      <c r="BF626" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52890,7 +53669,8 @@
       <c r="BB627" s="1"/>
       <c r="BC627" s="1"/>
       <c r="BD627" s="1"/>
-      <c r="BE627" s="1" t="str">
+      <c r="BE627" s="1"/>
+      <c r="BF627" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52955,7 +53735,8 @@
       <c r="BB628" s="1"/>
       <c r="BC628" s="1"/>
       <c r="BD628" s="1"/>
-      <c r="BE628" s="1" t="str">
+      <c r="BE628" s="1"/>
+      <c r="BF628" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53020,7 +53801,8 @@
       <c r="BB629" s="1"/>
       <c r="BC629" s="1"/>
       <c r="BD629" s="1"/>
-      <c r="BE629" s="1" t="str">
+      <c r="BE629" s="1"/>
+      <c r="BF629" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53085,7 +53867,8 @@
       <c r="BB630" s="1"/>
       <c r="BC630" s="1"/>
       <c r="BD630" s="1"/>
-      <c r="BE630" s="1" t="str">
+      <c r="BE630" s="1"/>
+      <c r="BF630" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53150,7 +53933,8 @@
       <c r="BB631" s="1"/>
       <c r="BC631" s="1"/>
       <c r="BD631" s="1"/>
-      <c r="BE631" s="1" t="str">
+      <c r="BE631" s="1"/>
+      <c r="BF631" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53215,7 +53999,8 @@
       <c r="BB632" s="1"/>
       <c r="BC632" s="1"/>
       <c r="BD632" s="1"/>
-      <c r="BE632" s="1" t="str">
+      <c r="BE632" s="1"/>
+      <c r="BF632" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53280,7 +54065,8 @@
       <c r="BB633" s="1"/>
       <c r="BC633" s="1"/>
       <c r="BD633" s="1"/>
-      <c r="BE633" s="1" t="str">
+      <c r="BE633" s="1"/>
+      <c r="BF633" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53345,7 +54131,8 @@
       <c r="BB634" s="1"/>
       <c r="BC634" s="1"/>
       <c r="BD634" s="1"/>
-      <c r="BE634" s="1" t="str">
+      <c r="BE634" s="1"/>
+      <c r="BF634" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53410,7 +54197,8 @@
       <c r="BB635" s="1"/>
       <c r="BC635" s="1"/>
       <c r="BD635" s="1"/>
-      <c r="BE635" s="1" t="str">
+      <c r="BE635" s="1"/>
+      <c r="BF635" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53475,7 +54263,8 @@
       <c r="BB636" s="1"/>
       <c r="BC636" s="1"/>
       <c r="BD636" s="1"/>
-      <c r="BE636" s="1" t="str">
+      <c r="BE636" s="1"/>
+      <c r="BF636" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53540,7 +54329,8 @@
       <c r="BB637" s="1"/>
       <c r="BC637" s="1"/>
       <c r="BD637" s="1"/>
-      <c r="BE637" s="1" t="str">
+      <c r="BE637" s="1"/>
+      <c r="BF637" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53605,7 +54395,8 @@
       <c r="BB638" s="1"/>
       <c r="BC638" s="1"/>
       <c r="BD638" s="1"/>
-      <c r="BE638" s="1" t="str">
+      <c r="BE638" s="1"/>
+      <c r="BF638" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53670,7 +54461,8 @@
       <c r="BB639" s="1"/>
       <c r="BC639" s="1"/>
       <c r="BD639" s="1"/>
-      <c r="BE639" s="1" t="str">
+      <c r="BE639" s="1"/>
+      <c r="BF639" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53735,7 +54527,8 @@
       <c r="BB640" s="1"/>
       <c r="BC640" s="1"/>
       <c r="BD640" s="1"/>
-      <c r="BE640" s="1" t="str">
+      <c r="BE640" s="1"/>
+      <c r="BF640" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53800,7 +54593,8 @@
       <c r="BB641" s="1"/>
       <c r="BC641" s="1"/>
       <c r="BD641" s="1"/>
-      <c r="BE641" s="1" t="str">
+      <c r="BE641" s="1"/>
+      <c r="BF641" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53865,7 +54659,8 @@
       <c r="BB642" s="1"/>
       <c r="BC642" s="1"/>
       <c r="BD642" s="1"/>
-      <c r="BE642" s="1" t="str">
+      <c r="BE642" s="1"/>
+      <c r="BF642" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53930,7 +54725,8 @@
       <c r="BB643" s="1"/>
       <c r="BC643" s="1"/>
       <c r="BD643" s="1"/>
-      <c r="BE643" s="1" t="str">
+      <c r="BE643" s="1"/>
+      <c r="BF643" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53995,7 +54791,8 @@
       <c r="BB644" s="1"/>
       <c r="BC644" s="1"/>
       <c r="BD644" s="1"/>
-      <c r="BE644" s="1" t="str">
+      <c r="BE644" s="1"/>
+      <c r="BF644" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54060,7 +54857,8 @@
       <c r="BB645" s="1"/>
       <c r="BC645" s="1"/>
       <c r="BD645" s="1"/>
-      <c r="BE645" s="1" t="str">
+      <c r="BE645" s="1"/>
+      <c r="BF645" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54125,7 +54923,8 @@
       <c r="BB646" s="1"/>
       <c r="BC646" s="1"/>
       <c r="BD646" s="1"/>
-      <c r="BE646" s="1" t="str">
+      <c r="BE646" s="1"/>
+      <c r="BF646" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54190,7 +54989,8 @@
       <c r="BB647" s="1"/>
       <c r="BC647" s="1"/>
       <c r="BD647" s="1"/>
-      <c r="BE647" s="1" t="str">
+      <c r="BE647" s="1"/>
+      <c r="BF647" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54255,7 +55055,8 @@
       <c r="BB648" s="1"/>
       <c r="BC648" s="1"/>
       <c r="BD648" s="1"/>
-      <c r="BE648" s="1" t="str">
+      <c r="BE648" s="1"/>
+      <c r="BF648" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54320,7 +55121,8 @@
       <c r="BB649" s="1"/>
       <c r="BC649" s="1"/>
       <c r="BD649" s="1"/>
-      <c r="BE649" s="1" t="str">
+      <c r="BE649" s="1"/>
+      <c r="BF649" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54385,7 +55187,8 @@
       <c r="BB650" s="1"/>
       <c r="BC650" s="1"/>
       <c r="BD650" s="1"/>
-      <c r="BE650" s="1" t="str">
+      <c r="BE650" s="1"/>
+      <c r="BF650" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54450,7 +55253,8 @@
       <c r="BB651" s="1"/>
       <c r="BC651" s="1"/>
       <c r="BD651" s="1"/>
-      <c r="BE651" s="1" t="str">
+      <c r="BE651" s="1"/>
+      <c r="BF651" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54515,7 +55319,8 @@
       <c r="BB652" s="1"/>
       <c r="BC652" s="1"/>
       <c r="BD652" s="1"/>
-      <c r="BE652" s="1" t="str">
+      <c r="BE652" s="1"/>
+      <c r="BF652" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54580,7 +55385,8 @@
       <c r="BB653" s="1"/>
       <c r="BC653" s="1"/>
       <c r="BD653" s="1"/>
-      <c r="BE653" s="1" t="str">
+      <c r="BE653" s="1"/>
+      <c r="BF653" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54645,7 +55451,8 @@
       <c r="BB654" s="1"/>
       <c r="BC654" s="1"/>
       <c r="BD654" s="1"/>
-      <c r="BE654" s="1" t="str">
+      <c r="BE654" s="1"/>
+      <c r="BF654" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54710,7 +55517,8 @@
       <c r="BB655" s="1"/>
       <c r="BC655" s="1"/>
       <c r="BD655" s="1"/>
-      <c r="BE655" s="1" t="str">
+      <c r="BE655" s="1"/>
+      <c r="BF655" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54775,7 +55583,8 @@
       <c r="BB656" s="1"/>
       <c r="BC656" s="1"/>
       <c r="BD656" s="1"/>
-      <c r="BE656" s="1" t="str">
+      <c r="BE656" s="1"/>
+      <c r="BF656" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54840,7 +55649,8 @@
       <c r="BB657" s="1"/>
       <c r="BC657" s="1"/>
       <c r="BD657" s="1"/>
-      <c r="BE657" s="1" t="str">
+      <c r="BE657" s="1"/>
+      <c r="BF657" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54905,7 +55715,8 @@
       <c r="BB658" s="1"/>
       <c r="BC658" s="1"/>
       <c r="BD658" s="1"/>
-      <c r="BE658" s="1" t="str">
+      <c r="BE658" s="1"/>
+      <c r="BF658" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54970,7 +55781,8 @@
       <c r="BB659" s="1"/>
       <c r="BC659" s="1"/>
       <c r="BD659" s="1"/>
-      <c r="BE659" s="1" t="str">
+      <c r="BE659" s="1"/>
+      <c r="BF659" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55035,7 +55847,8 @@
       <c r="BB660" s="1"/>
       <c r="BC660" s="1"/>
       <c r="BD660" s="1"/>
-      <c r="BE660" s="1" t="str">
+      <c r="BE660" s="1"/>
+      <c r="BF660" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55100,7 +55913,8 @@
       <c r="BB661" s="1"/>
       <c r="BC661" s="1"/>
       <c r="BD661" s="1"/>
-      <c r="BE661" s="1" t="str">
+      <c r="BE661" s="1"/>
+      <c r="BF661" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55165,7 +55979,8 @@
       <c r="BB662" s="1"/>
       <c r="BC662" s="1"/>
       <c r="BD662" s="1"/>
-      <c r="BE662" s="1" t="str">
+      <c r="BE662" s="1"/>
+      <c r="BF662" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55230,7 +56045,8 @@
       <c r="BB663" s="1"/>
       <c r="BC663" s="1"/>
       <c r="BD663" s="1"/>
-      <c r="BE663" s="1" t="str">
+      <c r="BE663" s="1"/>
+      <c r="BF663" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55295,7 +56111,8 @@
       <c r="BB664" s="1"/>
       <c r="BC664" s="1"/>
       <c r="BD664" s="1"/>
-      <c r="BE664" s="1" t="str">
+      <c r="BE664" s="1"/>
+      <c r="BF664" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55360,7 +56177,8 @@
       <c r="BB665" s="1"/>
       <c r="BC665" s="1"/>
       <c r="BD665" s="1"/>
-      <c r="BE665" s="1" t="str">
+      <c r="BE665" s="1"/>
+      <c r="BF665" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55425,7 +56243,8 @@
       <c r="BB666" s="1"/>
       <c r="BC666" s="1"/>
       <c r="BD666" s="1"/>
-      <c r="BE666" s="1" t="str">
+      <c r="BE666" s="1"/>
+      <c r="BF666" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55490,7 +56309,8 @@
       <c r="BB667" s="1"/>
       <c r="BC667" s="1"/>
       <c r="BD667" s="1"/>
-      <c r="BE667" s="1" t="str">
+      <c r="BE667" s="1"/>
+      <c r="BF667" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55555,7 +56375,8 @@
       <c r="BB668" s="1"/>
       <c r="BC668" s="1"/>
       <c r="BD668" s="1"/>
-      <c r="BE668" s="1" t="str">
+      <c r="BE668" s="1"/>
+      <c r="BF668" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55620,7 +56441,8 @@
       <c r="BB669" s="1"/>
       <c r="BC669" s="1"/>
       <c r="BD669" s="1"/>
-      <c r="BE669" s="1" t="str">
+      <c r="BE669" s="1"/>
+      <c r="BF669" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55685,7 +56507,8 @@
       <c r="BB670" s="1"/>
       <c r="BC670" s="1"/>
       <c r="BD670" s="1"/>
-      <c r="BE670" s="1" t="str">
+      <c r="BE670" s="1"/>
+      <c r="BF670" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55750,7 +56573,8 @@
       <c r="BB671" s="1"/>
       <c r="BC671" s="1"/>
       <c r="BD671" s="1"/>
-      <c r="BE671" s="1" t="str">
+      <c r="BE671" s="1"/>
+      <c r="BF671" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55815,7 +56639,8 @@
       <c r="BB672" s="1"/>
       <c r="BC672" s="1"/>
       <c r="BD672" s="1"/>
-      <c r="BE672" s="1" t="str">
+      <c r="BE672" s="1"/>
+      <c r="BF672" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55880,7 +56705,8 @@
       <c r="BB673" s="1"/>
       <c r="BC673" s="1"/>
       <c r="BD673" s="1"/>
-      <c r="BE673" s="1" t="str">
+      <c r="BE673" s="1"/>
+      <c r="BF673" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55945,7 +56771,8 @@
       <c r="BB674" s="1"/>
       <c r="BC674" s="1"/>
       <c r="BD674" s="1"/>
-      <c r="BE674" s="1" t="str">
+      <c r="BE674" s="1"/>
+      <c r="BF674" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56010,7 +56837,8 @@
       <c r="BB675" s="1"/>
       <c r="BC675" s="1"/>
       <c r="BD675" s="1"/>
-      <c r="BE675" s="1" t="str">
+      <c r="BE675" s="1"/>
+      <c r="BF675" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56075,7 +56903,8 @@
       <c r="BB676" s="1"/>
       <c r="BC676" s="1"/>
       <c r="BD676" s="1"/>
-      <c r="BE676" s="1" t="str">
+      <c r="BE676" s="1"/>
+      <c r="BF676" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56140,7 +56969,8 @@
       <c r="BB677" s="1"/>
       <c r="BC677" s="1"/>
       <c r="BD677" s="1"/>
-      <c r="BE677" s="1" t="str">
+      <c r="BE677" s="1"/>
+      <c r="BF677" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56205,7 +57035,8 @@
       <c r="BB678" s="1"/>
       <c r="BC678" s="1"/>
       <c r="BD678" s="1"/>
-      <c r="BE678" s="1" t="str">
+      <c r="BE678" s="1"/>
+      <c r="BF678" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56270,7 +57101,8 @@
       <c r="BB679" s="1"/>
       <c r="BC679" s="1"/>
       <c r="BD679" s="1"/>
-      <c r="BE679" s="1" t="str">
+      <c r="BE679" s="1"/>
+      <c r="BF679" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56335,7 +57167,8 @@
       <c r="BB680" s="1"/>
       <c r="BC680" s="1"/>
       <c r="BD680" s="1"/>
-      <c r="BE680" s="1" t="str">
+      <c r="BE680" s="1"/>
+      <c r="BF680" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56400,7 +57233,8 @@
       <c r="BB681" s="1"/>
       <c r="BC681" s="1"/>
       <c r="BD681" s="1"/>
-      <c r="BE681" s="1" t="str">
+      <c r="BE681" s="1"/>
+      <c r="BF681" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56465,7 +57299,8 @@
       <c r="BB682" s="1"/>
       <c r="BC682" s="1"/>
       <c r="BD682" s="1"/>
-      <c r="BE682" s="1" t="str">
+      <c r="BE682" s="1"/>
+      <c r="BF682" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56530,7 +57365,8 @@
       <c r="BB683" s="1"/>
       <c r="BC683" s="1"/>
       <c r="BD683" s="1"/>
-      <c r="BE683" s="1" t="str">
+      <c r="BE683" s="1"/>
+      <c r="BF683" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56595,7 +57431,8 @@
       <c r="BB684" s="1"/>
       <c r="BC684" s="1"/>
       <c r="BD684" s="1"/>
-      <c r="BE684" s="1" t="str">
+      <c r="BE684" s="1"/>
+      <c r="BF684" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56660,7 +57497,8 @@
       <c r="BB685" s="1"/>
       <c r="BC685" s="1"/>
       <c r="BD685" s="1"/>
-      <c r="BE685" s="1" t="str">
+      <c r="BE685" s="1"/>
+      <c r="BF685" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56725,7 +57563,8 @@
       <c r="BB686" s="1"/>
       <c r="BC686" s="1"/>
       <c r="BD686" s="1"/>
-      <c r="BE686" s="1" t="str">
+      <c r="BE686" s="1"/>
+      <c r="BF686" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56790,7 +57629,8 @@
       <c r="BB687" s="1"/>
       <c r="BC687" s="1"/>
       <c r="BD687" s="1"/>
-      <c r="BE687" s="1" t="str">
+      <c r="BE687" s="1"/>
+      <c r="BF687" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56855,7 +57695,8 @@
       <c r="BB688" s="1"/>
       <c r="BC688" s="1"/>
       <c r="BD688" s="1"/>
-      <c r="BE688" s="1" t="str">
+      <c r="BE688" s="1"/>
+      <c r="BF688" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56920,7 +57761,8 @@
       <c r="BB689" s="1"/>
       <c r="BC689" s="1"/>
       <c r="BD689" s="1"/>
-      <c r="BE689" s="1" t="str">
+      <c r="BE689" s="1"/>
+      <c r="BF689" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56985,7 +57827,8 @@
       <c r="BB690" s="1"/>
       <c r="BC690" s="1"/>
       <c r="BD690" s="1"/>
-      <c r="BE690" s="1" t="str">
+      <c r="BE690" s="1"/>
+      <c r="BF690" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57050,7 +57893,8 @@
       <c r="BB691" s="1"/>
       <c r="BC691" s="1"/>
       <c r="BD691" s="1"/>
-      <c r="BE691" s="1" t="str">
+      <c r="BE691" s="1"/>
+      <c r="BF691" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57115,7 +57959,8 @@
       <c r="BB692" s="1"/>
       <c r="BC692" s="1"/>
       <c r="BD692" s="1"/>
-      <c r="BE692" s="1" t="str">
+      <c r="BE692" s="1"/>
+      <c r="BF692" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57180,7 +58025,8 @@
       <c r="BB693" s="1"/>
       <c r="BC693" s="1"/>
       <c r="BD693" s="1"/>
-      <c r="BE693" s="1" t="str">
+      <c r="BE693" s="1"/>
+      <c r="BF693" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57245,7 +58091,8 @@
       <c r="BB694" s="1"/>
       <c r="BC694" s="1"/>
       <c r="BD694" s="1"/>
-      <c r="BE694" s="1" t="str">
+      <c r="BE694" s="1"/>
+      <c r="BF694" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57310,7 +58157,8 @@
       <c r="BB695" s="1"/>
       <c r="BC695" s="1"/>
       <c r="BD695" s="1"/>
-      <c r="BE695" s="1" t="str">
+      <c r="BE695" s="1"/>
+      <c r="BF695" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57375,7 +58223,8 @@
       <c r="BB696" s="1"/>
       <c r="BC696" s="1"/>
       <c r="BD696" s="1"/>
-      <c r="BE696" s="1" t="str">
+      <c r="BE696" s="1"/>
+      <c r="BF696" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57440,7 +58289,8 @@
       <c r="BB697" s="1"/>
       <c r="BC697" s="1"/>
       <c r="BD697" s="1"/>
-      <c r="BE697" s="1" t="str">
+      <c r="BE697" s="1"/>
+      <c r="BF697" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57505,7 +58355,8 @@
       <c r="BB698" s="1"/>
       <c r="BC698" s="1"/>
       <c r="BD698" s="1"/>
-      <c r="BE698" s="1" t="str">
+      <c r="BE698" s="1"/>
+      <c r="BF698" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57570,7 +58421,8 @@
       <c r="BB699" s="1"/>
       <c r="BC699" s="1"/>
       <c r="BD699" s="1"/>
-      <c r="BE699" s="1" t="str">
+      <c r="BE699" s="1"/>
+      <c r="BF699" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57635,7 +58487,8 @@
       <c r="BB700" s="1"/>
       <c r="BC700" s="1"/>
       <c r="BD700" s="1"/>
-      <c r="BE700" s="1" t="str">
+      <c r="BE700" s="1"/>
+      <c r="BF700" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>

--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -12257,17 +12257,20 @@
         <v>PAGO FRACCIONADO</v>
       </c>
       <c r="W53" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),700.0)</f>
-        <v>700</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X53" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"29/05/2025")</f>
-        <v>29/05/2025</v>
-      </c>
-      <c r="Y53" s="1"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
+        <v>31/05/2025</v>
+      </c>
+      <c r="Y53" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45808.0)</f>
+        <v>45808</v>
+      </c>
       <c r="Z53" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
-        <v>PAGO FRACCIONADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
       </c>
       <c r="AA53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
@@ -12341,8 +12344,8 @@
         <v>45775</v>
       </c>
       <c r="AU53" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),25.0)</f>
+        <v>25</v>
       </c>
       <c r="AV53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
@@ -12365,8 +12368,8 @@
         <v>Angelica Iparraguirre</v>
       </c>
       <c r="BA53" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5439739413680782)</f>
-        <v>0.5439739414</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BB53" s="6">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1480.0)</f>
@@ -16589,17 +16592,20 @@
         <v>PAGO FRACCIONADO</v>
       </c>
       <c r="W72" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),550.0)</f>
-        <v>550</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="X72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
         <v>31/05/2025</v>
       </c>
-      <c r="Y72" s="1"/>
+      <c r="Y72" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
       <c r="Z72" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
-        <v>PAGO FRACCIONADO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
       </c>
       <c r="AA72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
@@ -16615,12 +16621,12 @@
         <v>0</v>
       </c>
       <c r="AE72" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
-        <v>850</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1000.0)</f>
+        <v>1000</v>
       </c>
       <c r="AF72" s="4">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
-        <v>850</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1000.0)</f>
+        <v>1000</v>
       </c>
       <c r="AG72" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -16679,8 +16685,8 @@
         <v>45775</v>
       </c>
       <c r="AU72" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.0)</f>
-        <v>9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),12.0)</f>
+        <v>12</v>
       </c>
       <c r="AV72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
@@ -16703,12 +16709,12 @@
         <v>Juan Manuel Rodríguez</v>
       </c>
       <c r="BA72" s="5">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.35294117647058826)</f>
-        <v>0.3529411765</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BB72" s="6">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
-        <v>850</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1000.0)</f>
+        <v>1000</v>
       </c>
       <c r="BC72" s="1"/>
       <c r="BD72" s="1" t="str">
@@ -17178,198 +17184,624 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B75" s="1"/>
+      <c r="A75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),74.0)</f>
+        <v>74</v>
+      </c>
+      <c r="B75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181466.0)</f>
+        <v>181466</v>
+      </c>
       <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
+      <c r="D75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MERY ELIZABETH")</f>
+        <v>MERY ELIZABETH</v>
+      </c>
+      <c r="E75" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CANTO GALICIA")</f>
+        <v>CANTO GALICIA</v>
+      </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
-      <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
-      <c r="P75" s="1"/>
-      <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
-      <c r="U75" s="1"/>
-      <c r="V75" s="1"/>
-      <c r="W75" s="1"/>
-      <c r="X75" s="1"/>
-      <c r="Y75" s="1"/>
-      <c r="Z75" s="1"/>
-      <c r="AA75" s="1"/>
+      <c r="I75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño Gráfico Publicitario")</f>
+        <v>Diseño Gráfico Publicitario</v>
+      </c>
+      <c r="J75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño")</f>
+        <v>Diseño</v>
+      </c>
+      <c r="K75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO CON CONVA")</f>
+        <v>TRASLADO CON CONVA</v>
+      </c>
+      <c r="P75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RECA")</f>
+        <v>RECA</v>
+      </c>
+      <c r="Q75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RECATEGORIZACIÓN")</f>
+        <v>RECATEGORIZACIÓN</v>
+      </c>
+      <c r="R75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T75" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
+      <c r="U75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W75" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y75" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45807.0)</f>
+        <v>45807</v>
+      </c>
+      <c r="Z75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB75" s="1"/>
-      <c r="AC75" s="1"/>
-      <c r="AD75" s="1"/>
-      <c r="AE75" s="1"/>
-      <c r="AF75" s="1"/>
-      <c r="AG75" s="1"/>
-      <c r="AH75" s="1"/>
-      <c r="AI75" s="1"/>
+      <c r="AC75" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD75" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE75" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AF75" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AG75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="AJ75" s="1"/>
-      <c r="AK75" s="1"/>
-      <c r="AL75" s="1"/>
+      <c r="AK75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01 Nacional")</f>
+        <v>01 Nacional</v>
+      </c>
       <c r="AM75" s="1"/>
-      <c r="AN75" s="1"/>
+      <c r="AN75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
       <c r="AO75" s="1"/>
-      <c r="AP75" s="1"/>
-      <c r="AQ75" s="1"/>
-      <c r="AR75" s="1"/>
-      <c r="AS75" s="1"/>
-      <c r="AT75" s="1"/>
-      <c r="AU75" s="1"/>
-      <c r="AV75" s="1"/>
-      <c r="AW75" s="1"/>
-      <c r="AX75" s="1"/>
-      <c r="AY75" s="1"/>
-      <c r="AZ75" s="1"/>
-      <c r="BA75" s="1"/>
-      <c r="BB75" s="1"/>
-      <c r="BC75" s="1"/>
-      <c r="BD75" s="1"/>
-      <c r="BE75" s="1"/>
+      <c r="AP75" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ75" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR75" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45802.0)</f>
+        <v>45802</v>
+      </c>
+      <c r="AS75" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT75" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="AV75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FORMULARIO")</f>
+        <v>FORMULARIO</v>
+      </c>
+      <c r="AX75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NO SUFICIENCIA")</f>
+        <v>NO SUFICIENCIA</v>
+      </c>
+      <c r="AY75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rosa Ugarte")</f>
+        <v>Rosa Ugarte</v>
+      </c>
+      <c r="BA75" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB75" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="BC75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BF75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B76" s="1"/>
+      <c r="A76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),75.0)</f>
+        <v>75</v>
+      </c>
+      <c r="B76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5221256.0)</f>
+        <v>5221256</v>
+      </c>
       <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
+      <c r="D76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HANS ANTONIO")</f>
+        <v>HANS ANTONIO</v>
+      </c>
+      <c r="E76" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"THOL HUAMAN")</f>
+        <v>THOL HUAMAN</v>
+      </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1"/>
-      <c r="W76" s="1"/>
+      <c r="I76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
+        <v>Administración y Marketing</v>
+      </c>
+      <c r="J76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
+        <v>Negocios</v>
+      </c>
+      <c r="K76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Nueva")</f>
+        <v>Nueva</v>
+      </c>
+      <c r="L76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Virtual")</f>
+        <v>Virtual</v>
+      </c>
+      <c r="N76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Nocturno - A distancia")</f>
+        <v>Nocturno - A distancia</v>
+      </c>
+      <c r="O76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T76" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45808.0)</f>
+        <v>45808</v>
+      </c>
+      <c r="U76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Pago Link")</f>
+        <v>Pago Link</v>
+      </c>
+      <c r="V76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="W76" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
+        <v>375</v>
+      </c>
       <c r="X76" s="1"/>
       <c r="Y76" s="1"/>
-      <c r="Z76" s="1"/>
-      <c r="AA76" s="1"/>
+      <c r="Z76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
+        <v>PAGO FRACCIONADO</v>
+      </c>
+      <c r="AA76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB76" s="1"/>
-      <c r="AC76" s="1"/>
-      <c r="AD76" s="1"/>
-      <c r="AE76" s="1"/>
-      <c r="AF76" s="1"/>
-      <c r="AG76" s="1"/>
-      <c r="AH76" s="1"/>
-      <c r="AI76" s="1"/>
+      <c r="AC76" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD76" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE76" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
+      </c>
+      <c r="AF76" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
+      </c>
+      <c r="AG76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="AJ76" s="1"/>
-      <c r="AK76" s="1"/>
-      <c r="AL76" s="1"/>
+      <c r="AK76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
+        <v>Más de 15 kms</v>
+      </c>
+      <c r="AL76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"08 901 a 1,299")</f>
+        <v>08 901 a 1,299</v>
+      </c>
       <c r="AM76" s="1"/>
-      <c r="AN76" s="1"/>
+      <c r="AN76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="AO76" s="1"/>
-      <c r="AP76" s="1"/>
-      <c r="AQ76" s="1"/>
-      <c r="AR76" s="1"/>
-      <c r="AS76" s="1"/>
-      <c r="AT76" s="1"/>
-      <c r="AU76" s="1"/>
-      <c r="AV76" s="1"/>
-      <c r="AW76" s="1"/>
-      <c r="AX76" s="1"/>
-      <c r="AY76" s="1"/>
-      <c r="AZ76" s="1"/>
-      <c r="BA76" s="1"/>
-      <c r="BB76" s="1"/>
-      <c r="BC76" s="1"/>
-      <c r="BD76" s="1"/>
-      <c r="BE76" s="1"/>
+      <c r="AP76" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ76" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR76" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45801.0)</f>
+        <v>45801</v>
+      </c>
+      <c r="AS76" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT76" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.0)</f>
+        <v>7</v>
+      </c>
+      <c r="AV76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FORMULARIO")</f>
+        <v>FORMULARIO</v>
+      </c>
+      <c r="AX76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NO SUFICIENCIA")</f>
+        <v>NO SUFICIENCIA</v>
+      </c>
+      <c r="AY76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Rosa Ugarte")</f>
+        <v>Rosa Ugarte</v>
+      </c>
+      <c r="BA76" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
+      <c r="BB76" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
+      </c>
+      <c r="BC76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BF76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B77" s="1"/>
+      <c r="A77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),76.0)</f>
+        <v>76</v>
+      </c>
+      <c r="B77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3053351.0)</f>
+        <v>3053351</v>
+      </c>
       <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
+      <c r="D77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SHIRLEI LISET ")</f>
+        <v>SHIRLEI LISET </v>
+      </c>
+      <c r="E77" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AREVALO DIAZ")</f>
+        <v>AREVALO DIAZ</v>
+      </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-      <c r="N77" s="1"/>
-      <c r="O77" s="1"/>
-      <c r="P77" s="1"/>
-      <c r="Q77" s="1"/>
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1"/>
-      <c r="W77" s="1"/>
-      <c r="X77" s="1"/>
-      <c r="Y77" s="1"/>
-      <c r="Z77" s="1"/>
-      <c r="AA77" s="1"/>
+      <c r="I77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
+        <v>Comunicación Audiovisual y Cine</v>
+      </c>
+      <c r="J77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicaciones")</f>
+        <v>Comunicaciones</v>
+      </c>
+      <c r="K77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Ordinaria")</f>
+        <v>Admisión Ordinaria</v>
+      </c>
+      <c r="M77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NUEVO")</f>
+        <v>NUEVO</v>
+      </c>
+      <c r="P77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEBASTIAN")</f>
+        <v>SEBASTIAN</v>
+      </c>
+      <c r="T77" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45808.0)</f>
+        <v>45808</v>
+      </c>
+      <c r="U77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W77" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y77" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45808.0)</f>
+        <v>45808</v>
+      </c>
+      <c r="Z77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB77" s="1"/>
-      <c r="AC77" s="1"/>
-      <c r="AD77" s="1"/>
-      <c r="AE77" s="1"/>
-      <c r="AF77" s="1"/>
-      <c r="AG77" s="1"/>
-      <c r="AH77" s="1"/>
-      <c r="AI77" s="1"/>
+      <c r="AC77" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),50.0)</f>
+        <v>50</v>
+      </c>
+      <c r="AD77" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),95.0)</f>
+        <v>95</v>
+      </c>
+      <c r="AE77" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
+        <v>1200</v>
+      </c>
+      <c r="AF77" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
+        <v>1200</v>
+      </c>
+      <c r="AG77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="AJ77" s="1"/>
-      <c r="AK77" s="1"/>
-      <c r="AL77" s="1"/>
+      <c r="AK77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
+        <v>Más de 15 kms</v>
+      </c>
+      <c r="AL77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01 Nacional")</f>
+        <v>01 Nacional</v>
+      </c>
       <c r="AM77" s="1"/>
-      <c r="AN77" s="1"/>
+      <c r="AN77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
       <c r="AO77" s="1"/>
-      <c r="AP77" s="1"/>
-      <c r="AQ77" s="1"/>
-      <c r="AR77" s="1"/>
-      <c r="AS77" s="1"/>
-      <c r="AT77" s="1"/>
-      <c r="AU77" s="1"/>
-      <c r="AV77" s="1"/>
-      <c r="AW77" s="1"/>
-      <c r="AX77" s="1"/>
-      <c r="AY77" s="1"/>
-      <c r="AZ77" s="1"/>
-      <c r="BA77" s="1"/>
-      <c r="BB77" s="1"/>
-      <c r="BC77" s="1"/>
-      <c r="BD77" s="1"/>
-      <c r="BE77" s="1"/>
+      <c r="AP77" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AQ77" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AR77" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45782.0)</f>
+        <v>45782</v>
+      </c>
+      <c r="AS77" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
+        <v>45778</v>
+      </c>
+      <c r="AT77" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45775.0)</f>
+        <v>45775</v>
+      </c>
+      <c r="AU77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),26.0)</f>
+        <v>26</v>
+      </c>
+      <c r="AV77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEARCH MARCA")</f>
+        <v>SEARCH MARCA</v>
+      </c>
+      <c r="AY77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Andrea Araujo Antara")</f>
+        <v>Andrea Araujo Antara</v>
+      </c>
+      <c r="BA77" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB77" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
+        <v>1200</v>
+      </c>
+      <c r="BC77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BF77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>

--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -17113,7 +17113,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
       </c>
-      <c r="AO74" s="1"/>
+      <c r="AO74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2023.0)</f>
+        <v>2023</v>
+      </c>
       <c r="AP74" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
         <v>45778</v>
@@ -17192,7 +17195,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),181466.0)</f>
         <v>181466</v>
       </c>
-      <c r="C75" s="1"/>
+      <c r="C75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000026016")</f>
+        <v>0000026016</v>
+      </c>
       <c r="D75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MERY ELIZABETH")</f>
         <v>MERY ELIZABETH</v>
@@ -17201,9 +17207,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CANTO GALICIA")</f>
         <v>CANTO GALICIA</v>
       </c>
-      <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-      <c r="H75" s="1"/>
+      <c r="F75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6914091E7)</f>
+        <v>46914091</v>
+      </c>
+      <c r="G75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.74712397E8)</f>
+        <v>974712397</v>
+      </c>
+      <c r="H75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"mcantogalicia@gmail.com")</f>
+        <v>mcantogalicia@gmail.com</v>
+      </c>
       <c r="I75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño Gráfico Publicitario")</f>
         <v>Diseño Gráfico Publicitario</v>
@@ -17309,7 +17324,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="AJ75" s="1"/>
+      <c r="AJ75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1072727.0)</f>
+        <v>1072727</v>
+      </c>
       <c r="AK75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
         <v>10 kms a 15 kms</v>
@@ -17318,12 +17336,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01 Nacional")</f>
         <v>01 Nacional</v>
       </c>
-      <c r="AM75" s="1"/>
+      <c r="AM75" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SISE")</f>
+        <v>SISE</v>
+      </c>
       <c r="AN75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
       </c>
-      <c r="AO75" s="1"/>
+      <c r="AO75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2007.0)</f>
+        <v>2007</v>
+      </c>
       <c r="AP75" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
         <v>45778</v>
@@ -17402,7 +17426,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5221256.0)</f>
         <v>5221256</v>
       </c>
-      <c r="C76" s="1"/>
+      <c r="C76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"2013001836")</f>
+        <v>2013001836</v>
+      </c>
       <c r="D76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"HANS ANTONIO")</f>
         <v>HANS ANTONIO</v>
@@ -17411,9 +17438,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"THOL HUAMAN")</f>
         <v>THOL HUAMAN</v>
       </c>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
+      <c r="F76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.709832E7)</f>
+        <v>47098320</v>
+      </c>
+      <c r="G76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.52870667E8)</f>
+        <v>952870667</v>
+      </c>
+      <c r="H76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Thol.Hans@gmail.com")</f>
+        <v>Thol.Hans@gmail.com</v>
+      </c>
       <c r="I76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
         <v>Administración y Marketing</v>
@@ -17513,7 +17549,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="AJ76" s="1"/>
+      <c r="AJ76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1234384.0)</f>
+        <v>1234384</v>
+      </c>
       <c r="AK76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
         <v>Más de 15 kms</v>
@@ -17522,12 +17561,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"08 901 a 1,299")</f>
         <v>08 901 a 1,299</v>
       </c>
-      <c r="AM76" s="1"/>
+      <c r="AM76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AN76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="AO76" s="1"/>
+      <c r="AO76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2014.0)</f>
+        <v>2014</v>
+      </c>
       <c r="AP76" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
         <v>45778</v>
@@ -17606,7 +17651,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3053351.0)</f>
         <v>3053351</v>
       </c>
-      <c r="C77" s="1"/>
+      <c r="C77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000427542")</f>
+        <v>0000427542</v>
+      </c>
       <c r="D77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SHIRLEI LISET ")</f>
         <v>SHIRLEI LISET </v>
@@ -17615,9 +17663,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AREVALO DIAZ")</f>
         <v>AREVALO DIAZ</v>
       </c>
-      <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
+      <c r="F77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.1905873E7)</f>
+        <v>71905873</v>
+      </c>
+      <c r="G77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.02396153E8)</f>
+        <v>902396153</v>
+      </c>
+      <c r="H77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Shirleyadiaz03@gmail.com")</f>
+        <v>Shirleyadiaz03@gmail.com</v>
+      </c>
       <c r="I77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Comunicación Audiovisual y Cine")</f>
         <v>Comunicación Audiovisual y Cine</v>
@@ -17723,7 +17780,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="AJ77" s="1"/>
+      <c r="AJ77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),583088.0)</f>
+        <v>583088</v>
+      </c>
       <c r="AK77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Más de 15 kms")</f>
         <v>Más de 15 kms</v>
@@ -17732,12 +17792,18 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01 Nacional")</f>
         <v>01 Nacional</v>
       </c>
-      <c r="AM77" s="1"/>
+      <c r="AM77" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
       <c r="AN77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
-      <c r="AO77" s="1"/>
+      <c r="AO77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2023.0)</f>
+        <v>2023</v>
+      </c>
       <c r="AP77" s="3">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45778.0)</f>
         <v>45778</v>

--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -498,10 +498,14 @@
         <v>CURSO A NIVELAR</v>
       </c>
       <c r="BE1" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TIENE CREDENCIALES")</f>
+        <v>TIENE CREDENCIALES</v>
+      </c>
+      <c r="BF1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CONFIRMADO INICIA UCAL")</f>
         <v>CONFIRMADO INICIA UCAL</v>
       </c>
-      <c r="BF1" s="1" t="str">
+      <c r="BG1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Respuestas NEE")</f>
         <v>Respuestas NEE</v>
       </c>
@@ -726,10 +730,14 @@
         <v> -</v>
       </c>
       <c r="BE2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF2" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF2" s="1" t="str">
+      <c r="BG2" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -957,10 +965,14 @@
         <v> -</v>
       </c>
       <c r="BE3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF3" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF3" s="1" t="str">
+      <c r="BG3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1188,10 +1200,14 @@
         <v> -</v>
       </c>
       <c r="BE4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF4" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF4" s="1" t="str">
+      <c r="BG4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1416,10 +1432,14 @@
         <v> -</v>
       </c>
       <c r="BE5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF5" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF5" s="1" t="str">
+      <c r="BG5" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1644,10 +1664,14 @@
         <v> -</v>
       </c>
       <c r="BE6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF6" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF6" s="1" t="str">
+      <c r="BG6" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -1866,10 +1890,14 @@
         <v> -</v>
       </c>
       <c r="BE7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF7" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF7" s="1" t="str">
+      <c r="BG7" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2097,10 +2125,14 @@
         <v> -</v>
       </c>
       <c r="BE8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF8" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF8" s="1" t="str">
+      <c r="BG8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2325,10 +2357,14 @@
         <v> -</v>
       </c>
       <c r="BE9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF9" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF9" s="1" t="str">
+      <c r="BG9" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2553,10 +2589,14 @@
         <v> -</v>
       </c>
       <c r="BE10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF10" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF10" s="1" t="str">
+      <c r="BG10" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -2784,10 +2824,14 @@
         <v> -</v>
       </c>
       <c r="BE11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF11" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF11" s="1" t="str">
+      <c r="BG11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3015,10 +3059,14 @@
         <v> -</v>
       </c>
       <c r="BE12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF12" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF12" s="1" t="str">
+      <c r="BG12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3246,10 +3294,14 @@
         <v> -</v>
       </c>
       <c r="BE13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF13" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF13" s="1" t="str">
+      <c r="BG13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3474,10 +3526,14 @@
         <v> -</v>
       </c>
       <c r="BE14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF14" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF14" s="1" t="str">
+      <c r="BG14" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3702,10 +3758,14 @@
         <v> -</v>
       </c>
       <c r="BE15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF15" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF15" s="1" t="str">
+      <c r="BG15" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -3927,10 +3987,14 @@
         <v> -</v>
       </c>
       <c r="BE16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF16" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF16" s="1" t="str">
+      <c r="BG16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4155,10 +4219,14 @@
         <v> -</v>
       </c>
       <c r="BE17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF17" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF17" s="1" t="str">
+      <c r="BG17" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4383,10 +4451,14 @@
         <v> -</v>
       </c>
       <c r="BE18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF18" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF18" s="1" t="str">
+      <c r="BG18" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4605,10 +4677,14 @@
         <v> -</v>
       </c>
       <c r="BE19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF19" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF19" s="1" t="str">
+      <c r="BG19" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -4836,10 +4912,14 @@
         <v> -</v>
       </c>
       <c r="BE20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF20" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF20" s="1" t="str">
+      <c r="BG20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5067,10 +5147,14 @@
         <v> -</v>
       </c>
       <c r="BE21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF21" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF21" s="1" t="str">
+      <c r="BG21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5289,10 +5373,14 @@
         <v> -</v>
       </c>
       <c r="BE22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF22" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF22" s="1" t="str">
+      <c r="BG22" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5517,10 +5605,14 @@
         <v> -</v>
       </c>
       <c r="BE23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF23" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF23" s="1" t="str">
+      <c r="BG23" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5745,10 +5837,14 @@
         <v> -</v>
       </c>
       <c r="BE24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF24" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF24" s="1" t="str">
+      <c r="BG24" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -5970,10 +6066,14 @@
         <v> -</v>
       </c>
       <c r="BE25" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF25" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF25" s="1" t="str">
+      <c r="BG25" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6198,10 +6298,14 @@
         <v> -</v>
       </c>
       <c r="BE26" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF26" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF26" s="1" t="str">
+      <c r="BG26" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6423,10 +6527,14 @@
         <v>Matemáticas</v>
       </c>
       <c r="BE27" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF27" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF27" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG27" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6654,10 +6762,14 @@
         <v> -</v>
       </c>
       <c r="BE28" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF28" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF28" s="1" t="str">
+      <c r="BG28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -6888,7 +7000,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF29" s="1" t="str">
+      <c r="BF29" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG29" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7116,10 +7232,14 @@
         <v> -</v>
       </c>
       <c r="BE30" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF30" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF30" s="1" t="str">
+      <c r="BG30" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7344,10 +7464,14 @@
         <v> -</v>
       </c>
       <c r="BE31" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF31" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF31" s="1" t="str">
+      <c r="BG31" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7578,7 +7702,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF32" s="1" t="str">
+      <c r="BF32" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG32" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -7806,10 +7934,14 @@
         <v>Ninguno</v>
       </c>
       <c r="BE33" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF33" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF33" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG33" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8037,10 +8169,14 @@
         <v> -</v>
       </c>
       <c r="BE34" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF34" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF34" s="1" t="str">
+      <c r="BG34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8268,10 +8404,14 @@
         <v> -</v>
       </c>
       <c r="BE35" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF35" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF35" s="1" t="str">
+      <c r="BG35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8493,10 +8633,14 @@
         <v>Matemáticas y Redaccion</v>
       </c>
       <c r="BE36" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF36" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF36" s="1" t="str">
+      <c r="BG36" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8727,7 +8871,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF37" s="1" t="str">
+      <c r="BF37" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG37" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -8952,10 +9100,14 @@
         <v> -</v>
       </c>
       <c r="BE38" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF38" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF38" s="1" t="str">
+      <c r="BG38" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9186,7 +9338,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF39" s="1" t="str">
+      <c r="BF39" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG39" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9417,7 +9573,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF40" s="1" t="str">
+      <c r="BF40" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG40" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9648,7 +9808,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF41" s="1" t="str">
+      <c r="BF41" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG41" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -9879,7 +10043,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF42" s="1" t="str">
+      <c r="BF42" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG42" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10101,10 +10269,14 @@
         <v>Redaccion</v>
       </c>
       <c r="BE43" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF43" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF43" s="1" t="str">
+      <c r="BG43" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10326,10 +10498,14 @@
         <v> -</v>
       </c>
       <c r="BE44" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF44" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF44" s="1" t="str">
+      <c r="BG44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10557,10 +10733,14 @@
         <v> -</v>
       </c>
       <c r="BE45" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF45" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF45" s="1" t="str">
+      <c r="BG45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -10788,10 +10968,14 @@
         <v>Matemáticas y Redaccion</v>
       </c>
       <c r="BE46" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF46" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF46" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG46" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11019,10 +11203,14 @@
         <v> -</v>
       </c>
       <c r="BE47" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF47" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF47" s="1" t="str">
+      <c r="BG47" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11241,10 +11429,14 @@
         <v> -</v>
       </c>
       <c r="BE48" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF48" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF48" s="1" t="str">
+      <c r="BG48" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11472,10 +11664,14 @@
         <v> -</v>
       </c>
       <c r="BE49" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF49" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF49" s="1" t="str">
+      <c r="BG49" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11700,7 +11896,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF50" s="1" t="str">
+      <c r="BF50" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG50" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -11928,10 +12128,14 @@
         <v>Redaccion</v>
       </c>
       <c r="BE51" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF51" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF51" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG51" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12159,10 +12363,14 @@
         <v>Matemáticas y Redaccion</v>
       </c>
       <c r="BE52" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF52" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF52" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG52" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12384,10 +12592,14 @@
         <v>Matemáticas y Redaccion</v>
       </c>
       <c r="BE53" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF53" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF53" s="1" t="str">
+      <c r="BG53" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12426,8 +12638,8 @@
         <v>tsajamivega@gmail.com</v>
       </c>
       <c r="I54" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
-        <v>Administración y Marketing</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
+        <v>Administración y Marketing</v>
       </c>
       <c r="J54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
@@ -12615,10 +12827,14 @@
         <v> -</v>
       </c>
       <c r="BE54" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF54" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF54" s="1" t="str">
+      <c r="BG54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -12657,8 +12873,8 @@
         <v>gabrielac.t120708@gmail.com</v>
       </c>
       <c r="I55" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
-        <v>Administración y Marketing</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
+        <v>Administración y Marketing</v>
       </c>
       <c r="J55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
@@ -12846,10 +13062,14 @@
         <v>Redaccion</v>
       </c>
       <c r="BE55" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF55" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF55" s="1" t="str">
+      <c r="BG55" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13077,10 +13297,14 @@
         <v> -</v>
       </c>
       <c r="BE56" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF56" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF56" s="1" t="str">
+      <c r="BG56" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13305,10 +13529,14 @@
         <v> -</v>
       </c>
       <c r="BE57" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF57" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF57" s="1" t="str">
+      <c r="BG57" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13539,7 +13767,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF58" s="1" t="str">
+      <c r="BF58" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG58" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13770,7 +14002,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
-      <c r="BF59" s="1" t="str">
+      <c r="BF59" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BG59" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -13995,10 +14231,14 @@
         <v> -</v>
       </c>
       <c r="BE60" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF60" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF60" s="1" t="str">
+      <c r="BG60" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14220,7 +14460,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF61" s="1" t="str">
+      <c r="BF61" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG61" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14445,10 +14689,14 @@
         <v> -</v>
       </c>
       <c r="BE62" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF62" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF62" s="1" t="str">
+      <c r="BG62" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14676,10 +14924,14 @@
         <v> -</v>
       </c>
       <c r="BE63" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF63" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF63" s="1" t="str">
+      <c r="BG63" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -14901,7 +15153,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF64" s="1" t="str">
+      <c r="BF64" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG64" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15123,10 +15379,14 @@
         <v> -</v>
       </c>
       <c r="BE65" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF65" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF65" s="1" t="str">
+      <c r="BG65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15345,10 +15605,14 @@
         <v> -</v>
       </c>
       <c r="BE66" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF66" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF66" s="1" t="str">
+      <c r="BG66" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15573,10 +15837,14 @@
         <v> -</v>
       </c>
       <c r="BE67" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF67" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF67" s="1" t="str">
+      <c r="BG67" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -15804,10 +16072,14 @@
         <v> -</v>
       </c>
       <c r="BE68" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF68" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF68" s="1" t="str">
+      <c r="BG68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16035,10 +16307,14 @@
         <v> -</v>
       </c>
       <c r="BE69" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF69" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF69" s="1" t="str">
+      <c r="BG69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16266,10 +16542,14 @@
         <v> -</v>
       </c>
       <c r="BE70" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF70" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF70" s="1" t="str">
+      <c r="BG70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16494,10 +16774,14 @@
         <v> -</v>
       </c>
       <c r="BE71" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF71" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF71" s="1" t="str">
+      <c r="BG71" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16722,10 +17006,14 @@
         <v> -</v>
       </c>
       <c r="BE72" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF72" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF72" s="1" t="str">
+      <c r="BG72" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -16950,10 +17238,14 @@
         <v> -</v>
       </c>
       <c r="BE73" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF73" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF73" s="1" t="str">
+      <c r="BG73" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17178,10 +17470,14 @@
         <v> -</v>
       </c>
       <c r="BE74" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF74" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF74" s="1" t="str">
+      <c r="BG74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17400,19 +17696,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
         <v>850</v>
       </c>
-      <c r="BC75" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC75" s="1"/>
       <c r="BD75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
       </c>
       <c r="BE75" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF75" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF75" s="1" t="str">
+      <c r="BG75" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17451,8 +17748,8 @@
         <v>Thol.Hans@gmail.com</v>
       </c>
       <c r="I76" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
-        <v>Administración y Marketing</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Marketing")</f>
+        <v>Administración y Marketing</v>
       </c>
       <c r="J76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
@@ -17637,7 +17934,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF76" s="1" t="str">
+      <c r="BF76" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BG76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17865,10 +18166,14 @@
         <v> -</v>
       </c>
       <c r="BE77" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BF77" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="BF77" s="1" t="str">
+      <c r="BG77" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -17934,7 +18239,8 @@
       <c r="BC78" s="1"/>
       <c r="BD78" s="1"/>
       <c r="BE78" s="1"/>
-      <c r="BF78" s="1" t="str">
+      <c r="BF78" s="1"/>
+      <c r="BG78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18000,7 +18306,8 @@
       <c r="BC79" s="1"/>
       <c r="BD79" s="1"/>
       <c r="BE79" s="1"/>
-      <c r="BF79" s="1" t="str">
+      <c r="BF79" s="1"/>
+      <c r="BG79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18066,7 +18373,8 @@
       <c r="BC80" s="1"/>
       <c r="BD80" s="1"/>
       <c r="BE80" s="1"/>
-      <c r="BF80" s="1" t="str">
+      <c r="BF80" s="1"/>
+      <c r="BG80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18132,7 +18440,8 @@
       <c r="BC81" s="1"/>
       <c r="BD81" s="1"/>
       <c r="BE81" s="1"/>
-      <c r="BF81" s="1" t="str">
+      <c r="BF81" s="1"/>
+      <c r="BG81" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18198,7 +18507,8 @@
       <c r="BC82" s="1"/>
       <c r="BD82" s="1"/>
       <c r="BE82" s="1"/>
-      <c r="BF82" s="1" t="str">
+      <c r="BF82" s="1"/>
+      <c r="BG82" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18264,7 +18574,8 @@
       <c r="BC83" s="1"/>
       <c r="BD83" s="1"/>
       <c r="BE83" s="1"/>
-      <c r="BF83" s="1" t="str">
+      <c r="BF83" s="1"/>
+      <c r="BG83" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18330,7 +18641,8 @@
       <c r="BC84" s="1"/>
       <c r="BD84" s="1"/>
       <c r="BE84" s="1"/>
-      <c r="BF84" s="1" t="str">
+      <c r="BF84" s="1"/>
+      <c r="BG84" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18396,7 +18708,8 @@
       <c r="BC85" s="1"/>
       <c r="BD85" s="1"/>
       <c r="BE85" s="1"/>
-      <c r="BF85" s="1" t="str">
+      <c r="BF85" s="1"/>
+      <c r="BG85" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18462,7 +18775,8 @@
       <c r="BC86" s="1"/>
       <c r="BD86" s="1"/>
       <c r="BE86" s="1"/>
-      <c r="BF86" s="1" t="str">
+      <c r="BF86" s="1"/>
+      <c r="BG86" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18528,7 +18842,8 @@
       <c r="BC87" s="1"/>
       <c r="BD87" s="1"/>
       <c r="BE87" s="1"/>
-      <c r="BF87" s="1" t="str">
+      <c r="BF87" s="1"/>
+      <c r="BG87" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18594,7 +18909,8 @@
       <c r="BC88" s="1"/>
       <c r="BD88" s="1"/>
       <c r="BE88" s="1"/>
-      <c r="BF88" s="1" t="str">
+      <c r="BF88" s="1"/>
+      <c r="BG88" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18660,7 +18976,8 @@
       <c r="BC89" s="1"/>
       <c r="BD89" s="1"/>
       <c r="BE89" s="1"/>
-      <c r="BF89" s="1" t="str">
+      <c r="BF89" s="1"/>
+      <c r="BG89" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18726,7 +19043,8 @@
       <c r="BC90" s="1"/>
       <c r="BD90" s="1"/>
       <c r="BE90" s="1"/>
-      <c r="BF90" s="1" t="str">
+      <c r="BF90" s="1"/>
+      <c r="BG90" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18792,7 +19110,8 @@
       <c r="BC91" s="1"/>
       <c r="BD91" s="1"/>
       <c r="BE91" s="1"/>
-      <c r="BF91" s="1" t="str">
+      <c r="BF91" s="1"/>
+      <c r="BG91" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18858,7 +19177,8 @@
       <c r="BC92" s="1"/>
       <c r="BD92" s="1"/>
       <c r="BE92" s="1"/>
-      <c r="BF92" s="1" t="str">
+      <c r="BF92" s="1"/>
+      <c r="BG92" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18924,7 +19244,8 @@
       <c r="BC93" s="1"/>
       <c r="BD93" s="1"/>
       <c r="BE93" s="1"/>
-      <c r="BF93" s="1" t="str">
+      <c r="BF93" s="1"/>
+      <c r="BG93" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -18990,7 +19311,8 @@
       <c r="BC94" s="1"/>
       <c r="BD94" s="1"/>
       <c r="BE94" s="1"/>
-      <c r="BF94" s="1" t="str">
+      <c r="BF94" s="1"/>
+      <c r="BG94" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19056,7 +19378,8 @@
       <c r="BC95" s="1"/>
       <c r="BD95" s="1"/>
       <c r="BE95" s="1"/>
-      <c r="BF95" s="1" t="str">
+      <c r="BF95" s="1"/>
+      <c r="BG95" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19122,7 +19445,8 @@
       <c r="BC96" s="1"/>
       <c r="BD96" s="1"/>
       <c r="BE96" s="1"/>
-      <c r="BF96" s="1" t="str">
+      <c r="BF96" s="1"/>
+      <c r="BG96" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19188,7 +19512,8 @@
       <c r="BC97" s="1"/>
       <c r="BD97" s="1"/>
       <c r="BE97" s="1"/>
-      <c r="BF97" s="1" t="str">
+      <c r="BF97" s="1"/>
+      <c r="BG97" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19254,7 +19579,8 @@
       <c r="BC98" s="1"/>
       <c r="BD98" s="1"/>
       <c r="BE98" s="1"/>
-      <c r="BF98" s="1" t="str">
+      <c r="BF98" s="1"/>
+      <c r="BG98" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19320,7 +19646,8 @@
       <c r="BC99" s="1"/>
       <c r="BD99" s="1"/>
       <c r="BE99" s="1"/>
-      <c r="BF99" s="1" t="str">
+      <c r="BF99" s="1"/>
+      <c r="BG99" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19386,7 +19713,8 @@
       <c r="BC100" s="1"/>
       <c r="BD100" s="1"/>
       <c r="BE100" s="1"/>
-      <c r="BF100" s="1" t="str">
+      <c r="BF100" s="1"/>
+      <c r="BG100" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19452,7 +19780,8 @@
       <c r="BC101" s="1"/>
       <c r="BD101" s="1"/>
       <c r="BE101" s="1"/>
-      <c r="BF101" s="1" t="str">
+      <c r="BF101" s="1"/>
+      <c r="BG101" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19518,7 +19847,8 @@
       <c r="BC102" s="1"/>
       <c r="BD102" s="1"/>
       <c r="BE102" s="1"/>
-      <c r="BF102" s="1" t="str">
+      <c r="BF102" s="1"/>
+      <c r="BG102" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19584,7 +19914,8 @@
       <c r="BC103" s="1"/>
       <c r="BD103" s="1"/>
       <c r="BE103" s="1"/>
-      <c r="BF103" s="1" t="str">
+      <c r="BF103" s="1"/>
+      <c r="BG103" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19650,7 +19981,8 @@
       <c r="BC104" s="1"/>
       <c r="BD104" s="1"/>
       <c r="BE104" s="1"/>
-      <c r="BF104" s="1" t="str">
+      <c r="BF104" s="1"/>
+      <c r="BG104" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19716,7 +20048,8 @@
       <c r="BC105" s="1"/>
       <c r="BD105" s="1"/>
       <c r="BE105" s="1"/>
-      <c r="BF105" s="1" t="str">
+      <c r="BF105" s="1"/>
+      <c r="BG105" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19782,7 +20115,8 @@
       <c r="BC106" s="1"/>
       <c r="BD106" s="1"/>
       <c r="BE106" s="1"/>
-      <c r="BF106" s="1" t="str">
+      <c r="BF106" s="1"/>
+      <c r="BG106" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19848,7 +20182,8 @@
       <c r="BC107" s="1"/>
       <c r="BD107" s="1"/>
       <c r="BE107" s="1"/>
-      <c r="BF107" s="1" t="str">
+      <c r="BF107" s="1"/>
+      <c r="BG107" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19914,7 +20249,8 @@
       <c r="BC108" s="1"/>
       <c r="BD108" s="1"/>
       <c r="BE108" s="1"/>
-      <c r="BF108" s="1" t="str">
+      <c r="BF108" s="1"/>
+      <c r="BG108" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -19980,7 +20316,8 @@
       <c r="BC109" s="1"/>
       <c r="BD109" s="1"/>
       <c r="BE109" s="1"/>
-      <c r="BF109" s="1" t="str">
+      <c r="BF109" s="1"/>
+      <c r="BG109" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20046,7 +20383,8 @@
       <c r="BC110" s="1"/>
       <c r="BD110" s="1"/>
       <c r="BE110" s="1"/>
-      <c r="BF110" s="1" t="str">
+      <c r="BF110" s="1"/>
+      <c r="BG110" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20112,7 +20450,8 @@
       <c r="BC111" s="1"/>
       <c r="BD111" s="1"/>
       <c r="BE111" s="1"/>
-      <c r="BF111" s="1" t="str">
+      <c r="BF111" s="1"/>
+      <c r="BG111" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20178,7 +20517,8 @@
       <c r="BC112" s="1"/>
       <c r="BD112" s="1"/>
       <c r="BE112" s="1"/>
-      <c r="BF112" s="1" t="str">
+      <c r="BF112" s="1"/>
+      <c r="BG112" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20244,7 +20584,8 @@
       <c r="BC113" s="1"/>
       <c r="BD113" s="1"/>
       <c r="BE113" s="1"/>
-      <c r="BF113" s="1" t="str">
+      <c r="BF113" s="1"/>
+      <c r="BG113" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20310,7 +20651,8 @@
       <c r="BC114" s="1"/>
       <c r="BD114" s="1"/>
       <c r="BE114" s="1"/>
-      <c r="BF114" s="1" t="str">
+      <c r="BF114" s="1"/>
+      <c r="BG114" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20376,7 +20718,8 @@
       <c r="BC115" s="1"/>
       <c r="BD115" s="1"/>
       <c r="BE115" s="1"/>
-      <c r="BF115" s="1" t="str">
+      <c r="BF115" s="1"/>
+      <c r="BG115" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20442,7 +20785,8 @@
       <c r="BC116" s="1"/>
       <c r="BD116" s="1"/>
       <c r="BE116" s="1"/>
-      <c r="BF116" s="1" t="str">
+      <c r="BF116" s="1"/>
+      <c r="BG116" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20508,7 +20852,8 @@
       <c r="BC117" s="1"/>
       <c r="BD117" s="1"/>
       <c r="BE117" s="1"/>
-      <c r="BF117" s="1" t="str">
+      <c r="BF117" s="1"/>
+      <c r="BG117" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20574,7 +20919,8 @@
       <c r="BC118" s="1"/>
       <c r="BD118" s="1"/>
       <c r="BE118" s="1"/>
-      <c r="BF118" s="1" t="str">
+      <c r="BF118" s="1"/>
+      <c r="BG118" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20640,7 +20986,8 @@
       <c r="BC119" s="1"/>
       <c r="BD119" s="1"/>
       <c r="BE119" s="1"/>
-      <c r="BF119" s="1" t="str">
+      <c r="BF119" s="1"/>
+      <c r="BG119" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20706,7 +21053,8 @@
       <c r="BC120" s="1"/>
       <c r="BD120" s="1"/>
       <c r="BE120" s="1"/>
-      <c r="BF120" s="1" t="str">
+      <c r="BF120" s="1"/>
+      <c r="BG120" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20772,7 +21120,8 @@
       <c r="BC121" s="1"/>
       <c r="BD121" s="1"/>
       <c r="BE121" s="1"/>
-      <c r="BF121" s="1" t="str">
+      <c r="BF121" s="1"/>
+      <c r="BG121" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20838,7 +21187,8 @@
       <c r="BC122" s="1"/>
       <c r="BD122" s="1"/>
       <c r="BE122" s="1"/>
-      <c r="BF122" s="1" t="str">
+      <c r="BF122" s="1"/>
+      <c r="BG122" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20904,7 +21254,8 @@
       <c r="BC123" s="1"/>
       <c r="BD123" s="1"/>
       <c r="BE123" s="1"/>
-      <c r="BF123" s="1" t="str">
+      <c r="BF123" s="1"/>
+      <c r="BG123" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -20970,7 +21321,8 @@
       <c r="BC124" s="1"/>
       <c r="BD124" s="1"/>
       <c r="BE124" s="1"/>
-      <c r="BF124" s="1" t="str">
+      <c r="BF124" s="1"/>
+      <c r="BG124" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21036,7 +21388,8 @@
       <c r="BC125" s="1"/>
       <c r="BD125" s="1"/>
       <c r="BE125" s="1"/>
-      <c r="BF125" s="1" t="str">
+      <c r="BF125" s="1"/>
+      <c r="BG125" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21102,7 +21455,8 @@
       <c r="BC126" s="1"/>
       <c r="BD126" s="1"/>
       <c r="BE126" s="1"/>
-      <c r="BF126" s="1" t="str">
+      <c r="BF126" s="1"/>
+      <c r="BG126" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21168,7 +21522,8 @@
       <c r="BC127" s="1"/>
       <c r="BD127" s="1"/>
       <c r="BE127" s="1"/>
-      <c r="BF127" s="1" t="str">
+      <c r="BF127" s="1"/>
+      <c r="BG127" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21234,7 +21589,8 @@
       <c r="BC128" s="1"/>
       <c r="BD128" s="1"/>
       <c r="BE128" s="1"/>
-      <c r="BF128" s="1" t="str">
+      <c r="BF128" s="1"/>
+      <c r="BG128" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21300,7 +21656,8 @@
       <c r="BC129" s="1"/>
       <c r="BD129" s="1"/>
       <c r="BE129" s="1"/>
-      <c r="BF129" s="1" t="str">
+      <c r="BF129" s="1"/>
+      <c r="BG129" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21366,7 +21723,8 @@
       <c r="BC130" s="1"/>
       <c r="BD130" s="1"/>
       <c r="BE130" s="1"/>
-      <c r="BF130" s="1" t="str">
+      <c r="BF130" s="1"/>
+      <c r="BG130" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21432,7 +21790,8 @@
       <c r="BC131" s="1"/>
       <c r="BD131" s="1"/>
       <c r="BE131" s="1"/>
-      <c r="BF131" s="1" t="str">
+      <c r="BF131" s="1"/>
+      <c r="BG131" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21498,7 +21857,8 @@
       <c r="BC132" s="1"/>
       <c r="BD132" s="1"/>
       <c r="BE132" s="1"/>
-      <c r="BF132" s="1" t="str">
+      <c r="BF132" s="1"/>
+      <c r="BG132" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21564,7 +21924,8 @@
       <c r="BC133" s="1"/>
       <c r="BD133" s="1"/>
       <c r="BE133" s="1"/>
-      <c r="BF133" s="1" t="str">
+      <c r="BF133" s="1"/>
+      <c r="BG133" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21630,7 +21991,8 @@
       <c r="BC134" s="1"/>
       <c r="BD134" s="1"/>
       <c r="BE134" s="1"/>
-      <c r="BF134" s="1" t="str">
+      <c r="BF134" s="1"/>
+      <c r="BG134" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21696,7 +22058,8 @@
       <c r="BC135" s="1"/>
       <c r="BD135" s="1"/>
       <c r="BE135" s="1"/>
-      <c r="BF135" s="1" t="str">
+      <c r="BF135" s="1"/>
+      <c r="BG135" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21762,7 +22125,8 @@
       <c r="BC136" s="1"/>
       <c r="BD136" s="1"/>
       <c r="BE136" s="1"/>
-      <c r="BF136" s="1" t="str">
+      <c r="BF136" s="1"/>
+      <c r="BG136" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21828,7 +22192,8 @@
       <c r="BC137" s="1"/>
       <c r="BD137" s="1"/>
       <c r="BE137" s="1"/>
-      <c r="BF137" s="1" t="str">
+      <c r="BF137" s="1"/>
+      <c r="BG137" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21894,7 +22259,8 @@
       <c r="BC138" s="1"/>
       <c r="BD138" s="1"/>
       <c r="BE138" s="1"/>
-      <c r="BF138" s="1" t="str">
+      <c r="BF138" s="1"/>
+      <c r="BG138" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -21960,7 +22326,8 @@
       <c r="BC139" s="1"/>
       <c r="BD139" s="1"/>
       <c r="BE139" s="1"/>
-      <c r="BF139" s="1" t="str">
+      <c r="BF139" s="1"/>
+      <c r="BG139" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22026,7 +22393,8 @@
       <c r="BC140" s="1"/>
       <c r="BD140" s="1"/>
       <c r="BE140" s="1"/>
-      <c r="BF140" s="1" t="str">
+      <c r="BF140" s="1"/>
+      <c r="BG140" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22092,7 +22460,8 @@
       <c r="BC141" s="1"/>
       <c r="BD141" s="1"/>
       <c r="BE141" s="1"/>
-      <c r="BF141" s="1" t="str">
+      <c r="BF141" s="1"/>
+      <c r="BG141" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22158,7 +22527,8 @@
       <c r="BC142" s="1"/>
       <c r="BD142" s="1"/>
       <c r="BE142" s="1"/>
-      <c r="BF142" s="1" t="str">
+      <c r="BF142" s="1"/>
+      <c r="BG142" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22224,7 +22594,8 @@
       <c r="BC143" s="1"/>
       <c r="BD143" s="1"/>
       <c r="BE143" s="1"/>
-      <c r="BF143" s="1" t="str">
+      <c r="BF143" s="1"/>
+      <c r="BG143" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22290,7 +22661,8 @@
       <c r="BC144" s="1"/>
       <c r="BD144" s="1"/>
       <c r="BE144" s="1"/>
-      <c r="BF144" s="1" t="str">
+      <c r="BF144" s="1"/>
+      <c r="BG144" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22356,7 +22728,8 @@
       <c r="BC145" s="1"/>
       <c r="BD145" s="1"/>
       <c r="BE145" s="1"/>
-      <c r="BF145" s="1" t="str">
+      <c r="BF145" s="1"/>
+      <c r="BG145" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22422,7 +22795,8 @@
       <c r="BC146" s="1"/>
       <c r="BD146" s="1"/>
       <c r="BE146" s="1"/>
-      <c r="BF146" s="1" t="str">
+      <c r="BF146" s="1"/>
+      <c r="BG146" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22488,7 +22862,8 @@
       <c r="BC147" s="1"/>
       <c r="BD147" s="1"/>
       <c r="BE147" s="1"/>
-      <c r="BF147" s="1" t="str">
+      <c r="BF147" s="1"/>
+      <c r="BG147" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22554,7 +22929,8 @@
       <c r="BC148" s="1"/>
       <c r="BD148" s="1"/>
       <c r="BE148" s="1"/>
-      <c r="BF148" s="1" t="str">
+      <c r="BF148" s="1"/>
+      <c r="BG148" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22620,7 +22996,8 @@
       <c r="BC149" s="1"/>
       <c r="BD149" s="1"/>
       <c r="BE149" s="1"/>
-      <c r="BF149" s="1" t="str">
+      <c r="BF149" s="1"/>
+      <c r="BG149" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22686,7 +23063,8 @@
       <c r="BC150" s="1"/>
       <c r="BD150" s="1"/>
       <c r="BE150" s="1"/>
-      <c r="BF150" s="1" t="str">
+      <c r="BF150" s="1"/>
+      <c r="BG150" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22752,7 +23130,8 @@
       <c r="BC151" s="1"/>
       <c r="BD151" s="1"/>
       <c r="BE151" s="1"/>
-      <c r="BF151" s="1" t="str">
+      <c r="BF151" s="1"/>
+      <c r="BG151" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22818,7 +23197,8 @@
       <c r="BC152" s="1"/>
       <c r="BD152" s="1"/>
       <c r="BE152" s="1"/>
-      <c r="BF152" s="1" t="str">
+      <c r="BF152" s="1"/>
+      <c r="BG152" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22884,7 +23264,8 @@
       <c r="BC153" s="1"/>
       <c r="BD153" s="1"/>
       <c r="BE153" s="1"/>
-      <c r="BF153" s="1" t="str">
+      <c r="BF153" s="1"/>
+      <c r="BG153" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -22950,7 +23331,8 @@
       <c r="BC154" s="1"/>
       <c r="BD154" s="1"/>
       <c r="BE154" s="1"/>
-      <c r="BF154" s="1" t="str">
+      <c r="BF154" s="1"/>
+      <c r="BG154" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23016,7 +23398,8 @@
       <c r="BC155" s="1"/>
       <c r="BD155" s="1"/>
       <c r="BE155" s="1"/>
-      <c r="BF155" s="1" t="str">
+      <c r="BF155" s="1"/>
+      <c r="BG155" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23082,7 +23465,8 @@
       <c r="BC156" s="1"/>
       <c r="BD156" s="1"/>
       <c r="BE156" s="1"/>
-      <c r="BF156" s="1" t="str">
+      <c r="BF156" s="1"/>
+      <c r="BG156" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23148,7 +23532,8 @@
       <c r="BC157" s="1"/>
       <c r="BD157" s="1"/>
       <c r="BE157" s="1"/>
-      <c r="BF157" s="1" t="str">
+      <c r="BF157" s="1"/>
+      <c r="BG157" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23214,7 +23599,8 @@
       <c r="BC158" s="1"/>
       <c r="BD158" s="1"/>
       <c r="BE158" s="1"/>
-      <c r="BF158" s="1" t="str">
+      <c r="BF158" s="1"/>
+      <c r="BG158" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23280,7 +23666,8 @@
       <c r="BC159" s="1"/>
       <c r="BD159" s="1"/>
       <c r="BE159" s="1"/>
-      <c r="BF159" s="1" t="str">
+      <c r="BF159" s="1"/>
+      <c r="BG159" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23346,7 +23733,8 @@
       <c r="BC160" s="1"/>
       <c r="BD160" s="1"/>
       <c r="BE160" s="1"/>
-      <c r="BF160" s="1" t="str">
+      <c r="BF160" s="1"/>
+      <c r="BG160" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23412,7 +23800,8 @@
       <c r="BC161" s="1"/>
       <c r="BD161" s="1"/>
       <c r="BE161" s="1"/>
-      <c r="BF161" s="1" t="str">
+      <c r="BF161" s="1"/>
+      <c r="BG161" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23478,7 +23867,8 @@
       <c r="BC162" s="1"/>
       <c r="BD162" s="1"/>
       <c r="BE162" s="1"/>
-      <c r="BF162" s="1" t="str">
+      <c r="BF162" s="1"/>
+      <c r="BG162" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23544,7 +23934,8 @@
       <c r="BC163" s="1"/>
       <c r="BD163" s="1"/>
       <c r="BE163" s="1"/>
-      <c r="BF163" s="1" t="str">
+      <c r="BF163" s="1"/>
+      <c r="BG163" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23610,7 +24001,8 @@
       <c r="BC164" s="1"/>
       <c r="BD164" s="1"/>
       <c r="BE164" s="1"/>
-      <c r="BF164" s="1" t="str">
+      <c r="BF164" s="1"/>
+      <c r="BG164" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23676,7 +24068,8 @@
       <c r="BC165" s="1"/>
       <c r="BD165" s="1"/>
       <c r="BE165" s="1"/>
-      <c r="BF165" s="1" t="str">
+      <c r="BF165" s="1"/>
+      <c r="BG165" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23742,7 +24135,8 @@
       <c r="BC166" s="1"/>
       <c r="BD166" s="1"/>
       <c r="BE166" s="1"/>
-      <c r="BF166" s="1" t="str">
+      <c r="BF166" s="1"/>
+      <c r="BG166" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23808,7 +24202,8 @@
       <c r="BC167" s="1"/>
       <c r="BD167" s="1"/>
       <c r="BE167" s="1"/>
-      <c r="BF167" s="1" t="str">
+      <c r="BF167" s="1"/>
+      <c r="BG167" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23874,7 +24269,8 @@
       <c r="BC168" s="1"/>
       <c r="BD168" s="1"/>
       <c r="BE168" s="1"/>
-      <c r="BF168" s="1" t="str">
+      <c r="BF168" s="1"/>
+      <c r="BG168" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -23940,7 +24336,8 @@
       <c r="BC169" s="1"/>
       <c r="BD169" s="1"/>
       <c r="BE169" s="1"/>
-      <c r="BF169" s="1" t="str">
+      <c r="BF169" s="1"/>
+      <c r="BG169" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24006,7 +24403,8 @@
       <c r="BC170" s="1"/>
       <c r="BD170" s="1"/>
       <c r="BE170" s="1"/>
-      <c r="BF170" s="1" t="str">
+      <c r="BF170" s="1"/>
+      <c r="BG170" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24072,7 +24470,8 @@
       <c r="BC171" s="1"/>
       <c r="BD171" s="1"/>
       <c r="BE171" s="1"/>
-      <c r="BF171" s="1" t="str">
+      <c r="BF171" s="1"/>
+      <c r="BG171" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24138,7 +24537,8 @@
       <c r="BC172" s="1"/>
       <c r="BD172" s="1"/>
       <c r="BE172" s="1"/>
-      <c r="BF172" s="1" t="str">
+      <c r="BF172" s="1"/>
+      <c r="BG172" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24204,7 +24604,8 @@
       <c r="BC173" s="1"/>
       <c r="BD173" s="1"/>
       <c r="BE173" s="1"/>
-      <c r="BF173" s="1" t="str">
+      <c r="BF173" s="1"/>
+      <c r="BG173" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24270,7 +24671,8 @@
       <c r="BC174" s="1"/>
       <c r="BD174" s="1"/>
       <c r="BE174" s="1"/>
-      <c r="BF174" s="1" t="str">
+      <c r="BF174" s="1"/>
+      <c r="BG174" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24336,7 +24738,8 @@
       <c r="BC175" s="1"/>
       <c r="BD175" s="1"/>
       <c r="BE175" s="1"/>
-      <c r="BF175" s="1" t="str">
+      <c r="BF175" s="1"/>
+      <c r="BG175" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24402,7 +24805,8 @@
       <c r="BC176" s="1"/>
       <c r="BD176" s="1"/>
       <c r="BE176" s="1"/>
-      <c r="BF176" s="1" t="str">
+      <c r="BF176" s="1"/>
+      <c r="BG176" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24468,7 +24872,8 @@
       <c r="BC177" s="1"/>
       <c r="BD177" s="1"/>
       <c r="BE177" s="1"/>
-      <c r="BF177" s="1" t="str">
+      <c r="BF177" s="1"/>
+      <c r="BG177" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24534,7 +24939,8 @@
       <c r="BC178" s="1"/>
       <c r="BD178" s="1"/>
       <c r="BE178" s="1"/>
-      <c r="BF178" s="1" t="str">
+      <c r="BF178" s="1"/>
+      <c r="BG178" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24600,7 +25006,8 @@
       <c r="BC179" s="1"/>
       <c r="BD179" s="1"/>
       <c r="BE179" s="1"/>
-      <c r="BF179" s="1" t="str">
+      <c r="BF179" s="1"/>
+      <c r="BG179" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24666,7 +25073,8 @@
       <c r="BC180" s="1"/>
       <c r="BD180" s="1"/>
       <c r="BE180" s="1"/>
-      <c r="BF180" s="1" t="str">
+      <c r="BF180" s="1"/>
+      <c r="BG180" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24732,7 +25140,8 @@
       <c r="BC181" s="1"/>
       <c r="BD181" s="1"/>
       <c r="BE181" s="1"/>
-      <c r="BF181" s="1" t="str">
+      <c r="BF181" s="1"/>
+      <c r="BG181" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24798,7 +25207,8 @@
       <c r="BC182" s="1"/>
       <c r="BD182" s="1"/>
       <c r="BE182" s="1"/>
-      <c r="BF182" s="1" t="str">
+      <c r="BF182" s="1"/>
+      <c r="BG182" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24864,7 +25274,8 @@
       <c r="BC183" s="1"/>
       <c r="BD183" s="1"/>
       <c r="BE183" s="1"/>
-      <c r="BF183" s="1" t="str">
+      <c r="BF183" s="1"/>
+      <c r="BG183" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24930,7 +25341,8 @@
       <c r="BC184" s="1"/>
       <c r="BD184" s="1"/>
       <c r="BE184" s="1"/>
-      <c r="BF184" s="1" t="str">
+      <c r="BF184" s="1"/>
+      <c r="BG184" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -24996,7 +25408,8 @@
       <c r="BC185" s="1"/>
       <c r="BD185" s="1"/>
       <c r="BE185" s="1"/>
-      <c r="BF185" s="1" t="str">
+      <c r="BF185" s="1"/>
+      <c r="BG185" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25062,7 +25475,8 @@
       <c r="BC186" s="1"/>
       <c r="BD186" s="1"/>
       <c r="BE186" s="1"/>
-      <c r="BF186" s="1" t="str">
+      <c r="BF186" s="1"/>
+      <c r="BG186" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25128,7 +25542,8 @@
       <c r="BC187" s="1"/>
       <c r="BD187" s="1"/>
       <c r="BE187" s="1"/>
-      <c r="BF187" s="1" t="str">
+      <c r="BF187" s="1"/>
+      <c r="BG187" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25194,7 +25609,8 @@
       <c r="BC188" s="1"/>
       <c r="BD188" s="1"/>
       <c r="BE188" s="1"/>
-      <c r="BF188" s="1" t="str">
+      <c r="BF188" s="1"/>
+      <c r="BG188" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25260,7 +25676,8 @@
       <c r="BC189" s="1"/>
       <c r="BD189" s="1"/>
       <c r="BE189" s="1"/>
-      <c r="BF189" s="1" t="str">
+      <c r="BF189" s="1"/>
+      <c r="BG189" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25326,7 +25743,8 @@
       <c r="BC190" s="1"/>
       <c r="BD190" s="1"/>
       <c r="BE190" s="1"/>
-      <c r="BF190" s="1" t="str">
+      <c r="BF190" s="1"/>
+      <c r="BG190" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25392,7 +25810,8 @@
       <c r="BC191" s="1"/>
       <c r="BD191" s="1"/>
       <c r="BE191" s="1"/>
-      <c r="BF191" s="1" t="str">
+      <c r="BF191" s="1"/>
+      <c r="BG191" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25458,7 +25877,8 @@
       <c r="BC192" s="1"/>
       <c r="BD192" s="1"/>
       <c r="BE192" s="1"/>
-      <c r="BF192" s="1" t="str">
+      <c r="BF192" s="1"/>
+      <c r="BG192" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25524,7 +25944,8 @@
       <c r="BC193" s="1"/>
       <c r="BD193" s="1"/>
       <c r="BE193" s="1"/>
-      <c r="BF193" s="1" t="str">
+      <c r="BF193" s="1"/>
+      <c r="BG193" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25590,7 +26011,8 @@
       <c r="BC194" s="1"/>
       <c r="BD194" s="1"/>
       <c r="BE194" s="1"/>
-      <c r="BF194" s="1" t="str">
+      <c r="BF194" s="1"/>
+      <c r="BG194" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25656,7 +26078,8 @@
       <c r="BC195" s="1"/>
       <c r="BD195" s="1"/>
       <c r="BE195" s="1"/>
-      <c r="BF195" s="1" t="str">
+      <c r="BF195" s="1"/>
+      <c r="BG195" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25722,7 +26145,8 @@
       <c r="BC196" s="1"/>
       <c r="BD196" s="1"/>
       <c r="BE196" s="1"/>
-      <c r="BF196" s="1" t="str">
+      <c r="BF196" s="1"/>
+      <c r="BG196" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25788,7 +26212,8 @@
       <c r="BC197" s="1"/>
       <c r="BD197" s="1"/>
       <c r="BE197" s="1"/>
-      <c r="BF197" s="1" t="str">
+      <c r="BF197" s="1"/>
+      <c r="BG197" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25854,7 +26279,8 @@
       <c r="BC198" s="1"/>
       <c r="BD198" s="1"/>
       <c r="BE198" s="1"/>
-      <c r="BF198" s="1" t="str">
+      <c r="BF198" s="1"/>
+      <c r="BG198" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25920,7 +26346,8 @@
       <c r="BC199" s="1"/>
       <c r="BD199" s="1"/>
       <c r="BE199" s="1"/>
-      <c r="BF199" s="1" t="str">
+      <c r="BF199" s="1"/>
+      <c r="BG199" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -25986,7 +26413,8 @@
       <c r="BC200" s="1"/>
       <c r="BD200" s="1"/>
       <c r="BE200" s="1"/>
-      <c r="BF200" s="1" t="str">
+      <c r="BF200" s="1"/>
+      <c r="BG200" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26052,7 +26480,8 @@
       <c r="BC201" s="1"/>
       <c r="BD201" s="1"/>
       <c r="BE201" s="1"/>
-      <c r="BF201" s="1" t="str">
+      <c r="BF201" s="1"/>
+      <c r="BG201" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26118,7 +26547,8 @@
       <c r="BC202" s="1"/>
       <c r="BD202" s="1"/>
       <c r="BE202" s="1"/>
-      <c r="BF202" s="1" t="str">
+      <c r="BF202" s="1"/>
+      <c r="BG202" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26184,7 +26614,8 @@
       <c r="BC203" s="1"/>
       <c r="BD203" s="1"/>
       <c r="BE203" s="1"/>
-      <c r="BF203" s="1" t="str">
+      <c r="BF203" s="1"/>
+      <c r="BG203" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26250,7 +26681,8 @@
       <c r="BC204" s="1"/>
       <c r="BD204" s="1"/>
       <c r="BE204" s="1"/>
-      <c r="BF204" s="1" t="str">
+      <c r="BF204" s="1"/>
+      <c r="BG204" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26316,7 +26748,8 @@
       <c r="BC205" s="1"/>
       <c r="BD205" s="1"/>
       <c r="BE205" s="1"/>
-      <c r="BF205" s="1" t="str">
+      <c r="BF205" s="1"/>
+      <c r="BG205" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26382,7 +26815,8 @@
       <c r="BC206" s="1"/>
       <c r="BD206" s="1"/>
       <c r="BE206" s="1"/>
-      <c r="BF206" s="1" t="str">
+      <c r="BF206" s="1"/>
+      <c r="BG206" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26448,7 +26882,8 @@
       <c r="BC207" s="1"/>
       <c r="BD207" s="1"/>
       <c r="BE207" s="1"/>
-      <c r="BF207" s="1" t="str">
+      <c r="BF207" s="1"/>
+      <c r="BG207" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26514,7 +26949,8 @@
       <c r="BC208" s="1"/>
       <c r="BD208" s="1"/>
       <c r="BE208" s="1"/>
-      <c r="BF208" s="1" t="str">
+      <c r="BF208" s="1"/>
+      <c r="BG208" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26580,7 +27016,8 @@
       <c r="BC209" s="1"/>
       <c r="BD209" s="1"/>
       <c r="BE209" s="1"/>
-      <c r="BF209" s="1" t="str">
+      <c r="BF209" s="1"/>
+      <c r="BG209" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26646,7 +27083,8 @@
       <c r="BC210" s="1"/>
       <c r="BD210" s="1"/>
       <c r="BE210" s="1"/>
-      <c r="BF210" s="1" t="str">
+      <c r="BF210" s="1"/>
+      <c r="BG210" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26712,7 +27150,8 @@
       <c r="BC211" s="1"/>
       <c r="BD211" s="1"/>
       <c r="BE211" s="1"/>
-      <c r="BF211" s="1" t="str">
+      <c r="BF211" s="1"/>
+      <c r="BG211" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26778,7 +27217,8 @@
       <c r="BC212" s="1"/>
       <c r="BD212" s="1"/>
       <c r="BE212" s="1"/>
-      <c r="BF212" s="1" t="str">
+      <c r="BF212" s="1"/>
+      <c r="BG212" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26844,7 +27284,8 @@
       <c r="BC213" s="1"/>
       <c r="BD213" s="1"/>
       <c r="BE213" s="1"/>
-      <c r="BF213" s="1" t="str">
+      <c r="BF213" s="1"/>
+      <c r="BG213" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26910,7 +27351,8 @@
       <c r="BC214" s="1"/>
       <c r="BD214" s="1"/>
       <c r="BE214" s="1"/>
-      <c r="BF214" s="1" t="str">
+      <c r="BF214" s="1"/>
+      <c r="BG214" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -26976,7 +27418,8 @@
       <c r="BC215" s="1"/>
       <c r="BD215" s="1"/>
       <c r="BE215" s="1"/>
-      <c r="BF215" s="1" t="str">
+      <c r="BF215" s="1"/>
+      <c r="BG215" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27042,7 +27485,8 @@
       <c r="BC216" s="1"/>
       <c r="BD216" s="1"/>
       <c r="BE216" s="1"/>
-      <c r="BF216" s="1" t="str">
+      <c r="BF216" s="1"/>
+      <c r="BG216" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27108,7 +27552,8 @@
       <c r="BC217" s="1"/>
       <c r="BD217" s="1"/>
       <c r="BE217" s="1"/>
-      <c r="BF217" s="1" t="str">
+      <c r="BF217" s="1"/>
+      <c r="BG217" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27174,7 +27619,8 @@
       <c r="BC218" s="1"/>
       <c r="BD218" s="1"/>
       <c r="BE218" s="1"/>
-      <c r="BF218" s="1" t="str">
+      <c r="BF218" s="1"/>
+      <c r="BG218" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27240,7 +27686,8 @@
       <c r="BC219" s="1"/>
       <c r="BD219" s="1"/>
       <c r="BE219" s="1"/>
-      <c r="BF219" s="1" t="str">
+      <c r="BF219" s="1"/>
+      <c r="BG219" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27306,7 +27753,8 @@
       <c r="BC220" s="1"/>
       <c r="BD220" s="1"/>
       <c r="BE220" s="1"/>
-      <c r="BF220" s="1" t="str">
+      <c r="BF220" s="1"/>
+      <c r="BG220" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27372,7 +27820,8 @@
       <c r="BC221" s="1"/>
       <c r="BD221" s="1"/>
       <c r="BE221" s="1"/>
-      <c r="BF221" s="1" t="str">
+      <c r="BF221" s="1"/>
+      <c r="BG221" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27438,7 +27887,8 @@
       <c r="BC222" s="1"/>
       <c r="BD222" s="1"/>
       <c r="BE222" s="1"/>
-      <c r="BF222" s="1" t="str">
+      <c r="BF222" s="1"/>
+      <c r="BG222" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27504,7 +27954,8 @@
       <c r="BC223" s="1"/>
       <c r="BD223" s="1"/>
       <c r="BE223" s="1"/>
-      <c r="BF223" s="1" t="str">
+      <c r="BF223" s="1"/>
+      <c r="BG223" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27570,7 +28021,8 @@
       <c r="BC224" s="1"/>
       <c r="BD224" s="1"/>
       <c r="BE224" s="1"/>
-      <c r="BF224" s="1" t="str">
+      <c r="BF224" s="1"/>
+      <c r="BG224" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27636,7 +28088,8 @@
       <c r="BC225" s="1"/>
       <c r="BD225" s="1"/>
       <c r="BE225" s="1"/>
-      <c r="BF225" s="1" t="str">
+      <c r="BF225" s="1"/>
+      <c r="BG225" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27702,7 +28155,8 @@
       <c r="BC226" s="1"/>
       <c r="BD226" s="1"/>
       <c r="BE226" s="1"/>
-      <c r="BF226" s="1" t="str">
+      <c r="BF226" s="1"/>
+      <c r="BG226" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27768,7 +28222,8 @@
       <c r="BC227" s="1"/>
       <c r="BD227" s="1"/>
       <c r="BE227" s="1"/>
-      <c r="BF227" s="1" t="str">
+      <c r="BF227" s="1"/>
+      <c r="BG227" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27834,7 +28289,8 @@
       <c r="BC228" s="1"/>
       <c r="BD228" s="1"/>
       <c r="BE228" s="1"/>
-      <c r="BF228" s="1" t="str">
+      <c r="BF228" s="1"/>
+      <c r="BG228" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27900,7 +28356,8 @@
       <c r="BC229" s="1"/>
       <c r="BD229" s="1"/>
       <c r="BE229" s="1"/>
-      <c r="BF229" s="1" t="str">
+      <c r="BF229" s="1"/>
+      <c r="BG229" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -27966,7 +28423,8 @@
       <c r="BC230" s="1"/>
       <c r="BD230" s="1"/>
       <c r="BE230" s="1"/>
-      <c r="BF230" s="1" t="str">
+      <c r="BF230" s="1"/>
+      <c r="BG230" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28032,7 +28490,8 @@
       <c r="BC231" s="1"/>
       <c r="BD231" s="1"/>
       <c r="BE231" s="1"/>
-      <c r="BF231" s="1" t="str">
+      <c r="BF231" s="1"/>
+      <c r="BG231" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28098,7 +28557,8 @@
       <c r="BC232" s="1"/>
       <c r="BD232" s="1"/>
       <c r="BE232" s="1"/>
-      <c r="BF232" s="1" t="str">
+      <c r="BF232" s="1"/>
+      <c r="BG232" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28164,7 +28624,8 @@
       <c r="BC233" s="1"/>
       <c r="BD233" s="1"/>
       <c r="BE233" s="1"/>
-      <c r="BF233" s="1" t="str">
+      <c r="BF233" s="1"/>
+      <c r="BG233" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28230,7 +28691,8 @@
       <c r="BC234" s="1"/>
       <c r="BD234" s="1"/>
       <c r="BE234" s="1"/>
-      <c r="BF234" s="1" t="str">
+      <c r="BF234" s="1"/>
+      <c r="BG234" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28296,7 +28758,8 @@
       <c r="BC235" s="1"/>
       <c r="BD235" s="1"/>
       <c r="BE235" s="1"/>
-      <c r="BF235" s="1" t="str">
+      <c r="BF235" s="1"/>
+      <c r="BG235" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28362,7 +28825,8 @@
       <c r="BC236" s="1"/>
       <c r="BD236" s="1"/>
       <c r="BE236" s="1"/>
-      <c r="BF236" s="1" t="str">
+      <c r="BF236" s="1"/>
+      <c r="BG236" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28428,7 +28892,8 @@
       <c r="BC237" s="1"/>
       <c r="BD237" s="1"/>
       <c r="BE237" s="1"/>
-      <c r="BF237" s="1" t="str">
+      <c r="BF237" s="1"/>
+      <c r="BG237" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28494,7 +28959,8 @@
       <c r="BC238" s="1"/>
       <c r="BD238" s="1"/>
       <c r="BE238" s="1"/>
-      <c r="BF238" s="1" t="str">
+      <c r="BF238" s="1"/>
+      <c r="BG238" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28560,7 +29026,8 @@
       <c r="BC239" s="1"/>
       <c r="BD239" s="1"/>
       <c r="BE239" s="1"/>
-      <c r="BF239" s="1" t="str">
+      <c r="BF239" s="1"/>
+      <c r="BG239" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28626,7 +29093,8 @@
       <c r="BC240" s="1"/>
       <c r="BD240" s="1"/>
       <c r="BE240" s="1"/>
-      <c r="BF240" s="1" t="str">
+      <c r="BF240" s="1"/>
+      <c r="BG240" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28692,7 +29160,8 @@
       <c r="BC241" s="1"/>
       <c r="BD241" s="1"/>
       <c r="BE241" s="1"/>
-      <c r="BF241" s="1" t="str">
+      <c r="BF241" s="1"/>
+      <c r="BG241" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28758,7 +29227,8 @@
       <c r="BC242" s="1"/>
       <c r="BD242" s="1"/>
       <c r="BE242" s="1"/>
-      <c r="BF242" s="1" t="str">
+      <c r="BF242" s="1"/>
+      <c r="BG242" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28824,7 +29294,8 @@
       <c r="BC243" s="1"/>
       <c r="BD243" s="1"/>
       <c r="BE243" s="1"/>
-      <c r="BF243" s="1" t="str">
+      <c r="BF243" s="1"/>
+      <c r="BG243" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28890,7 +29361,8 @@
       <c r="BC244" s="1"/>
       <c r="BD244" s="1"/>
       <c r="BE244" s="1"/>
-      <c r="BF244" s="1" t="str">
+      <c r="BF244" s="1"/>
+      <c r="BG244" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -28956,7 +29428,8 @@
       <c r="BC245" s="1"/>
       <c r="BD245" s="1"/>
       <c r="BE245" s="1"/>
-      <c r="BF245" s="1" t="str">
+      <c r="BF245" s="1"/>
+      <c r="BG245" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29022,7 +29495,8 @@
       <c r="BC246" s="1"/>
       <c r="BD246" s="1"/>
       <c r="BE246" s="1"/>
-      <c r="BF246" s="1" t="str">
+      <c r="BF246" s="1"/>
+      <c r="BG246" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29088,7 +29562,8 @@
       <c r="BC247" s="1"/>
       <c r="BD247" s="1"/>
       <c r="BE247" s="1"/>
-      <c r="BF247" s="1" t="str">
+      <c r="BF247" s="1"/>
+      <c r="BG247" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29154,7 +29629,8 @@
       <c r="BC248" s="1"/>
       <c r="BD248" s="1"/>
       <c r="BE248" s="1"/>
-      <c r="BF248" s="1" t="str">
+      <c r="BF248" s="1"/>
+      <c r="BG248" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29220,7 +29696,8 @@
       <c r="BC249" s="1"/>
       <c r="BD249" s="1"/>
       <c r="BE249" s="1"/>
-      <c r="BF249" s="1" t="str">
+      <c r="BF249" s="1"/>
+      <c r="BG249" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29286,7 +29763,8 @@
       <c r="BC250" s="1"/>
       <c r="BD250" s="1"/>
       <c r="BE250" s="1"/>
-      <c r="BF250" s="1" t="str">
+      <c r="BF250" s="1"/>
+      <c r="BG250" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29352,7 +29830,8 @@
       <c r="BC251" s="1"/>
       <c r="BD251" s="1"/>
       <c r="BE251" s="1"/>
-      <c r="BF251" s="1" t="str">
+      <c r="BF251" s="1"/>
+      <c r="BG251" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29418,7 +29897,8 @@
       <c r="BC252" s="1"/>
       <c r="BD252" s="1"/>
       <c r="BE252" s="1"/>
-      <c r="BF252" s="1" t="str">
+      <c r="BF252" s="1"/>
+      <c r="BG252" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29484,7 +29964,8 @@
       <c r="BC253" s="1"/>
       <c r="BD253" s="1"/>
       <c r="BE253" s="1"/>
-      <c r="BF253" s="1" t="str">
+      <c r="BF253" s="1"/>
+      <c r="BG253" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29550,7 +30031,8 @@
       <c r="BC254" s="1"/>
       <c r="BD254" s="1"/>
       <c r="BE254" s="1"/>
-      <c r="BF254" s="1" t="str">
+      <c r="BF254" s="1"/>
+      <c r="BG254" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29616,7 +30098,8 @@
       <c r="BC255" s="1"/>
       <c r="BD255" s="1"/>
       <c r="BE255" s="1"/>
-      <c r="BF255" s="1" t="str">
+      <c r="BF255" s="1"/>
+      <c r="BG255" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29682,7 +30165,8 @@
       <c r="BC256" s="1"/>
       <c r="BD256" s="1"/>
       <c r="BE256" s="1"/>
-      <c r="BF256" s="1" t="str">
+      <c r="BF256" s="1"/>
+      <c r="BG256" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29748,7 +30232,8 @@
       <c r="BC257" s="1"/>
       <c r="BD257" s="1"/>
       <c r="BE257" s="1"/>
-      <c r="BF257" s="1" t="str">
+      <c r="BF257" s="1"/>
+      <c r="BG257" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29814,7 +30299,8 @@
       <c r="BC258" s="1"/>
       <c r="BD258" s="1"/>
       <c r="BE258" s="1"/>
-      <c r="BF258" s="1" t="str">
+      <c r="BF258" s="1"/>
+      <c r="BG258" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29880,7 +30366,8 @@
       <c r="BC259" s="1"/>
       <c r="BD259" s="1"/>
       <c r="BE259" s="1"/>
-      <c r="BF259" s="1" t="str">
+      <c r="BF259" s="1"/>
+      <c r="BG259" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -29946,7 +30433,8 @@
       <c r="BC260" s="1"/>
       <c r="BD260" s="1"/>
       <c r="BE260" s="1"/>
-      <c r="BF260" s="1" t="str">
+      <c r="BF260" s="1"/>
+      <c r="BG260" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30012,7 +30500,8 @@
       <c r="BC261" s="1"/>
       <c r="BD261" s="1"/>
       <c r="BE261" s="1"/>
-      <c r="BF261" s="1" t="str">
+      <c r="BF261" s="1"/>
+      <c r="BG261" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30078,7 +30567,8 @@
       <c r="BC262" s="1"/>
       <c r="BD262" s="1"/>
       <c r="BE262" s="1"/>
-      <c r="BF262" s="1" t="str">
+      <c r="BF262" s="1"/>
+      <c r="BG262" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30144,7 +30634,8 @@
       <c r="BC263" s="1"/>
       <c r="BD263" s="1"/>
       <c r="BE263" s="1"/>
-      <c r="BF263" s="1" t="str">
+      <c r="BF263" s="1"/>
+      <c r="BG263" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30210,7 +30701,8 @@
       <c r="BC264" s="1"/>
       <c r="BD264" s="1"/>
       <c r="BE264" s="1"/>
-      <c r="BF264" s="1" t="str">
+      <c r="BF264" s="1"/>
+      <c r="BG264" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30276,7 +30768,8 @@
       <c r="BC265" s="1"/>
       <c r="BD265" s="1"/>
       <c r="BE265" s="1"/>
-      <c r="BF265" s="1" t="str">
+      <c r="BF265" s="1"/>
+      <c r="BG265" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30342,7 +30835,8 @@
       <c r="BC266" s="1"/>
       <c r="BD266" s="1"/>
       <c r="BE266" s="1"/>
-      <c r="BF266" s="1" t="str">
+      <c r="BF266" s="1"/>
+      <c r="BG266" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30408,7 +30902,8 @@
       <c r="BC267" s="1"/>
       <c r="BD267" s="1"/>
       <c r="BE267" s="1"/>
-      <c r="BF267" s="1" t="str">
+      <c r="BF267" s="1"/>
+      <c r="BG267" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30474,7 +30969,8 @@
       <c r="BC268" s="1"/>
       <c r="BD268" s="1"/>
       <c r="BE268" s="1"/>
-      <c r="BF268" s="1" t="str">
+      <c r="BF268" s="1"/>
+      <c r="BG268" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30540,7 +31036,8 @@
       <c r="BC269" s="1"/>
       <c r="BD269" s="1"/>
       <c r="BE269" s="1"/>
-      <c r="BF269" s="1" t="str">
+      <c r="BF269" s="1"/>
+      <c r="BG269" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30606,7 +31103,8 @@
       <c r="BC270" s="1"/>
       <c r="BD270" s="1"/>
       <c r="BE270" s="1"/>
-      <c r="BF270" s="1" t="str">
+      <c r="BF270" s="1"/>
+      <c r="BG270" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30672,7 +31170,8 @@
       <c r="BC271" s="1"/>
       <c r="BD271" s="1"/>
       <c r="BE271" s="1"/>
-      <c r="BF271" s="1" t="str">
+      <c r="BF271" s="1"/>
+      <c r="BG271" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30738,7 +31237,8 @@
       <c r="BC272" s="1"/>
       <c r="BD272" s="1"/>
       <c r="BE272" s="1"/>
-      <c r="BF272" s="1" t="str">
+      <c r="BF272" s="1"/>
+      <c r="BG272" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30804,7 +31304,8 @@
       <c r="BC273" s="1"/>
       <c r="BD273" s="1"/>
       <c r="BE273" s="1"/>
-      <c r="BF273" s="1" t="str">
+      <c r="BF273" s="1"/>
+      <c r="BG273" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30870,7 +31371,8 @@
       <c r="BC274" s="1"/>
       <c r="BD274" s="1"/>
       <c r="BE274" s="1"/>
-      <c r="BF274" s="1" t="str">
+      <c r="BF274" s="1"/>
+      <c r="BG274" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -30936,7 +31438,8 @@
       <c r="BC275" s="1"/>
       <c r="BD275" s="1"/>
       <c r="BE275" s="1"/>
-      <c r="BF275" s="1" t="str">
+      <c r="BF275" s="1"/>
+      <c r="BG275" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31002,7 +31505,8 @@
       <c r="BC276" s="1"/>
       <c r="BD276" s="1"/>
       <c r="BE276" s="1"/>
-      <c r="BF276" s="1" t="str">
+      <c r="BF276" s="1"/>
+      <c r="BG276" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31068,7 +31572,8 @@
       <c r="BC277" s="1"/>
       <c r="BD277" s="1"/>
       <c r="BE277" s="1"/>
-      <c r="BF277" s="1" t="str">
+      <c r="BF277" s="1"/>
+      <c r="BG277" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31134,7 +31639,8 @@
       <c r="BC278" s="1"/>
       <c r="BD278" s="1"/>
       <c r="BE278" s="1"/>
-      <c r="BF278" s="1" t="str">
+      <c r="BF278" s="1"/>
+      <c r="BG278" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31200,7 +31706,8 @@
       <c r="BC279" s="1"/>
       <c r="BD279" s="1"/>
       <c r="BE279" s="1"/>
-      <c r="BF279" s="1" t="str">
+      <c r="BF279" s="1"/>
+      <c r="BG279" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31266,7 +31773,8 @@
       <c r="BC280" s="1"/>
       <c r="BD280" s="1"/>
       <c r="BE280" s="1"/>
-      <c r="BF280" s="1" t="str">
+      <c r="BF280" s="1"/>
+      <c r="BG280" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31332,7 +31840,8 @@
       <c r="BC281" s="1"/>
       <c r="BD281" s="1"/>
       <c r="BE281" s="1"/>
-      <c r="BF281" s="1" t="str">
+      <c r="BF281" s="1"/>
+      <c r="BG281" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31398,7 +31907,8 @@
       <c r="BC282" s="1"/>
       <c r="BD282" s="1"/>
       <c r="BE282" s="1"/>
-      <c r="BF282" s="1" t="str">
+      <c r="BF282" s="1"/>
+      <c r="BG282" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31464,7 +31974,8 @@
       <c r="BC283" s="1"/>
       <c r="BD283" s="1"/>
       <c r="BE283" s="1"/>
-      <c r="BF283" s="1" t="str">
+      <c r="BF283" s="1"/>
+      <c r="BG283" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31530,7 +32041,8 @@
       <c r="BC284" s="1"/>
       <c r="BD284" s="1"/>
       <c r="BE284" s="1"/>
-      <c r="BF284" s="1" t="str">
+      <c r="BF284" s="1"/>
+      <c r="BG284" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31596,7 +32108,8 @@
       <c r="BC285" s="1"/>
       <c r="BD285" s="1"/>
       <c r="BE285" s="1"/>
-      <c r="BF285" s="1" t="str">
+      <c r="BF285" s="1"/>
+      <c r="BG285" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31662,7 +32175,8 @@
       <c r="BC286" s="1"/>
       <c r="BD286" s="1"/>
       <c r="BE286" s="1"/>
-      <c r="BF286" s="1" t="str">
+      <c r="BF286" s="1"/>
+      <c r="BG286" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31728,7 +32242,8 @@
       <c r="BC287" s="1"/>
       <c r="BD287" s="1"/>
       <c r="BE287" s="1"/>
-      <c r="BF287" s="1" t="str">
+      <c r="BF287" s="1"/>
+      <c r="BG287" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31794,7 +32309,8 @@
       <c r="BC288" s="1"/>
       <c r="BD288" s="1"/>
       <c r="BE288" s="1"/>
-      <c r="BF288" s="1" t="str">
+      <c r="BF288" s="1"/>
+      <c r="BG288" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31860,7 +32376,8 @@
       <c r="BC289" s="1"/>
       <c r="BD289" s="1"/>
       <c r="BE289" s="1"/>
-      <c r="BF289" s="1" t="str">
+      <c r="BF289" s="1"/>
+      <c r="BG289" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31926,7 +32443,8 @@
       <c r="BC290" s="1"/>
       <c r="BD290" s="1"/>
       <c r="BE290" s="1"/>
-      <c r="BF290" s="1" t="str">
+      <c r="BF290" s="1"/>
+      <c r="BG290" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -31992,7 +32510,8 @@
       <c r="BC291" s="1"/>
       <c r="BD291" s="1"/>
       <c r="BE291" s="1"/>
-      <c r="BF291" s="1" t="str">
+      <c r="BF291" s="1"/>
+      <c r="BG291" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32058,7 +32577,8 @@
       <c r="BC292" s="1"/>
       <c r="BD292" s="1"/>
       <c r="BE292" s="1"/>
-      <c r="BF292" s="1" t="str">
+      <c r="BF292" s="1"/>
+      <c r="BG292" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32124,7 +32644,8 @@
       <c r="BC293" s="1"/>
       <c r="BD293" s="1"/>
       <c r="BE293" s="1"/>
-      <c r="BF293" s="1" t="str">
+      <c r="BF293" s="1"/>
+      <c r="BG293" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32190,7 +32711,8 @@
       <c r="BC294" s="1"/>
       <c r="BD294" s="1"/>
       <c r="BE294" s="1"/>
-      <c r="BF294" s="1" t="str">
+      <c r="BF294" s="1"/>
+      <c r="BG294" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32256,7 +32778,8 @@
       <c r="BC295" s="1"/>
       <c r="BD295" s="1"/>
       <c r="BE295" s="1"/>
-      <c r="BF295" s="1" t="str">
+      <c r="BF295" s="1"/>
+      <c r="BG295" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32322,7 +32845,8 @@
       <c r="BC296" s="1"/>
       <c r="BD296" s="1"/>
       <c r="BE296" s="1"/>
-      <c r="BF296" s="1" t="str">
+      <c r="BF296" s="1"/>
+      <c r="BG296" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32388,7 +32912,8 @@
       <c r="BC297" s="1"/>
       <c r="BD297" s="1"/>
       <c r="BE297" s="1"/>
-      <c r="BF297" s="1" t="str">
+      <c r="BF297" s="1"/>
+      <c r="BG297" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32454,7 +32979,8 @@
       <c r="BC298" s="1"/>
       <c r="BD298" s="1"/>
       <c r="BE298" s="1"/>
-      <c r="BF298" s="1" t="str">
+      <c r="BF298" s="1"/>
+      <c r="BG298" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32520,7 +33046,8 @@
       <c r="BC299" s="1"/>
       <c r="BD299" s="1"/>
       <c r="BE299" s="1"/>
-      <c r="BF299" s="1" t="str">
+      <c r="BF299" s="1"/>
+      <c r="BG299" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32586,7 +33113,8 @@
       <c r="BC300" s="1"/>
       <c r="BD300" s="1"/>
       <c r="BE300" s="1"/>
-      <c r="BF300" s="1" t="str">
+      <c r="BF300" s="1"/>
+      <c r="BG300" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32652,7 +33180,8 @@
       <c r="BC301" s="1"/>
       <c r="BD301" s="1"/>
       <c r="BE301" s="1"/>
-      <c r="BF301" s="1" t="str">
+      <c r="BF301" s="1"/>
+      <c r="BG301" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32718,7 +33247,8 @@
       <c r="BC302" s="1"/>
       <c r="BD302" s="1"/>
       <c r="BE302" s="1"/>
-      <c r="BF302" s="1" t="str">
+      <c r="BF302" s="1"/>
+      <c r="BG302" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32784,7 +33314,8 @@
       <c r="BC303" s="1"/>
       <c r="BD303" s="1"/>
       <c r="BE303" s="1"/>
-      <c r="BF303" s="1" t="str">
+      <c r="BF303" s="1"/>
+      <c r="BG303" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32850,7 +33381,8 @@
       <c r="BC304" s="1"/>
       <c r="BD304" s="1"/>
       <c r="BE304" s="1"/>
-      <c r="BF304" s="1" t="str">
+      <c r="BF304" s="1"/>
+      <c r="BG304" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32916,7 +33448,8 @@
       <c r="BC305" s="1"/>
       <c r="BD305" s="1"/>
       <c r="BE305" s="1"/>
-      <c r="BF305" s="1" t="str">
+      <c r="BF305" s="1"/>
+      <c r="BG305" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -32982,7 +33515,8 @@
       <c r="BC306" s="1"/>
       <c r="BD306" s="1"/>
       <c r="BE306" s="1"/>
-      <c r="BF306" s="1" t="str">
+      <c r="BF306" s="1"/>
+      <c r="BG306" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33048,7 +33582,8 @@
       <c r="BC307" s="1"/>
       <c r="BD307" s="1"/>
       <c r="BE307" s="1"/>
-      <c r="BF307" s="1" t="str">
+      <c r="BF307" s="1"/>
+      <c r="BG307" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33114,7 +33649,8 @@
       <c r="BC308" s="1"/>
       <c r="BD308" s="1"/>
       <c r="BE308" s="1"/>
-      <c r="BF308" s="1" t="str">
+      <c r="BF308" s="1"/>
+      <c r="BG308" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33180,7 +33716,8 @@
       <c r="BC309" s="1"/>
       <c r="BD309" s="1"/>
       <c r="BE309" s="1"/>
-      <c r="BF309" s="1" t="str">
+      <c r="BF309" s="1"/>
+      <c r="BG309" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33246,7 +33783,8 @@
       <c r="BC310" s="1"/>
       <c r="BD310" s="1"/>
       <c r="BE310" s="1"/>
-      <c r="BF310" s="1" t="str">
+      <c r="BF310" s="1"/>
+      <c r="BG310" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33312,7 +33850,8 @@
       <c r="BC311" s="1"/>
       <c r="BD311" s="1"/>
       <c r="BE311" s="1"/>
-      <c r="BF311" s="1" t="str">
+      <c r="BF311" s="1"/>
+      <c r="BG311" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33378,7 +33917,8 @@
       <c r="BC312" s="1"/>
       <c r="BD312" s="1"/>
       <c r="BE312" s="1"/>
-      <c r="BF312" s="1" t="str">
+      <c r="BF312" s="1"/>
+      <c r="BG312" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33444,7 +33984,8 @@
       <c r="BC313" s="1"/>
       <c r="BD313" s="1"/>
       <c r="BE313" s="1"/>
-      <c r="BF313" s="1" t="str">
+      <c r="BF313" s="1"/>
+      <c r="BG313" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33510,7 +34051,8 @@
       <c r="BC314" s="1"/>
       <c r="BD314" s="1"/>
       <c r="BE314" s="1"/>
-      <c r="BF314" s="1" t="str">
+      <c r="BF314" s="1"/>
+      <c r="BG314" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33576,7 +34118,8 @@
       <c r="BC315" s="1"/>
       <c r="BD315" s="1"/>
       <c r="BE315" s="1"/>
-      <c r="BF315" s="1" t="str">
+      <c r="BF315" s="1"/>
+      <c r="BG315" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33642,7 +34185,8 @@
       <c r="BC316" s="1"/>
       <c r="BD316" s="1"/>
       <c r="BE316" s="1"/>
-      <c r="BF316" s="1" t="str">
+      <c r="BF316" s="1"/>
+      <c r="BG316" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33708,7 +34252,8 @@
       <c r="BC317" s="1"/>
       <c r="BD317" s="1"/>
       <c r="BE317" s="1"/>
-      <c r="BF317" s="1" t="str">
+      <c r="BF317" s="1"/>
+      <c r="BG317" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33774,7 +34319,8 @@
       <c r="BC318" s="1"/>
       <c r="BD318" s="1"/>
       <c r="BE318" s="1"/>
-      <c r="BF318" s="1" t="str">
+      <c r="BF318" s="1"/>
+      <c r="BG318" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33840,7 +34386,8 @@
       <c r="BC319" s="1"/>
       <c r="BD319" s="1"/>
       <c r="BE319" s="1"/>
-      <c r="BF319" s="1" t="str">
+      <c r="BF319" s="1"/>
+      <c r="BG319" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33906,7 +34453,8 @@
       <c r="BC320" s="1"/>
       <c r="BD320" s="1"/>
       <c r="BE320" s="1"/>
-      <c r="BF320" s="1" t="str">
+      <c r="BF320" s="1"/>
+      <c r="BG320" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -33972,7 +34520,8 @@
       <c r="BC321" s="1"/>
       <c r="BD321" s="1"/>
       <c r="BE321" s="1"/>
-      <c r="BF321" s="1" t="str">
+      <c r="BF321" s="1"/>
+      <c r="BG321" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34038,7 +34587,8 @@
       <c r="BC322" s="1"/>
       <c r="BD322" s="1"/>
       <c r="BE322" s="1"/>
-      <c r="BF322" s="1" t="str">
+      <c r="BF322" s="1"/>
+      <c r="BG322" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34104,7 +34654,8 @@
       <c r="BC323" s="1"/>
       <c r="BD323" s="1"/>
       <c r="BE323" s="1"/>
-      <c r="BF323" s="1" t="str">
+      <c r="BF323" s="1"/>
+      <c r="BG323" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34170,7 +34721,8 @@
       <c r="BC324" s="1"/>
       <c r="BD324" s="1"/>
       <c r="BE324" s="1"/>
-      <c r="BF324" s="1" t="str">
+      <c r="BF324" s="1"/>
+      <c r="BG324" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34236,7 +34788,8 @@
       <c r="BC325" s="1"/>
       <c r="BD325" s="1"/>
       <c r="BE325" s="1"/>
-      <c r="BF325" s="1" t="str">
+      <c r="BF325" s="1"/>
+      <c r="BG325" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34302,7 +34855,8 @@
       <c r="BC326" s="1"/>
       <c r="BD326" s="1"/>
       <c r="BE326" s="1"/>
-      <c r="BF326" s="1" t="str">
+      <c r="BF326" s="1"/>
+      <c r="BG326" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34368,7 +34922,8 @@
       <c r="BC327" s="1"/>
       <c r="BD327" s="1"/>
       <c r="BE327" s="1"/>
-      <c r="BF327" s="1" t="str">
+      <c r="BF327" s="1"/>
+      <c r="BG327" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34434,7 +34989,8 @@
       <c r="BC328" s="1"/>
       <c r="BD328" s="1"/>
       <c r="BE328" s="1"/>
-      <c r="BF328" s="1" t="str">
+      <c r="BF328" s="1"/>
+      <c r="BG328" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34500,7 +35056,8 @@
       <c r="BC329" s="1"/>
       <c r="BD329" s="1"/>
       <c r="BE329" s="1"/>
-      <c r="BF329" s="1" t="str">
+      <c r="BF329" s="1"/>
+      <c r="BG329" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34566,7 +35123,8 @@
       <c r="BC330" s="1"/>
       <c r="BD330" s="1"/>
       <c r="BE330" s="1"/>
-      <c r="BF330" s="1" t="str">
+      <c r="BF330" s="1"/>
+      <c r="BG330" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34632,7 +35190,8 @@
       <c r="BC331" s="1"/>
       <c r="BD331" s="1"/>
       <c r="BE331" s="1"/>
-      <c r="BF331" s="1" t="str">
+      <c r="BF331" s="1"/>
+      <c r="BG331" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34698,7 +35257,8 @@
       <c r="BC332" s="1"/>
       <c r="BD332" s="1"/>
       <c r="BE332" s="1"/>
-      <c r="BF332" s="1" t="str">
+      <c r="BF332" s="1"/>
+      <c r="BG332" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34764,7 +35324,8 @@
       <c r="BC333" s="1"/>
       <c r="BD333" s="1"/>
       <c r="BE333" s="1"/>
-      <c r="BF333" s="1" t="str">
+      <c r="BF333" s="1"/>
+      <c r="BG333" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34830,7 +35391,8 @@
       <c r="BC334" s="1"/>
       <c r="BD334" s="1"/>
       <c r="BE334" s="1"/>
-      <c r="BF334" s="1" t="str">
+      <c r="BF334" s="1"/>
+      <c r="BG334" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34896,7 +35458,8 @@
       <c r="BC335" s="1"/>
       <c r="BD335" s="1"/>
       <c r="BE335" s="1"/>
-      <c r="BF335" s="1" t="str">
+      <c r="BF335" s="1"/>
+      <c r="BG335" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -34962,7 +35525,8 @@
       <c r="BC336" s="1"/>
       <c r="BD336" s="1"/>
       <c r="BE336" s="1"/>
-      <c r="BF336" s="1" t="str">
+      <c r="BF336" s="1"/>
+      <c r="BG336" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35028,7 +35592,8 @@
       <c r="BC337" s="1"/>
       <c r="BD337" s="1"/>
       <c r="BE337" s="1"/>
-      <c r="BF337" s="1" t="str">
+      <c r="BF337" s="1"/>
+      <c r="BG337" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35094,7 +35659,8 @@
       <c r="BC338" s="1"/>
       <c r="BD338" s="1"/>
       <c r="BE338" s="1"/>
-      <c r="BF338" s="1" t="str">
+      <c r="BF338" s="1"/>
+      <c r="BG338" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35160,7 +35726,8 @@
       <c r="BC339" s="1"/>
       <c r="BD339" s="1"/>
       <c r="BE339" s="1"/>
-      <c r="BF339" s="1" t="str">
+      <c r="BF339" s="1"/>
+      <c r="BG339" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35226,7 +35793,8 @@
       <c r="BC340" s="1"/>
       <c r="BD340" s="1"/>
       <c r="BE340" s="1"/>
-      <c r="BF340" s="1" t="str">
+      <c r="BF340" s="1"/>
+      <c r="BG340" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35292,7 +35860,8 @@
       <c r="BC341" s="1"/>
       <c r="BD341" s="1"/>
       <c r="BE341" s="1"/>
-      <c r="BF341" s="1" t="str">
+      <c r="BF341" s="1"/>
+      <c r="BG341" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35358,7 +35927,8 @@
       <c r="BC342" s="1"/>
       <c r="BD342" s="1"/>
       <c r="BE342" s="1"/>
-      <c r="BF342" s="1" t="str">
+      <c r="BF342" s="1"/>
+      <c r="BG342" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35424,7 +35994,8 @@
       <c r="BC343" s="1"/>
       <c r="BD343" s="1"/>
       <c r="BE343" s="1"/>
-      <c r="BF343" s="1" t="str">
+      <c r="BF343" s="1"/>
+      <c r="BG343" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35490,7 +36061,8 @@
       <c r="BC344" s="1"/>
       <c r="BD344" s="1"/>
       <c r="BE344" s="1"/>
-      <c r="BF344" s="1" t="str">
+      <c r="BF344" s="1"/>
+      <c r="BG344" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35556,7 +36128,8 @@
       <c r="BC345" s="1"/>
       <c r="BD345" s="1"/>
       <c r="BE345" s="1"/>
-      <c r="BF345" s="1" t="str">
+      <c r="BF345" s="1"/>
+      <c r="BG345" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35622,7 +36195,8 @@
       <c r="BC346" s="1"/>
       <c r="BD346" s="1"/>
       <c r="BE346" s="1"/>
-      <c r="BF346" s="1" t="str">
+      <c r="BF346" s="1"/>
+      <c r="BG346" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35688,7 +36262,8 @@
       <c r="BC347" s="1"/>
       <c r="BD347" s="1"/>
       <c r="BE347" s="1"/>
-      <c r="BF347" s="1" t="str">
+      <c r="BF347" s="1"/>
+      <c r="BG347" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35754,7 +36329,8 @@
       <c r="BC348" s="1"/>
       <c r="BD348" s="1"/>
       <c r="BE348" s="1"/>
-      <c r="BF348" s="1" t="str">
+      <c r="BF348" s="1"/>
+      <c r="BG348" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35820,7 +36396,8 @@
       <c r="BC349" s="1"/>
       <c r="BD349" s="1"/>
       <c r="BE349" s="1"/>
-      <c r="BF349" s="1" t="str">
+      <c r="BF349" s="1"/>
+      <c r="BG349" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35886,7 +36463,8 @@
       <c r="BC350" s="1"/>
       <c r="BD350" s="1"/>
       <c r="BE350" s="1"/>
-      <c r="BF350" s="1" t="str">
+      <c r="BF350" s="1"/>
+      <c r="BG350" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -35952,7 +36530,8 @@
       <c r="BC351" s="1"/>
       <c r="BD351" s="1"/>
       <c r="BE351" s="1"/>
-      <c r="BF351" s="1" t="str">
+      <c r="BF351" s="1"/>
+      <c r="BG351" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36018,7 +36597,8 @@
       <c r="BC352" s="1"/>
       <c r="BD352" s="1"/>
       <c r="BE352" s="1"/>
-      <c r="BF352" s="1" t="str">
+      <c r="BF352" s="1"/>
+      <c r="BG352" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36084,7 +36664,8 @@
       <c r="BC353" s="1"/>
       <c r="BD353" s="1"/>
       <c r="BE353" s="1"/>
-      <c r="BF353" s="1" t="str">
+      <c r="BF353" s="1"/>
+      <c r="BG353" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36150,7 +36731,8 @@
       <c r="BC354" s="1"/>
       <c r="BD354" s="1"/>
       <c r="BE354" s="1"/>
-      <c r="BF354" s="1" t="str">
+      <c r="BF354" s="1"/>
+      <c r="BG354" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36216,7 +36798,8 @@
       <c r="BC355" s="1"/>
       <c r="BD355" s="1"/>
       <c r="BE355" s="1"/>
-      <c r="BF355" s="1" t="str">
+      <c r="BF355" s="1"/>
+      <c r="BG355" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36282,7 +36865,8 @@
       <c r="BC356" s="1"/>
       <c r="BD356" s="1"/>
       <c r="BE356" s="1"/>
-      <c r="BF356" s="1" t="str">
+      <c r="BF356" s="1"/>
+      <c r="BG356" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36348,7 +36932,8 @@
       <c r="BC357" s="1"/>
       <c r="BD357" s="1"/>
       <c r="BE357" s="1"/>
-      <c r="BF357" s="1" t="str">
+      <c r="BF357" s="1"/>
+      <c r="BG357" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36414,7 +36999,8 @@
       <c r="BC358" s="1"/>
       <c r="BD358" s="1"/>
       <c r="BE358" s="1"/>
-      <c r="BF358" s="1" t="str">
+      <c r="BF358" s="1"/>
+      <c r="BG358" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36480,7 +37066,8 @@
       <c r="BC359" s="1"/>
       <c r="BD359" s="1"/>
       <c r="BE359" s="1"/>
-      <c r="BF359" s="1" t="str">
+      <c r="BF359" s="1"/>
+      <c r="BG359" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36546,7 +37133,8 @@
       <c r="BC360" s="1"/>
       <c r="BD360" s="1"/>
       <c r="BE360" s="1"/>
-      <c r="BF360" s="1" t="str">
+      <c r="BF360" s="1"/>
+      <c r="BG360" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36612,7 +37200,8 @@
       <c r="BC361" s="1"/>
       <c r="BD361" s="1"/>
       <c r="BE361" s="1"/>
-      <c r="BF361" s="1" t="str">
+      <c r="BF361" s="1"/>
+      <c r="BG361" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36678,7 +37267,8 @@
       <c r="BC362" s="1"/>
       <c r="BD362" s="1"/>
       <c r="BE362" s="1"/>
-      <c r="BF362" s="1" t="str">
+      <c r="BF362" s="1"/>
+      <c r="BG362" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36744,7 +37334,8 @@
       <c r="BC363" s="1"/>
       <c r="BD363" s="1"/>
       <c r="BE363" s="1"/>
-      <c r="BF363" s="1" t="str">
+      <c r="BF363" s="1"/>
+      <c r="BG363" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36810,7 +37401,8 @@
       <c r="BC364" s="1"/>
       <c r="BD364" s="1"/>
       <c r="BE364" s="1"/>
-      <c r="BF364" s="1" t="str">
+      <c r="BF364" s="1"/>
+      <c r="BG364" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36876,7 +37468,8 @@
       <c r="BC365" s="1"/>
       <c r="BD365" s="1"/>
       <c r="BE365" s="1"/>
-      <c r="BF365" s="1" t="str">
+      <c r="BF365" s="1"/>
+      <c r="BG365" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -36942,7 +37535,8 @@
       <c r="BC366" s="1"/>
       <c r="BD366" s="1"/>
       <c r="BE366" s="1"/>
-      <c r="BF366" s="1" t="str">
+      <c r="BF366" s="1"/>
+      <c r="BG366" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37008,7 +37602,8 @@
       <c r="BC367" s="1"/>
       <c r="BD367" s="1"/>
       <c r="BE367" s="1"/>
-      <c r="BF367" s="1" t="str">
+      <c r="BF367" s="1"/>
+      <c r="BG367" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37074,7 +37669,8 @@
       <c r="BC368" s="1"/>
       <c r="BD368" s="1"/>
       <c r="BE368" s="1"/>
-      <c r="BF368" s="1" t="str">
+      <c r="BF368" s="1"/>
+      <c r="BG368" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37140,7 +37736,8 @@
       <c r="BC369" s="1"/>
       <c r="BD369" s="1"/>
       <c r="BE369" s="1"/>
-      <c r="BF369" s="1" t="str">
+      <c r="BF369" s="1"/>
+      <c r="BG369" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37206,7 +37803,8 @@
       <c r="BC370" s="1"/>
       <c r="BD370" s="1"/>
       <c r="BE370" s="1"/>
-      <c r="BF370" s="1" t="str">
+      <c r="BF370" s="1"/>
+      <c r="BG370" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37272,7 +37870,8 @@
       <c r="BC371" s="1"/>
       <c r="BD371" s="1"/>
       <c r="BE371" s="1"/>
-      <c r="BF371" s="1" t="str">
+      <c r="BF371" s="1"/>
+      <c r="BG371" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37338,7 +37937,8 @@
       <c r="BC372" s="1"/>
       <c r="BD372" s="1"/>
       <c r="BE372" s="1"/>
-      <c r="BF372" s="1" t="str">
+      <c r="BF372" s="1"/>
+      <c r="BG372" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37404,7 +38004,8 @@
       <c r="BC373" s="1"/>
       <c r="BD373" s="1"/>
       <c r="BE373" s="1"/>
-      <c r="BF373" s="1" t="str">
+      <c r="BF373" s="1"/>
+      <c r="BG373" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37470,7 +38071,8 @@
       <c r="BC374" s="1"/>
       <c r="BD374" s="1"/>
       <c r="BE374" s="1"/>
-      <c r="BF374" s="1" t="str">
+      <c r="BF374" s="1"/>
+      <c r="BG374" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37536,7 +38138,8 @@
       <c r="BC375" s="1"/>
       <c r="BD375" s="1"/>
       <c r="BE375" s="1"/>
-      <c r="BF375" s="1" t="str">
+      <c r="BF375" s="1"/>
+      <c r="BG375" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37602,7 +38205,8 @@
       <c r="BC376" s="1"/>
       <c r="BD376" s="1"/>
       <c r="BE376" s="1"/>
-      <c r="BF376" s="1" t="str">
+      <c r="BF376" s="1"/>
+      <c r="BG376" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37668,7 +38272,8 @@
       <c r="BC377" s="1"/>
       <c r="BD377" s="1"/>
       <c r="BE377" s="1"/>
-      <c r="BF377" s="1" t="str">
+      <c r="BF377" s="1"/>
+      <c r="BG377" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37734,7 +38339,8 @@
       <c r="BC378" s="1"/>
       <c r="BD378" s="1"/>
       <c r="BE378" s="1"/>
-      <c r="BF378" s="1" t="str">
+      <c r="BF378" s="1"/>
+      <c r="BG378" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37800,7 +38406,8 @@
       <c r="BC379" s="1"/>
       <c r="BD379" s="1"/>
       <c r="BE379" s="1"/>
-      <c r="BF379" s="1" t="str">
+      <c r="BF379" s="1"/>
+      <c r="BG379" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37866,7 +38473,8 @@
       <c r="BC380" s="1"/>
       <c r="BD380" s="1"/>
       <c r="BE380" s="1"/>
-      <c r="BF380" s="1" t="str">
+      <c r="BF380" s="1"/>
+      <c r="BG380" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37932,7 +38540,8 @@
       <c r="BC381" s="1"/>
       <c r="BD381" s="1"/>
       <c r="BE381" s="1"/>
-      <c r="BF381" s="1" t="str">
+      <c r="BF381" s="1"/>
+      <c r="BG381" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -37998,7 +38607,8 @@
       <c r="BC382" s="1"/>
       <c r="BD382" s="1"/>
       <c r="BE382" s="1"/>
-      <c r="BF382" s="1" t="str">
+      <c r="BF382" s="1"/>
+      <c r="BG382" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38064,7 +38674,8 @@
       <c r="BC383" s="1"/>
       <c r="BD383" s="1"/>
       <c r="BE383" s="1"/>
-      <c r="BF383" s="1" t="str">
+      <c r="BF383" s="1"/>
+      <c r="BG383" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38130,7 +38741,8 @@
       <c r="BC384" s="1"/>
       <c r="BD384" s="1"/>
       <c r="BE384" s="1"/>
-      <c r="BF384" s="1" t="str">
+      <c r="BF384" s="1"/>
+      <c r="BG384" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38196,7 +38808,8 @@
       <c r="BC385" s="1"/>
       <c r="BD385" s="1"/>
       <c r="BE385" s="1"/>
-      <c r="BF385" s="1" t="str">
+      <c r="BF385" s="1"/>
+      <c r="BG385" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38262,7 +38875,8 @@
       <c r="BC386" s="1"/>
       <c r="BD386" s="1"/>
       <c r="BE386" s="1"/>
-      <c r="BF386" s="1" t="str">
+      <c r="BF386" s="1"/>
+      <c r="BG386" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38328,7 +38942,8 @@
       <c r="BC387" s="1"/>
       <c r="BD387" s="1"/>
       <c r="BE387" s="1"/>
-      <c r="BF387" s="1" t="str">
+      <c r="BF387" s="1"/>
+      <c r="BG387" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38394,7 +39009,8 @@
       <c r="BC388" s="1"/>
       <c r="BD388" s="1"/>
       <c r="BE388" s="1"/>
-      <c r="BF388" s="1" t="str">
+      <c r="BF388" s="1"/>
+      <c r="BG388" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38460,7 +39076,8 @@
       <c r="BC389" s="1"/>
       <c r="BD389" s="1"/>
       <c r="BE389" s="1"/>
-      <c r="BF389" s="1" t="str">
+      <c r="BF389" s="1"/>
+      <c r="BG389" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38526,7 +39143,8 @@
       <c r="BC390" s="1"/>
       <c r="BD390" s="1"/>
       <c r="BE390" s="1"/>
-      <c r="BF390" s="1" t="str">
+      <c r="BF390" s="1"/>
+      <c r="BG390" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38592,7 +39210,8 @@
       <c r="BC391" s="1"/>
       <c r="BD391" s="1"/>
       <c r="BE391" s="1"/>
-      <c r="BF391" s="1" t="str">
+      <c r="BF391" s="1"/>
+      <c r="BG391" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38658,7 +39277,8 @@
       <c r="BC392" s="1"/>
       <c r="BD392" s="1"/>
       <c r="BE392" s="1"/>
-      <c r="BF392" s="1" t="str">
+      <c r="BF392" s="1"/>
+      <c r="BG392" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38724,7 +39344,8 @@
       <c r="BC393" s="1"/>
       <c r="BD393" s="1"/>
       <c r="BE393" s="1"/>
-      <c r="BF393" s="1" t="str">
+      <c r="BF393" s="1"/>
+      <c r="BG393" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38790,7 +39411,8 @@
       <c r="BC394" s="1"/>
       <c r="BD394" s="1"/>
       <c r="BE394" s="1"/>
-      <c r="BF394" s="1" t="str">
+      <c r="BF394" s="1"/>
+      <c r="BG394" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38856,7 +39478,8 @@
       <c r="BC395" s="1"/>
       <c r="BD395" s="1"/>
       <c r="BE395" s="1"/>
-      <c r="BF395" s="1" t="str">
+      <c r="BF395" s="1"/>
+      <c r="BG395" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38922,7 +39545,8 @@
       <c r="BC396" s="1"/>
       <c r="BD396" s="1"/>
       <c r="BE396" s="1"/>
-      <c r="BF396" s="1" t="str">
+      <c r="BF396" s="1"/>
+      <c r="BG396" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -38988,7 +39612,8 @@
       <c r="BC397" s="1"/>
       <c r="BD397" s="1"/>
       <c r="BE397" s="1"/>
-      <c r="BF397" s="1" t="str">
+      <c r="BF397" s="1"/>
+      <c r="BG397" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39054,7 +39679,8 @@
       <c r="BC398" s="1"/>
       <c r="BD398" s="1"/>
       <c r="BE398" s="1"/>
-      <c r="BF398" s="1" t="str">
+      <c r="BF398" s="1"/>
+      <c r="BG398" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39120,7 +39746,8 @@
       <c r="BC399" s="1"/>
       <c r="BD399" s="1"/>
       <c r="BE399" s="1"/>
-      <c r="BF399" s="1" t="str">
+      <c r="BF399" s="1"/>
+      <c r="BG399" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39186,7 +39813,8 @@
       <c r="BC400" s="1"/>
       <c r="BD400" s="1"/>
       <c r="BE400" s="1"/>
-      <c r="BF400" s="1" t="str">
+      <c r="BF400" s="1"/>
+      <c r="BG400" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39252,7 +39880,8 @@
       <c r="BC401" s="1"/>
       <c r="BD401" s="1"/>
       <c r="BE401" s="1"/>
-      <c r="BF401" s="1" t="str">
+      <c r="BF401" s="1"/>
+      <c r="BG401" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39318,7 +39947,8 @@
       <c r="BC402" s="1"/>
       <c r="BD402" s="1"/>
       <c r="BE402" s="1"/>
-      <c r="BF402" s="1" t="str">
+      <c r="BF402" s="1"/>
+      <c r="BG402" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39384,7 +40014,8 @@
       <c r="BC403" s="1"/>
       <c r="BD403" s="1"/>
       <c r="BE403" s="1"/>
-      <c r="BF403" s="1" t="str">
+      <c r="BF403" s="1"/>
+      <c r="BG403" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39450,7 +40081,8 @@
       <c r="BC404" s="1"/>
       <c r="BD404" s="1"/>
       <c r="BE404" s="1"/>
-      <c r="BF404" s="1" t="str">
+      <c r="BF404" s="1"/>
+      <c r="BG404" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39516,7 +40148,8 @@
       <c r="BC405" s="1"/>
       <c r="BD405" s="1"/>
       <c r="BE405" s="1"/>
-      <c r="BF405" s="1" t="str">
+      <c r="BF405" s="1"/>
+      <c r="BG405" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39582,7 +40215,8 @@
       <c r="BC406" s="1"/>
       <c r="BD406" s="1"/>
       <c r="BE406" s="1"/>
-      <c r="BF406" s="1" t="str">
+      <c r="BF406" s="1"/>
+      <c r="BG406" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39648,7 +40282,8 @@
       <c r="BC407" s="1"/>
       <c r="BD407" s="1"/>
       <c r="BE407" s="1"/>
-      <c r="BF407" s="1" t="str">
+      <c r="BF407" s="1"/>
+      <c r="BG407" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39714,7 +40349,8 @@
       <c r="BC408" s="1"/>
       <c r="BD408" s="1"/>
       <c r="BE408" s="1"/>
-      <c r="BF408" s="1" t="str">
+      <c r="BF408" s="1"/>
+      <c r="BG408" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39780,7 +40416,8 @@
       <c r="BC409" s="1"/>
       <c r="BD409" s="1"/>
       <c r="BE409" s="1"/>
-      <c r="BF409" s="1" t="str">
+      <c r="BF409" s="1"/>
+      <c r="BG409" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39846,7 +40483,8 @@
       <c r="BC410" s="1"/>
       <c r="BD410" s="1"/>
       <c r="BE410" s="1"/>
-      <c r="BF410" s="1" t="str">
+      <c r="BF410" s="1"/>
+      <c r="BG410" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39912,7 +40550,8 @@
       <c r="BC411" s="1"/>
       <c r="BD411" s="1"/>
       <c r="BE411" s="1"/>
-      <c r="BF411" s="1" t="str">
+      <c r="BF411" s="1"/>
+      <c r="BG411" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -39978,7 +40617,8 @@
       <c r="BC412" s="1"/>
       <c r="BD412" s="1"/>
       <c r="BE412" s="1"/>
-      <c r="BF412" s="1" t="str">
+      <c r="BF412" s="1"/>
+      <c r="BG412" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40044,7 +40684,8 @@
       <c r="BC413" s="1"/>
       <c r="BD413" s="1"/>
       <c r="BE413" s="1"/>
-      <c r="BF413" s="1" t="str">
+      <c r="BF413" s="1"/>
+      <c r="BG413" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40110,7 +40751,8 @@
       <c r="BC414" s="1"/>
       <c r="BD414" s="1"/>
       <c r="BE414" s="1"/>
-      <c r="BF414" s="1" t="str">
+      <c r="BF414" s="1"/>
+      <c r="BG414" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40176,7 +40818,8 @@
       <c r="BC415" s="1"/>
       <c r="BD415" s="1"/>
       <c r="BE415" s="1"/>
-      <c r="BF415" s="1" t="str">
+      <c r="BF415" s="1"/>
+      <c r="BG415" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40242,7 +40885,8 @@
       <c r="BC416" s="1"/>
       <c r="BD416" s="1"/>
       <c r="BE416" s="1"/>
-      <c r="BF416" s="1" t="str">
+      <c r="BF416" s="1"/>
+      <c r="BG416" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40308,7 +40952,8 @@
       <c r="BC417" s="1"/>
       <c r="BD417" s="1"/>
       <c r="BE417" s="1"/>
-      <c r="BF417" s="1" t="str">
+      <c r="BF417" s="1"/>
+      <c r="BG417" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40374,7 +41019,8 @@
       <c r="BC418" s="1"/>
       <c r="BD418" s="1"/>
       <c r="BE418" s="1"/>
-      <c r="BF418" s="1" t="str">
+      <c r="BF418" s="1"/>
+      <c r="BG418" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40440,7 +41086,8 @@
       <c r="BC419" s="1"/>
       <c r="BD419" s="1"/>
       <c r="BE419" s="1"/>
-      <c r="BF419" s="1" t="str">
+      <c r="BF419" s="1"/>
+      <c r="BG419" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40506,7 +41153,8 @@
       <c r="BC420" s="1"/>
       <c r="BD420" s="1"/>
       <c r="BE420" s="1"/>
-      <c r="BF420" s="1" t="str">
+      <c r="BF420" s="1"/>
+      <c r="BG420" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40572,7 +41220,8 @@
       <c r="BC421" s="1"/>
       <c r="BD421" s="1"/>
       <c r="BE421" s="1"/>
-      <c r="BF421" s="1" t="str">
+      <c r="BF421" s="1"/>
+      <c r="BG421" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40638,7 +41287,8 @@
       <c r="BC422" s="1"/>
       <c r="BD422" s="1"/>
       <c r="BE422" s="1"/>
-      <c r="BF422" s="1" t="str">
+      <c r="BF422" s="1"/>
+      <c r="BG422" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40704,7 +41354,8 @@
       <c r="BC423" s="1"/>
       <c r="BD423" s="1"/>
       <c r="BE423" s="1"/>
-      <c r="BF423" s="1" t="str">
+      <c r="BF423" s="1"/>
+      <c r="BG423" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40770,7 +41421,8 @@
       <c r="BC424" s="1"/>
       <c r="BD424" s="1"/>
       <c r="BE424" s="1"/>
-      <c r="BF424" s="1" t="str">
+      <c r="BF424" s="1"/>
+      <c r="BG424" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40836,7 +41488,8 @@
       <c r="BC425" s="1"/>
       <c r="BD425" s="1"/>
       <c r="BE425" s="1"/>
-      <c r="BF425" s="1" t="str">
+      <c r="BF425" s="1"/>
+      <c r="BG425" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40902,7 +41555,8 @@
       <c r="BC426" s="1"/>
       <c r="BD426" s="1"/>
       <c r="BE426" s="1"/>
-      <c r="BF426" s="1" t="str">
+      <c r="BF426" s="1"/>
+      <c r="BG426" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -40968,7 +41622,8 @@
       <c r="BC427" s="1"/>
       <c r="BD427" s="1"/>
       <c r="BE427" s="1"/>
-      <c r="BF427" s="1" t="str">
+      <c r="BF427" s="1"/>
+      <c r="BG427" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41034,7 +41689,8 @@
       <c r="BC428" s="1"/>
       <c r="BD428" s="1"/>
       <c r="BE428" s="1"/>
-      <c r="BF428" s="1" t="str">
+      <c r="BF428" s="1"/>
+      <c r="BG428" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41100,7 +41756,8 @@
       <c r="BC429" s="1"/>
       <c r="BD429" s="1"/>
       <c r="BE429" s="1"/>
-      <c r="BF429" s="1" t="str">
+      <c r="BF429" s="1"/>
+      <c r="BG429" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41166,7 +41823,8 @@
       <c r="BC430" s="1"/>
       <c r="BD430" s="1"/>
       <c r="BE430" s="1"/>
-      <c r="BF430" s="1" t="str">
+      <c r="BF430" s="1"/>
+      <c r="BG430" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41232,7 +41890,8 @@
       <c r="BC431" s="1"/>
       <c r="BD431" s="1"/>
       <c r="BE431" s="1"/>
-      <c r="BF431" s="1" t="str">
+      <c r="BF431" s="1"/>
+      <c r="BG431" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41298,7 +41957,8 @@
       <c r="BC432" s="1"/>
       <c r="BD432" s="1"/>
       <c r="BE432" s="1"/>
-      <c r="BF432" s="1" t="str">
+      <c r="BF432" s="1"/>
+      <c r="BG432" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41364,7 +42024,8 @@
       <c r="BC433" s="1"/>
       <c r="BD433" s="1"/>
       <c r="BE433" s="1"/>
-      <c r="BF433" s="1" t="str">
+      <c r="BF433" s="1"/>
+      <c r="BG433" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41430,7 +42091,8 @@
       <c r="BC434" s="1"/>
       <c r="BD434" s="1"/>
       <c r="BE434" s="1"/>
-      <c r="BF434" s="1" t="str">
+      <c r="BF434" s="1"/>
+      <c r="BG434" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41496,7 +42158,8 @@
       <c r="BC435" s="1"/>
       <c r="BD435" s="1"/>
       <c r="BE435" s="1"/>
-      <c r="BF435" s="1" t="str">
+      <c r="BF435" s="1"/>
+      <c r="BG435" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41562,7 +42225,8 @@
       <c r="BC436" s="1"/>
       <c r="BD436" s="1"/>
       <c r="BE436" s="1"/>
-      <c r="BF436" s="1" t="str">
+      <c r="BF436" s="1"/>
+      <c r="BG436" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41628,7 +42292,8 @@
       <c r="BC437" s="1"/>
       <c r="BD437" s="1"/>
       <c r="BE437" s="1"/>
-      <c r="BF437" s="1" t="str">
+      <c r="BF437" s="1"/>
+      <c r="BG437" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41694,7 +42359,8 @@
       <c r="BC438" s="1"/>
       <c r="BD438" s="1"/>
       <c r="BE438" s="1"/>
-      <c r="BF438" s="1" t="str">
+      <c r="BF438" s="1"/>
+      <c r="BG438" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41760,7 +42426,8 @@
       <c r="BC439" s="1"/>
       <c r="BD439" s="1"/>
       <c r="BE439" s="1"/>
-      <c r="BF439" s="1" t="str">
+      <c r="BF439" s="1"/>
+      <c r="BG439" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41826,7 +42493,8 @@
       <c r="BC440" s="1"/>
       <c r="BD440" s="1"/>
       <c r="BE440" s="1"/>
-      <c r="BF440" s="1" t="str">
+      <c r="BF440" s="1"/>
+      <c r="BG440" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41892,7 +42560,8 @@
       <c r="BC441" s="1"/>
       <c r="BD441" s="1"/>
       <c r="BE441" s="1"/>
-      <c r="BF441" s="1" t="str">
+      <c r="BF441" s="1"/>
+      <c r="BG441" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -41958,7 +42627,8 @@
       <c r="BC442" s="1"/>
       <c r="BD442" s="1"/>
       <c r="BE442" s="1"/>
-      <c r="BF442" s="1" t="str">
+      <c r="BF442" s="1"/>
+      <c r="BG442" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42024,7 +42694,8 @@
       <c r="BC443" s="1"/>
       <c r="BD443" s="1"/>
       <c r="BE443" s="1"/>
-      <c r="BF443" s="1" t="str">
+      <c r="BF443" s="1"/>
+      <c r="BG443" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42090,7 +42761,8 @@
       <c r="BC444" s="1"/>
       <c r="BD444" s="1"/>
       <c r="BE444" s="1"/>
-      <c r="BF444" s="1" t="str">
+      <c r="BF444" s="1"/>
+      <c r="BG444" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42156,7 +42828,8 @@
       <c r="BC445" s="1"/>
       <c r="BD445" s="1"/>
       <c r="BE445" s="1"/>
-      <c r="BF445" s="1" t="str">
+      <c r="BF445" s="1"/>
+      <c r="BG445" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42222,7 +42895,8 @@
       <c r="BC446" s="1"/>
       <c r="BD446" s="1"/>
       <c r="BE446" s="1"/>
-      <c r="BF446" s="1" t="str">
+      <c r="BF446" s="1"/>
+      <c r="BG446" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42288,7 +42962,8 @@
       <c r="BC447" s="1"/>
       <c r="BD447" s="1"/>
       <c r="BE447" s="1"/>
-      <c r="BF447" s="1" t="str">
+      <c r="BF447" s="1"/>
+      <c r="BG447" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42354,7 +43029,8 @@
       <c r="BC448" s="1"/>
       <c r="BD448" s="1"/>
       <c r="BE448" s="1"/>
-      <c r="BF448" s="1" t="str">
+      <c r="BF448" s="1"/>
+      <c r="BG448" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42420,7 +43096,8 @@
       <c r="BC449" s="1"/>
       <c r="BD449" s="1"/>
       <c r="BE449" s="1"/>
-      <c r="BF449" s="1" t="str">
+      <c r="BF449" s="1"/>
+      <c r="BG449" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42486,7 +43163,8 @@
       <c r="BC450" s="1"/>
       <c r="BD450" s="1"/>
       <c r="BE450" s="1"/>
-      <c r="BF450" s="1" t="str">
+      <c r="BF450" s="1"/>
+      <c r="BG450" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42552,7 +43230,8 @@
       <c r="BC451" s="1"/>
       <c r="BD451" s="1"/>
       <c r="BE451" s="1"/>
-      <c r="BF451" s="1" t="str">
+      <c r="BF451" s="1"/>
+      <c r="BG451" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42618,7 +43297,8 @@
       <c r="BC452" s="1"/>
       <c r="BD452" s="1"/>
       <c r="BE452" s="1"/>
-      <c r="BF452" s="1" t="str">
+      <c r="BF452" s="1"/>
+      <c r="BG452" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42684,7 +43364,8 @@
       <c r="BC453" s="1"/>
       <c r="BD453" s="1"/>
       <c r="BE453" s="1"/>
-      <c r="BF453" s="1" t="str">
+      <c r="BF453" s="1"/>
+      <c r="BG453" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42750,7 +43431,8 @@
       <c r="BC454" s="1"/>
       <c r="BD454" s="1"/>
       <c r="BE454" s="1"/>
-      <c r="BF454" s="1" t="str">
+      <c r="BF454" s="1"/>
+      <c r="BG454" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42816,7 +43498,8 @@
       <c r="BC455" s="1"/>
       <c r="BD455" s="1"/>
       <c r="BE455" s="1"/>
-      <c r="BF455" s="1" t="str">
+      <c r="BF455" s="1"/>
+      <c r="BG455" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42882,7 +43565,8 @@
       <c r="BC456" s="1"/>
       <c r="BD456" s="1"/>
       <c r="BE456" s="1"/>
-      <c r="BF456" s="1" t="str">
+      <c r="BF456" s="1"/>
+      <c r="BG456" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -42948,7 +43632,8 @@
       <c r="BC457" s="1"/>
       <c r="BD457" s="1"/>
       <c r="BE457" s="1"/>
-      <c r="BF457" s="1" t="str">
+      <c r="BF457" s="1"/>
+      <c r="BG457" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43014,7 +43699,8 @@
       <c r="BC458" s="1"/>
       <c r="BD458" s="1"/>
       <c r="BE458" s="1"/>
-      <c r="BF458" s="1" t="str">
+      <c r="BF458" s="1"/>
+      <c r="BG458" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43080,7 +43766,8 @@
       <c r="BC459" s="1"/>
       <c r="BD459" s="1"/>
       <c r="BE459" s="1"/>
-      <c r="BF459" s="1" t="str">
+      <c r="BF459" s="1"/>
+      <c r="BG459" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43146,7 +43833,8 @@
       <c r="BC460" s="1"/>
       <c r="BD460" s="1"/>
       <c r="BE460" s="1"/>
-      <c r="BF460" s="1" t="str">
+      <c r="BF460" s="1"/>
+      <c r="BG460" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43212,7 +43900,8 @@
       <c r="BC461" s="1"/>
       <c r="BD461" s="1"/>
       <c r="BE461" s="1"/>
-      <c r="BF461" s="1" t="str">
+      <c r="BF461" s="1"/>
+      <c r="BG461" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43278,7 +43967,8 @@
       <c r="BC462" s="1"/>
       <c r="BD462" s="1"/>
       <c r="BE462" s="1"/>
-      <c r="BF462" s="1" t="str">
+      <c r="BF462" s="1"/>
+      <c r="BG462" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43344,7 +44034,8 @@
       <c r="BC463" s="1"/>
       <c r="BD463" s="1"/>
       <c r="BE463" s="1"/>
-      <c r="BF463" s="1" t="str">
+      <c r="BF463" s="1"/>
+      <c r="BG463" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43410,7 +44101,8 @@
       <c r="BC464" s="1"/>
       <c r="BD464" s="1"/>
       <c r="BE464" s="1"/>
-      <c r="BF464" s="1" t="str">
+      <c r="BF464" s="1"/>
+      <c r="BG464" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43476,7 +44168,8 @@
       <c r="BC465" s="1"/>
       <c r="BD465" s="1"/>
       <c r="BE465" s="1"/>
-      <c r="BF465" s="1" t="str">
+      <c r="BF465" s="1"/>
+      <c r="BG465" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43542,7 +44235,8 @@
       <c r="BC466" s="1"/>
       <c r="BD466" s="1"/>
       <c r="BE466" s="1"/>
-      <c r="BF466" s="1" t="str">
+      <c r="BF466" s="1"/>
+      <c r="BG466" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43608,7 +44302,8 @@
       <c r="BC467" s="1"/>
       <c r="BD467" s="1"/>
       <c r="BE467" s="1"/>
-      <c r="BF467" s="1" t="str">
+      <c r="BF467" s="1"/>
+      <c r="BG467" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43674,7 +44369,8 @@
       <c r="BC468" s="1"/>
       <c r="BD468" s="1"/>
       <c r="BE468" s="1"/>
-      <c r="BF468" s="1" t="str">
+      <c r="BF468" s="1"/>
+      <c r="BG468" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43740,7 +44436,8 @@
       <c r="BC469" s="1"/>
       <c r="BD469" s="1"/>
       <c r="BE469" s="1"/>
-      <c r="BF469" s="1" t="str">
+      <c r="BF469" s="1"/>
+      <c r="BG469" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43806,7 +44503,8 @@
       <c r="BC470" s="1"/>
       <c r="BD470" s="1"/>
       <c r="BE470" s="1"/>
-      <c r="BF470" s="1" t="str">
+      <c r="BF470" s="1"/>
+      <c r="BG470" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43872,7 +44570,8 @@
       <c r="BC471" s="1"/>
       <c r="BD471" s="1"/>
       <c r="BE471" s="1"/>
-      <c r="BF471" s="1" t="str">
+      <c r="BF471" s="1"/>
+      <c r="BG471" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -43938,7 +44637,8 @@
       <c r="BC472" s="1"/>
       <c r="BD472" s="1"/>
       <c r="BE472" s="1"/>
-      <c r="BF472" s="1" t="str">
+      <c r="BF472" s="1"/>
+      <c r="BG472" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44004,7 +44704,8 @@
       <c r="BC473" s="1"/>
       <c r="BD473" s="1"/>
       <c r="BE473" s="1"/>
-      <c r="BF473" s="1" t="str">
+      <c r="BF473" s="1"/>
+      <c r="BG473" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44070,7 +44771,8 @@
       <c r="BC474" s="1"/>
       <c r="BD474" s="1"/>
       <c r="BE474" s="1"/>
-      <c r="BF474" s="1" t="str">
+      <c r="BF474" s="1"/>
+      <c r="BG474" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44136,7 +44838,8 @@
       <c r="BC475" s="1"/>
       <c r="BD475" s="1"/>
       <c r="BE475" s="1"/>
-      <c r="BF475" s="1" t="str">
+      <c r="BF475" s="1"/>
+      <c r="BG475" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44202,7 +44905,8 @@
       <c r="BC476" s="1"/>
       <c r="BD476" s="1"/>
       <c r="BE476" s="1"/>
-      <c r="BF476" s="1" t="str">
+      <c r="BF476" s="1"/>
+      <c r="BG476" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44268,7 +44972,8 @@
       <c r="BC477" s="1"/>
       <c r="BD477" s="1"/>
       <c r="BE477" s="1"/>
-      <c r="BF477" s="1" t="str">
+      <c r="BF477" s="1"/>
+      <c r="BG477" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44334,7 +45039,8 @@
       <c r="BC478" s="1"/>
       <c r="BD478" s="1"/>
       <c r="BE478" s="1"/>
-      <c r="BF478" s="1" t="str">
+      <c r="BF478" s="1"/>
+      <c r="BG478" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44400,7 +45106,8 @@
       <c r="BC479" s="1"/>
       <c r="BD479" s="1"/>
       <c r="BE479" s="1"/>
-      <c r="BF479" s="1" t="str">
+      <c r="BF479" s="1"/>
+      <c r="BG479" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44466,7 +45173,8 @@
       <c r="BC480" s="1"/>
       <c r="BD480" s="1"/>
       <c r="BE480" s="1"/>
-      <c r="BF480" s="1" t="str">
+      <c r="BF480" s="1"/>
+      <c r="BG480" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44532,7 +45240,8 @@
       <c r="BC481" s="1"/>
       <c r="BD481" s="1"/>
       <c r="BE481" s="1"/>
-      <c r="BF481" s="1" t="str">
+      <c r="BF481" s="1"/>
+      <c r="BG481" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44598,7 +45307,8 @@
       <c r="BC482" s="1"/>
       <c r="BD482" s="1"/>
       <c r="BE482" s="1"/>
-      <c r="BF482" s="1" t="str">
+      <c r="BF482" s="1"/>
+      <c r="BG482" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44664,7 +45374,8 @@
       <c r="BC483" s="1"/>
       <c r="BD483" s="1"/>
       <c r="BE483" s="1"/>
-      <c r="BF483" s="1" t="str">
+      <c r="BF483" s="1"/>
+      <c r="BG483" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44730,7 +45441,8 @@
       <c r="BC484" s="1"/>
       <c r="BD484" s="1"/>
       <c r="BE484" s="1"/>
-      <c r="BF484" s="1" t="str">
+      <c r="BF484" s="1"/>
+      <c r="BG484" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44796,7 +45508,8 @@
       <c r="BC485" s="1"/>
       <c r="BD485" s="1"/>
       <c r="BE485" s="1"/>
-      <c r="BF485" s="1" t="str">
+      <c r="BF485" s="1"/>
+      <c r="BG485" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44862,7 +45575,8 @@
       <c r="BC486" s="1"/>
       <c r="BD486" s="1"/>
       <c r="BE486" s="1"/>
-      <c r="BF486" s="1" t="str">
+      <c r="BF486" s="1"/>
+      <c r="BG486" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44928,7 +45642,8 @@
       <c r="BC487" s="1"/>
       <c r="BD487" s="1"/>
       <c r="BE487" s="1"/>
-      <c r="BF487" s="1" t="str">
+      <c r="BF487" s="1"/>
+      <c r="BG487" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -44994,7 +45709,8 @@
       <c r="BC488" s="1"/>
       <c r="BD488" s="1"/>
       <c r="BE488" s="1"/>
-      <c r="BF488" s="1" t="str">
+      <c r="BF488" s="1"/>
+      <c r="BG488" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45060,7 +45776,8 @@
       <c r="BC489" s="1"/>
       <c r="BD489" s="1"/>
       <c r="BE489" s="1"/>
-      <c r="BF489" s="1" t="str">
+      <c r="BF489" s="1"/>
+      <c r="BG489" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45126,7 +45843,8 @@
       <c r="BC490" s="1"/>
       <c r="BD490" s="1"/>
       <c r="BE490" s="1"/>
-      <c r="BF490" s="1" t="str">
+      <c r="BF490" s="1"/>
+      <c r="BG490" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45192,7 +45910,8 @@
       <c r="BC491" s="1"/>
       <c r="BD491" s="1"/>
       <c r="BE491" s="1"/>
-      <c r="BF491" s="1" t="str">
+      <c r="BF491" s="1"/>
+      <c r="BG491" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45258,7 +45977,8 @@
       <c r="BC492" s="1"/>
       <c r="BD492" s="1"/>
       <c r="BE492" s="1"/>
-      <c r="BF492" s="1" t="str">
+      <c r="BF492" s="1"/>
+      <c r="BG492" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45324,7 +46044,8 @@
       <c r="BC493" s="1"/>
       <c r="BD493" s="1"/>
       <c r="BE493" s="1"/>
-      <c r="BF493" s="1" t="str">
+      <c r="BF493" s="1"/>
+      <c r="BG493" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45390,7 +46111,8 @@
       <c r="BC494" s="1"/>
       <c r="BD494" s="1"/>
       <c r="BE494" s="1"/>
-      <c r="BF494" s="1" t="str">
+      <c r="BF494" s="1"/>
+      <c r="BG494" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45456,7 +46178,8 @@
       <c r="BC495" s="1"/>
       <c r="BD495" s="1"/>
       <c r="BE495" s="1"/>
-      <c r="BF495" s="1" t="str">
+      <c r="BF495" s="1"/>
+      <c r="BG495" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45522,7 +46245,8 @@
       <c r="BC496" s="1"/>
       <c r="BD496" s="1"/>
       <c r="BE496" s="1"/>
-      <c r="BF496" s="1" t="str">
+      <c r="BF496" s="1"/>
+      <c r="BG496" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45588,7 +46312,8 @@
       <c r="BC497" s="1"/>
       <c r="BD497" s="1"/>
       <c r="BE497" s="1"/>
-      <c r="BF497" s="1" t="str">
+      <c r="BF497" s="1"/>
+      <c r="BG497" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45654,7 +46379,8 @@
       <c r="BC498" s="1"/>
       <c r="BD498" s="1"/>
       <c r="BE498" s="1"/>
-      <c r="BF498" s="1" t="str">
+      <c r="BF498" s="1"/>
+      <c r="BG498" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45720,7 +46446,8 @@
       <c r="BC499" s="1"/>
       <c r="BD499" s="1"/>
       <c r="BE499" s="1"/>
-      <c r="BF499" s="1" t="str">
+      <c r="BF499" s="1"/>
+      <c r="BG499" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45786,7 +46513,8 @@
       <c r="BC500" s="1"/>
       <c r="BD500" s="1"/>
       <c r="BE500" s="1"/>
-      <c r="BF500" s="1" t="str">
+      <c r="BF500" s="1"/>
+      <c r="BG500" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45852,7 +46580,8 @@
       <c r="BC501" s="1"/>
       <c r="BD501" s="1"/>
       <c r="BE501" s="1"/>
-      <c r="BF501" s="1" t="str">
+      <c r="BF501" s="1"/>
+      <c r="BG501" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45918,7 +46647,8 @@
       <c r="BC502" s="1"/>
       <c r="BD502" s="1"/>
       <c r="BE502" s="1"/>
-      <c r="BF502" s="1" t="str">
+      <c r="BF502" s="1"/>
+      <c r="BG502" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -45984,7 +46714,8 @@
       <c r="BC503" s="1"/>
       <c r="BD503" s="1"/>
       <c r="BE503" s="1"/>
-      <c r="BF503" s="1" t="str">
+      <c r="BF503" s="1"/>
+      <c r="BG503" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46050,7 +46781,8 @@
       <c r="BC504" s="1"/>
       <c r="BD504" s="1"/>
       <c r="BE504" s="1"/>
-      <c r="BF504" s="1" t="str">
+      <c r="BF504" s="1"/>
+      <c r="BG504" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46116,7 +46848,8 @@
       <c r="BC505" s="1"/>
       <c r="BD505" s="1"/>
       <c r="BE505" s="1"/>
-      <c r="BF505" s="1" t="str">
+      <c r="BF505" s="1"/>
+      <c r="BG505" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46182,7 +46915,8 @@
       <c r="BC506" s="1"/>
       <c r="BD506" s="1"/>
       <c r="BE506" s="1"/>
-      <c r="BF506" s="1" t="str">
+      <c r="BF506" s="1"/>
+      <c r="BG506" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46248,7 +46982,8 @@
       <c r="BC507" s="1"/>
       <c r="BD507" s="1"/>
       <c r="BE507" s="1"/>
-      <c r="BF507" s="1" t="str">
+      <c r="BF507" s="1"/>
+      <c r="BG507" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46314,7 +47049,8 @@
       <c r="BC508" s="1"/>
       <c r="BD508" s="1"/>
       <c r="BE508" s="1"/>
-      <c r="BF508" s="1" t="str">
+      <c r="BF508" s="1"/>
+      <c r="BG508" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46380,7 +47116,8 @@
       <c r="BC509" s="1"/>
       <c r="BD509" s="1"/>
       <c r="BE509" s="1"/>
-      <c r="BF509" s="1" t="str">
+      <c r="BF509" s="1"/>
+      <c r="BG509" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46446,7 +47183,8 @@
       <c r="BC510" s="1"/>
       <c r="BD510" s="1"/>
       <c r="BE510" s="1"/>
-      <c r="BF510" s="1" t="str">
+      <c r="BF510" s="1"/>
+      <c r="BG510" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46512,7 +47250,8 @@
       <c r="BC511" s="1"/>
       <c r="BD511" s="1"/>
       <c r="BE511" s="1"/>
-      <c r="BF511" s="1" t="str">
+      <c r="BF511" s="1"/>
+      <c r="BG511" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46578,7 +47317,8 @@
       <c r="BC512" s="1"/>
       <c r="BD512" s="1"/>
       <c r="BE512" s="1"/>
-      <c r="BF512" s="1" t="str">
+      <c r="BF512" s="1"/>
+      <c r="BG512" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46644,7 +47384,8 @@
       <c r="BC513" s="1"/>
       <c r="BD513" s="1"/>
       <c r="BE513" s="1"/>
-      <c r="BF513" s="1" t="str">
+      <c r="BF513" s="1"/>
+      <c r="BG513" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46710,7 +47451,8 @@
       <c r="BC514" s="1"/>
       <c r="BD514" s="1"/>
       <c r="BE514" s="1"/>
-      <c r="BF514" s="1" t="str">
+      <c r="BF514" s="1"/>
+      <c r="BG514" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46776,7 +47518,8 @@
       <c r="BC515" s="1"/>
       <c r="BD515" s="1"/>
       <c r="BE515" s="1"/>
-      <c r="BF515" s="1" t="str">
+      <c r="BF515" s="1"/>
+      <c r="BG515" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46842,7 +47585,8 @@
       <c r="BC516" s="1"/>
       <c r="BD516" s="1"/>
       <c r="BE516" s="1"/>
-      <c r="BF516" s="1" t="str">
+      <c r="BF516" s="1"/>
+      <c r="BG516" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46908,7 +47652,8 @@
       <c r="BC517" s="1"/>
       <c r="BD517" s="1"/>
       <c r="BE517" s="1"/>
-      <c r="BF517" s="1" t="str">
+      <c r="BF517" s="1"/>
+      <c r="BG517" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -46974,7 +47719,8 @@
       <c r="BC518" s="1"/>
       <c r="BD518" s="1"/>
       <c r="BE518" s="1"/>
-      <c r="BF518" s="1" t="str">
+      <c r="BF518" s="1"/>
+      <c r="BG518" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47040,7 +47786,8 @@
       <c r="BC519" s="1"/>
       <c r="BD519" s="1"/>
       <c r="BE519" s="1"/>
-      <c r="BF519" s="1" t="str">
+      <c r="BF519" s="1"/>
+      <c r="BG519" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47106,7 +47853,8 @@
       <c r="BC520" s="1"/>
       <c r="BD520" s="1"/>
       <c r="BE520" s="1"/>
-      <c r="BF520" s="1" t="str">
+      <c r="BF520" s="1"/>
+      <c r="BG520" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47172,7 +47920,8 @@
       <c r="BC521" s="1"/>
       <c r="BD521" s="1"/>
       <c r="BE521" s="1"/>
-      <c r="BF521" s="1" t="str">
+      <c r="BF521" s="1"/>
+      <c r="BG521" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47238,7 +47987,8 @@
       <c r="BC522" s="1"/>
       <c r="BD522" s="1"/>
       <c r="BE522" s="1"/>
-      <c r="BF522" s="1" t="str">
+      <c r="BF522" s="1"/>
+      <c r="BG522" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47304,7 +48054,8 @@
       <c r="BC523" s="1"/>
       <c r="BD523" s="1"/>
       <c r="BE523" s="1"/>
-      <c r="BF523" s="1" t="str">
+      <c r="BF523" s="1"/>
+      <c r="BG523" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47370,7 +48121,8 @@
       <c r="BC524" s="1"/>
       <c r="BD524" s="1"/>
       <c r="BE524" s="1"/>
-      <c r="BF524" s="1" t="str">
+      <c r="BF524" s="1"/>
+      <c r="BG524" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47436,7 +48188,8 @@
       <c r="BC525" s="1"/>
       <c r="BD525" s="1"/>
       <c r="BE525" s="1"/>
-      <c r="BF525" s="1" t="str">
+      <c r="BF525" s="1"/>
+      <c r="BG525" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47502,7 +48255,8 @@
       <c r="BC526" s="1"/>
       <c r="BD526" s="1"/>
       <c r="BE526" s="1"/>
-      <c r="BF526" s="1" t="str">
+      <c r="BF526" s="1"/>
+      <c r="BG526" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47568,7 +48322,8 @@
       <c r="BC527" s="1"/>
       <c r="BD527" s="1"/>
       <c r="BE527" s="1"/>
-      <c r="BF527" s="1" t="str">
+      <c r="BF527" s="1"/>
+      <c r="BG527" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47634,7 +48389,8 @@
       <c r="BC528" s="1"/>
       <c r="BD528" s="1"/>
       <c r="BE528" s="1"/>
-      <c r="BF528" s="1" t="str">
+      <c r="BF528" s="1"/>
+      <c r="BG528" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47700,7 +48456,8 @@
       <c r="BC529" s="1"/>
       <c r="BD529" s="1"/>
       <c r="BE529" s="1"/>
-      <c r="BF529" s="1" t="str">
+      <c r="BF529" s="1"/>
+      <c r="BG529" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47766,7 +48523,8 @@
       <c r="BC530" s="1"/>
       <c r="BD530" s="1"/>
       <c r="BE530" s="1"/>
-      <c r="BF530" s="1" t="str">
+      <c r="BF530" s="1"/>
+      <c r="BG530" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47832,7 +48590,8 @@
       <c r="BC531" s="1"/>
       <c r="BD531" s="1"/>
       <c r="BE531" s="1"/>
-      <c r="BF531" s="1" t="str">
+      <c r="BF531" s="1"/>
+      <c r="BG531" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47898,7 +48657,8 @@
       <c r="BC532" s="1"/>
       <c r="BD532" s="1"/>
       <c r="BE532" s="1"/>
-      <c r="BF532" s="1" t="str">
+      <c r="BF532" s="1"/>
+      <c r="BG532" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -47964,7 +48724,8 @@
       <c r="BC533" s="1"/>
       <c r="BD533" s="1"/>
       <c r="BE533" s="1"/>
-      <c r="BF533" s="1" t="str">
+      <c r="BF533" s="1"/>
+      <c r="BG533" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48030,7 +48791,8 @@
       <c r="BC534" s="1"/>
       <c r="BD534" s="1"/>
       <c r="BE534" s="1"/>
-      <c r="BF534" s="1" t="str">
+      <c r="BF534" s="1"/>
+      <c r="BG534" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48096,7 +48858,8 @@
       <c r="BC535" s="1"/>
       <c r="BD535" s="1"/>
       <c r="BE535" s="1"/>
-      <c r="BF535" s="1" t="str">
+      <c r="BF535" s="1"/>
+      <c r="BG535" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48162,7 +48925,8 @@
       <c r="BC536" s="1"/>
       <c r="BD536" s="1"/>
       <c r="BE536" s="1"/>
-      <c r="BF536" s="1" t="str">
+      <c r="BF536" s="1"/>
+      <c r="BG536" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48228,7 +48992,8 @@
       <c r="BC537" s="1"/>
       <c r="BD537" s="1"/>
       <c r="BE537" s="1"/>
-      <c r="BF537" s="1" t="str">
+      <c r="BF537" s="1"/>
+      <c r="BG537" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48294,7 +49059,8 @@
       <c r="BC538" s="1"/>
       <c r="BD538" s="1"/>
       <c r="BE538" s="1"/>
-      <c r="BF538" s="1" t="str">
+      <c r="BF538" s="1"/>
+      <c r="BG538" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48360,7 +49126,8 @@
       <c r="BC539" s="1"/>
       <c r="BD539" s="1"/>
       <c r="BE539" s="1"/>
-      <c r="BF539" s="1" t="str">
+      <c r="BF539" s="1"/>
+      <c r="BG539" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48426,7 +49193,8 @@
       <c r="BC540" s="1"/>
       <c r="BD540" s="1"/>
       <c r="BE540" s="1"/>
-      <c r="BF540" s="1" t="str">
+      <c r="BF540" s="1"/>
+      <c r="BG540" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48492,7 +49260,8 @@
       <c r="BC541" s="1"/>
       <c r="BD541" s="1"/>
       <c r="BE541" s="1"/>
-      <c r="BF541" s="1" t="str">
+      <c r="BF541" s="1"/>
+      <c r="BG541" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48558,7 +49327,8 @@
       <c r="BC542" s="1"/>
       <c r="BD542" s="1"/>
       <c r="BE542" s="1"/>
-      <c r="BF542" s="1" t="str">
+      <c r="BF542" s="1"/>
+      <c r="BG542" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48624,7 +49394,8 @@
       <c r="BC543" s="1"/>
       <c r="BD543" s="1"/>
       <c r="BE543" s="1"/>
-      <c r="BF543" s="1" t="str">
+      <c r="BF543" s="1"/>
+      <c r="BG543" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48690,7 +49461,8 @@
       <c r="BC544" s="1"/>
       <c r="BD544" s="1"/>
       <c r="BE544" s="1"/>
-      <c r="BF544" s="1" t="str">
+      <c r="BF544" s="1"/>
+      <c r="BG544" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48756,7 +49528,8 @@
       <c r="BC545" s="1"/>
       <c r="BD545" s="1"/>
       <c r="BE545" s="1"/>
-      <c r="BF545" s="1" t="str">
+      <c r="BF545" s="1"/>
+      <c r="BG545" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48822,7 +49595,8 @@
       <c r="BC546" s="1"/>
       <c r="BD546" s="1"/>
       <c r="BE546" s="1"/>
-      <c r="BF546" s="1" t="str">
+      <c r="BF546" s="1"/>
+      <c r="BG546" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48888,7 +49662,8 @@
       <c r="BC547" s="1"/>
       <c r="BD547" s="1"/>
       <c r="BE547" s="1"/>
-      <c r="BF547" s="1" t="str">
+      <c r="BF547" s="1"/>
+      <c r="BG547" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -48954,7 +49729,8 @@
       <c r="BC548" s="1"/>
       <c r="BD548" s="1"/>
       <c r="BE548" s="1"/>
-      <c r="BF548" s="1" t="str">
+      <c r="BF548" s="1"/>
+      <c r="BG548" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49020,7 +49796,8 @@
       <c r="BC549" s="1"/>
       <c r="BD549" s="1"/>
       <c r="BE549" s="1"/>
-      <c r="BF549" s="1" t="str">
+      <c r="BF549" s="1"/>
+      <c r="BG549" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49086,7 +49863,8 @@
       <c r="BC550" s="1"/>
       <c r="BD550" s="1"/>
       <c r="BE550" s="1"/>
-      <c r="BF550" s="1" t="str">
+      <c r="BF550" s="1"/>
+      <c r="BG550" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49152,7 +49930,8 @@
       <c r="BC551" s="1"/>
       <c r="BD551" s="1"/>
       <c r="BE551" s="1"/>
-      <c r="BF551" s="1" t="str">
+      <c r="BF551" s="1"/>
+      <c r="BG551" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49218,7 +49997,8 @@
       <c r="BC552" s="1"/>
       <c r="BD552" s="1"/>
       <c r="BE552" s="1"/>
-      <c r="BF552" s="1" t="str">
+      <c r="BF552" s="1"/>
+      <c r="BG552" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49284,7 +50064,8 @@
       <c r="BC553" s="1"/>
       <c r="BD553" s="1"/>
       <c r="BE553" s="1"/>
-      <c r="BF553" s="1" t="str">
+      <c r="BF553" s="1"/>
+      <c r="BG553" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49350,7 +50131,8 @@
       <c r="BC554" s="1"/>
       <c r="BD554" s="1"/>
       <c r="BE554" s="1"/>
-      <c r="BF554" s="1" t="str">
+      <c r="BF554" s="1"/>
+      <c r="BG554" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49416,7 +50198,8 @@
       <c r="BC555" s="1"/>
       <c r="BD555" s="1"/>
       <c r="BE555" s="1"/>
-      <c r="BF555" s="1" t="str">
+      <c r="BF555" s="1"/>
+      <c r="BG555" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49482,7 +50265,8 @@
       <c r="BC556" s="1"/>
       <c r="BD556" s="1"/>
       <c r="BE556" s="1"/>
-      <c r="BF556" s="1" t="str">
+      <c r="BF556" s="1"/>
+      <c r="BG556" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49548,7 +50332,8 @@
       <c r="BC557" s="1"/>
       <c r="BD557" s="1"/>
       <c r="BE557" s="1"/>
-      <c r="BF557" s="1" t="str">
+      <c r="BF557" s="1"/>
+      <c r="BG557" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49614,7 +50399,8 @@
       <c r="BC558" s="1"/>
       <c r="BD558" s="1"/>
       <c r="BE558" s="1"/>
-      <c r="BF558" s="1" t="str">
+      <c r="BF558" s="1"/>
+      <c r="BG558" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49680,7 +50466,8 @@
       <c r="BC559" s="1"/>
       <c r="BD559" s="1"/>
       <c r="BE559" s="1"/>
-      <c r="BF559" s="1" t="str">
+      <c r="BF559" s="1"/>
+      <c r="BG559" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49746,7 +50533,8 @@
       <c r="BC560" s="1"/>
       <c r="BD560" s="1"/>
       <c r="BE560" s="1"/>
-      <c r="BF560" s="1" t="str">
+      <c r="BF560" s="1"/>
+      <c r="BG560" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49812,7 +50600,8 @@
       <c r="BC561" s="1"/>
       <c r="BD561" s="1"/>
       <c r="BE561" s="1"/>
-      <c r="BF561" s="1" t="str">
+      <c r="BF561" s="1"/>
+      <c r="BG561" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49878,7 +50667,8 @@
       <c r="BC562" s="1"/>
       <c r="BD562" s="1"/>
       <c r="BE562" s="1"/>
-      <c r="BF562" s="1" t="str">
+      <c r="BF562" s="1"/>
+      <c r="BG562" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -49944,7 +50734,8 @@
       <c r="BC563" s="1"/>
       <c r="BD563" s="1"/>
       <c r="BE563" s="1"/>
-      <c r="BF563" s="1" t="str">
+      <c r="BF563" s="1"/>
+      <c r="BG563" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50010,7 +50801,8 @@
       <c r="BC564" s="1"/>
       <c r="BD564" s="1"/>
       <c r="BE564" s="1"/>
-      <c r="BF564" s="1" t="str">
+      <c r="BF564" s="1"/>
+      <c r="BG564" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50076,7 +50868,8 @@
       <c r="BC565" s="1"/>
       <c r="BD565" s="1"/>
       <c r="BE565" s="1"/>
-      <c r="BF565" s="1" t="str">
+      <c r="BF565" s="1"/>
+      <c r="BG565" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50142,7 +50935,8 @@
       <c r="BC566" s="1"/>
       <c r="BD566" s="1"/>
       <c r="BE566" s="1"/>
-      <c r="BF566" s="1" t="str">
+      <c r="BF566" s="1"/>
+      <c r="BG566" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50208,7 +51002,8 @@
       <c r="BC567" s="1"/>
       <c r="BD567" s="1"/>
       <c r="BE567" s="1"/>
-      <c r="BF567" s="1" t="str">
+      <c r="BF567" s="1"/>
+      <c r="BG567" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50274,7 +51069,8 @@
       <c r="BC568" s="1"/>
       <c r="BD568" s="1"/>
       <c r="BE568" s="1"/>
-      <c r="BF568" s="1" t="str">
+      <c r="BF568" s="1"/>
+      <c r="BG568" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50340,7 +51136,8 @@
       <c r="BC569" s="1"/>
       <c r="BD569" s="1"/>
       <c r="BE569" s="1"/>
-      <c r="BF569" s="1" t="str">
+      <c r="BF569" s="1"/>
+      <c r="BG569" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50406,7 +51203,8 @@
       <c r="BC570" s="1"/>
       <c r="BD570" s="1"/>
       <c r="BE570" s="1"/>
-      <c r="BF570" s="1" t="str">
+      <c r="BF570" s="1"/>
+      <c r="BG570" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50472,7 +51270,8 @@
       <c r="BC571" s="1"/>
       <c r="BD571" s="1"/>
       <c r="BE571" s="1"/>
-      <c r="BF571" s="1" t="str">
+      <c r="BF571" s="1"/>
+      <c r="BG571" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50538,7 +51337,8 @@
       <c r="BC572" s="1"/>
       <c r="BD572" s="1"/>
       <c r="BE572" s="1"/>
-      <c r="BF572" s="1" t="str">
+      <c r="BF572" s="1"/>
+      <c r="BG572" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50604,7 +51404,8 @@
       <c r="BC573" s="1"/>
       <c r="BD573" s="1"/>
       <c r="BE573" s="1"/>
-      <c r="BF573" s="1" t="str">
+      <c r="BF573" s="1"/>
+      <c r="BG573" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50670,7 +51471,8 @@
       <c r="BC574" s="1"/>
       <c r="BD574" s="1"/>
       <c r="BE574" s="1"/>
-      <c r="BF574" s="1" t="str">
+      <c r="BF574" s="1"/>
+      <c r="BG574" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50736,7 +51538,8 @@
       <c r="BC575" s="1"/>
       <c r="BD575" s="1"/>
       <c r="BE575" s="1"/>
-      <c r="BF575" s="1" t="str">
+      <c r="BF575" s="1"/>
+      <c r="BG575" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50802,7 +51605,8 @@
       <c r="BC576" s="1"/>
       <c r="BD576" s="1"/>
       <c r="BE576" s="1"/>
-      <c r="BF576" s="1" t="str">
+      <c r="BF576" s="1"/>
+      <c r="BG576" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50868,7 +51672,8 @@
       <c r="BC577" s="1"/>
       <c r="BD577" s="1"/>
       <c r="BE577" s="1"/>
-      <c r="BF577" s="1" t="str">
+      <c r="BF577" s="1"/>
+      <c r="BG577" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -50934,7 +51739,8 @@
       <c r="BC578" s="1"/>
       <c r="BD578" s="1"/>
       <c r="BE578" s="1"/>
-      <c r="BF578" s="1" t="str">
+      <c r="BF578" s="1"/>
+      <c r="BG578" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51000,7 +51806,8 @@
       <c r="BC579" s="1"/>
       <c r="BD579" s="1"/>
       <c r="BE579" s="1"/>
-      <c r="BF579" s="1" t="str">
+      <c r="BF579" s="1"/>
+      <c r="BG579" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51066,7 +51873,8 @@
       <c r="BC580" s="1"/>
       <c r="BD580" s="1"/>
       <c r="BE580" s="1"/>
-      <c r="BF580" s="1" t="str">
+      <c r="BF580" s="1"/>
+      <c r="BG580" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51132,7 +51940,8 @@
       <c r="BC581" s="1"/>
       <c r="BD581" s="1"/>
       <c r="BE581" s="1"/>
-      <c r="BF581" s="1" t="str">
+      <c r="BF581" s="1"/>
+      <c r="BG581" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51198,7 +52007,8 @@
       <c r="BC582" s="1"/>
       <c r="BD582" s="1"/>
       <c r="BE582" s="1"/>
-      <c r="BF582" s="1" t="str">
+      <c r="BF582" s="1"/>
+      <c r="BG582" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51264,7 +52074,8 @@
       <c r="BC583" s="1"/>
       <c r="BD583" s="1"/>
       <c r="BE583" s="1"/>
-      <c r="BF583" s="1" t="str">
+      <c r="BF583" s="1"/>
+      <c r="BG583" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51330,7 +52141,8 @@
       <c r="BC584" s="1"/>
       <c r="BD584" s="1"/>
       <c r="BE584" s="1"/>
-      <c r="BF584" s="1" t="str">
+      <c r="BF584" s="1"/>
+      <c r="BG584" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51396,7 +52208,8 @@
       <c r="BC585" s="1"/>
       <c r="BD585" s="1"/>
       <c r="BE585" s="1"/>
-      <c r="BF585" s="1" t="str">
+      <c r="BF585" s="1"/>
+      <c r="BG585" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51462,7 +52275,8 @@
       <c r="BC586" s="1"/>
       <c r="BD586" s="1"/>
       <c r="BE586" s="1"/>
-      <c r="BF586" s="1" t="str">
+      <c r="BF586" s="1"/>
+      <c r="BG586" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51528,7 +52342,8 @@
       <c r="BC587" s="1"/>
       <c r="BD587" s="1"/>
       <c r="BE587" s="1"/>
-      <c r="BF587" s="1" t="str">
+      <c r="BF587" s="1"/>
+      <c r="BG587" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51594,7 +52409,8 @@
       <c r="BC588" s="1"/>
       <c r="BD588" s="1"/>
       <c r="BE588" s="1"/>
-      <c r="BF588" s="1" t="str">
+      <c r="BF588" s="1"/>
+      <c r="BG588" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51660,7 +52476,8 @@
       <c r="BC589" s="1"/>
       <c r="BD589" s="1"/>
       <c r="BE589" s="1"/>
-      <c r="BF589" s="1" t="str">
+      <c r="BF589" s="1"/>
+      <c r="BG589" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51726,7 +52543,8 @@
       <c r="BC590" s="1"/>
       <c r="BD590" s="1"/>
       <c r="BE590" s="1"/>
-      <c r="BF590" s="1" t="str">
+      <c r="BF590" s="1"/>
+      <c r="BG590" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51792,7 +52610,8 @@
       <c r="BC591" s="1"/>
       <c r="BD591" s="1"/>
       <c r="BE591" s="1"/>
-      <c r="BF591" s="1" t="str">
+      <c r="BF591" s="1"/>
+      <c r="BG591" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51858,7 +52677,8 @@
       <c r="BC592" s="1"/>
       <c r="BD592" s="1"/>
       <c r="BE592" s="1"/>
-      <c r="BF592" s="1" t="str">
+      <c r="BF592" s="1"/>
+      <c r="BG592" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51924,7 +52744,8 @@
       <c r="BC593" s="1"/>
       <c r="BD593" s="1"/>
       <c r="BE593" s="1"/>
-      <c r="BF593" s="1" t="str">
+      <c r="BF593" s="1"/>
+      <c r="BG593" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -51990,7 +52811,8 @@
       <c r="BC594" s="1"/>
       <c r="BD594" s="1"/>
       <c r="BE594" s="1"/>
-      <c r="BF594" s="1" t="str">
+      <c r="BF594" s="1"/>
+      <c r="BG594" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52056,7 +52878,8 @@
       <c r="BC595" s="1"/>
       <c r="BD595" s="1"/>
       <c r="BE595" s="1"/>
-      <c r="BF595" s="1" t="str">
+      <c r="BF595" s="1"/>
+      <c r="BG595" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52122,7 +52945,8 @@
       <c r="BC596" s="1"/>
       <c r="BD596" s="1"/>
       <c r="BE596" s="1"/>
-      <c r="BF596" s="1" t="str">
+      <c r="BF596" s="1"/>
+      <c r="BG596" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52188,7 +53012,8 @@
       <c r="BC597" s="1"/>
       <c r="BD597" s="1"/>
       <c r="BE597" s="1"/>
-      <c r="BF597" s="1" t="str">
+      <c r="BF597" s="1"/>
+      <c r="BG597" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52254,7 +53079,8 @@
       <c r="BC598" s="1"/>
       <c r="BD598" s="1"/>
       <c r="BE598" s="1"/>
-      <c r="BF598" s="1" t="str">
+      <c r="BF598" s="1"/>
+      <c r="BG598" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52320,7 +53146,8 @@
       <c r="BC599" s="1"/>
       <c r="BD599" s="1"/>
       <c r="BE599" s="1"/>
-      <c r="BF599" s="1" t="str">
+      <c r="BF599" s="1"/>
+      <c r="BG599" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52386,7 +53213,8 @@
       <c r="BC600" s="1"/>
       <c r="BD600" s="1"/>
       <c r="BE600" s="1"/>
-      <c r="BF600" s="1" t="str">
+      <c r="BF600" s="1"/>
+      <c r="BG600" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52452,7 +53280,8 @@
       <c r="BC601" s="1"/>
       <c r="BD601" s="1"/>
       <c r="BE601" s="1"/>
-      <c r="BF601" s="1" t="str">
+      <c r="BF601" s="1"/>
+      <c r="BG601" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52518,7 +53347,8 @@
       <c r="BC602" s="1"/>
       <c r="BD602" s="1"/>
       <c r="BE602" s="1"/>
-      <c r="BF602" s="1" t="str">
+      <c r="BF602" s="1"/>
+      <c r="BG602" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52584,7 +53414,8 @@
       <c r="BC603" s="1"/>
       <c r="BD603" s="1"/>
       <c r="BE603" s="1"/>
-      <c r="BF603" s="1" t="str">
+      <c r="BF603" s="1"/>
+      <c r="BG603" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52650,7 +53481,8 @@
       <c r="BC604" s="1"/>
       <c r="BD604" s="1"/>
       <c r="BE604" s="1"/>
-      <c r="BF604" s="1" t="str">
+      <c r="BF604" s="1"/>
+      <c r="BG604" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52716,7 +53548,8 @@
       <c r="BC605" s="1"/>
       <c r="BD605" s="1"/>
       <c r="BE605" s="1"/>
-      <c r="BF605" s="1" t="str">
+      <c r="BF605" s="1"/>
+      <c r="BG605" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52782,7 +53615,8 @@
       <c r="BC606" s="1"/>
       <c r="BD606" s="1"/>
       <c r="BE606" s="1"/>
-      <c r="BF606" s="1" t="str">
+      <c r="BF606" s="1"/>
+      <c r="BG606" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52848,7 +53682,8 @@
       <c r="BC607" s="1"/>
       <c r="BD607" s="1"/>
       <c r="BE607" s="1"/>
-      <c r="BF607" s="1" t="str">
+      <c r="BF607" s="1"/>
+      <c r="BG607" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52914,7 +53749,8 @@
       <c r="BC608" s="1"/>
       <c r="BD608" s="1"/>
       <c r="BE608" s="1"/>
-      <c r="BF608" s="1" t="str">
+      <c r="BF608" s="1"/>
+      <c r="BG608" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -52980,7 +53816,8 @@
       <c r="BC609" s="1"/>
       <c r="BD609" s="1"/>
       <c r="BE609" s="1"/>
-      <c r="BF609" s="1" t="str">
+      <c r="BF609" s="1"/>
+      <c r="BG609" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53046,7 +53883,8 @@
       <c r="BC610" s="1"/>
       <c r="BD610" s="1"/>
       <c r="BE610" s="1"/>
-      <c r="BF610" s="1" t="str">
+      <c r="BF610" s="1"/>
+      <c r="BG610" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53112,7 +53950,8 @@
       <c r="BC611" s="1"/>
       <c r="BD611" s="1"/>
       <c r="BE611" s="1"/>
-      <c r="BF611" s="1" t="str">
+      <c r="BF611" s="1"/>
+      <c r="BG611" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53178,7 +54017,8 @@
       <c r="BC612" s="1"/>
       <c r="BD612" s="1"/>
       <c r="BE612" s="1"/>
-      <c r="BF612" s="1" t="str">
+      <c r="BF612" s="1"/>
+      <c r="BG612" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53244,7 +54084,8 @@
       <c r="BC613" s="1"/>
       <c r="BD613" s="1"/>
       <c r="BE613" s="1"/>
-      <c r="BF613" s="1" t="str">
+      <c r="BF613" s="1"/>
+      <c r="BG613" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53310,7 +54151,8 @@
       <c r="BC614" s="1"/>
       <c r="BD614" s="1"/>
       <c r="BE614" s="1"/>
-      <c r="BF614" s="1" t="str">
+      <c r="BF614" s="1"/>
+      <c r="BG614" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53376,7 +54218,8 @@
       <c r="BC615" s="1"/>
       <c r="BD615" s="1"/>
       <c r="BE615" s="1"/>
-      <c r="BF615" s="1" t="str">
+      <c r="BF615" s="1"/>
+      <c r="BG615" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53442,7 +54285,8 @@
       <c r="BC616" s="1"/>
       <c r="BD616" s="1"/>
       <c r="BE616" s="1"/>
-      <c r="BF616" s="1" t="str">
+      <c r="BF616" s="1"/>
+      <c r="BG616" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53508,7 +54352,8 @@
       <c r="BC617" s="1"/>
       <c r="BD617" s="1"/>
       <c r="BE617" s="1"/>
-      <c r="BF617" s="1" t="str">
+      <c r="BF617" s="1"/>
+      <c r="BG617" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53574,7 +54419,8 @@
       <c r="BC618" s="1"/>
       <c r="BD618" s="1"/>
       <c r="BE618" s="1"/>
-      <c r="BF618" s="1" t="str">
+      <c r="BF618" s="1"/>
+      <c r="BG618" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53640,7 +54486,8 @@
       <c r="BC619" s="1"/>
       <c r="BD619" s="1"/>
       <c r="BE619" s="1"/>
-      <c r="BF619" s="1" t="str">
+      <c r="BF619" s="1"/>
+      <c r="BG619" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53706,7 +54553,8 @@
       <c r="BC620" s="1"/>
       <c r="BD620" s="1"/>
       <c r="BE620" s="1"/>
-      <c r="BF620" s="1" t="str">
+      <c r="BF620" s="1"/>
+      <c r="BG620" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53772,7 +54620,8 @@
       <c r="BC621" s="1"/>
       <c r="BD621" s="1"/>
       <c r="BE621" s="1"/>
-      <c r="BF621" s="1" t="str">
+      <c r="BF621" s="1"/>
+      <c r="BG621" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53838,7 +54687,8 @@
       <c r="BC622" s="1"/>
       <c r="BD622" s="1"/>
       <c r="BE622" s="1"/>
-      <c r="BF622" s="1" t="str">
+      <c r="BF622" s="1"/>
+      <c r="BG622" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53904,7 +54754,8 @@
       <c r="BC623" s="1"/>
       <c r="BD623" s="1"/>
       <c r="BE623" s="1"/>
-      <c r="BF623" s="1" t="str">
+      <c r="BF623" s="1"/>
+      <c r="BG623" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -53970,7 +54821,8 @@
       <c r="BC624" s="1"/>
       <c r="BD624" s="1"/>
       <c r="BE624" s="1"/>
-      <c r="BF624" s="1" t="str">
+      <c r="BF624" s="1"/>
+      <c r="BG624" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54036,7 +54888,8 @@
       <c r="BC625" s="1"/>
       <c r="BD625" s="1"/>
       <c r="BE625" s="1"/>
-      <c r="BF625" s="1" t="str">
+      <c r="BF625" s="1"/>
+      <c r="BG625" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54102,7 +54955,8 @@
       <c r="BC626" s="1"/>
       <c r="BD626" s="1"/>
       <c r="BE626" s="1"/>
-      <c r="BF626" s="1" t="str">
+      <c r="BF626" s="1"/>
+      <c r="BG626" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54168,7 +55022,8 @@
       <c r="BC627" s="1"/>
       <c r="BD627" s="1"/>
       <c r="BE627" s="1"/>
-      <c r="BF627" s="1" t="str">
+      <c r="BF627" s="1"/>
+      <c r="BG627" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54234,7 +55089,8 @@
       <c r="BC628" s="1"/>
       <c r="BD628" s="1"/>
       <c r="BE628" s="1"/>
-      <c r="BF628" s="1" t="str">
+      <c r="BF628" s="1"/>
+      <c r="BG628" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54300,7 +55156,8 @@
       <c r="BC629" s="1"/>
       <c r="BD629" s="1"/>
       <c r="BE629" s="1"/>
-      <c r="BF629" s="1" t="str">
+      <c r="BF629" s="1"/>
+      <c r="BG629" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54366,7 +55223,8 @@
       <c r="BC630" s="1"/>
       <c r="BD630" s="1"/>
       <c r="BE630" s="1"/>
-      <c r="BF630" s="1" t="str">
+      <c r="BF630" s="1"/>
+      <c r="BG630" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54432,7 +55290,8 @@
       <c r="BC631" s="1"/>
       <c r="BD631" s="1"/>
       <c r="BE631" s="1"/>
-      <c r="BF631" s="1" t="str">
+      <c r="BF631" s="1"/>
+      <c r="BG631" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54498,7 +55357,8 @@
       <c r="BC632" s="1"/>
       <c r="BD632" s="1"/>
       <c r="BE632" s="1"/>
-      <c r="BF632" s="1" t="str">
+      <c r="BF632" s="1"/>
+      <c r="BG632" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54564,7 +55424,8 @@
       <c r="BC633" s="1"/>
       <c r="BD633" s="1"/>
       <c r="BE633" s="1"/>
-      <c r="BF633" s="1" t="str">
+      <c r="BF633" s="1"/>
+      <c r="BG633" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54630,7 +55491,8 @@
       <c r="BC634" s="1"/>
       <c r="BD634" s="1"/>
       <c r="BE634" s="1"/>
-      <c r="BF634" s="1" t="str">
+      <c r="BF634" s="1"/>
+      <c r="BG634" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54696,7 +55558,8 @@
       <c r="BC635" s="1"/>
       <c r="BD635" s="1"/>
       <c r="BE635" s="1"/>
-      <c r="BF635" s="1" t="str">
+      <c r="BF635" s="1"/>
+      <c r="BG635" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54762,7 +55625,8 @@
       <c r="BC636" s="1"/>
       <c r="BD636" s="1"/>
       <c r="BE636" s="1"/>
-      <c r="BF636" s="1" t="str">
+      <c r="BF636" s="1"/>
+      <c r="BG636" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54828,7 +55692,8 @@
       <c r="BC637" s="1"/>
       <c r="BD637" s="1"/>
       <c r="BE637" s="1"/>
-      <c r="BF637" s="1" t="str">
+      <c r="BF637" s="1"/>
+      <c r="BG637" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54894,7 +55759,8 @@
       <c r="BC638" s="1"/>
       <c r="BD638" s="1"/>
       <c r="BE638" s="1"/>
-      <c r="BF638" s="1" t="str">
+      <c r="BF638" s="1"/>
+      <c r="BG638" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -54960,7 +55826,8 @@
       <c r="BC639" s="1"/>
       <c r="BD639" s="1"/>
       <c r="BE639" s="1"/>
-      <c r="BF639" s="1" t="str">
+      <c r="BF639" s="1"/>
+      <c r="BG639" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55026,7 +55893,8 @@
       <c r="BC640" s="1"/>
       <c r="BD640" s="1"/>
       <c r="BE640" s="1"/>
-      <c r="BF640" s="1" t="str">
+      <c r="BF640" s="1"/>
+      <c r="BG640" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55092,7 +55960,8 @@
       <c r="BC641" s="1"/>
       <c r="BD641" s="1"/>
       <c r="BE641" s="1"/>
-      <c r="BF641" s="1" t="str">
+      <c r="BF641" s="1"/>
+      <c r="BG641" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55158,7 +56027,8 @@
       <c r="BC642" s="1"/>
       <c r="BD642" s="1"/>
       <c r="BE642" s="1"/>
-      <c r="BF642" s="1" t="str">
+      <c r="BF642" s="1"/>
+      <c r="BG642" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55224,7 +56094,8 @@
       <c r="BC643" s="1"/>
       <c r="BD643" s="1"/>
       <c r="BE643" s="1"/>
-      <c r="BF643" s="1" t="str">
+      <c r="BF643" s="1"/>
+      <c r="BG643" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55290,7 +56161,8 @@
       <c r="BC644" s="1"/>
       <c r="BD644" s="1"/>
       <c r="BE644" s="1"/>
-      <c r="BF644" s="1" t="str">
+      <c r="BF644" s="1"/>
+      <c r="BG644" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55356,7 +56228,8 @@
       <c r="BC645" s="1"/>
       <c r="BD645" s="1"/>
       <c r="BE645" s="1"/>
-      <c r="BF645" s="1" t="str">
+      <c r="BF645" s="1"/>
+      <c r="BG645" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55422,7 +56295,8 @@
       <c r="BC646" s="1"/>
       <c r="BD646" s="1"/>
       <c r="BE646" s="1"/>
-      <c r="BF646" s="1" t="str">
+      <c r="BF646" s="1"/>
+      <c r="BG646" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55488,7 +56362,8 @@
       <c r="BC647" s="1"/>
       <c r="BD647" s="1"/>
       <c r="BE647" s="1"/>
-      <c r="BF647" s="1" t="str">
+      <c r="BF647" s="1"/>
+      <c r="BG647" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55554,7 +56429,8 @@
       <c r="BC648" s="1"/>
       <c r="BD648" s="1"/>
       <c r="BE648" s="1"/>
-      <c r="BF648" s="1" t="str">
+      <c r="BF648" s="1"/>
+      <c r="BG648" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55620,7 +56496,8 @@
       <c r="BC649" s="1"/>
       <c r="BD649" s="1"/>
       <c r="BE649" s="1"/>
-      <c r="BF649" s="1" t="str">
+      <c r="BF649" s="1"/>
+      <c r="BG649" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55686,7 +56563,8 @@
       <c r="BC650" s="1"/>
       <c r="BD650" s="1"/>
       <c r="BE650" s="1"/>
-      <c r="BF650" s="1" t="str">
+      <c r="BF650" s="1"/>
+      <c r="BG650" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55752,7 +56630,8 @@
       <c r="BC651" s="1"/>
       <c r="BD651" s="1"/>
       <c r="BE651" s="1"/>
-      <c r="BF651" s="1" t="str">
+      <c r="BF651" s="1"/>
+      <c r="BG651" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55818,7 +56697,8 @@
       <c r="BC652" s="1"/>
       <c r="BD652" s="1"/>
       <c r="BE652" s="1"/>
-      <c r="BF652" s="1" t="str">
+      <c r="BF652" s="1"/>
+      <c r="BG652" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55884,7 +56764,8 @@
       <c r="BC653" s="1"/>
       <c r="BD653" s="1"/>
       <c r="BE653" s="1"/>
-      <c r="BF653" s="1" t="str">
+      <c r="BF653" s="1"/>
+      <c r="BG653" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -55950,7 +56831,8 @@
       <c r="BC654" s="1"/>
       <c r="BD654" s="1"/>
       <c r="BE654" s="1"/>
-      <c r="BF654" s="1" t="str">
+      <c r="BF654" s="1"/>
+      <c r="BG654" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56016,7 +56898,8 @@
       <c r="BC655" s="1"/>
       <c r="BD655" s="1"/>
       <c r="BE655" s="1"/>
-      <c r="BF655" s="1" t="str">
+      <c r="BF655" s="1"/>
+      <c r="BG655" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56082,7 +56965,8 @@
       <c r="BC656" s="1"/>
       <c r="BD656" s="1"/>
       <c r="BE656" s="1"/>
-      <c r="BF656" s="1" t="str">
+      <c r="BF656" s="1"/>
+      <c r="BG656" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56148,7 +57032,8 @@
       <c r="BC657" s="1"/>
       <c r="BD657" s="1"/>
       <c r="BE657" s="1"/>
-      <c r="BF657" s="1" t="str">
+      <c r="BF657" s="1"/>
+      <c r="BG657" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56214,7 +57099,8 @@
       <c r="BC658" s="1"/>
       <c r="BD658" s="1"/>
       <c r="BE658" s="1"/>
-      <c r="BF658" s="1" t="str">
+      <c r="BF658" s="1"/>
+      <c r="BG658" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56280,7 +57166,8 @@
       <c r="BC659" s="1"/>
       <c r="BD659" s="1"/>
       <c r="BE659" s="1"/>
-      <c r="BF659" s="1" t="str">
+      <c r="BF659" s="1"/>
+      <c r="BG659" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56346,7 +57233,8 @@
       <c r="BC660" s="1"/>
       <c r="BD660" s="1"/>
       <c r="BE660" s="1"/>
-      <c r="BF660" s="1" t="str">
+      <c r="BF660" s="1"/>
+      <c r="BG660" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56412,7 +57300,8 @@
       <c r="BC661" s="1"/>
       <c r="BD661" s="1"/>
       <c r="BE661" s="1"/>
-      <c r="BF661" s="1" t="str">
+      <c r="BF661" s="1"/>
+      <c r="BG661" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56478,7 +57367,8 @@
       <c r="BC662" s="1"/>
       <c r="BD662" s="1"/>
       <c r="BE662" s="1"/>
-      <c r="BF662" s="1" t="str">
+      <c r="BF662" s="1"/>
+      <c r="BG662" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56544,7 +57434,8 @@
       <c r="BC663" s="1"/>
       <c r="BD663" s="1"/>
       <c r="BE663" s="1"/>
-      <c r="BF663" s="1" t="str">
+      <c r="BF663" s="1"/>
+      <c r="BG663" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56610,7 +57501,8 @@
       <c r="BC664" s="1"/>
       <c r="BD664" s="1"/>
       <c r="BE664" s="1"/>
-      <c r="BF664" s="1" t="str">
+      <c r="BF664" s="1"/>
+      <c r="BG664" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56676,7 +57568,8 @@
       <c r="BC665" s="1"/>
       <c r="BD665" s="1"/>
       <c r="BE665" s="1"/>
-      <c r="BF665" s="1" t="str">
+      <c r="BF665" s="1"/>
+      <c r="BG665" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56742,7 +57635,8 @@
       <c r="BC666" s="1"/>
       <c r="BD666" s="1"/>
       <c r="BE666" s="1"/>
-      <c r="BF666" s="1" t="str">
+      <c r="BF666" s="1"/>
+      <c r="BG666" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56808,7 +57702,8 @@
       <c r="BC667" s="1"/>
       <c r="BD667" s="1"/>
       <c r="BE667" s="1"/>
-      <c r="BF667" s="1" t="str">
+      <c r="BF667" s="1"/>
+      <c r="BG667" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56874,7 +57769,8 @@
       <c r="BC668" s="1"/>
       <c r="BD668" s="1"/>
       <c r="BE668" s="1"/>
-      <c r="BF668" s="1" t="str">
+      <c r="BF668" s="1"/>
+      <c r="BG668" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -56940,7 +57836,8 @@
       <c r="BC669" s="1"/>
       <c r="BD669" s="1"/>
       <c r="BE669" s="1"/>
-      <c r="BF669" s="1" t="str">
+      <c r="BF669" s="1"/>
+      <c r="BG669" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57006,7 +57903,8 @@
       <c r="BC670" s="1"/>
       <c r="BD670" s="1"/>
       <c r="BE670" s="1"/>
-      <c r="BF670" s="1" t="str">
+      <c r="BF670" s="1"/>
+      <c r="BG670" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57072,7 +57970,8 @@
       <c r="BC671" s="1"/>
       <c r="BD671" s="1"/>
       <c r="BE671" s="1"/>
-      <c r="BF671" s="1" t="str">
+      <c r="BF671" s="1"/>
+      <c r="BG671" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57138,7 +58037,8 @@
       <c r="BC672" s="1"/>
       <c r="BD672" s="1"/>
       <c r="BE672" s="1"/>
-      <c r="BF672" s="1" t="str">
+      <c r="BF672" s="1"/>
+      <c r="BG672" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57204,7 +58104,8 @@
       <c r="BC673" s="1"/>
       <c r="BD673" s="1"/>
       <c r="BE673" s="1"/>
-      <c r="BF673" s="1" t="str">
+      <c r="BF673" s="1"/>
+      <c r="BG673" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57270,7 +58171,8 @@
       <c r="BC674" s="1"/>
       <c r="BD674" s="1"/>
       <c r="BE674" s="1"/>
-      <c r="BF674" s="1" t="str">
+      <c r="BF674" s="1"/>
+      <c r="BG674" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57336,7 +58238,8 @@
       <c r="BC675" s="1"/>
       <c r="BD675" s="1"/>
       <c r="BE675" s="1"/>
-      <c r="BF675" s="1" t="str">
+      <c r="BF675" s="1"/>
+      <c r="BG675" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57402,7 +58305,8 @@
       <c r="BC676" s="1"/>
       <c r="BD676" s="1"/>
       <c r="BE676" s="1"/>
-      <c r="BF676" s="1" t="str">
+      <c r="BF676" s="1"/>
+      <c r="BG676" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57468,7 +58372,8 @@
       <c r="BC677" s="1"/>
       <c r="BD677" s="1"/>
       <c r="BE677" s="1"/>
-      <c r="BF677" s="1" t="str">
+      <c r="BF677" s="1"/>
+      <c r="BG677" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57534,7 +58439,8 @@
       <c r="BC678" s="1"/>
       <c r="BD678" s="1"/>
       <c r="BE678" s="1"/>
-      <c r="BF678" s="1" t="str">
+      <c r="BF678" s="1"/>
+      <c r="BG678" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57600,7 +58506,8 @@
       <c r="BC679" s="1"/>
       <c r="BD679" s="1"/>
       <c r="BE679" s="1"/>
-      <c r="BF679" s="1" t="str">
+      <c r="BF679" s="1"/>
+      <c r="BG679" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57666,7 +58573,8 @@
       <c r="BC680" s="1"/>
       <c r="BD680" s="1"/>
       <c r="BE680" s="1"/>
-      <c r="BF680" s="1" t="str">
+      <c r="BF680" s="1"/>
+      <c r="BG680" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57732,7 +58640,8 @@
       <c r="BC681" s="1"/>
       <c r="BD681" s="1"/>
       <c r="BE681" s="1"/>
-      <c r="BF681" s="1" t="str">
+      <c r="BF681" s="1"/>
+      <c r="BG681" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57798,7 +58707,8 @@
       <c r="BC682" s="1"/>
       <c r="BD682" s="1"/>
       <c r="BE682" s="1"/>
-      <c r="BF682" s="1" t="str">
+      <c r="BF682" s="1"/>
+      <c r="BG682" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57864,7 +58774,8 @@
       <c r="BC683" s="1"/>
       <c r="BD683" s="1"/>
       <c r="BE683" s="1"/>
-      <c r="BF683" s="1" t="str">
+      <c r="BF683" s="1"/>
+      <c r="BG683" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57930,7 +58841,8 @@
       <c r="BC684" s="1"/>
       <c r="BD684" s="1"/>
       <c r="BE684" s="1"/>
-      <c r="BF684" s="1" t="str">
+      <c r="BF684" s="1"/>
+      <c r="BG684" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -57996,7 +58908,8 @@
       <c r="BC685" s="1"/>
       <c r="BD685" s="1"/>
       <c r="BE685" s="1"/>
-      <c r="BF685" s="1" t="str">
+      <c r="BF685" s="1"/>
+      <c r="BG685" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58062,7 +58975,8 @@
       <c r="BC686" s="1"/>
       <c r="BD686" s="1"/>
       <c r="BE686" s="1"/>
-      <c r="BF686" s="1" t="str">
+      <c r="BF686" s="1"/>
+      <c r="BG686" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58128,7 +59042,8 @@
       <c r="BC687" s="1"/>
       <c r="BD687" s="1"/>
       <c r="BE687" s="1"/>
-      <c r="BF687" s="1" t="str">
+      <c r="BF687" s="1"/>
+      <c r="BG687" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58194,7 +59109,8 @@
       <c r="BC688" s="1"/>
       <c r="BD688" s="1"/>
       <c r="BE688" s="1"/>
-      <c r="BF688" s="1" t="str">
+      <c r="BF688" s="1"/>
+      <c r="BG688" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58260,7 +59176,8 @@
       <c r="BC689" s="1"/>
       <c r="BD689" s="1"/>
       <c r="BE689" s="1"/>
-      <c r="BF689" s="1" t="str">
+      <c r="BF689" s="1"/>
+      <c r="BG689" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58326,7 +59243,8 @@
       <c r="BC690" s="1"/>
       <c r="BD690" s="1"/>
       <c r="BE690" s="1"/>
-      <c r="BF690" s="1" t="str">
+      <c r="BF690" s="1"/>
+      <c r="BG690" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58392,7 +59310,8 @@
       <c r="BC691" s="1"/>
       <c r="BD691" s="1"/>
       <c r="BE691" s="1"/>
-      <c r="BF691" s="1" t="str">
+      <c r="BF691" s="1"/>
+      <c r="BG691" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58458,7 +59377,8 @@
       <c r="BC692" s="1"/>
       <c r="BD692" s="1"/>
       <c r="BE692" s="1"/>
-      <c r="BF692" s="1" t="str">
+      <c r="BF692" s="1"/>
+      <c r="BG692" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58524,7 +59444,8 @@
       <c r="BC693" s="1"/>
       <c r="BD693" s="1"/>
       <c r="BE693" s="1"/>
-      <c r="BF693" s="1" t="str">
+      <c r="BF693" s="1"/>
+      <c r="BG693" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58590,7 +59511,8 @@
       <c r="BC694" s="1"/>
       <c r="BD694" s="1"/>
       <c r="BE694" s="1"/>
-      <c r="BF694" s="1" t="str">
+      <c r="BF694" s="1"/>
+      <c r="BG694" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58656,7 +59578,8 @@
       <c r="BC695" s="1"/>
       <c r="BD695" s="1"/>
       <c r="BE695" s="1"/>
-      <c r="BF695" s="1" t="str">
+      <c r="BF695" s="1"/>
+      <c r="BG695" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58722,7 +59645,8 @@
       <c r="BC696" s="1"/>
       <c r="BD696" s="1"/>
       <c r="BE696" s="1"/>
-      <c r="BF696" s="1" t="str">
+      <c r="BF696" s="1"/>
+      <c r="BG696" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58788,7 +59712,8 @@
       <c r="BC697" s="1"/>
       <c r="BD697" s="1"/>
       <c r="BE697" s="1"/>
-      <c r="BF697" s="1" t="str">
+      <c r="BF697" s="1"/>
+      <c r="BG697" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58854,7 +59779,8 @@
       <c r="BC698" s="1"/>
       <c r="BD698" s="1"/>
       <c r="BE698" s="1"/>
-      <c r="BF698" s="1" t="str">
+      <c r="BF698" s="1"/>
+      <c r="BG698" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58920,7 +59846,8 @@
       <c r="BC699" s="1"/>
       <c r="BD699" s="1"/>
       <c r="BE699" s="1"/>
-      <c r="BF699" s="1" t="str">
+      <c r="BF699" s="1"/>
+      <c r="BG699" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
@@ -58986,7 +59913,8 @@
       <c r="BC700" s="1"/>
       <c r="BD700" s="1"/>
       <c r="BE700" s="1"/>
-      <c r="BF700" s="1" t="str">
+      <c r="BF700" s="1"/>
+      <c r="BG700" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>

--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -956,10 +956,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1000.0)</f>
         <v>1000</v>
       </c>
-      <c r="BC3" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC3" s="1"/>
       <c r="BD3" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -1191,10 +1188,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1300.0)</f>
         <v>1300</v>
       </c>
-      <c r="BC4" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC4" s="1"/>
       <c r="BD4" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -2116,10 +2110,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),880.0)</f>
         <v>880</v>
       </c>
-      <c r="BC8" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC8" s="1"/>
       <c r="BD8" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -2815,10 +2806,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),980.0)</f>
         <v>980</v>
       </c>
-      <c r="BC11" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC11" s="1"/>
       <c r="BD11" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -3050,10 +3038,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1200.0)</f>
         <v>1200</v>
       </c>
-      <c r="BC12" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC12" s="1"/>
       <c r="BD12" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -3285,10 +3270,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),740.0)</f>
         <v>740</v>
       </c>
-      <c r="BC13" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC13" s="1"/>
       <c r="BD13" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -3978,10 +3960,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),820.0)</f>
         <v>820</v>
       </c>
-      <c r="BC16" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC16" s="1"/>
       <c r="BD16" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -4903,10 +4882,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),740.0)</f>
         <v>740</v>
       </c>
-      <c r="BC20" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC20" s="1"/>
       <c r="BD20" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -5138,10 +5114,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1180.0)</f>
         <v>1180</v>
       </c>
-      <c r="BC21" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
+      <c r="BC21" s="1"/>
       <c r="BD21" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
         <v> -</v>
@@ -6754,8 +6727,8 @@
         <v>1050</v>
       </c>
       <c r="BC28" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -6766,8 +6739,8 @@
         <v>1</v>
       </c>
       <c r="BF28" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BG28" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
@@ -8396,8 +8369,8 @@
         <v>750</v>
       </c>
       <c r="BC35" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD35" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -10490,8 +10463,8 @@
         <v>1100</v>
       </c>
       <c r="BC44" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD44" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -12819,8 +12792,8 @@
         <v>750</v>
       </c>
       <c r="BC54" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD54" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -14337,8 +14310,8 @@
         <v>475</v>
       </c>
       <c r="X61" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
-        <v>31/05/2025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/06/2025")</f>
+        <v>12/06/2025</v>
       </c>
       <c r="Y61" s="1"/>
       <c r="Z61" s="1" t="str">
@@ -15030,8 +15003,8 @@
         <v>475</v>
       </c>
       <c r="X64" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"31/05/2025")</f>
-        <v>31/05/2025</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"12/06/2025")</f>
+        <v>12/06/2025</v>
       </c>
       <c r="Y64" s="1"/>
       <c r="Z64" s="1" t="str">
@@ -15371,8 +15344,8 @@
         <v>1050</v>
       </c>
       <c r="BC65" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD65" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -16064,8 +16037,8 @@
         <v>950</v>
       </c>
       <c r="BC68" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -16076,8 +16049,8 @@
         <v>1</v>
       </c>
       <c r="BF68" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BG68" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
@@ -16299,8 +16272,8 @@
         <v>1150</v>
       </c>
       <c r="BC69" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -16311,8 +16284,8 @@
         <v>1</v>
       </c>
       <c r="BF69" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BG69" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
@@ -16534,8 +16507,8 @@
         <v>1050</v>
       </c>
       <c r="BC70" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD70" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -17462,8 +17435,8 @@
         <v>1050</v>
       </c>
       <c r="BC74" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BD74" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
@@ -17807,7 +17780,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),375.0)</f>
         <v>375</v>
       </c>
-      <c r="X76" s="1"/>
+      <c r="X76" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"13/06/2025")</f>
+        <v>13/06/2025</v>
+      </c>
       <c r="Y76" s="1"/>
       <c r="Z76" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO FRACCIONADO")</f>
@@ -18179,201 +18155,696 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-      <c r="H78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="1"/>
-      <c r="M78" s="1"/>
-      <c r="N78" s="1"/>
-      <c r="O78" s="1"/>
-      <c r="P78" s="1"/>
-      <c r="Q78" s="1"/>
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
-      <c r="U78" s="1"/>
-      <c r="V78" s="1"/>
-      <c r="W78" s="1"/>
-      <c r="X78" s="1"/>
-      <c r="Y78" s="1"/>
-      <c r="Z78" s="1"/>
-      <c r="AA78" s="1"/>
+      <c r="A78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),77.0)</f>
+        <v>77</v>
+      </c>
+      <c r="B78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5244977.0)</f>
+        <v>5244977</v>
+      </c>
+      <c r="C78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000428174")</f>
+        <v>0000428174</v>
+      </c>
+      <c r="D78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CAMILA ISABEL")</f>
+        <v>CAMILA ISABEL</v>
+      </c>
+      <c r="E78" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BUSTAMANTE VERA")</f>
+        <v>BUSTAMANTE VERA</v>
+      </c>
+      <c r="F78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.1228799E7)</f>
+        <v>71228799</v>
+      </c>
+      <c r="G78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.21741889E8)</f>
+        <v>921741889</v>
+      </c>
+      <c r="H78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"isabelvera0624@gmail.com")</f>
+        <v>isabelvera0624@gmail.com</v>
+      </c>
+      <c r="I78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño Gráfico Publicitario")</f>
+        <v>Diseño Gráfico Publicitario</v>
+      </c>
+      <c r="J78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diseño")</f>
+        <v>Diseño</v>
+      </c>
+      <c r="K78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Antigua")</f>
+        <v>Antigua</v>
+      </c>
+      <c r="L78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO CON CONVA")</f>
+        <v>TRASLADO CON CONVA</v>
+      </c>
+      <c r="P78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T78" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45814.0)</f>
+        <v>45814</v>
+      </c>
+      <c r="U78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W78" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y78" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45814.0)</f>
+        <v>45814</v>
+      </c>
+      <c r="Z78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB78" s="1"/>
-      <c r="AC78" s="1"/>
-      <c r="AD78" s="1"/>
-      <c r="AE78" s="1"/>
-      <c r="AF78" s="1"/>
-      <c r="AG78" s="1"/>
-      <c r="AH78" s="1"/>
-      <c r="AI78" s="1"/>
-      <c r="AJ78" s="1"/>
-      <c r="AK78" s="1"/>
-      <c r="AL78" s="1"/>
+      <c r="AC78" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD78" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE78" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AF78" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AG78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),692459.0)</f>
+        <v>692459</v>
+      </c>
+      <c r="AK78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"01 Nacional")</f>
+        <v>01 Nacional</v>
+      </c>
       <c r="AM78" s="1"/>
-      <c r="AN78" s="1"/>
-      <c r="AO78" s="1"/>
-      <c r="AP78" s="1"/>
-      <c r="AQ78" s="1"/>
-      <c r="AR78" s="1"/>
-      <c r="AS78" s="1"/>
-      <c r="AT78" s="1"/>
-      <c r="AU78" s="1"/>
-      <c r="AV78" s="1"/>
-      <c r="AW78" s="1"/>
-      <c r="AX78" s="1"/>
-      <c r="AY78" s="1"/>
-      <c r="AZ78" s="1"/>
-      <c r="BA78" s="1"/>
-      <c r="BB78" s="1"/>
-      <c r="BC78" s="1"/>
-      <c r="BD78" s="1"/>
-      <c r="BE78" s="1"/>
-      <c r="BF78" s="1"/>
+      <c r="AN78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
+      <c r="AO78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2019.0)</f>
+        <v>2019</v>
+      </c>
+      <c r="AP78" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ78" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR78" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45813.0)</f>
+        <v>45813</v>
+      </c>
+      <c r="AS78" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AT78" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AU78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AV78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"FORMULARIO")</f>
+        <v>FORMULARIO</v>
+      </c>
+      <c r="AX78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEARCH MARCA")</f>
+        <v>SEARCH MARCA</v>
+      </c>
+      <c r="AY78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Sergio Valderrama Rodriguez")</f>
+        <v>Sergio Valderrama Rodriguez</v>
+      </c>
+      <c r="BA78" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB78" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="BC78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD78" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF78" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BG78" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1"/>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
-      <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
-      <c r="U79" s="1"/>
-      <c r="V79" s="1"/>
-      <c r="W79" s="1"/>
-      <c r="X79" s="1"/>
-      <c r="Y79" s="1"/>
-      <c r="Z79" s="1"/>
-      <c r="AA79" s="1"/>
+      <c r="A79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),78.0)</f>
+        <v>78</v>
+      </c>
+      <c r="B79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3137502.0)</f>
+        <v>3137502</v>
+      </c>
+      <c r="C79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000138896")</f>
+        <v>0000138896</v>
+      </c>
+      <c r="D79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"LUIS FERNANDO")</f>
+        <v>LUIS FERNANDO</v>
+      </c>
+      <c r="E79" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SANCHEZ GRANADOS")</f>
+        <v>SANCHEZ GRANADOS</v>
+      </c>
+      <c r="F79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),7.3859255E7)</f>
+        <v>73859255</v>
+      </c>
+      <c r="G79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.34433033E8)</f>
+        <v>934433033</v>
+      </c>
+      <c r="H79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"73859255@gmail.com")</f>
+        <v>73859255@gmail.com</v>
+      </c>
+      <c r="I79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Administración y Negocios Internacionales")</f>
+        <v>Administración y Negocios Internacionales</v>
+      </c>
+      <c r="J79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
+        <v>Negocios</v>
+      </c>
+      <c r="K79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Nueva")</f>
+        <v>Nueva</v>
+      </c>
+      <c r="L79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Virtual")</f>
+        <v>Virtual</v>
+      </c>
+      <c r="N79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Nocturno - A distancia")</f>
+        <v>Nocturno - A distancia</v>
+      </c>
+      <c r="O79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO CON CONVA")</f>
+        <v>TRASLADO CON CONVA</v>
+      </c>
+      <c r="P79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCALA REGULAR")</f>
+        <v>ESCALA REGULAR</v>
+      </c>
+      <c r="Q79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="T79" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="U79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W79" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y79" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45815.0)</f>
+        <v>45815</v>
+      </c>
+      <c r="Z79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB79" s="1"/>
-      <c r="AC79" s="1"/>
-      <c r="AD79" s="1"/>
-      <c r="AE79" s="1"/>
-      <c r="AF79" s="1"/>
-      <c r="AG79" s="1"/>
-      <c r="AH79" s="1"/>
-      <c r="AI79" s="1"/>
-      <c r="AJ79" s="1"/>
-      <c r="AK79" s="1"/>
-      <c r="AL79" s="1"/>
+      <c r="AC79" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD79" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE79" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
+      </c>
+      <c r="AF79" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
+      </c>
+      <c r="AG79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1441310.0)</f>
+        <v>1441310</v>
+      </c>
+      <c r="AK79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Menos de 5 kms")</f>
+        <v>Menos de 5 kms</v>
+      </c>
+      <c r="AL79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
       <c r="AM79" s="1"/>
-      <c r="AN79" s="1"/>
-      <c r="AO79" s="1"/>
-      <c r="AP79" s="1"/>
-      <c r="AQ79" s="1"/>
-      <c r="AR79" s="1"/>
-      <c r="AS79" s="1"/>
-      <c r="AT79" s="1"/>
-      <c r="AU79" s="1"/>
-      <c r="AV79" s="1"/>
-      <c r="AW79" s="1"/>
-      <c r="AX79" s="1"/>
-      <c r="AY79" s="1"/>
-      <c r="AZ79" s="1"/>
-      <c r="BA79" s="1"/>
-      <c r="BB79" s="1"/>
-      <c r="BC79" s="1"/>
-      <c r="BD79" s="1"/>
-      <c r="BE79" s="1"/>
-      <c r="BF79" s="1"/>
+      <c r="AN79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
+      <c r="AO79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2024.0)</f>
+        <v>2024</v>
+      </c>
+      <c r="AP79" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ79" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR79" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45811.0)</f>
+        <v>45811</v>
+      </c>
+      <c r="AS79" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AT79" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AU79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="AV79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ORGANICO")</f>
+        <v>ORGANICO</v>
+      </c>
+      <c r="AY79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Andrea Araujo Antara")</f>
+        <v>Andrea Araujo Antara</v>
+      </c>
+      <c r="BA79" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB79" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),750.0)</f>
+        <v>750</v>
+      </c>
+      <c r="BC79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD79" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF79" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BG79" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
-        <v/>
-      </c>
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1"/>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
-      <c r="Q80" s="1"/>
-      <c r="R80" s="1"/>
-      <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
-      <c r="U80" s="1"/>
-      <c r="V80" s="1"/>
-      <c r="W80" s="1"/>
-      <c r="X80" s="1"/>
-      <c r="Y80" s="1"/>
-      <c r="Z80" s="1"/>
-      <c r="AA80" s="1"/>
+      <c r="A80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),79.0)</f>
+        <v>79</v>
+      </c>
+      <c r="B80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5247088.0)</f>
+        <v>5247088</v>
+      </c>
+      <c r="C80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"0000428316")</f>
+        <v>0000428316</v>
+      </c>
+      <c r="D80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MAHEBA ALEXA")</f>
+        <v>MAHEBA ALEXA</v>
+      </c>
+      <c r="E80" s="2" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"MACAZANA MONTAÑEZ")</f>
+        <v>MACAZANA MONTAÑEZ</v>
+      </c>
+      <c r="F80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),6.2852392E7)</f>
+        <v>62852392</v>
+      </c>
+      <c r="G80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),9.37403097E8)</f>
+        <v>937403097</v>
+      </c>
+      <c r="H80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"XXGNTH@gmail.com")</f>
+        <v>XXGNTH@gmail.com</v>
+      </c>
+      <c r="I80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Marketing e Innovación")</f>
+        <v>Marketing e Innovación</v>
+      </c>
+      <c r="J80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Negocios")</f>
+        <v>Negocios</v>
+      </c>
+      <c r="K80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Nueva")</f>
+        <v>Nueva</v>
+      </c>
+      <c r="L80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Admisión Extraordinaria (Traslados)")</f>
+        <v>Admisión Extraordinaria (Traslados)</v>
+      </c>
+      <c r="M80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Semi-presencial")</f>
+        <v>Semi-presencial</v>
+      </c>
+      <c r="N80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Diurno")</f>
+        <v>Diurno</v>
+      </c>
+      <c r="O80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"TRASLADO SIN CONVA")</f>
+        <v>TRASLADO SIN CONVA</v>
+      </c>
+      <c r="P80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA")</f>
+        <v>BECA</v>
+      </c>
+      <c r="Q80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="R80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
+        <v>NINGUNO</v>
+      </c>
+      <c r="S80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRIGO")</f>
+        <v>RODRIGO</v>
+      </c>
+      <c r="T80" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45817.0)</f>
+        <v>45817</v>
+      </c>
+      <c r="U80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CARGO")</f>
+        <v>CARGO</v>
+      </c>
+      <c r="V80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="W80" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="X80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"-")</f>
+        <v>-</v>
+      </c>
+      <c r="Y80" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45817.0)</f>
+        <v>45817</v>
+      </c>
+      <c r="Z80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PAGO COMPLETO")</f>
+        <v>PAGO COMPLETO</v>
+      </c>
+      <c r="AA80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"#N/A")</f>
+        <v>#N/A</v>
+      </c>
       <c r="AB80" s="1"/>
-      <c r="AC80" s="1"/>
-      <c r="AD80" s="1"/>
-      <c r="AE80" s="1"/>
-      <c r="AF80" s="1"/>
-      <c r="AG80" s="1"/>
-      <c r="AH80" s="1"/>
-      <c r="AI80" s="1"/>
-      <c r="AJ80" s="1"/>
-      <c r="AK80" s="1"/>
-      <c r="AL80" s="1"/>
+      <c r="AC80" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD80" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE80" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1050.0)</f>
+        <v>1050</v>
+      </c>
+      <c r="AF80" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="AG80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AH80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AI80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1254358.0)</f>
+        <v>1254358</v>
+      </c>
+      <c r="AK80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"10 kms a 15 kms")</f>
+        <v>10 kms a 15 kms</v>
+      </c>
+      <c r="AL80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
+        <v>05 301 a 550</v>
+      </c>
       <c r="AM80" s="1"/>
-      <c r="AN80" s="1"/>
-      <c r="AO80" s="1"/>
-      <c r="AP80" s="1"/>
-      <c r="AQ80" s="1"/>
-      <c r="AR80" s="1"/>
-      <c r="AS80" s="1"/>
-      <c r="AT80" s="1"/>
-      <c r="AU80" s="1"/>
-      <c r="AV80" s="1"/>
-      <c r="AW80" s="1"/>
-      <c r="AX80" s="1"/>
-      <c r="AY80" s="1"/>
-      <c r="AZ80" s="1"/>
-      <c r="BA80" s="1"/>
-      <c r="BB80" s="1"/>
-      <c r="BC80" s="1"/>
-      <c r="BD80" s="1"/>
-      <c r="BE80" s="1"/>
-      <c r="BF80" s="1"/>
+      <c r="AN80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
+        <v> </v>
+      </c>
+      <c r="AO80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2022.0)</f>
+        <v>2022</v>
+      </c>
+      <c r="AP80" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AQ80" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AR80" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45814.0)</f>
+        <v>45814</v>
+      </c>
+      <c r="AS80" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45809.0)</f>
+        <v>45809</v>
+      </c>
+      <c r="AT80" s="2">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),45803.0)</f>
+        <v>45803</v>
+      </c>
+      <c r="AU80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="AV80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"DIGITAL")</f>
+        <v>DIGITAL</v>
+      </c>
+      <c r="AW80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BIDIRECCIONAL")</f>
+        <v>BIDIRECCIONAL</v>
+      </c>
+      <c r="AX80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SEARCH MARCA")</f>
+        <v>SEARCH MARCA</v>
+      </c>
+      <c r="AY80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="AZ80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Angelica Iparraguirre")</f>
+        <v>Angelica Iparraguirre</v>
+      </c>
+      <c r="BA80" s="5">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="BB80" s="6">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),850.0)</f>
+        <v>850</v>
+      </c>
+      <c r="BC80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BD80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," -")</f>
+        <v> -</v>
+      </c>
+      <c r="BE80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="BF80" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="BG80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
         <v/>

--- a/DATA_VENTA_25.2.xlsx
+++ b/DATA_VENTA_25.2.xlsx
@@ -8146,8 +8146,8 @@
         <v>1</v>
       </c>
       <c r="BF34" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BG34" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
@@ -10710,8 +10710,8 @@
         <v>1</v>
       </c>
       <c r="BF45" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="BG45" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"")</f>
@@ -18684,8 +18684,8 @@
         <v>BECA</v>
       </c>
       <c r="Q80" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
-        <v>NINGUNO</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"BECA CARRERAS NUEVAS")</f>
+        <v>BECA CARRERAS NUEVAS</v>
       </c>
       <c r="R80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NINGUNO")</f>
@@ -18768,7 +18768,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"05 301 a 550")</f>
         <v>05 301 a 550</v>
       </c>
-      <c r="AM80" s="1"/>
+      <c r="AM80" s="1" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Universidad Privada del Norte(UPN)")</f>
+        <v>Universidad Privada del Norte(UPN)</v>
+      </c>
       <c r="AN80" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," ")</f>
         <v> </v>
